--- a/बजेट माग estimate/नगर बजेट estimate/bhotange chihaanpaati/2.bhotange chihaanpaati.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/bhotange chihaanpaati/2.bhotange chihaanpaati.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F0B825-526E-4359-B78D-19914342B3EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4231312-D497-48D0-A20F-EC4E75643B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,11 +11,12 @@
     <sheet name="estimate" sheetId="13" r:id="rId1"/>
     <sheet name="bhotange chihaanpaati" sheetId="14" r:id="rId2"/>
     <sheet name="chihaan" sheetId="15" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="16" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="description_103">[1]Abstract!$B$16</definedName>
@@ -35,7 +36,7 @@
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'bhotange chihaanpaati'!$A$1:$K$158</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">chihaan!$A$1:$K$159</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">chihaan!$A$1:$K$167</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$158</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'bhotange chihaanpaati'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">chihaan!$1:$8</definedName>
@@ -91,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="111">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -390,6 +391,69 @@
   <si>
     <t>-for toe wall</t>
   </si>
+  <si>
+    <t>Foundation size</t>
+  </si>
+  <si>
+    <t>Plinth size</t>
+  </si>
+  <si>
+    <t>Depth</t>
+  </si>
+  <si>
+    <t>Depth from GL</t>
+  </si>
+  <si>
+    <t>Footing size</t>
+  </si>
+  <si>
+    <t>Length in PL area</t>
+  </si>
+  <si>
+    <t>Breadth in PL area</t>
+  </si>
+  <si>
+    <t>Toe wall</t>
+  </si>
+  <si>
+    <t>Length L1</t>
+  </si>
+  <si>
+    <t>Length L2</t>
+  </si>
+  <si>
+    <t>Ht. H1</t>
+  </si>
+  <si>
+    <t>Ht. H2</t>
+  </si>
+  <si>
+    <t>Tie beam size</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Column size</t>
+  </si>
+  <si>
+    <t>Length/B</t>
+  </si>
+  <si>
+    <t>Ht. above PL upto ceiling</t>
+  </si>
+  <si>
+    <t>Ht. upto plinth</t>
+  </si>
+  <si>
+    <t>-beam for inclined support</t>
+  </si>
+  <si>
+    <t>-beam for top roof inclined support</t>
+  </si>
+  <si>
+    <t>-top roof</t>
+  </si>
 </sst>
 </file>
 
@@ -399,7 +463,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,16 +576,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -579,6 +655,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -588,7 +675,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -704,6 +791,25 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -726,25 +832,40 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1286,113 +1407,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -4695,11 +4816,11 @@
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="55">
+      <c r="C153" s="49">
         <f>J151</f>
         <v>791637.34255256748</v>
       </c>
-      <c r="D153" s="56"/>
+      <c r="D153" s="50"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -4714,21 +4835,21 @@
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="57">
+      <c r="C154" s="51">
         <v>700000</v>
       </c>
-      <c r="D154" s="58"/>
+      <c r="D154" s="52"/>
       <c r="E154" s="39"/>
     </row>
     <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="57">
+      <c r="C155" s="51">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="58"/>
+      <c r="D155" s="52"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>84.003111558098539</v>
@@ -4738,11 +4859,11 @@
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="59">
+      <c r="C156" s="53">
         <f>C153-C155</f>
         <v>126637.34255256748</v>
       </c>
-      <c r="D156" s="59"/>
+      <c r="D156" s="53"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>15.996888441901461</v>
@@ -4752,11 +4873,11 @@
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="55">
+      <c r="C157" s="49">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="56"/>
+      <c r="D157" s="50"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
@@ -4765,23 +4886,17 @@
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="55">
+      <c r="C158" s="49">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="56"/>
+      <c r="D158" s="50"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -4791,6 +4906,12 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -4817,113 +4938,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -8226,11 +8347,11 @@
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="55">
+      <c r="C153" s="49">
         <f>J151</f>
         <v>791637.34255256748</v>
       </c>
-      <c r="D153" s="56"/>
+      <c r="D153" s="50"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -8245,21 +8366,21 @@
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="57">
+      <c r="C154" s="51">
         <v>700000</v>
       </c>
-      <c r="D154" s="58"/>
+      <c r="D154" s="52"/>
       <c r="E154" s="39"/>
     </row>
     <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="57">
+      <c r="C155" s="51">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="58"/>
+      <c r="D155" s="52"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>84.003111558098539</v>
@@ -8269,11 +8390,11 @@
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="59">
+      <c r="C156" s="53">
         <f>C153-C155</f>
         <v>126637.34255256748</v>
       </c>
-      <c r="D156" s="59"/>
+      <c r="D156" s="53"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>15.996888441901461</v>
@@ -8283,11 +8404,11 @@
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="55">
+      <c r="C157" s="49">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="56"/>
+      <c r="D157" s="50"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
@@ -8296,17 +8417,24 @@
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="55">
+      <c r="C158" s="49">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="56"/>
+      <c r="D158" s="50"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="C158:D158"/>
     <mergeCell ref="A7:F7"/>
@@ -8315,13 +8443,6 @@
     <mergeCell ref="C154:D154"/>
     <mergeCell ref="C155:D155"/>
     <mergeCell ref="C156:D156"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -8333,7 +8454,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAEEC707-87B5-428A-A0F5-809434590EB3}">
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:M167"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -8345,118 +8466,119 @@
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5703125" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-    </row>
-    <row r="2" spans="1:14" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-    </row>
-    <row r="5" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-    </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-    </row>
-    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-    </row>
-    <row r="8" spans="1:14" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+    </row>
+    <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -8491,7 +8613,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>1</v>
       </c>
@@ -8508,7 +8630,7 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="16" t="s">
         <v>57</v>
@@ -8517,12 +8639,15 @@
         <v>4</v>
       </c>
       <c r="D10" s="3">
+        <f>Sheet1!B4</f>
         <v>1.5</v>
       </c>
       <c r="E10" s="3">
+        <f>Sheet1!C4</f>
         <v>1.5</v>
       </c>
       <c r="F10" s="3">
+        <f>Sheet1!D4</f>
         <v>1.5</v>
       </c>
       <c r="G10" s="3">
@@ -8534,7 +8659,7 @@
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
       <c r="B11" s="16" t="s">
         <v>89</v>
@@ -8543,8 +8668,8 @@
         <v>4</v>
       </c>
       <c r="D11" s="3">
-        <f>(7.333)/3.281</f>
-        <v>2.234989332520573</v>
+        <f>Sheet1!K4</f>
+        <v>2.3876866808899719</v>
       </c>
       <c r="E11" s="3">
         <v>0.23</v>
@@ -8554,14 +8679,14 @@
       </c>
       <c r="G11" s="3">
         <f>PRODUCT(C11:F11)</f>
-        <v>1.0280950929594637</v>
+        <v>1.0983358732093871</v>
       </c>
       <c r="H11" s="15"/>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:14" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="s">
         <v>16</v>
@@ -8572,7 +8697,7 @@
       <c r="F12" s="20"/>
       <c r="G12" s="2">
         <f>SUM(G10:G11)</f>
-        <v>14.528095092959465</v>
+        <v>14.598335873209386</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>28</v>
@@ -8582,11 +8707,11 @@
       </c>
       <c r="J12" s="22">
         <f>G12*I12</f>
-        <v>9793.6794640658336</v>
+        <v>9841.0301788479119</v>
       </c>
       <c r="K12" s="20"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -8599,7 +8724,7 @@
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
     </row>
-    <row r="14" spans="1:14" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
         <v>2</v>
       </c>
@@ -8616,7 +8741,7 @@
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="str">
         <f t="shared" ref="B15:E16" si="0">B10</f>
@@ -8627,11 +8752,11 @@
         <v>4</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" si="0"/>
+        <f>Sheet1!B4</f>
         <v>1.5</v>
       </c>
       <c r="E15" s="3">
-        <f t="shared" si="0"/>
+        <f>Sheet1!C4</f>
         <v>1.5</v>
       </c>
       <c r="F15" s="3"/>
@@ -8644,7 +8769,7 @@
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="str">
         <f t="shared" si="0"/>
@@ -8655,8 +8780,8 @@
         <v>4</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" si="0"/>
-        <v>2.234989332520573</v>
+        <f>Sheet1!K4</f>
+        <v>2.3876866808899719</v>
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
@@ -8665,16 +8790,12 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3">
         <f>PRODUCT(C16:F16)</f>
-        <v>2.0561901859189273</v>
+        <v>2.1966717464187742</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
-      <c r="N16">
-        <f>0.5-0.05-0.055+0.45</f>
-        <v>0.84499999999999997</v>
-      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
@@ -8685,17 +8806,17 @@
         <v>1</v>
       </c>
       <c r="D17" s="3">
-        <f>(14-1.17*2)/3.281</f>
-        <v>3.5537945748247486</v>
+        <f>Sheet1!R4</f>
+        <v>3.5669917708015841</v>
       </c>
       <c r="E17" s="3">
         <f>D17</f>
-        <v>3.5537945748247486</v>
+        <v>3.5669917708015841</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
         <f>PRODUCT(C17:F17)</f>
-        <v>12.629455880053815</v>
+        <v>12.723430292966221</v>
       </c>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
@@ -8713,7 +8834,7 @@
       <c r="F18" s="20"/>
       <c r="G18" s="2">
         <f>SUM(G15:G17)</f>
-        <v>23.68564606597274</v>
+        <v>23.920102039384993</v>
       </c>
       <c r="H18" s="21" t="s">
         <v>34</v>
@@ -8723,7 +8844,7 @@
       </c>
       <c r="J18" s="22">
         <f>G18*I18</f>
-        <v>24099.434302745285</v>
+        <v>24337.986222013049</v>
       </c>
       <c r="K18" s="20"/>
     </row>
@@ -8741,7 +8862,7 @@
       <c r="I19" s="26"/>
       <c r="J19" s="22">
         <f>0.13*G18*6360.9/10</f>
-        <v>1958.6063387935981</v>
+        <v>1977.9939018102118</v>
       </c>
       <c r="K19" s="26"/>
     </row>
@@ -8759,7 +8880,7 @@
       <c r="I20" s="15"/>
       <c r="J20" s="22">
         <f>0.13*G18*2256.3/10</f>
-        <v>694.74500184250587</v>
+        <v>701.62204100903671</v>
       </c>
       <c r="K20" s="15"/>
     </row>
@@ -8796,19 +8917,19 @@
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="str">
-        <f>B15</f>
+        <f t="shared" ref="B23:E24" si="1">B15</f>
         <v>-for foundation</v>
       </c>
       <c r="C23" s="15">
-        <f>C15</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="D23" s="3">
-        <f>D15</f>
+        <f>Sheet1!B4</f>
         <v>1.5</v>
       </c>
       <c r="E23" s="3">
-        <f>E15</f>
+        <f>Sheet1!C4</f>
         <v>1.5</v>
       </c>
       <c r="F23" s="3">
@@ -8826,19 +8947,19 @@
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="15"/>
       <c r="B24" s="16" t="str">
-        <f>B16</f>
+        <f t="shared" si="1"/>
         <v>-for toe wall</v>
       </c>
       <c r="C24" s="15">
-        <f>C16</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="D24" s="3">
-        <f>D16</f>
-        <v>2.234989332520573</v>
+        <f>Sheet1!K4</f>
+        <v>2.3876866808899719</v>
       </c>
       <c r="E24" s="3">
-        <f>E16</f>
+        <f t="shared" si="1"/>
         <v>0.23</v>
       </c>
       <c r="F24" s="3">
@@ -8846,7 +8967,7 @@
       </c>
       <c r="G24" s="3">
         <f>PRODUCT(C24:F24)</f>
-        <v>0.15421426394391954</v>
+        <v>0.16475038098140807</v>
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="15"/>
@@ -8860,88 +8981,76 @@
         <v>-for flooring</v>
       </c>
       <c r="C25" s="15">
-        <f t="shared" ref="C25:E25" si="1">C17</f>
+        <f t="shared" ref="C25" si="2">C17</f>
         <v>1</v>
       </c>
       <c r="D25" s="3">
-        <f t="shared" si="1"/>
-        <v>3.5537945748247486</v>
+        <f>Sheet1!R4</f>
+        <v>3.5669917708015841</v>
       </c>
       <c r="E25" s="3">
-        <f t="shared" si="1"/>
-        <v>3.5537945748247486</v>
+        <f>Sheet1!R4</f>
+        <v>3.5669917708015841</v>
       </c>
       <c r="F25" s="3">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G25" s="3">
         <f>PRODUCT(C25:F25)</f>
-        <v>0.94720919100403611</v>
+        <v>0.95425727197246646</v>
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="16" t="str">
-        <f>B93</f>
-        <v>-for flooring at existing paati</v>
-      </c>
-      <c r="C26" s="15">
-        <f>C93</f>
-        <v>1</v>
-      </c>
-      <c r="D26" s="3">
-        <f>D93</f>
-        <v>5.1813471502590671</v>
-      </c>
-      <c r="E26" s="3">
-        <f>E93</f>
-        <v>7.5434318805242304</v>
-      </c>
-      <c r="F26" s="3">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G26" s="3">
-        <f>PRODUCT(C26:F26)</f>
-        <v>2.9313854457995716</v>
-      </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-    </row>
-    <row r="27" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="18" t="s">
+    <row r="26" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="2">
-        <f>SUM(G23:G26)</f>
-        <v>4.7078089007475272</v>
-      </c>
-      <c r="H27" s="21" t="s">
+      <c r="C26" s="19"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="2">
+        <f>SUM(G23:G25)</f>
+        <v>1.7940076529538744</v>
+      </c>
+      <c r="H26" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I26" s="2">
         <v>4495.6400000000003</v>
       </c>
+      <c r="J26" s="22">
+        <f>G26*I26</f>
+        <v>8065.2125649255568</v>
+      </c>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="24"/>
+      <c r="B27" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
       <c r="J27" s="22">
-        <f>G27*I27</f>
-        <v>21164.614006556614</v>
-      </c>
-      <c r="K27" s="20"/>
+        <f>0.13*G26*2866.82</f>
+        <v>668.60261255335945</v>
+      </c>
+      <c r="K27" s="26"/>
     </row>
     <row r="28" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
       <c r="B28" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="27"/>
@@ -8951,15 +9060,15 @@
       <c r="H28" s="26"/>
       <c r="I28" s="26"/>
       <c r="J28" s="22">
-        <f>0.13*G27*2866.82</f>
-        <v>1754.5372926693335</v>
+        <f>0.13*G26*(2065.63+805.06)</f>
+        <v>669.50517780356051</v>
       </c>
       <c r="K28" s="26"/>
     </row>
     <row r="29" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
       <c r="B29" s="25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="27"/>
@@ -8969,34 +9078,32 @@
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
       <c r="J29" s="22">
-        <f>0.13*G27*(2065.63+805.06)</f>
-        <v>1756.9057913272995</v>
+        <f>0.13*G26*1493.61</f>
+        <v>348.3412101686967</v>
       </c>
       <c r="K29" s="26"/>
     </row>
-    <row r="30" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="24"/>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
       <c r="B30" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
+        <v>36</v>
+      </c>
+      <c r="C30" s="15"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
       <c r="J30" s="22">
-        <f>0.13*G27*1493.61</f>
-        <v>914.11195879191678</v>
-      </c>
-      <c r="K30" s="26"/>
+        <f>0.13*G26*33.6</f>
+        <v>7.8362254281025248</v>
+      </c>
+      <c r="K30" s="15"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="15"/>
-      <c r="B31" s="25" t="s">
-        <v>36</v>
-      </c>
+      <c r="B31" s="15"/>
       <c r="C31" s="15"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -9004,71 +9111,87 @@
       <c r="G31" s="3"/>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
-      <c r="J31" s="22">
-        <f>0.13*G27*33.6</f>
-        <v>20.5637092784652</v>
-      </c>
+      <c r="J31" s="15"/>
       <c r="K31" s="15"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-    </row>
-    <row r="33" spans="1:13" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="11">
+    <row r="32" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A32" s="11">
         <v>4</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B32" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
+      <c r="B33" s="16" t="str">
+        <f>B23</f>
+        <v>-for foundation</v>
+      </c>
+      <c r="C33" s="15">
+        <v>4</v>
+      </c>
+      <c r="D33" s="3">
+        <f>Sheet1!B4</f>
+        <v>1.5</v>
+      </c>
+      <c r="E33" s="3">
+        <f>Sheet1!C4</f>
+        <v>1.5</v>
+      </c>
+      <c r="F33" s="3">
+        <f>Sheet1!G4</f>
+        <v>0.35</v>
+      </c>
+      <c r="G33" s="3">
+        <f>PRODUCT(C33:F33)</f>
+        <v>3.15</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="M33" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
-      <c r="B34" s="16" t="str">
-        <f>B23</f>
-        <v>-for foundation</v>
+      <c r="B34" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="C34" s="15">
         <v>4</v>
       </c>
       <c r="D34" s="3">
-        <v>1.5</v>
+        <f>Sheet1!O4</f>
+        <v>0.35</v>
       </c>
       <c r="E34" s="3">
-        <v>1.5</v>
+        <f>Sheet1!O4</f>
+        <v>0.35</v>
       </c>
       <c r="F34" s="3">
-        <v>0.45</v>
+        <f>Sheet1!P4</f>
+        <v>1.3699999999999999</v>
       </c>
       <c r="G34" s="3">
         <f>PRODUCT(C34:F34)</f>
-        <v>4.05</v>
+        <v>0.6712999999999999</v>
       </c>
       <c r="H34" s="15"/>
       <c r="I34" s="15"/>
       <c r="J34" s="15"/>
       <c r="K34" s="15"/>
-      <c r="M34" t="s">
-        <v>87</v>
-      </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="15"/>
@@ -9080,19 +9203,20 @@
         <v>4</v>
       </c>
       <c r="D35" s="3">
-        <f>D24</f>
-        <v>2.234989332520573</v>
+        <f>Sheet1!R4</f>
+        <v>3.5669917708015841</v>
       </c>
       <c r="E35" s="3">
-        <f>E24</f>
+        <f>Sheet1!S4</f>
         <v>0.23</v>
       </c>
       <c r="F35" s="3">
+        <f>Sheet1!T4</f>
         <v>0.23</v>
       </c>
       <c r="G35" s="3">
         <f>PRODUCT(C35:F35)</f>
-        <v>0.47292374276135329</v>
+        <v>0.75477545870161533</v>
       </c>
       <c r="H35" s="15"/>
       <c r="I35" s="15"/>
@@ -9102,25 +9226,26 @@
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C36" s="15">
         <v>4</v>
       </c>
       <c r="D36" s="3">
-        <f>(1.5-3.5/3.281)</f>
-        <v>0.43325205729960392</v>
+        <f>Sheet1!O4</f>
+        <v>0.35</v>
       </c>
       <c r="E36" s="3">
+        <f>Sheet1!O4</f>
         <v>0.35</v>
       </c>
       <c r="F36" s="3">
-        <f>(3.5+1.6)/3.281</f>
-        <v>1.55440414507772</v>
+        <f>Sheet1!Q4</f>
+        <v>3.0722340749771408</v>
       </c>
       <c r="G36" s="3">
-        <f>PRODUCT(C36:F36)</f>
-        <v>0.94282831122193578</v>
+        <f t="shared" ref="G36:G43" si="3">PRODUCT(C36:F36)</f>
+        <v>1.5053946967387988</v>
       </c>
       <c r="H36" s="15"/>
       <c r="I36" s="15"/>
@@ -9130,24 +9255,26 @@
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="15"/>
       <c r="B37" s="16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C37" s="15">
         <v>4</v>
       </c>
       <c r="D37" s="3">
+        <f>Sheet1!R4</f>
+        <v>3.5669917708015841</v>
+      </c>
+      <c r="E37" s="3">
+        <f>E35</f>
+        <v>0.23</v>
+      </c>
+      <c r="F37" s="3">
+        <f>Sheet1!W4</f>
         <v>0.35</v>
       </c>
-      <c r="E37" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="F37" s="3">
-        <f>10.5/3.281</f>
-        <v>3.2002438281011885</v>
-      </c>
       <c r="G37" s="3">
-        <f t="shared" ref="G37:G43" si="2">PRODUCT(C37:F37)</f>
-        <v>1.5681194757695822</v>
+        <f t="shared" si="3"/>
+        <v>1.1485713501981101</v>
       </c>
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
@@ -9157,25 +9284,25 @@
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
       <c r="B38" s="16" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C38" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" s="3">
-        <f>D35</f>
-        <v>2.234989332520573</v>
+        <f>Sheet1!R4</f>
+        <v>3.5669917708015841</v>
       </c>
       <c r="E38" s="3">
-        <f>E35</f>
         <v>0.23</v>
       </c>
       <c r="F38" s="3">
-        <v>0.23</v>
+        <f>Sheet1!W4</f>
+        <v>0.35</v>
       </c>
       <c r="G38" s="3">
-        <f t="shared" si="2"/>
-        <v>0.47292374276135329</v>
+        <f t="shared" si="3"/>
+        <v>0.57428567509905504</v>
       </c>
       <c r="H38" s="15"/>
       <c r="I38" s="15"/>
@@ -9185,24 +9312,24 @@
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="15"/>
       <c r="B39" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C39" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" s="3">
-        <f>D38</f>
-        <v>2.234989332520573</v>
+        <f>0.23</f>
+        <v>0.23</v>
       </c>
       <c r="E39" s="3">
         <v>0.23</v>
       </c>
       <c r="F39" s="3">
-        <v>0.23</v>
+        <v>1.8</v>
       </c>
       <c r="G39" s="3">
-        <f t="shared" si="2"/>
-        <v>0.23646187138067665</v>
+        <f t="shared" si="3"/>
+        <v>0.38088000000000005</v>
       </c>
       <c r="H39" s="15"/>
       <c r="I39" s="15"/>
@@ -9212,24 +9339,25 @@
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="15"/>
       <c r="B40" s="16" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C40" s="15">
+        <f>4</f>
         <v>4</v>
       </c>
       <c r="D40" s="3">
-        <f>0.23</f>
-        <v>0.23</v>
+        <f>6.5/3.281</f>
+        <v>1.9811033221578787</v>
       </c>
       <c r="E40" s="3">
         <v>0.23</v>
       </c>
       <c r="F40" s="3">
-        <v>1.5</v>
+        <v>0.23</v>
       </c>
       <c r="G40" s="3">
-        <f t="shared" si="2"/>
-        <v>0.31740000000000002</v>
+        <f t="shared" si="3"/>
+        <v>0.41920146296860716</v>
       </c>
       <c r="H40" s="15"/>
       <c r="I40" s="15"/>
@@ -9245,19 +9373,19 @@
         <v>4</v>
       </c>
       <c r="D41" s="3">
-        <f>((12+5.5)/2)/3.281</f>
-        <v>2.6668698567509903</v>
+        <f>((12.75+7.25)/2)/3.281</f>
+        <v>3.047851264858275</v>
       </c>
       <c r="E41" s="3">
+        <f>3/3.281</f>
+        <v>0.91435537945748246</v>
+      </c>
+      <c r="F41" s="3">
         <v>0.1</v>
       </c>
-      <c r="F41" s="3">
-        <f>0.75</f>
-        <v>0.75</v>
-      </c>
       <c r="G41" s="3">
-        <f t="shared" si="2"/>
-        <v>0.800060957025297</v>
+        <f t="shared" si="3"/>
+        <v>1.1147276799237824</v>
       </c>
       <c r="H41" s="15"/>
       <c r="I41" s="15"/>
@@ -9273,18 +9401,18 @@
         <v>2</v>
       </c>
       <c r="D42" s="3">
-        <f>12/3.281</f>
-        <v>3.6574215178299299</v>
+        <f>Sheet1!H4</f>
+        <v>4.2669917708015843</v>
       </c>
       <c r="E42" s="3">
         <v>0.6</v>
       </c>
       <c r="F42" s="3">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="G42" s="3">
-        <f t="shared" si="2"/>
-        <v>0.5486132276744895</v>
+        <f t="shared" si="3"/>
+        <v>0.5120390124961901</v>
       </c>
       <c r="H42" s="15"/>
       <c r="I42" s="15"/>
@@ -9298,125 +9426,163 @@
         <v>2</v>
       </c>
       <c r="D43" s="3">
-        <f>(12+4)/3.281</f>
-        <v>4.8765620237732392</v>
+        <f>(Sheet1!H4+E42*2)</f>
+        <v>5.4669917708015845</v>
       </c>
       <c r="E43" s="3">
         <v>0.6</v>
       </c>
       <c r="F43" s="3">
-        <v>0.125</v>
+        <v>0.1</v>
       </c>
       <c r="G43" s="3">
-        <f t="shared" si="2"/>
-        <v>0.73148430356598582</v>
+        <f t="shared" si="3"/>
+        <v>0.65603901249619012</v>
       </c>
       <c r="H43" s="15"/>
       <c r="I43" s="15"/>
       <c r="J43" s="15"/>
       <c r="K43" s="15"/>
     </row>
-    <row r="44" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="18" t="s">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="15"/>
+      <c r="B44" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" s="15">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="D44" s="3">
+        <f>6.5/3.281</f>
+        <v>1.9811033221578787</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="G44" s="3">
+        <f t="shared" ref="G44:G47" si="4">PRODUCT(C44:F44)</f>
+        <v>0.41920146296860716</v>
+      </c>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="15"/>
+      <c r="B45" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="15">
+        <v>4</v>
+      </c>
+      <c r="D45" s="3">
+        <f>3.25/3.281</f>
+        <v>0.99055166107893933</v>
+      </c>
+      <c r="E45" s="3">
+        <f>4/3.281</f>
+        <v>1.2191405059433098</v>
+      </c>
+      <c r="F45" s="3">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G45" s="3">
+        <f t="shared" si="4"/>
+        <v>0.36228649597522916</v>
+      </c>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="15"/>
+      <c r="B46" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C46" s="15">
+        <v>2</v>
+      </c>
+      <c r="D46" s="3">
+        <f>(8+1.75*2)/3.281</f>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E46" s="3">
+        <f>1.75/3.281</f>
+        <v>0.53337397135019804</v>
+      </c>
+      <c r="F46" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G46" s="3">
+        <f t="shared" si="4"/>
+        <v>0.37389824264110194</v>
+      </c>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="15"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="15">
+        <v>2</v>
+      </c>
+      <c r="D47" s="3">
+        <f>(8)/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E47" s="3">
+        <f>1.75/3.281</f>
+        <v>0.53337397135019804</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="G47" s="3">
+        <f t="shared" si="4"/>
+        <v>0.26010312531554919</v>
+      </c>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+    </row>
+    <row r="48" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="17"/>
+      <c r="B48" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="2">
-        <f>SUM(G34:G43)</f>
-        <v>10.140815632160672</v>
-      </c>
-      <c r="H44" s="21" t="s">
+      <c r="C48" s="19"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="2">
+        <f>SUM(G33:G45)</f>
+        <v>11.668702307566186</v>
+      </c>
+      <c r="H48" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I44" s="2">
+      <c r="I48" s="2">
         <v>13957.29</v>
       </c>
-      <c r="J44" s="22">
-        <f>G44*I44</f>
-        <v>141538.30461459982</v>
-      </c>
-      <c r="K44" s="20"/>
-    </row>
-    <row r="45" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="26"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="22">
-        <f>0.13*G44*5212.4</f>
-        <v>6871.5383621396577</v>
-      </c>
-      <c r="K45" s="26"/>
-    </row>
-    <row r="46" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="26"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="22">
-        <f>0.13*G44*(1912.03+921.59)</f>
-        <v>3735.5783389084063</v>
-      </c>
-      <c r="K46" s="26"/>
-    </row>
-    <row r="47" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="24"/>
-      <c r="B47" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="26"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="22">
-        <f>0.13*G44*1350.6</f>
-        <v>1780.5041270635065</v>
-      </c>
-      <c r="K47" s="26"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="15"/>
-      <c r="B48" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C48" s="15"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
       <c r="J48" s="22">
-        <f>0.13*G44*56</f>
-        <v>73.825137802129703</v>
-      </c>
-      <c r="K48" s="15"/>
+        <f>G48*I48</f>
+        <v>162863.46203037046</v>
+      </c>
+      <c r="K48" s="20"/>
     </row>
     <row r="49" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="24"/>
       <c r="B49" s="25" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C49" s="26"/>
       <c r="D49" s="27"/>
@@ -9426,193 +9592,153 @@
       <c r="H49" s="26"/>
       <c r="I49" s="26"/>
       <c r="J49" s="22">
-        <f>0.13*G44*392.92</f>
-        <v>517.98880616451436</v>
+        <f>0.13*G48*5212.4</f>
+        <v>7906.8527080345384</v>
       </c>
       <c r="K49" s="26"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="15"/>
+    <row r="50" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="24"/>
       <c r="B50" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C50" s="15"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
+        <v>33</v>
+      </c>
+      <c r="C50" s="26"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
       <c r="J50" s="22">
-        <f>0.13*G44*14.15</f>
-        <v>18.654030355359559</v>
-      </c>
-      <c r="K50" s="15"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="15"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
-    </row>
-    <row r="52" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A52" s="11">
-        <v>5</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" s="13"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="15"/>
-      <c r="B53" s="16" t="str">
-        <f>B36</f>
-        <v>-for neck column</v>
-      </c>
-      <c r="C53" s="15">
-        <f>C36</f>
-        <v>4</v>
-      </c>
-      <c r="D53" s="3">
-        <f>D36</f>
-        <v>0.43325205729960392</v>
-      </c>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3">
-        <f>F36-0.23</f>
-        <v>1.32440414507772</v>
-      </c>
-      <c r="G53" s="3">
-        <f>PRODUCT(C53:F53)</f>
-        <v>2.2952032822041812</v>
-      </c>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
+        <f>0.13*G48*(1912.03+921.59)</f>
+        <v>4298.4068702595405</v>
+      </c>
+      <c r="K50" s="26"/>
+    </row>
+    <row r="51" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="24"/>
+      <c r="B51" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="26"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="22">
+        <f>0.13*G48*1350.6</f>
+        <v>2048.7674137578556</v>
+      </c>
+      <c r="K51" s="26"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="15"/>
+      <c r="B52" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="15"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="22">
+        <f>0.13*G48*56</f>
+        <v>84.948152799081839</v>
+      </c>
+      <c r="K52" s="15"/>
+    </row>
+    <row r="53" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="24"/>
+      <c r="B53" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="26"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="26"/>
+      <c r="J53" s="22">
+        <f>0.13*G48*392.92</f>
+        <v>596.03264638955784</v>
+      </c>
+      <c r="K53" s="26"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="15"/>
-      <c r="B54" s="16" t="str">
-        <f>B35</f>
-        <v>-for tie beam</v>
-      </c>
-      <c r="C54" s="15">
-        <f>C35</f>
-        <v>4</v>
-      </c>
-      <c r="D54" s="3">
-        <f>D35</f>
-        <v>2.234989332520573</v>
-      </c>
+      <c r="B54" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" s="15"/>
+      <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="3">
-        <f>0.23*2</f>
-        <v>0.46</v>
-      </c>
-      <c r="G54" s="3">
-        <f>PRODUCT(C54:F54)</f>
-        <v>4.1123803718378547</v>
-      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
       <c r="H54" s="15"/>
       <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
+      <c r="J54" s="22">
+        <f>0.13*G48*14.15</f>
+        <v>21.464577894767999</v>
+      </c>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="15"/>
-      <c r="B55" s="16" t="str">
-        <f t="shared" ref="B55:D61" si="3">B37</f>
-        <v>-GF column</v>
-      </c>
-      <c r="C55" s="15">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="D55" s="3">
-        <f>0.35*4</f>
-        <v>1.4</v>
-      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="3">
-        <f>F37</f>
-        <v>3.2002438281011885</v>
-      </c>
-      <c r="G55" s="3">
-        <f t="shared" ref="G55:G61" si="4">PRODUCT(C55:F55)</f>
-        <v>17.921365437366653</v>
-      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
       <c r="H55" s="15"/>
       <c r="I55" s="15"/>
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="15"/>
-      <c r="B56" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>-for beam</v>
-      </c>
-      <c r="C56" s="15">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="D56" s="3">
-        <f t="shared" si="3"/>
-        <v>2.234989332520573</v>
-      </c>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3">
-        <f>0.23*2</f>
-        <v>0.46</v>
-      </c>
-      <c r="G56" s="3">
-        <f t="shared" si="4"/>
-        <v>4.1123803718378547</v>
-      </c>
-      <c r="H56" s="15"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
+    <row r="56" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+      <c r="A56" s="11">
+        <v>5</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="15"/>
       <c r="B57" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>-for support beam</v>
+        <f>B34</f>
+        <v>-for neck column</v>
       </c>
       <c r="C57" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f>C34</f>
+        <v>4</v>
       </c>
       <c r="D57" s="3">
-        <f t="shared" si="3"/>
-        <v>2.234989332520573</v>
+        <f>D34</f>
+        <v>0.35</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3">
-        <f>0.23*2</f>
-        <v>0.46</v>
+        <f>Sheet1!P4</f>
+        <v>1.3699999999999999</v>
       </c>
       <c r="G57" s="3">
-        <f t="shared" si="4"/>
-        <v>2.0561901859189273</v>
+        <f>PRODUCT(C57:F57)</f>
+        <v>1.9179999999999997</v>
       </c>
       <c r="H57" s="15"/>
       <c r="I57" s="15"/>
@@ -9622,25 +9748,25 @@
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="15"/>
       <c r="B58" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>-for column over support beam</v>
+        <f>B35</f>
+        <v>-for tie beam</v>
       </c>
       <c r="C58" s="15">
-        <f t="shared" si="3"/>
+        <f>C35</f>
         <v>4</v>
       </c>
       <c r="D58" s="3">
-        <f t="shared" si="3"/>
-        <v>0.23</v>
+        <f>Sheet1!R4</f>
+        <v>3.5669917708015841</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3">
-        <f>F40</f>
-        <v>1.5</v>
+        <f>Sheet1!T4*2</f>
+        <v>0.46</v>
       </c>
       <c r="G58" s="3">
-        <f t="shared" si="4"/>
-        <v>1.3800000000000001</v>
+        <f>PRODUCT(C58:F58)</f>
+        <v>6.5632648582749153</v>
       </c>
       <c r="H58" s="15"/>
       <c r="I58" s="15"/>
@@ -9650,25 +9776,25 @@
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="15"/>
       <c r="B59" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>-for inclined slab</v>
+        <f>B36</f>
+        <v>-GF column</v>
       </c>
       <c r="C59" s="15">
-        <f t="shared" si="3"/>
+        <f>C36</f>
         <v>4</v>
       </c>
       <c r="D59" s="3">
-        <f t="shared" si="3"/>
-        <v>2.6668698567509903</v>
+        <f>0.35*4</f>
+        <v>1.4</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3">
-        <f>F41</f>
-        <v>0.75</v>
+        <f>Sheet1!Q4</f>
+        <v>3.0722340749771408</v>
       </c>
       <c r="G59" s="3">
-        <f t="shared" si="4"/>
-        <v>8.0006095702529709</v>
+        <f t="shared" ref="G59:G63" si="5">PRODUCT(C59:F59)</f>
+        <v>17.204510819871988</v>
       </c>
       <c r="H59" s="15"/>
       <c r="I59" s="15"/>
@@ -9678,25 +9804,25 @@
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="15"/>
       <c r="B60" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v>-for cantilever</v>
+        <f>B37</f>
+        <v>-for beam</v>
       </c>
       <c r="C60" s="15">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f>C37</f>
+        <v>4</v>
       </c>
       <c r="D60" s="3">
-        <f t="shared" si="3"/>
-        <v>3.6574215178299299</v>
-      </c>
-      <c r="E60" s="3">
-        <f>E42</f>
-        <v>0.6</v>
-      </c>
-      <c r="F60" s="3"/>
+        <f>D37</f>
+        <v>3.5669917708015841</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3">
+        <f>0.23*2</f>
+        <v>0.46</v>
+      </c>
       <c r="G60" s="3">
-        <f t="shared" si="4"/>
-        <v>4.388905821395916</v>
+        <f t="shared" si="5"/>
+        <v>6.5632648582749153</v>
       </c>
       <c r="H60" s="15"/>
       <c r="I60" s="15"/>
@@ -9705,428 +9831,410 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="15"/>
-      <c r="B61" s="16"/>
+      <c r="B61" s="16" t="str">
+        <f>B38</f>
+        <v>-for support beam</v>
+      </c>
       <c r="C61" s="15">
-        <f>C43</f>
+        <f>C38</f>
         <v>2</v>
       </c>
       <c r="D61" s="3">
-        <f t="shared" si="3"/>
-        <v>4.8765620237732392</v>
-      </c>
-      <c r="E61" s="3">
-        <f>E43</f>
-        <v>0.6</v>
-      </c>
-      <c r="F61" s="3"/>
+        <f>D38</f>
+        <v>3.5669917708015841</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3">
+        <f>0.23*2</f>
+        <v>0.46</v>
+      </c>
       <c r="G61" s="3">
-        <f t="shared" si="4"/>
-        <v>5.8518744285278865</v>
+        <f t="shared" si="5"/>
+        <v>3.2816324291374577</v>
       </c>
       <c r="H61" s="15"/>
       <c r="I61" s="15"/>
       <c r="J61" s="15"/>
       <c r="K61" s="15"/>
     </row>
-    <row r="62" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17"/>
-      <c r="B62" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" s="19"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="2">
-        <f>SUM(G53:G61)</f>
-        <v>50.118909469342242</v>
-      </c>
-      <c r="H62" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I62" s="2">
-        <v>922.71</v>
-      </c>
-      <c r="J62" s="22">
-        <f>G62*I62</f>
-        <v>46245.218956456782</v>
-      </c>
-      <c r="K62" s="20"/>
-    </row>
-    <row r="63" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="24"/>
-      <c r="B63" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C63" s="26"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="22">
-        <f>0.13*G62*20062.02/100</f>
-        <v>1307.1325333977736</v>
-      </c>
-      <c r="K63" s="26"/>
-    </row>
-    <row r="64" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="24"/>
-      <c r="B64" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C64" s="26"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="26"/>
-      <c r="J64" s="22">
-        <f>0.13*G62*13328.25/100</f>
-        <v>868.39656167518899</v>
-      </c>
-      <c r="K64" s="26"/>
-    </row>
-    <row r="65" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="24"/>
-      <c r="B65" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C65" s="26"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="26"/>
-      <c r="I65" s="26"/>
-      <c r="J65" s="22">
-        <f>0.13*G62*10137.6/100</f>
-        <v>660.51109362732518</v>
-      </c>
-      <c r="K65" s="26"/>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="15"/>
+      <c r="B62" s="16" t="str">
+        <f>B39</f>
+        <v>-for column over support beam</v>
+      </c>
+      <c r="C62" s="15">
+        <f>C39</f>
+        <v>4</v>
+      </c>
+      <c r="D62" s="3">
+        <f>D39</f>
+        <v>0.23</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3">
+        <f>F39</f>
+        <v>1.8</v>
+      </c>
+      <c r="G62" s="3">
+        <f t="shared" si="5"/>
+        <v>1.6560000000000001</v>
+      </c>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="15"/>
+      <c r="B63" s="16" t="str">
+        <f>B41</f>
+        <v>-for inclined slab</v>
+      </c>
+      <c r="C63" s="15">
+        <f>C41</f>
+        <v>4</v>
+      </c>
+      <c r="D63" s="3">
+        <f>D41</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="E63" s="3">
+        <f>E41</f>
+        <v>0.91435537945748246</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3">
+        <f t="shared" si="5"/>
+        <v>11.147276799237824</v>
+      </c>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="15"/>
+      <c r="B64" s="16" t="str">
+        <f t="shared" ref="B64:E64" si="6">B42</f>
+        <v>-for cantilever</v>
+      </c>
+      <c r="C64" s="15">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="D64" s="3">
+        <f t="shared" si="6"/>
+        <v>4.2669917708015843</v>
+      </c>
+      <c r="E64" s="3">
+        <f t="shared" si="6"/>
+        <v>0.6</v>
+      </c>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3">
+        <f t="shared" ref="G64:G69" si="7">PRODUCT(C64:F64)</f>
+        <v>5.1203901249619008</v>
+      </c>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="15"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="15">
+        <f t="shared" ref="B65:E65" si="8">C43</f>
+        <v>2</v>
+      </c>
+      <c r="D65" s="3">
+        <f t="shared" si="8"/>
+        <v>5.4669917708015845</v>
+      </c>
+      <c r="E65" s="3">
+        <f t="shared" si="8"/>
+        <v>0.6</v>
+      </c>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3">
+        <f t="shared" si="7"/>
+        <v>6.5603901249619012</v>
+      </c>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="15"/>
-      <c r="B66" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C66" s="15"/>
-      <c r="D66" s="3"/>
+      <c r="B66" s="16" t="str">
+        <f t="shared" ref="B66:E66" si="9">B44</f>
+        <v>-beam for top roof inclined support</v>
+      </c>
+      <c r="C66" s="15">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="D66" s="3">
+        <f t="shared" si="9"/>
+        <v>1.9811033221578787</v>
+      </c>
       <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
+      <c r="F66" s="3">
+        <f>F44*2</f>
+        <v>0.46</v>
+      </c>
+      <c r="G66" s="3">
+        <f t="shared" si="7"/>
+        <v>3.6452301127704967</v>
+      </c>
       <c r="H66" s="15"/>
       <c r="I66" s="15"/>
-      <c r="J66" s="22">
-        <f>0.13*G62*3300/100</f>
-        <v>215.01012162347823</v>
-      </c>
+      <c r="J66" s="15"/>
       <c r="K66" s="15"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="15"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
+      <c r="B67" s="16" t="str">
+        <f t="shared" ref="B67:F67" si="10">B45</f>
+        <v>-top roof</v>
+      </c>
+      <c r="C67" s="15">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="D67" s="3">
+        <f t="shared" si="10"/>
+        <v>0.99055166107893933</v>
+      </c>
+      <c r="E67" s="3">
+        <f t="shared" si="10"/>
+        <v>1.2191405059433098</v>
+      </c>
       <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
+      <c r="G67" s="3">
+        <f t="shared" si="7"/>
+        <v>4.8304866130030559</v>
+      </c>
       <c r="H67" s="15"/>
       <c r="I67" s="15"/>
       <c r="J67" s="15"/>
       <c r="K67" s="15"/>
     </row>
-    <row r="68" spans="1:13" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A68" s="11">
-        <v>6</v>
-      </c>
-      <c r="B68" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E68" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="F68" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="G68" s="23"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="15"/>
+      <c r="B68" s="16" t="str">
+        <f t="shared" ref="B68:F68" si="11">B46</f>
+        <v>-for cantilever</v>
+      </c>
+      <c r="C68" s="15">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="D68" s="3">
+        <f t="shared" si="11"/>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E68" s="3">
+        <f t="shared" si="11"/>
+        <v>0.53337397135019804</v>
+      </c>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3">
+        <f t="shared" si="7"/>
+        <v>3.7389824264110194</v>
+      </c>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="15"/>
-      <c r="B69" s="16" t="str">
-        <f>B34</f>
-        <v>-for foundation</v>
-      </c>
+      <c r="B69" s="16"/>
       <c r="C69" s="15">
-        <f>TRUNC((1.5-0.1)/0.15,0)+1</f>
-        <v>10</v>
+        <f t="shared" ref="B69:F69" si="12">C47</f>
+        <v>2</v>
       </c>
       <c r="D69" s="3">
-        <f>1.5</f>
-        <v>1.5</v>
+        <f t="shared" si="12"/>
+        <v>2.4382810118866196</v>
       </c>
       <c r="E69" s="3">
-        <f>12*12/162</f>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="F69" s="3">
-        <f t="shared" ref="F69:F87" si="5">PRODUCT(C69:E69)</f>
-        <v>13.333333333333332</v>
-      </c>
+        <f t="shared" si="12"/>
+        <v>0.53337397135019804</v>
+      </c>
+      <c r="F69" s="3"/>
       <c r="G69" s="3">
-        <f t="shared" ref="G69:G87" si="6">F69/1000</f>
-        <v>1.3333333333333332E-2</v>
+        <f t="shared" si="7"/>
+        <v>2.6010312531554916</v>
       </c>
       <c r="H69" s="15"/>
       <c r="I69" s="15"/>
       <c r="J69" s="15"/>
       <c r="K69" s="15"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="15"/>
-      <c r="B70" s="16"/>
-      <c r="C70" s="15">
-        <f>TRUNC((1.5-0.1)/0.15,0)+1</f>
-        <v>10</v>
-      </c>
-      <c r="D70" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="E70" s="3">
-        <f>12*12/162</f>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="F70" s="3">
-        <f t="shared" si="5"/>
-        <v>13.333333333333332</v>
-      </c>
-      <c r="G70" s="3">
-        <f t="shared" si="6"/>
-        <v>1.3333333333333332E-2</v>
-      </c>
-      <c r="H70" s="15"/>
-      <c r="I70" s="15"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A71" s="15"/>
-      <c r="B71" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C71" s="15">
-        <f>4*4</f>
+    <row r="70" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="17"/>
+      <c r="B70" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="3">
-        <f>(10.5+1.5+5-0.17*2)/3.281+0.45+0.45</f>
-        <v>5.9777202072538858</v>
-      </c>
-      <c r="E71" s="3">
-        <f t="shared" ref="E71" si="7">12*12/162</f>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="F71" s="3">
-        <f t="shared" si="5"/>
-        <v>85.01646516983304</v>
-      </c>
-      <c r="G71" s="3">
-        <f t="shared" si="6"/>
-        <v>8.5016465169833036E-2</v>
-      </c>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A72" s="15"/>
-      <c r="B72" s="16"/>
-      <c r="C72" s="15">
-        <f>4*4</f>
-        <v>16</v>
-      </c>
-      <c r="D72" s="3">
-        <f>(10.5+1.5+5-0.17*2)/3.281+0.45+0.45</f>
-        <v>5.9777202072538858</v>
-      </c>
-      <c r="E72" s="3">
-        <f>16*16/162</f>
-        <v>1.5802469135802468</v>
-      </c>
-      <c r="F72" s="3">
-        <f t="shared" si="5"/>
-        <v>151.14038252414761</v>
-      </c>
-      <c r="G72" s="3">
-        <f t="shared" si="6"/>
-        <v>0.1511403825241476</v>
-      </c>
-      <c r="H72" s="15"/>
-      <c r="I72" s="15"/>
-      <c r="J72" s="15"/>
-      <c r="K72" s="15"/>
-      <c r="M72">
-        <f>(10.5+1.5+5-0.17*2)/3.281</f>
-        <v>5.0777202072538854</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="15"/>
-      <c r="B73" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C73" s="15">
-        <f>4*(TRUNC((D72-0.45-0.45)/0.15,0)+1)</f>
-        <v>136</v>
-      </c>
-      <c r="D73" s="3">
-        <f>0.917*4/3.281</f>
-        <v>1.1179518439500153</v>
-      </c>
-      <c r="E73" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F73" s="3">
-        <f t="shared" si="5"/>
-        <v>60.065758331734159</v>
-      </c>
-      <c r="G73" s="3">
-        <f t="shared" si="6"/>
-        <v>6.0065758331734158E-2</v>
-      </c>
-      <c r="H73" s="15"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="15"/>
-      <c r="K73" s="15"/>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="15"/>
-      <c r="B74" s="16"/>
-      <c r="C74" s="15">
-        <f>4*(TRUNC((D72-0.45-0.45)/0.15,0)+1)</f>
-        <v>136</v>
-      </c>
-      <c r="D74" s="3">
-        <f>0.833*4/3.281</f>
-        <v>1.015544041450777</v>
-      </c>
-      <c r="E74" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F74" s="3">
-        <f t="shared" si="5"/>
-        <v>54.56355146165162</v>
-      </c>
-      <c r="G74" s="3">
-        <f t="shared" si="6"/>
-        <v>5.4563551461651622E-2</v>
-      </c>
-      <c r="H74" s="15"/>
-      <c r="I74" s="15"/>
-      <c r="J74" s="15"/>
-      <c r="K74" s="15"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="2">
+        <f>SUM(G57:G69)</f>
+        <v>74.830460420060959</v>
+      </c>
+      <c r="H70" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I70" s="2">
+        <v>922.71</v>
+      </c>
+      <c r="J70" s="22">
+        <f>G70*I70</f>
+        <v>69046.814134194443</v>
+      </c>
+      <c r="K70" s="20"/>
+    </row>
+    <row r="71" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="24"/>
+      <c r="B71" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C71" s="26"/>
+      <c r="D71" s="27"/>
+      <c r="E71" s="27"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="27"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="26"/>
+      <c r="J71" s="22">
+        <f>0.13*G70*20062.02/100</f>
+        <v>1951.6252516234129</v>
+      </c>
+      <c r="K71" s="26"/>
+    </row>
+    <row r="72" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="24"/>
+      <c r="B72" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C72" s="26"/>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
+      <c r="J72" s="22">
+        <f>0.13*G70*13328.25/100</f>
+        <v>1296.5668093217805</v>
+      </c>
+      <c r="K72" s="26"/>
+    </row>
+    <row r="73" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="24"/>
+      <c r="B73" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C73" s="26"/>
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="27"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="22">
+        <f>0.13*G70*10137.6/100</f>
+        <v>986.18165822073297</v>
+      </c>
+      <c r="K73" s="26"/>
+    </row>
+    <row r="74" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="71"/>
+      <c r="B74" s="72" t="s">
+        <v>50</v>
+      </c>
+      <c r="C74" s="71"/>
+      <c r="D74" s="73"/>
+      <c r="E74" s="73"/>
+      <c r="F74" s="73"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="71"/>
+      <c r="I74" s="71"/>
+      <c r="J74" s="74">
+        <f>0.13*G70*3300/100</f>
+        <v>321.02267520206152</v>
+      </c>
+      <c r="K74" s="71"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="15"/>
-      <c r="B75" s="16" t="str">
-        <f>B54</f>
-        <v>-for tie beam</v>
-      </c>
-      <c r="C75" s="15">
-        <f>4*4</f>
-        <v>16</v>
-      </c>
-      <c r="D75" s="3">
-        <f>(12+0.75*2)/3.281</f>
-        <v>4.1145992075586708</v>
-      </c>
-      <c r="E75" s="3">
-        <f>12*12/162</f>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="F75" s="3">
-        <f t="shared" si="5"/>
-        <v>58.518744285278871</v>
-      </c>
-      <c r="G75" s="3">
-        <f t="shared" si="6"/>
-        <v>5.8518744285278868E-2</v>
-      </c>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
       <c r="H75" s="15"/>
       <c r="I75" s="15"/>
       <c r="J75" s="15"/>
       <c r="K75" s="15"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="15"/>
-      <c r="B76" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C76" s="15">
-        <f>4*(TRUNC((D54-0.1)/0.15,0)+1)</f>
-        <v>60</v>
-      </c>
-      <c r="D76" s="3">
-        <f>(0.583*4+0.17*2)/3.281</f>
-        <v>0.81438585797013097</v>
-      </c>
-      <c r="E76" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
-      </c>
-      <c r="F76" s="3">
-        <f t="shared" si="5"/>
-        <v>19.303961077810513</v>
-      </c>
-      <c r="G76" s="3">
-        <f t="shared" si="6"/>
-        <v>1.9303961077810513E-2</v>
-      </c>
-      <c r="H76" s="15"/>
-      <c r="I76" s="15"/>
-      <c r="J76" s="15"/>
-      <c r="K76" s="15"/>
+    <row r="76" spans="1:13" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A76" s="11">
+        <v>6</v>
+      </c>
+      <c r="B76" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="F76" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="G76" s="23"/>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="13"/>
+      <c r="K76" s="13"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="15"/>
       <c r="B77" s="16" t="str">
-        <f>B56</f>
-        <v>-for beam</v>
+        <f>B33</f>
+        <v>-for foundation</v>
       </c>
       <c r="C77" s="15">
-        <f>4*(TRUNC((D54-0.1)/0.15,0)+1)</f>
-        <v>60</v>
+        <f>TRUNC((1.5-0.1)/0.15,0)+1</f>
+        <v>10</v>
       </c>
       <c r="D77" s="3">
-        <f>(0.583*4+0.17*2)/3.281</f>
-        <v>0.81438585797013097</v>
+        <f>1.5</f>
+        <v>1.5</v>
       </c>
       <c r="E77" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F77" s="3">
-        <f t="shared" si="5"/>
-        <v>19.303961077810513</v>
+        <f t="shared" ref="F77:F95" si="13">PRODUCT(C77:E77)</f>
+        <v>13.333333333333332</v>
       </c>
       <c r="G77" s="3">
-        <f t="shared" si="6"/>
-        <v>1.9303961077810513E-2</v>
+        <f t="shared" ref="G77:G95" si="14">F77/1000</f>
+        <v>1.3333333333333332E-2</v>
       </c>
       <c r="H77" s="15"/>
       <c r="I77" s="15"/>
@@ -10135,29 +10243,25 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="15"/>
-      <c r="B78" s="16" t="str">
-        <f>B57</f>
-        <v>-for support beam</v>
-      </c>
+      <c r="B78" s="16"/>
       <c r="C78" s="15">
-        <f>4*4</f>
-        <v>16</v>
+        <f>TRUNC((1.5-0.1)/0.15,0)+1</f>
+        <v>10</v>
       </c>
       <c r="D78" s="3">
-        <f>(12+0.75*2)/3.281</f>
-        <v>4.1145992075586708</v>
+        <v>1.5</v>
       </c>
       <c r="E78" s="3">
         <f>12*12/162</f>
         <v>0.88888888888888884</v>
       </c>
       <c r="F78" s="3">
-        <f t="shared" si="5"/>
-        <v>58.518744285278871</v>
+        <f t="shared" si="13"/>
+        <v>13.333333333333332</v>
       </c>
       <c r="G78" s="3">
-        <f t="shared" si="6"/>
-        <v>5.8518744285278868E-2</v>
+        <f t="shared" si="14"/>
+        <v>1.3333333333333332E-2</v>
       </c>
       <c r="H78" s="15"/>
       <c r="I78" s="15"/>
@@ -10166,26 +10270,28 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="15"/>
-      <c r="B79" s="16"/>
+      <c r="B79" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="C79" s="15">
-        <f>2*(TRUNC((D56-0.1)/0.15,0)+1)</f>
-        <v>30</v>
+        <f>4*4</f>
+        <v>16</v>
       </c>
       <c r="D79" s="3">
-        <f>(0.583*4+0.17*2)/3.281</f>
-        <v>0.81438585797013097</v>
+        <f>(10.5+1.5+5-0.17*2)/3.281+0.45+0.45</f>
+        <v>5.9777202072538858</v>
       </c>
       <c r="E79" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
+        <f t="shared" ref="E79" si="15">12*12/162</f>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F79" s="3">
-        <f t="shared" si="5"/>
-        <v>9.6519805389052564</v>
+        <f t="shared" si="13"/>
+        <v>85.01646516983304</v>
       </c>
       <c r="G79" s="3">
-        <f t="shared" si="6"/>
-        <v>9.6519805389052565E-3</v>
+        <f t="shared" si="14"/>
+        <v>8.5016465169833036E-2</v>
       </c>
       <c r="H79" s="15"/>
       <c r="I79" s="15"/>
@@ -10194,34 +10300,35 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="15"/>
-      <c r="B80" s="16" t="str">
-        <f>B58</f>
-        <v>-for column over support beam</v>
-      </c>
+      <c r="B80" s="16"/>
       <c r="C80" s="15">
-        <f>C58*4</f>
+        <f>4*4</f>
         <v>16</v>
       </c>
       <c r="D80" s="3">
-        <f>1.5+0.45+0.45</f>
-        <v>2.4</v>
+        <f>(10.5+1.5+5-0.17*2)/3.281+0.45+0.45</f>
+        <v>5.9777202072538858</v>
       </c>
       <c r="E80" s="3">
-        <f>12*12/162</f>
-        <v>0.88888888888888884</v>
+        <f>16*16/162</f>
+        <v>1.5802469135802468</v>
       </c>
       <c r="F80" s="3">
-        <f t="shared" si="5"/>
-        <v>34.133333333333333</v>
+        <f t="shared" si="13"/>
+        <v>151.14038252414761</v>
       </c>
       <c r="G80" s="3">
-        <f t="shared" si="6"/>
-        <v>3.4133333333333335E-2</v>
+        <f t="shared" si="14"/>
+        <v>0.1511403825241476</v>
       </c>
       <c r="H80" s="15"/>
       <c r="I80" s="15"/>
       <c r="J80" s="15"/>
       <c r="K80" s="15"/>
+      <c r="M80">
+        <f>(10.5+1.5+5-0.17*2)/3.281</f>
+        <v>5.0777202072538854</v>
+      </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="15"/>
@@ -10229,8 +10336,8 @@
         <v>71</v>
       </c>
       <c r="C81" s="15">
-        <f>4*(TRUNC((D80-0.1)/0.15,0)+1)</f>
-        <v>64</v>
+        <f>4*(TRUNC((D80-0.45-0.45)/0.15,0)+1)</f>
+        <v>136</v>
       </c>
       <c r="D81" s="3">
         <f>0.917*4/3.281</f>
@@ -10241,12 +10348,12 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F81" s="3">
-        <f t="shared" si="5"/>
-        <v>28.266239214933719</v>
+        <f t="shared" si="13"/>
+        <v>60.065758331734159</v>
       </c>
       <c r="G81" s="3">
-        <f t="shared" si="6"/>
-        <v>2.8266239214933719E-2</v>
+        <f t="shared" si="14"/>
+        <v>6.0065758331734158E-2</v>
       </c>
       <c r="H81" s="15"/>
       <c r="I81" s="15"/>
@@ -10255,29 +10362,26 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="15"/>
-      <c r="B82" s="16" t="str">
-        <f>B59</f>
-        <v>-for inclined slab</v>
-      </c>
+      <c r="B82" s="16"/>
       <c r="C82" s="15">
-        <f>4*(TRUNC((D83/0.15),0)+1)</f>
-        <v>24</v>
+        <f>4*(TRUNC((D80-0.45-0.45)/0.15,0)+1)</f>
+        <v>136</v>
       </c>
       <c r="D82" s="3">
-        <f>D59</f>
-        <v>2.6668698567509903</v>
+        <f>0.833*4/3.281</f>
+        <v>1.015544041450777</v>
       </c>
       <c r="E82" s="3">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
       </c>
       <c r="F82" s="3">
-        <f t="shared" si="5"/>
-        <v>39.509183062977634</v>
+        <f t="shared" si="13"/>
+        <v>54.56355146165162</v>
       </c>
       <c r="G82" s="3">
-        <f t="shared" si="6"/>
-        <v>3.9509183062977633E-2</v>
+        <f t="shared" si="14"/>
+        <v>5.4563551461651622E-2</v>
       </c>
       <c r="H82" s="15"/>
       <c r="I82" s="15"/>
@@ -10286,26 +10390,29 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="15"/>
-      <c r="B83" s="16"/>
+      <c r="B83" s="16" t="str">
+        <f>B58</f>
+        <v>-for tie beam</v>
+      </c>
       <c r="C83" s="15">
-        <f>4*(TRUNC((D82/0.15),0)+1)</f>
-        <v>72</v>
+        <f>4*4</f>
+        <v>16</v>
       </c>
       <c r="D83" s="3">
-        <f>F59</f>
-        <v>0.75</v>
+        <f>(12+0.75*2)/3.281</f>
+        <v>4.1145992075586708</v>
       </c>
       <c r="E83" s="3">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F83" s="3">
-        <f t="shared" si="5"/>
-        <v>33.333333333333329</v>
+        <f t="shared" si="13"/>
+        <v>58.518744285278871</v>
       </c>
       <c r="G83" s="3">
-        <f t="shared" si="6"/>
-        <v>3.3333333333333326E-2</v>
+        <f t="shared" si="14"/>
+        <v>5.8518744285278868E-2</v>
       </c>
       <c r="H83" s="15"/>
       <c r="I83" s="15"/>
@@ -10315,26 +10422,27 @@
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="15"/>
       <c r="B84" s="16" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C84" s="15">
-        <v>3</v>
+        <f>4*(TRUNC((D58-0.1)/0.15,0)+1)</f>
+        <v>96</v>
       </c>
       <c r="D84" s="3">
-        <f>(12+2+2)/3.281</f>
-        <v>4.8765620237732392</v>
+        <f>(0.583*4+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
       </c>
       <c r="E84" s="3">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
       </c>
       <c r="F84" s="3">
-        <f t="shared" si="5"/>
-        <v>9.030670414394887</v>
+        <f t="shared" si="13"/>
+        <v>30.886337724496816</v>
       </c>
       <c r="G84" s="3">
-        <f t="shared" si="6"/>
-        <v>9.0306704143948875E-3</v>
+        <f t="shared" si="14"/>
+        <v>3.0886337724496817E-2</v>
       </c>
       <c r="H84" s="15"/>
       <c r="I84" s="15"/>
@@ -10343,25 +10451,29 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="15"/>
-      <c r="B85" s="16"/>
+      <c r="B85" s="16" t="str">
+        <f>B60</f>
+        <v>-for beam</v>
+      </c>
       <c r="C85" s="15">
-        <f>26</f>
-        <v>26</v>
+        <f>4*(TRUNC((D58-0.1)/0.15,0)+1)</f>
+        <v>96</v>
       </c>
       <c r="D85" s="3">
-        <v>0.6</v>
+        <f>(0.583*4+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
       </c>
       <c r="E85" s="3">
-        <f t="shared" ref="E85:E87" si="8">10*10/162</f>
-        <v>0.61728395061728392</v>
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
       </c>
       <c r="F85" s="3">
-        <f t="shared" si="5"/>
-        <v>9.6296296296296298</v>
+        <f t="shared" si="13"/>
+        <v>30.886337724496816</v>
       </c>
       <c r="G85" s="3">
-        <f t="shared" si="6"/>
-        <v>9.6296296296296303E-3</v>
+        <f t="shared" si="14"/>
+        <v>3.0886337724496817E-2</v>
       </c>
       <c r="H85" s="15"/>
       <c r="I85" s="15"/>
@@ -10370,25 +10482,29 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="15"/>
-      <c r="B86" s="16"/>
+      <c r="B86" s="16" t="str">
+        <f>B61</f>
+        <v>-for support beam</v>
+      </c>
       <c r="C86" s="15">
-        <v>3</v>
+        <f>4*4</f>
+        <v>16</v>
       </c>
       <c r="D86" s="3">
-        <f>(12+2+2)/3.281</f>
-        <v>4.8765620237732392</v>
+        <f>(12+0.75*2)/3.281</f>
+        <v>4.1145992075586708</v>
       </c>
       <c r="E86" s="3">
-        <f t="shared" si="8"/>
-        <v>0.61728395061728392</v>
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F86" s="3">
-        <f t="shared" si="5"/>
-        <v>9.030670414394887</v>
+        <f t="shared" si="13"/>
+        <v>58.518744285278871</v>
       </c>
       <c r="G86" s="3">
-        <f t="shared" si="6"/>
-        <v>9.0306704143948875E-3</v>
+        <f t="shared" si="14"/>
+        <v>5.8518744285278868E-2</v>
       </c>
       <c r="H86" s="15"/>
       <c r="I86" s="15"/>
@@ -10399,115 +10515,174 @@
       <c r="A87" s="15"/>
       <c r="B87" s="16"/>
       <c r="C87" s="15">
-        <f>C85</f>
-        <v>26</v>
+        <f>2*(TRUNC((D60-0.1)/0.15,0)+1)</f>
+        <v>48</v>
       </c>
       <c r="D87" s="3">
-        <v>0.6</v>
+        <f>(0.583*4+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
       </c>
       <c r="E87" s="3">
-        <f t="shared" si="8"/>
-        <v>0.61728395061728392</v>
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
       </c>
       <c r="F87" s="3">
-        <f t="shared" si="5"/>
-        <v>9.6296296296296298</v>
+        <f t="shared" si="13"/>
+        <v>15.443168862248408</v>
       </c>
       <c r="G87" s="3">
-        <f t="shared" si="6"/>
-        <v>9.6296296296296303E-3</v>
+        <f t="shared" si="14"/>
+        <v>1.5443168862248408E-2</v>
       </c>
       <c r="H87" s="15"/>
       <c r="I87" s="15"/>
       <c r="J87" s="15"/>
       <c r="K87" s="15"/>
     </row>
-    <row r="88" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="17"/>
-      <c r="B88" s="18" t="s">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="15"/>
+      <c r="B88" s="16" t="str">
+        <f>B62</f>
+        <v>-for column over support beam</v>
+      </c>
+      <c r="C88" s="15">
+        <f>C62*4</f>
         <v>16</v>
       </c>
-      <c r="C88" s="19"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="20"/>
-      <c r="F88" s="20"/>
-      <c r="G88" s="2">
-        <f>SUM(G69:G87)</f>
-        <v>0.71531290445174434</v>
-      </c>
-      <c r="H88" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="I88" s="46">
-        <v>132360</v>
-      </c>
-      <c r="J88" s="22">
-        <f>G88*I88</f>
-        <v>94678.816033232884</v>
-      </c>
-      <c r="K88" s="20"/>
-    </row>
-    <row r="89" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="24"/>
-      <c r="B89" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C89" s="26"/>
-      <c r="D89" s="26"/>
-      <c r="E89" s="26"/>
-      <c r="F89" s="26"/>
-      <c r="G89" s="26"/>
-      <c r="H89" s="26"/>
-      <c r="I89" s="26"/>
-      <c r="J89" s="22">
-        <f>0.13*G88*105000</f>
-        <v>9764.0211457663099</v>
-      </c>
-      <c r="K89" s="26"/>
-    </row>
-    <row r="90" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="24"/>
-      <c r="B90" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C90" s="26"/>
-      <c r="D90" s="26"/>
-      <c r="E90" s="26"/>
-      <c r="F90" s="26"/>
-      <c r="G90" s="26"/>
-      <c r="H90" s="26"/>
-      <c r="I90" s="26"/>
-      <c r="J90" s="22">
-        <f>0.13*G88*1200</f>
-        <v>111.58881309447212</v>
-      </c>
-      <c r="K90" s="26"/>
+      <c r="D88" s="3">
+        <f>1.5+0.45+0.45</f>
+        <v>2.4</v>
+      </c>
+      <c r="E88" s="3">
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="F88" s="3">
+        <f t="shared" si="13"/>
+        <v>34.133333333333333</v>
+      </c>
+      <c r="G88" s="3">
+        <f t="shared" si="14"/>
+        <v>3.4133333333333335E-2</v>
+      </c>
+      <c r="H88" s="15"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="15"/>
+      <c r="B89" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C89" s="15">
+        <f>4*(TRUNC((D88-0.1)/0.15,0)+1)</f>
+        <v>64</v>
+      </c>
+      <c r="D89" s="3">
+        <f>0.917*4/3.281</f>
+        <v>1.1179518439500153</v>
+      </c>
+      <c r="E89" s="3">
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
+      </c>
+      <c r="F89" s="3">
+        <f t="shared" si="13"/>
+        <v>28.266239214933719</v>
+      </c>
+      <c r="G89" s="3">
+        <f t="shared" si="14"/>
+        <v>2.8266239214933719E-2</v>
+      </c>
+      <c r="H89" s="15"/>
+      <c r="I89" s="15"/>
+      <c r="J89" s="15"/>
+      <c r="K89" s="15"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="15"/>
+      <c r="B90" s="16" t="str">
+        <f>B63</f>
+        <v>-for inclined slab</v>
+      </c>
+      <c r="C90" s="15">
+        <f>4*(TRUNC((D91/0.15),0)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="D90" s="3">
+        <f>D63</f>
+        <v>3.047851264858275</v>
+      </c>
+      <c r="E90" s="3">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F90" s="3">
+        <f t="shared" si="13"/>
+        <v>7.5255586786624065</v>
+      </c>
+      <c r="G90" s="3">
+        <f t="shared" si="14"/>
+        <v>7.5255586786624066E-3</v>
+      </c>
+      <c r="H90" s="15"/>
+      <c r="I90" s="15"/>
+      <c r="J90" s="15"/>
+      <c r="K90" s="15"/>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="15"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="15"/>
-      <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="15">
+        <f>4*(TRUNC((D90/0.15),0)+1)</f>
+        <v>84</v>
+      </c>
+      <c r="D91" s="3">
+        <f>F63</f>
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F91" s="3">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
       <c r="H91" s="15"/>
       <c r="I91" s="15"/>
       <c r="J91" s="15"/>
       <c r="K91" s="15"/>
     </row>
-    <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A92" s="11">
-        <v>7</v>
-      </c>
-      <c r="B92" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="15"/>
+      <c r="B92" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C92" s="15">
+        <v>3</v>
+      </c>
+      <c r="D92" s="3">
+        <f>(12+2+2)/3.281</f>
+        <v>4.8765620237732392</v>
+      </c>
+      <c r="E92" s="3">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F92" s="3">
+        <f t="shared" si="13"/>
+        <v>9.030670414394887</v>
+      </c>
+      <c r="G92" s="3">
+        <f t="shared" si="14"/>
+        <v>9.0306704143948875E-3</v>
+      </c>
       <c r="H92" s="15"/>
       <c r="I92" s="15"/>
       <c r="J92" s="15"/>
@@ -10515,129 +10690,149 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="15"/>
-      <c r="B93" s="16" t="s">
-        <v>66</v>
-      </c>
+      <c r="B93" s="16"/>
       <c r="C93" s="15">
-        <v>1</v>
+        <f>26</f>
+        <v>26</v>
       </c>
       <c r="D93" s="3">
-        <f>(18.5-0.75*2)/3.281</f>
-        <v>5.1813471502590671</v>
+        <v>0.6</v>
       </c>
       <c r="E93" s="3">
-        <f>(8.75+17.5-0.75*2)/3.281</f>
-        <v>7.5434318805242304</v>
-      </c>
-      <c r="F93" s="15"/>
+        <f t="shared" ref="E93:E95" si="16">10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F93" s="3">
+        <f t="shared" si="13"/>
+        <v>9.6296296296296298</v>
+      </c>
       <c r="G93" s="3">
-        <f>PRODUCT(C93:F93)</f>
-        <v>39.08513927732762</v>
+        <f t="shared" si="14"/>
+        <v>9.6296296296296303E-3</v>
       </c>
       <c r="H93" s="15"/>
       <c r="I93" s="15"/>
       <c r="J93" s="15"/>
       <c r="K93" s="15"/>
     </row>
-    <row r="94" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="17"/>
-      <c r="B94" s="18" t="s">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="15"/>
+      <c r="B94" s="16"/>
+      <c r="C94" s="15">
+        <v>3</v>
+      </c>
+      <c r="D94" s="3">
+        <f>(12+2+2)/3.281</f>
+        <v>4.8765620237732392</v>
+      </c>
+      <c r="E94" s="3">
+        <f t="shared" si="16"/>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F94" s="3">
+        <f t="shared" si="13"/>
+        <v>9.030670414394887</v>
+      </c>
+      <c r="G94" s="3">
+        <f t="shared" si="14"/>
+        <v>9.0306704143948875E-3</v>
+      </c>
+      <c r="H94" s="15"/>
+      <c r="I94" s="15"/>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="15"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="15">
+        <f>C93</f>
+        <v>26</v>
+      </c>
+      <c r="D95" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E95" s="3">
+        <f t="shared" si="16"/>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F95" s="3">
+        <f t="shared" si="13"/>
+        <v>9.6296296296296298</v>
+      </c>
+      <c r="G95" s="3">
+        <f t="shared" si="14"/>
+        <v>9.6296296296296303E-3</v>
+      </c>
+      <c r="H95" s="15"/>
+      <c r="I95" s="15"/>
+      <c r="J95" s="15"/>
+      <c r="K95" s="15"/>
+    </row>
+    <row r="96" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="17"/>
+      <c r="B96" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C94" s="19"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="20"/>
-      <c r="F94" s="20"/>
-      <c r="G94" s="2">
-        <f>SUM(G93)</f>
-        <v>39.08513927732762</v>
-      </c>
-      <c r="H94" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I94" s="2">
-        <v>689.98</v>
-      </c>
-      <c r="J94" s="22">
-        <f>G94*I94</f>
-        <v>26967.964398570512</v>
-      </c>
-      <c r="K94" s="20"/>
-    </row>
-    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="24"/>
-      <c r="B95" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C95" s="26"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="27"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="27"/>
-      <c r="H95" s="26"/>
-      <c r="I95" s="26"/>
-      <c r="J95" s="22">
-        <f>0.13*G94*1694.03/10</f>
-        <v>860.74818036962699</v>
-      </c>
-      <c r="K95" s="26"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="15"/>
-      <c r="B96" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C96" s="26"/>
-      <c r="D96" s="27"/>
-      <c r="E96" s="27"/>
-      <c r="F96" s="27"/>
-      <c r="G96" s="27"/>
-      <c r="H96" s="26"/>
-      <c r="I96" s="26"/>
+      <c r="C96" s="19"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="20"/>
+      <c r="F96" s="20"/>
+      <c r="G96" s="2">
+        <f>SUM(G77:G95)</f>
+        <v>0.67895188835081155</v>
+      </c>
+      <c r="H96" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I96" s="46">
+        <v>132360</v>
+      </c>
       <c r="J96" s="22">
-        <f>0.13*G94*472.02/10</f>
-        <v>239.83657674189439</v>
-      </c>
-      <c r="K96" s="15"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="15"/>
+        <f>G96*I96</f>
+        <v>89866.071942113413</v>
+      </c>
+      <c r="K96" s="20"/>
+    </row>
+    <row r="97" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="24"/>
       <c r="B97" s="25" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C97" s="26"/>
-      <c r="D97" s="27"/>
-      <c r="E97" s="27"/>
-      <c r="F97" s="27"/>
-      <c r="G97" s="27"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26"/>
       <c r="H97" s="26"/>
       <c r="I97" s="26"/>
       <c r="J97" s="22">
-        <f>0.13*G94*1207.6/10</f>
-        <v>613.58978448691084</v>
-      </c>
-      <c r="K97" s="15"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="15"/>
-      <c r="B98" s="15"/>
-      <c r="C98" s="15"/>
-      <c r="D98" s="15"/>
-      <c r="E98" s="15"/>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
-      <c r="H98" s="15"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="15"/>
-      <c r="K98" s="15"/>
-    </row>
-    <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99" s="11">
-        <v>8</v>
-      </c>
-      <c r="B99" s="28" t="s">
-        <v>53</v>
-      </c>
+        <f>0.13*G96*105000</f>
+        <v>9267.6932759885785</v>
+      </c>
+      <c r="K97" s="26"/>
+    </row>
+    <row r="98" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="24"/>
+      <c r="B98" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="26"/>
+      <c r="J98" s="22">
+        <f>0.13*G96*1200</f>
+        <v>105.9164945827266</v>
+      </c>
+      <c r="K98" s="26"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="15"/>
+      <c r="B99" s="15"/>
       <c r="C99" s="15"/>
       <c r="D99" s="15"/>
       <c r="E99" s="15"/>
@@ -10648,28 +10843,18 @@
       <c r="J99" s="15"/>
       <c r="K99" s="15"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="15"/>
-      <c r="B100" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C100" s="45">
-        <f>2*2</f>
-        <v>4</v>
-      </c>
-      <c r="D100" s="3">
-        <f>D117</f>
-        <v>5.6385248399878085</v>
-      </c>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3">
-        <f>F117</f>
-        <v>2.2858884486437061</v>
-      </c>
-      <c r="G100" s="3">
-        <f>PRODUCT(C100:F100)</f>
-        <v>51.556155196474933</v>
-      </c>
+    <row r="100" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A100" s="11">
+        <v>7</v>
+      </c>
+      <c r="B100" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C100" s="15"/>
+      <c r="D100" s="15"/>
+      <c r="E100" s="15"/>
+      <c r="F100" s="15"/>
+      <c r="G100" s="15"/>
       <c r="H100" s="15"/>
       <c r="I100" s="15"/>
       <c r="J100" s="15"/>
@@ -10677,114 +10862,95 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="15"/>
-      <c r="B101" s="16"/>
-      <c r="C101" s="45">
-        <f>2*C118</f>
-        <v>4</v>
+      <c r="B101" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C101" s="15">
+        <v>1</v>
       </c>
       <c r="D101" s="3">
-        <f>D118</f>
-        <v>8.0006095702529709</v>
-      </c>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3">
-        <f>F118</f>
-        <v>2.2858884486437061</v>
-      </c>
+        <f>(18.5-0.75*2)/3.281</f>
+        <v>5.1813471502590671</v>
+      </c>
+      <c r="E101" s="3">
+        <f>(8.75+17.5-0.75*2)/3.281</f>
+        <v>7.5434318805242304</v>
+      </c>
+      <c r="F101" s="15"/>
       <c r="G101" s="3">
         <f>PRODUCT(C101:F101)</f>
-        <v>73.154003994998206</v>
+        <v>39.08513927732762</v>
       </c>
       <c r="H101" s="15"/>
       <c r="I101" s="15"/>
       <c r="J101" s="15"/>
       <c r="K101" s="15"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="15"/>
-      <c r="B102" s="16" t="str">
-        <f>B120</f>
-        <v>-deduction for window</v>
-      </c>
-      <c r="C102" s="45">
-        <f>2*C120</f>
-        <v>-4</v>
-      </c>
-      <c r="D102" s="3">
-        <f t="shared" ref="D102:D103" si="9">D120</f>
-        <v>1.8</v>
-      </c>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3">
-        <f t="shared" ref="F102:F103" si="10">F120</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G102" s="3">
-        <f t="shared" ref="G102:G103" si="11">PRODUCT(C102:F102)</f>
-        <v>-9.875038098140811</v>
-      </c>
-      <c r="H102" s="15"/>
-      <c r="I102" s="15"/>
-      <c r="J102" s="15"/>
-      <c r="K102" s="15"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="15"/>
-      <c r="B103" s="16" t="str">
-        <f>B121</f>
-        <v>-deduction for chain gate</v>
-      </c>
-      <c r="C103" s="45">
-        <f>2*C121</f>
-        <v>-2</v>
-      </c>
-      <c r="D103" s="3">
-        <f t="shared" si="9"/>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3">
-        <f t="shared" si="10"/>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G103" s="3">
-        <f t="shared" si="11"/>
-        <v>-6.6883660795426936</v>
-      </c>
-      <c r="H103" s="15"/>
-      <c r="I103" s="15"/>
-      <c r="J103" s="15"/>
-      <c r="K103" s="15"/>
-    </row>
-    <row r="104" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="17"/>
-      <c r="B104" s="18" t="s">
+    <row r="102" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="17"/>
+      <c r="B102" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C104" s="19"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="20"/>
-      <c r="F104" s="20"/>
-      <c r="G104" s="2">
-        <f>SUM(G100:G103)</f>
-        <v>108.14675501378964</v>
-      </c>
-      <c r="H104" s="21" t="s">
+      <c r="C102" s="19"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="20"/>
+      <c r="F102" s="20"/>
+      <c r="G102" s="2">
+        <f>SUM(G101)</f>
+        <v>39.08513927732762</v>
+      </c>
+      <c r="H102" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I104" s="2">
-        <v>415.5</v>
-      </c>
+      <c r="I102" s="2">
+        <v>689.98</v>
+      </c>
+      <c r="J102" s="22">
+        <f>G102*I102</f>
+        <v>26967.964398570512</v>
+      </c>
+      <c r="K102" s="20"/>
+    </row>
+    <row r="103" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="24"/>
+      <c r="B103" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C103" s="26"/>
+      <c r="D103" s="27"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="27"/>
+      <c r="G103" s="27"/>
+      <c r="H103" s="26"/>
+      <c r="I103" s="26"/>
+      <c r="J103" s="22">
+        <f>0.13*G102*1694.03/10</f>
+        <v>860.74818036962699</v>
+      </c>
+      <c r="K103" s="26"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="15"/>
+      <c r="B104" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C104" s="26"/>
+      <c r="D104" s="27"/>
+      <c r="E104" s="27"/>
+      <c r="F104" s="27"/>
+      <c r="G104" s="27"/>
+      <c r="H104" s="26"/>
+      <c r="I104" s="26"/>
       <c r="J104" s="22">
-        <f>G104*I104</f>
-        <v>44934.976708229595</v>
-      </c>
-      <c r="K104" s="20"/>
-    </row>
-    <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="24"/>
+        <f>0.13*G102*472.02/10</f>
+        <v>239.83657674189439</v>
+      </c>
+      <c r="K104" s="15"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="15"/>
       <c r="B105" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C105" s="26"/>
       <c r="D105" s="27"/>
@@ -10794,32 +10960,31 @@
       <c r="H105" s="26"/>
       <c r="I105" s="26"/>
       <c r="J105" s="22">
-        <f>0.13*G104*7010.67/100</f>
-        <v>985.63557426428201</v>
-      </c>
-      <c r="K105" s="26"/>
+        <f>0.13*G102*1207.6/10</f>
+        <v>613.58978448691084</v>
+      </c>
+      <c r="K105" s="15"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="15"/>
-      <c r="B106" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C106" s="26"/>
-      <c r="D106" s="27"/>
-      <c r="E106" s="27"/>
-      <c r="F106" s="27"/>
-      <c r="G106" s="27"/>
-      <c r="H106" s="26"/>
-      <c r="I106" s="26"/>
-      <c r="J106" s="22">
-        <f>0.13*G104*4639.73/100</f>
-        <v>652.30326673216928</v>
-      </c>
+      <c r="B106" s="15"/>
+      <c r="C106" s="15"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="15"/>
+      <c r="F106" s="15"/>
+      <c r="G106" s="15"/>
+      <c r="H106" s="15"/>
+      <c r="I106" s="15"/>
+      <c r="J106" s="15"/>
       <c r="K106" s="15"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="15"/>
-      <c r="B107" s="15"/>
+    <row r="107" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A107" s="11">
+        <v>8</v>
+      </c>
+      <c r="B107" s="28" t="s">
+        <v>53</v>
+      </c>
       <c r="C107" s="15"/>
       <c r="D107" s="15"/>
       <c r="E107" s="15"/>
@@ -10830,18 +10995,28 @@
       <c r="J107" s="15"/>
       <c r="K107" s="15"/>
     </row>
-    <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A108" s="11">
-        <v>9</v>
-      </c>
-      <c r="B108" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C108" s="15"/>
-      <c r="D108" s="15"/>
-      <c r="E108" s="15"/>
-      <c r="F108" s="15"/>
-      <c r="G108" s="15"/>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="15"/>
+      <c r="B108" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C108" s="45">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D108" s="3">
+        <f>D125</f>
+        <v>5.6385248399878085</v>
+      </c>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3">
+        <f>F125</f>
+        <v>2.2858884486437061</v>
+      </c>
+      <c r="G108" s="3">
+        <f>PRODUCT(C108:F108)</f>
+        <v>51.556155196474933</v>
+      </c>
       <c r="H108" s="15"/>
       <c r="I108" s="15"/>
       <c r="J108" s="15"/>
@@ -10849,177 +11024,171 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="15"/>
-      <c r="B109" s="16" t="str">
-        <f>B93</f>
-        <v>-for flooring at existing paati</v>
-      </c>
-      <c r="C109" s="15">
-        <f>C93</f>
-        <v>1</v>
+      <c r="B109" s="16"/>
+      <c r="C109" s="45">
+        <f>2*C126</f>
+        <v>4</v>
       </c>
       <c r="D109" s="3">
-        <f>D93</f>
-        <v>5.1813471502590671</v>
-      </c>
-      <c r="E109" s="3">
-        <f>E93</f>
-        <v>7.5434318805242304</v>
-      </c>
-      <c r="F109" s="15"/>
+        <f>D126</f>
+        <v>8.0006095702529709</v>
+      </c>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3">
+        <f>F126</f>
+        <v>2.2858884486437061</v>
+      </c>
       <c r="G109" s="3">
         <f>PRODUCT(C109:F109)</f>
-        <v>39.08513927732762</v>
+        <v>73.154003994998206</v>
       </c>
       <c r="H109" s="15"/>
       <c r="I109" s="15"/>
       <c r="J109" s="15"/>
       <c r="K109" s="15"/>
     </row>
-    <row r="110" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="17"/>
-      <c r="B110" s="18" t="s">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" s="15"/>
+      <c r="B110" s="16" t="str">
+        <f>B128</f>
+        <v>-deduction for window</v>
+      </c>
+      <c r="C110" s="45">
+        <f>2*C128</f>
+        <v>-4</v>
+      </c>
+      <c r="D110" s="3">
+        <f t="shared" ref="D110:D111" si="17">D128</f>
+        <v>1.8</v>
+      </c>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3">
+        <f t="shared" ref="F110:F111" si="18">F128</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="G110" s="3">
+        <f t="shared" ref="G110:G111" si="19">PRODUCT(C110:F110)</f>
+        <v>-9.875038098140811</v>
+      </c>
+      <c r="H110" s="15"/>
+      <c r="I110" s="15"/>
+      <c r="J110" s="15"/>
+      <c r="K110" s="15"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="15"/>
+      <c r="B111" s="16" t="str">
+        <f>B129</f>
+        <v>-deduction for chain gate</v>
+      </c>
+      <c r="C111" s="45">
+        <f>2*C129</f>
+        <v>-2</v>
+      </c>
+      <c r="D111" s="3">
+        <f t="shared" si="17"/>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3">
+        <f t="shared" si="18"/>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="G111" s="3">
+        <f t="shared" si="19"/>
+        <v>-6.6883660795426936</v>
+      </c>
+      <c r="H111" s="15"/>
+      <c r="I111" s="15"/>
+      <c r="J111" s="15"/>
+      <c r="K111" s="15"/>
+    </row>
+    <row r="112" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="17"/>
+      <c r="B112" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C110" s="19"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="20"/>
-      <c r="F110" s="20"/>
-      <c r="G110" s="2">
-        <f>SUM(G109:G109)</f>
-        <v>39.08513927732762</v>
-      </c>
-      <c r="H110" s="21" t="s">
+      <c r="C112" s="19"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="20"/>
+      <c r="F112" s="20"/>
+      <c r="G112" s="2">
+        <f>SUM(G108:G111)</f>
+        <v>108.14675501378964</v>
+      </c>
+      <c r="H112" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I110" s="2">
+      <c r="I112" s="2">
         <v>415.5</v>
       </c>
-      <c r="J110" s="22">
-        <f>G110*I110</f>
-        <v>16239.875369729627</v>
-      </c>
-      <c r="K110" s="20"/>
-    </row>
-    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="24"/>
-      <c r="B111" s="25" t="s">
+      <c r="J112" s="22">
+        <f>G112*I112</f>
+        <v>44934.976708229595</v>
+      </c>
+      <c r="K112" s="20"/>
+    </row>
+    <row r="113" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="24"/>
+      <c r="B113" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C111" s="26"/>
-      <c r="D111" s="27"/>
-      <c r="E111" s="27"/>
-      <c r="F111" s="27"/>
-      <c r="G111" s="27"/>
-      <c r="H111" s="26"/>
-      <c r="I111" s="26"/>
-      <c r="J111" s="22">
-        <f>0.13*G110*7010.67/100</f>
-        <v>356.21691739059713</v>
-      </c>
-      <c r="K111" s="26"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="15"/>
-      <c r="B112" s="25" t="s">
+      <c r="C113" s="26"/>
+      <c r="D113" s="27"/>
+      <c r="E113" s="27"/>
+      <c r="F113" s="27"/>
+      <c r="G113" s="27"/>
+      <c r="H113" s="26"/>
+      <c r="I113" s="26"/>
+      <c r="J113" s="22">
+        <f>0.13*G112*7010.67/100</f>
+        <v>985.63557426428201</v>
+      </c>
+      <c r="K113" s="26"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="15"/>
+      <c r="B114" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C112" s="26"/>
-      <c r="D112" s="27"/>
-      <c r="E112" s="27"/>
-      <c r="F112" s="27"/>
-      <c r="G112" s="27"/>
-      <c r="H112" s="26"/>
-      <c r="I112" s="26"/>
-      <c r="J112" s="22">
-        <f>0.13*G110*4639.73/100</f>
-        <v>235.74784123695386</v>
-      </c>
-      <c r="K112" s="15"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="15"/>
-      <c r="B113" s="15"/>
-      <c r="C113" s="15"/>
-      <c r="D113" s="15"/>
-      <c r="E113" s="15"/>
-      <c r="F113" s="15"/>
-      <c r="G113" s="15"/>
-      <c r="H113" s="15"/>
-      <c r="I113" s="15"/>
-      <c r="J113" s="15"/>
-      <c r="K113" s="15"/>
-    </row>
-    <row r="114" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="11">
-        <v>10</v>
-      </c>
-      <c r="B114" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C114" s="15"/>
-      <c r="D114" s="15"/>
-      <c r="E114" s="15"/>
-      <c r="F114" s="15"/>
-      <c r="G114" s="15"/>
-      <c r="H114" s="15"/>
-      <c r="I114" s="15"/>
-      <c r="J114" s="15"/>
+      <c r="C114" s="26"/>
+      <c r="D114" s="27"/>
+      <c r="E114" s="27"/>
+      <c r="F114" s="27"/>
+      <c r="G114" s="27"/>
+      <c r="H114" s="26"/>
+      <c r="I114" s="26"/>
+      <c r="J114" s="22">
+        <f>0.13*G112*4639.73/100</f>
+        <v>652.30326673216928</v>
+      </c>
       <c r="K114" s="15"/>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="15"/>
-      <c r="B115" s="60" t="str">
-        <f>B35</f>
-        <v>-for tie beam</v>
-      </c>
-      <c r="C115" s="61">
-        <f>C35</f>
-        <v>4</v>
-      </c>
-      <c r="D115" s="61">
-        <f>D35</f>
-        <v>2.234989332520573</v>
-      </c>
-      <c r="E115" s="61">
-        <v>0.23</v>
-      </c>
-      <c r="F115" s="61">
-        <v>1.2</v>
-      </c>
-      <c r="G115" s="61">
-        <f t="shared" ref="G115:G121" si="12">PRODUCT(C115:F115)</f>
-        <v>2.4674282231027127</v>
-      </c>
+      <c r="B115" s="15"/>
+      <c r="C115" s="15"/>
+      <c r="D115" s="15"/>
+      <c r="E115" s="15"/>
+      <c r="F115" s="15"/>
+      <c r="G115" s="15"/>
       <c r="H115" s="15"/>
       <c r="I115" s="15"/>
       <c r="J115" s="15"/>
       <c r="K115" s="15"/>
-      <c r="M115">
-        <f>7.833/3.281</f>
-        <v>2.3873818957634869</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="15"/>
-      <c r="B116" s="60"/>
-      <c r="C116" s="61">
-        <v>4</v>
-      </c>
-      <c r="D116" s="61">
-        <f>(1.917/3.281)*2</f>
-        <v>1.1685461749466626</v>
-      </c>
-      <c r="E116" s="61">
-        <v>0.23</v>
-      </c>
-      <c r="F116" s="61">
-        <f>0.6-0.075-0.055</f>
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="G116" s="61">
-        <f>PRODUCT(C116:F116)</f>
-        <v>0.50527936604693702</v>
-      </c>
+    </row>
+    <row r="116" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A116" s="11">
+        <v>9</v>
+      </c>
+      <c r="B116" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C116" s="15"/>
+      <c r="D116" s="15"/>
+      <c r="E116" s="15"/>
+      <c r="F116" s="15"/>
+      <c r="G116" s="15"/>
       <c r="H116" s="15"/>
       <c r="I116" s="15"/>
       <c r="J116" s="15"/>
@@ -11027,264 +11196,286 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="15"/>
-      <c r="B117" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C117" s="3">
-        <v>2</v>
+      <c r="B117" s="16" t="str">
+        <f>B101</f>
+        <v>-for flooring at existing paati</v>
+      </c>
+      <c r="C117" s="15">
+        <f>C101</f>
+        <v>1</v>
       </c>
       <c r="D117" s="3">
-        <f>18.5/3.281</f>
-        <v>5.6385248399878085</v>
+        <f>D101</f>
+        <v>5.1813471502590671</v>
       </c>
       <c r="E117" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F117" s="3">
-        <f>7.5/3.281</f>
-        <v>2.2858884486437061</v>
-      </c>
+        <f>E101</f>
+        <v>7.5434318805242304</v>
+      </c>
+      <c r="F117" s="15"/>
       <c r="G117" s="3">
-        <f t="shared" si="12"/>
-        <v>5.9289578475946181</v>
+        <f>PRODUCT(C117:F117)</f>
+        <v>39.08513927732762</v>
       </c>
       <c r="H117" s="15"/>
       <c r="I117" s="15"/>
       <c r="J117" s="15"/>
       <c r="K117" s="15"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="15"/>
-      <c r="B118" s="16"/>
-      <c r="C118" s="3">
-        <v>2</v>
-      </c>
-      <c r="D118" s="3">
-        <f>(8.75+17.5)/3.281</f>
-        <v>8.0006095702529709</v>
-      </c>
-      <c r="E118" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F118" s="3">
-        <f>7.5/3.281</f>
-        <v>2.2858884486437061</v>
-      </c>
-      <c r="G118" s="3">
-        <f t="shared" si="12"/>
-        <v>8.4127104594247939</v>
-      </c>
-      <c r="H118" s="15"/>
-      <c r="I118" s="15"/>
-      <c r="J118" s="15"/>
-      <c r="K118" s="15"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="15"/>
-      <c r="B119" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C119" s="3">
-        <v>1</v>
-      </c>
-      <c r="D119" s="3">
-        <f>D118</f>
-        <v>8.0006095702529709</v>
-      </c>
-      <c r="E119" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="F119" s="3">
-        <v>0.45</v>
-      </c>
-      <c r="G119" s="3">
-        <f t="shared" si="12"/>
-        <v>1.0800822919841511</v>
-      </c>
-      <c r="H119" s="15"/>
-      <c r="I119" s="15"/>
-      <c r="J119" s="15"/>
-      <c r="K119" s="15"/>
+    <row r="118" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="17"/>
+      <c r="B118" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" s="19"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="20"/>
+      <c r="F118" s="20"/>
+      <c r="G118" s="2">
+        <f>SUM(G117:G117)</f>
+        <v>39.08513927732762</v>
+      </c>
+      <c r="H118" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I118" s="2">
+        <v>415.5</v>
+      </c>
+      <c r="J118" s="22">
+        <f>G118*I118</f>
+        <v>16239.875369729627</v>
+      </c>
+      <c r="K118" s="20"/>
+    </row>
+    <row r="119" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="24"/>
+      <c r="B119" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C119" s="26"/>
+      <c r="D119" s="27"/>
+      <c r="E119" s="27"/>
+      <c r="F119" s="27"/>
+      <c r="G119" s="27"/>
+      <c r="H119" s="26"/>
+      <c r="I119" s="26"/>
+      <c r="J119" s="22">
+        <f>0.13*G118*7010.67/100</f>
+        <v>356.21691739059713</v>
+      </c>
+      <c r="K119" s="26"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="15"/>
-      <c r="B120" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C120" s="3">
-        <v>-2</v>
-      </c>
-      <c r="D120" s="3">
-        <f>1.8</f>
-        <v>1.8</v>
-      </c>
-      <c r="E120" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F120" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G120" s="3">
-        <f t="shared" si="12"/>
-        <v>-1.1356293812861933</v>
-      </c>
-      <c r="H120" s="15"/>
-      <c r="I120" s="15"/>
-      <c r="J120" s="15"/>
+      <c r="B120" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C120" s="26"/>
+      <c r="D120" s="27"/>
+      <c r="E120" s="27"/>
+      <c r="F120" s="27"/>
+      <c r="G120" s="27"/>
+      <c r="H120" s="26"/>
+      <c r="I120" s="26"/>
+      <c r="J120" s="22">
+        <f>0.13*G118*4639.73/100</f>
+        <v>235.74784123695386</v>
+      </c>
       <c r="K120" s="15"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="15"/>
-      <c r="B121" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C121" s="3">
-        <v>-1</v>
-      </c>
-      <c r="D121" s="3">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E121" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F121" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G121" s="3">
-        <f t="shared" si="12"/>
-        <v>-0.76916209914740985</v>
-      </c>
+      <c r="B121" s="15"/>
+      <c r="C121" s="15"/>
+      <c r="D121" s="15"/>
+      <c r="E121" s="15"/>
+      <c r="F121" s="15"/>
+      <c r="G121" s="15"/>
       <c r="H121" s="15"/>
       <c r="I121" s="15"/>
       <c r="J121" s="15"/>
       <c r="K121" s="15"/>
     </row>
-    <row r="122" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="17"/>
-      <c r="B122" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" s="19"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="20"/>
-      <c r="F122" s="20"/>
-      <c r="G122" s="2">
-        <f>SUM(G115:G121)</f>
-        <v>16.489666707719611</v>
-      </c>
-      <c r="H122" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I122" s="2">
-        <f>14491.84</f>
-        <v>14491.84</v>
-      </c>
-      <c r="J122" s="22">
-        <f>G122*I122</f>
-        <v>238965.61158159937</v>
-      </c>
-      <c r="K122" s="20"/>
-    </row>
-    <row r="123" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="24"/>
-      <c r="B123" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="C123" s="26"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="27"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="27"/>
-      <c r="H123" s="26"/>
-      <c r="I123" s="26"/>
-      <c r="J123" s="22">
-        <f>0.13*G122*8481.2</f>
-        <v>18180.780966596503</v>
-      </c>
-      <c r="K123" s="26"/>
-    </row>
-    <row r="124" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="24"/>
-      <c r="B124" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C124" s="26"/>
-      <c r="D124" s="27"/>
-      <c r="E124" s="27"/>
-      <c r="F124" s="27"/>
-      <c r="G124" s="27"/>
-      <c r="H124" s="26"/>
-      <c r="I124" s="26"/>
-      <c r="J124" s="22">
-        <f>0.13*G122*912.17</f>
-        <v>1955.3793065014775</v>
-      </c>
-      <c r="K124" s="26"/>
-    </row>
-    <row r="125" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="24"/>
-      <c r="B125" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C125" s="26"/>
-      <c r="D125" s="27"/>
-      <c r="E125" s="27"/>
-      <c r="F125" s="27"/>
-      <c r="G125" s="27"/>
-      <c r="H125" s="26"/>
-      <c r="I125" s="26"/>
-      <c r="J125" s="22">
-        <f>0.13*G122*953.37</f>
-        <v>2043.6979613880237</v>
-      </c>
-      <c r="K125" s="26"/>
-    </row>
-    <row r="126" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="24"/>
-      <c r="B126" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C126" s="26"/>
-      <c r="D126" s="27"/>
-      <c r="E126" s="27"/>
-      <c r="F126" s="27"/>
-      <c r="G126" s="27"/>
-      <c r="H126" s="26"/>
-      <c r="I126" s="26"/>
-      <c r="J126" s="22">
-        <f>0.13*G122*28</f>
-        <v>60.022386816099377</v>
-      </c>
-      <c r="K126" s="26"/>
+    <row r="122" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A122" s="11">
+        <v>10</v>
+      </c>
+      <c r="B122" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C122" s="15"/>
+      <c r="D122" s="15"/>
+      <c r="E122" s="15"/>
+      <c r="F122" s="15"/>
+      <c r="G122" s="15"/>
+      <c r="H122" s="15"/>
+      <c r="I122" s="15"/>
+      <c r="J122" s="15"/>
+      <c r="K122" s="15"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="15"/>
+      <c r="B123" s="47" t="str">
+        <f>B35</f>
+        <v>-for tie beam</v>
+      </c>
+      <c r="C123" s="48">
+        <f>C35</f>
+        <v>4</v>
+      </c>
+      <c r="D123" s="48">
+        <f>D35</f>
+        <v>3.5669917708015841</v>
+      </c>
+      <c r="E123" s="48">
+        <v>0.23</v>
+      </c>
+      <c r="F123" s="48">
+        <v>1.2</v>
+      </c>
+      <c r="G123" s="48">
+        <f t="shared" ref="G123:G129" si="20">PRODUCT(C123:F123)</f>
+        <v>3.9379589149649492</v>
+      </c>
+      <c r="H123" s="15"/>
+      <c r="I123" s="15"/>
+      <c r="J123" s="15"/>
+      <c r="K123" s="15"/>
+      <c r="M123">
+        <f>7.833/3.281</f>
+        <v>2.3873818957634869</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="15"/>
+      <c r="B124" s="47"/>
+      <c r="C124" s="48">
+        <v>4</v>
+      </c>
+      <c r="D124" s="48">
+        <f>(1.917/3.281)*2</f>
+        <v>1.1685461749466626</v>
+      </c>
+      <c r="E124" s="48">
+        <v>0.23</v>
+      </c>
+      <c r="F124" s="48">
+        <f>0.6-0.075-0.055</f>
+        <v>0.47000000000000003</v>
+      </c>
+      <c r="G124" s="48">
+        <f>PRODUCT(C124:F124)</f>
+        <v>0.50527936604693702</v>
+      </c>
+      <c r="H124" s="15"/>
+      <c r="I124" s="15"/>
+      <c r="J124" s="15"/>
+      <c r="K124" s="15"/>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="15"/>
+      <c r="B125" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C125" s="3">
+        <v>2</v>
+      </c>
+      <c r="D125" s="3">
+        <f>18.5/3.281</f>
+        <v>5.6385248399878085</v>
+      </c>
+      <c r="E125" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F125" s="3">
+        <f>7.5/3.281</f>
+        <v>2.2858884486437061</v>
+      </c>
+      <c r="G125" s="3">
+        <f t="shared" si="20"/>
+        <v>5.9289578475946181</v>
+      </c>
+      <c r="H125" s="15"/>
+      <c r="I125" s="15"/>
+      <c r="J125" s="15"/>
+      <c r="K125" s="15"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" s="15"/>
+      <c r="B126" s="16"/>
+      <c r="C126" s="3">
+        <v>2</v>
+      </c>
+      <c r="D126" s="3">
+        <f>(8.75+17.5)/3.281</f>
+        <v>8.0006095702529709</v>
+      </c>
+      <c r="E126" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F126" s="3">
+        <f>7.5/3.281</f>
+        <v>2.2858884486437061</v>
+      </c>
+      <c r="G126" s="3">
+        <f t="shared" si="20"/>
+        <v>8.4127104594247939</v>
+      </c>
+      <c r="H126" s="15"/>
+      <c r="I126" s="15"/>
+      <c r="J126" s="15"/>
+      <c r="K126" s="15"/>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="15"/>
-      <c r="B127" s="15"/>
-      <c r="C127" s="15"/>
-      <c r="D127" s="15"/>
-      <c r="E127" s="15"/>
-      <c r="F127" s="15"/>
-      <c r="G127" s="15"/>
+      <c r="B127" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C127" s="3">
+        <v>1</v>
+      </c>
+      <c r="D127" s="3">
+        <f>D126</f>
+        <v>8.0006095702529709</v>
+      </c>
+      <c r="E127" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F127" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="G127" s="3">
+        <f t="shared" si="20"/>
+        <v>1.0800822919841511</v>
+      </c>
       <c r="H127" s="15"/>
       <c r="I127" s="15"/>
       <c r="J127" s="15"/>
       <c r="K127" s="15"/>
     </row>
-    <row r="128" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="11">
-        <v>11</v>
-      </c>
-      <c r="B128" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C128" s="15"/>
-      <c r="D128" s="15"/>
-      <c r="E128" s="15"/>
-      <c r="F128" s="15"/>
-      <c r="G128" s="15"/>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="15"/>
+      <c r="B128" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C128" s="3">
+        <v>-2</v>
+      </c>
+      <c r="D128" s="3">
+        <f>1.8</f>
+        <v>1.8</v>
+      </c>
+      <c r="E128" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="F128" s="3">
+        <f>4.5/3.281</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="G128" s="3">
+        <f t="shared" si="20"/>
+        <v>-1.1356293812861933</v>
+      </c>
       <c r="H128" s="15"/>
       <c r="I128" s="15"/>
       <c r="J128" s="15"/>
@@ -11293,138 +11484,115 @@
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="15"/>
       <c r="B129" s="16" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C129" s="3">
-        <f>C100</f>
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="D129" s="3">
-        <f>18.5/3.281</f>
-        <v>5.6385248399878085</v>
-      </c>
-      <c r="E129" s="3"/>
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E129" s="3">
+        <v>0.23</v>
+      </c>
       <c r="F129" s="3">
-        <f>F100</f>
-        <v>2.2858884486437061</v>
+        <f>4.5/3.281</f>
+        <v>1.3715330691862238</v>
       </c>
       <c r="G129" s="3">
-        <f>PRODUCT(C129:F129)</f>
-        <v>51.556155196474933</v>
+        <f t="shared" si="20"/>
+        <v>-0.76916209914740985</v>
       </c>
       <c r="H129" s="15"/>
       <c r="I129" s="15"/>
       <c r="J129" s="15"/>
       <c r="K129" s="15"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A130" s="15"/>
-      <c r="B130" s="16"/>
-      <c r="C130" s="3">
-        <f>C101</f>
-        <v>4</v>
-      </c>
-      <c r="D130" s="3">
-        <f>(8.75+17.5)/3.281</f>
-        <v>8.0006095702529709</v>
-      </c>
-      <c r="E130" s="3"/>
-      <c r="F130" s="3">
-        <f>7.5/3.281</f>
-        <v>2.2858884486437061</v>
-      </c>
-      <c r="G130" s="3">
-        <f>PRODUCT(C130:F130)</f>
-        <v>73.154003994998206</v>
-      </c>
-      <c r="H130" s="15"/>
-      <c r="I130" s="15"/>
-      <c r="J130" s="15"/>
-      <c r="K130" s="15"/>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A131" s="15"/>
-      <c r="B131" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C131" s="3">
-        <f>-2*2</f>
-        <v>-4</v>
-      </c>
-      <c r="D131" s="3">
-        <f>1.8</f>
-        <v>1.8</v>
-      </c>
-      <c r="E131" s="3"/>
-      <c r="F131" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G131" s="3">
-        <f>PRODUCT(C131:F131)</f>
-        <v>-9.875038098140811</v>
-      </c>
-      <c r="H131" s="15"/>
-      <c r="I131" s="15"/>
-      <c r="J131" s="15"/>
-      <c r="K131" s="15"/>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A132" s="15"/>
-      <c r="B132" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C132" s="3">
-        <f>-1*2</f>
-        <v>-2</v>
-      </c>
-      <c r="D132" s="3">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E132" s="3"/>
-      <c r="F132" s="3">
-        <f>7/3.281</f>
-        <v>2.1334958854007922</v>
-      </c>
-      <c r="G132" s="3">
-        <f>PRODUCT(C132:F132)</f>
-        <v>-10.404125012621966</v>
-      </c>
-      <c r="H132" s="15"/>
-      <c r="I132" s="15"/>
-      <c r="J132" s="15"/>
-      <c r="K132" s="15"/>
-    </row>
-    <row r="133" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="17"/>
-      <c r="B133" s="18" t="s">
+    <row r="130" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="17"/>
+      <c r="B130" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C133" s="19"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="20"/>
-      <c r="F133" s="20"/>
-      <c r="G133" s="2">
-        <f>SUM(G129:G132)</f>
-        <v>104.43099608071037</v>
-      </c>
-      <c r="H133" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I133" s="2">
-        <v>253.8</v>
-      </c>
+      <c r="C130" s="19"/>
+      <c r="D130" s="1"/>
+      <c r="E130" s="20"/>
+      <c r="F130" s="20"/>
+      <c r="G130" s="2">
+        <f>SUM(G123:G129)</f>
+        <v>17.960197399581848</v>
+      </c>
+      <c r="H130" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I130" s="2">
+        <f>14491.84</f>
+        <v>14491.84</v>
+      </c>
+      <c r="J130" s="22">
+        <f>G130*I130</f>
+        <v>260276.30708315619</v>
+      </c>
+      <c r="K130" s="20"/>
+    </row>
+    <row r="131" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="24"/>
+      <c r="B131" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C131" s="26"/>
+      <c r="D131" s="27"/>
+      <c r="E131" s="27"/>
+      <c r="F131" s="27"/>
+      <c r="G131" s="27"/>
+      <c r="H131" s="26"/>
+      <c r="I131" s="26"/>
+      <c r="J131" s="22">
+        <f>0.13*G130*8481.2</f>
+        <v>19802.123404093367</v>
+      </c>
+      <c r="K131" s="26"/>
+    </row>
+    <row r="132" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="24"/>
+      <c r="B132" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C132" s="26"/>
+      <c r="D132" s="27"/>
+      <c r="E132" s="27"/>
+      <c r="F132" s="27"/>
+      <c r="G132" s="27"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
+      <c r="J132" s="22">
+        <f>0.13*G130*912.17</f>
+        <v>2129.7579240569548</v>
+      </c>
+      <c r="K132" s="26"/>
+    </row>
+    <row r="133" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="24"/>
+      <c r="B133" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C133" s="26"/>
+      <c r="D133" s="27"/>
+      <c r="E133" s="27"/>
+      <c r="F133" s="27"/>
+      <c r="G133" s="27"/>
+      <c r="H133" s="26"/>
+      <c r="I133" s="26"/>
       <c r="J133" s="22">
-        <f>G133*I133</f>
-        <v>26504.586805284292</v>
-      </c>
-      <c r="K133" s="20"/>
+        <f>0.13*G130*953.37</f>
+        <v>2225.9527413291153</v>
+      </c>
+      <c r="K133" s="26"/>
     </row>
     <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="24"/>
       <c r="B134" s="25" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C134" s="26"/>
       <c r="D134" s="27"/>
@@ -11434,54 +11602,63 @@
       <c r="H134" s="26"/>
       <c r="I134" s="26"/>
       <c r="J134" s="22">
-        <f>0.13*G133*2304/100</f>
-        <v>312.79171946094374</v>
+        <f>0.13*G130*28</f>
+        <v>65.375118534477934</v>
       </c>
       <c r="K134" s="26"/>
     </row>
-    <row r="135" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="24"/>
-      <c r="B135" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C135" s="26"/>
-      <c r="D135" s="27"/>
-      <c r="E135" s="27"/>
-      <c r="F135" s="27"/>
-      <c r="G135" s="27"/>
-      <c r="H135" s="26"/>
-      <c r="I135" s="26"/>
-      <c r="J135" s="22">
-        <f>0.13*G133*10432/100</f>
-        <v>1416.251396448162</v>
-      </c>
-      <c r="K135" s="26"/>
-    </row>
-    <row r="136" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="24"/>
-      <c r="B136" s="25"/>
-      <c r="C136" s="26"/>
-      <c r="D136" s="27"/>
-      <c r="E136" s="27"/>
-      <c r="F136" s="27"/>
-      <c r="G136" s="27"/>
-      <c r="H136" s="26"/>
-      <c r="I136" s="26"/>
-      <c r="J136" s="22"/>
-      <c r="K136" s="26"/>
-    </row>
-    <row r="137" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A137" s="11">
-        <v>12</v>
-      </c>
-      <c r="B137" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C137" s="15"/>
-      <c r="D137" s="15"/>
-      <c r="E137" s="15"/>
-      <c r="F137" s="15"/>
-      <c r="G137" s="15"/>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="15"/>
+      <c r="B135" s="15"/>
+      <c r="C135" s="15"/>
+      <c r="D135" s="15"/>
+      <c r="E135" s="15"/>
+      <c r="F135" s="15"/>
+      <c r="G135" s="15"/>
+      <c r="H135" s="15"/>
+      <c r="I135" s="15"/>
+      <c r="J135" s="15"/>
+      <c r="K135" s="15"/>
+    </row>
+    <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A136" s="11">
+        <v>11</v>
+      </c>
+      <c r="B136" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C136" s="15"/>
+      <c r="D136" s="15"/>
+      <c r="E136" s="15"/>
+      <c r="F136" s="15"/>
+      <c r="G136" s="15"/>
+      <c r="H136" s="15"/>
+      <c r="I136" s="15"/>
+      <c r="J136" s="15"/>
+      <c r="K136" s="15"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="15"/>
+      <c r="B137" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C137" s="3">
+        <f>C108</f>
+        <v>4</v>
+      </c>
+      <c r="D137" s="3">
+        <f>18.5/3.281</f>
+        <v>5.6385248399878085</v>
+      </c>
+      <c r="E137" s="3"/>
+      <c r="F137" s="3">
+        <f>F108</f>
+        <v>2.2858884486437061</v>
+      </c>
+      <c r="G137" s="3">
+        <f>PRODUCT(C137:F137)</f>
+        <v>51.556155196474933</v>
+      </c>
       <c r="H137" s="15"/>
       <c r="I137" s="15"/>
       <c r="J137" s="15"/>
@@ -11489,14 +11666,24 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="15"/>
-      <c r="B138" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3"/>
+      <c r="B138" s="16"/>
+      <c r="C138" s="3">
+        <f>C109</f>
+        <v>4</v>
+      </c>
+      <c r="D138" s="3">
+        <f>(8.75+17.5)/3.281</f>
+        <v>8.0006095702529709</v>
+      </c>
       <c r="E138" s="3"/>
-      <c r="F138" s="3"/>
-      <c r="G138" s="3"/>
+      <c r="F138" s="3">
+        <f>7.5/3.281</f>
+        <v>2.2858884486437061</v>
+      </c>
+      <c r="G138" s="3">
+        <f>PRODUCT(C138:F138)</f>
+        <v>73.154003994998206</v>
+      </c>
       <c r="H138" s="15"/>
       <c r="I138" s="15"/>
       <c r="J138" s="15"/>
@@ -11505,14 +11692,15 @@
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="15"/>
       <c r="B139" s="16" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C139" s="3">
-        <v>1</v>
+        <f>-2*2</f>
+        <v>-4</v>
       </c>
       <c r="D139" s="3">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
+        <f>1.8</f>
+        <v>1.8</v>
       </c>
       <c r="E139" s="3"/>
       <c r="F139" s="3">
@@ -11521,59 +11709,70 @@
       </c>
       <c r="G139" s="3">
         <f>PRODUCT(C139:F139)</f>
-        <v>3.3441830397713468</v>
+        <v>-9.875038098140811</v>
       </c>
       <c r="H139" s="15"/>
       <c r="I139" s="15"/>
       <c r="J139" s="15"/>
       <c r="K139" s="15"/>
     </row>
-    <row r="140" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="17"/>
-      <c r="B140" s="18" t="s">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="15"/>
+      <c r="B140" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C140" s="3">
+        <f>-1*2</f>
+        <v>-2</v>
+      </c>
+      <c r="D140" s="3">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3">
+        <f>7/3.281</f>
+        <v>2.1334958854007922</v>
+      </c>
+      <c r="G140" s="3">
+        <f>PRODUCT(C140:F140)</f>
+        <v>-10.404125012621966</v>
+      </c>
+      <c r="H140" s="15"/>
+      <c r="I140" s="15"/>
+      <c r="J140" s="15"/>
+      <c r="K140" s="15"/>
+    </row>
+    <row r="141" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="17"/>
+      <c r="B141" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C140" s="19"/>
-      <c r="D140" s="1"/>
-      <c r="E140" s="20"/>
-      <c r="F140" s="20"/>
-      <c r="G140" s="2">
-        <f>SUM(G138:G139)</f>
-        <v>3.3441830397713468</v>
-      </c>
-      <c r="H140" s="21" t="s">
+      <c r="C141" s="19"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="20"/>
+      <c r="F141" s="20"/>
+      <c r="G141" s="2">
+        <f>SUM(G137:G140)</f>
+        <v>104.43099608071037</v>
+      </c>
+      <c r="H141" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I140" s="2">
-        <v>6391.43</v>
-      </c>
-      <c r="J140" s="22">
-        <f>G140*I140</f>
-        <v>21374.111805885779</v>
-      </c>
-      <c r="K140" s="20"/>
-    </row>
-    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="24"/>
-      <c r="B141" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C141" s="26"/>
-      <c r="D141" s="27"/>
-      <c r="E141" s="27"/>
-      <c r="F141" s="27"/>
-      <c r="G141" s="27"/>
-      <c r="H141" s="26"/>
-      <c r="I141" s="26"/>
+      <c r="I141" s="2">
+        <v>253.8</v>
+      </c>
       <c r="J141" s="22">
-        <f>0.13*G140*2304/100</f>
-        <v>10.016497040723138</v>
-      </c>
-      <c r="K141" s="26"/>
+        <f>G141*I141</f>
+        <v>26504.586805284292</v>
+      </c>
+      <c r="K141" s="20"/>
     </row>
     <row r="142" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="24"/>
-      <c r="B142" s="25"/>
+      <c r="B142" s="25" t="s">
+        <v>74</v>
+      </c>
       <c r="C142" s="26"/>
       <c r="D142" s="27"/>
       <c r="E142" s="27"/>
@@ -11581,15 +11780,16 @@
       <c r="G142" s="27"/>
       <c r="H142" s="26"/>
       <c r="I142" s="26"/>
-      <c r="J142" s="22"/>
+      <c r="J142" s="22">
+        <f>0.13*G141*2304/100</f>
+        <v>312.79171946094374</v>
+      </c>
       <c r="K142" s="26"/>
     </row>
-    <row r="143" spans="1:11" s="10" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="24">
-        <v>13</v>
-      </c>
-      <c r="B143" s="28" t="s">
-        <v>78</v>
+    <row r="143" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="24"/>
+      <c r="B143" s="25" t="s">
+        <v>75</v>
       </c>
       <c r="C143" s="26"/>
       <c r="D143" s="27"/>
@@ -11598,294 +11798,441 @@
       <c r="G143" s="27"/>
       <c r="H143" s="26"/>
       <c r="I143" s="26"/>
-      <c r="J143" s="22"/>
+      <c r="J143" s="22">
+        <f>0.13*G141*10432/100</f>
+        <v>1416.251396448162</v>
+      </c>
       <c r="K143" s="26"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" s="15"/>
-      <c r="B144" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C144" s="3">
-        <v>2</v>
-      </c>
-      <c r="D144" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="E144" s="3"/>
-      <c r="F144" s="3">
+    <row r="144" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="24"/>
+      <c r="B144" s="25"/>
+      <c r="C144" s="26"/>
+      <c r="D144" s="27"/>
+      <c r="E144" s="27"/>
+      <c r="F144" s="27"/>
+      <c r="G144" s="27"/>
+      <c r="H144" s="26"/>
+      <c r="I144" s="26"/>
+      <c r="J144" s="22"/>
+      <c r="K144" s="26"/>
+    </row>
+    <row r="145" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A145" s="11">
+        <v>12</v>
+      </c>
+      <c r="B145" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C145" s="15"/>
+      <c r="D145" s="15"/>
+      <c r="E145" s="15"/>
+      <c r="F145" s="15"/>
+      <c r="G145" s="15"/>
+      <c r="H145" s="15"/>
+      <c r="I145" s="15"/>
+      <c r="J145" s="15"/>
+      <c r="K145" s="15"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" s="15"/>
+      <c r="B146" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+      <c r="H146" s="15"/>
+      <c r="I146" s="15"/>
+      <c r="J146" s="15"/>
+      <c r="K146" s="15"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" s="15"/>
+      <c r="B147" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C147" s="3">
+        <v>1</v>
+      </c>
+      <c r="D147" s="3">
+        <f>8/3.281</f>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E147" s="3"/>
+      <c r="F147" s="3">
         <f>4.5/3.281</f>
         <v>1.3715330691862238</v>
       </c>
-      <c r="G144" s="3">
-        <f>PRODUCT(C144:F144)</f>
-        <v>4.9375190490704055</v>
-      </c>
-      <c r="H144" s="15"/>
-      <c r="I144" s="15"/>
-      <c r="J144" s="15"/>
-      <c r="K144" s="15"/>
-    </row>
-    <row r="145" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="17"/>
-      <c r="B145" s="18" t="s">
+      <c r="G147" s="3">
+        <f>PRODUCT(C147:F147)</f>
+        <v>3.3441830397713468</v>
+      </c>
+      <c r="H147" s="15"/>
+      <c r="I147" s="15"/>
+      <c r="J147" s="15"/>
+      <c r="K147" s="15"/>
+    </row>
+    <row r="148" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="17"/>
+      <c r="B148" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C145" s="19"/>
-      <c r="D145" s="1"/>
-      <c r="E145" s="20"/>
-      <c r="F145" s="20"/>
-      <c r="G145" s="2">
-        <f>SUM(G143:G144)</f>
-        <v>4.9375190490704055</v>
-      </c>
-      <c r="H145" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I145" s="2">
-        <v>2485.56</v>
-      </c>
-      <c r="J145" s="22">
-        <f>G145*I145</f>
-        <v>12272.499847607436</v>
-      </c>
-      <c r="K145" s="20"/>
-    </row>
-    <row r="146" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="24"/>
-      <c r="B146" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C146" s="26"/>
-      <c r="D146" s="27"/>
-      <c r="E146" s="27"/>
-      <c r="F146" s="27"/>
-      <c r="G146" s="27"/>
-      <c r="H146" s="26"/>
-      <c r="I146" s="26"/>
-      <c r="J146" s="22">
-        <f>0.13*J145</f>
-        <v>1595.4249801889669</v>
-      </c>
-      <c r="K146" s="26"/>
-    </row>
-    <row r="147" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="24"/>
-      <c r="B147" s="25"/>
-      <c r="C147" s="26"/>
-      <c r="D147" s="27"/>
-      <c r="E147" s="27"/>
-      <c r="F147" s="27"/>
-      <c r="G147" s="27"/>
-      <c r="H147" s="26"/>
-      <c r="I147" s="26"/>
-      <c r="J147" s="22"/>
-      <c r="K147" s="26"/>
-    </row>
-    <row r="148" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="17">
-        <v>14</v>
-      </c>
-      <c r="B148" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C148" s="19">
-        <v>1</v>
-      </c>
+      <c r="C148" s="19"/>
       <c r="D148" s="1"/>
       <c r="E148" s="20"/>
       <c r="F148" s="20"/>
-      <c r="G148" s="21">
-        <f t="shared" ref="G148" si="13">PRODUCT(C148:F148)</f>
+      <c r="G148" s="2">
+        <f>SUM(G146:G147)</f>
+        <v>3.3441830397713468</v>
+      </c>
+      <c r="H148" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I148" s="2">
+        <v>6391.43</v>
+      </c>
+      <c r="J148" s="22">
+        <f>G148*I148</f>
+        <v>21374.111805885779</v>
+      </c>
+      <c r="K148" s="20"/>
+    </row>
+    <row r="149" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="24"/>
+      <c r="B149" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C149" s="26"/>
+      <c r="D149" s="27"/>
+      <c r="E149" s="27"/>
+      <c r="F149" s="27"/>
+      <c r="G149" s="27"/>
+      <c r="H149" s="26"/>
+      <c r="I149" s="26"/>
+      <c r="J149" s="22">
+        <f>0.13*G148*2304/100</f>
+        <v>10.016497040723138</v>
+      </c>
+      <c r="K149" s="26"/>
+    </row>
+    <row r="150" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="24"/>
+      <c r="B150" s="25"/>
+      <c r="C150" s="26"/>
+      <c r="D150" s="27"/>
+      <c r="E150" s="27"/>
+      <c r="F150" s="27"/>
+      <c r="G150" s="27"/>
+      <c r="H150" s="26"/>
+      <c r="I150" s="26"/>
+      <c r="J150" s="22"/>
+      <c r="K150" s="26"/>
+    </row>
+    <row r="151" spans="1:11" s="10" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="A151" s="24">
+        <v>13</v>
+      </c>
+      <c r="B151" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C151" s="26"/>
+      <c r="D151" s="27"/>
+      <c r="E151" s="27"/>
+      <c r="F151" s="27"/>
+      <c r="G151" s="27"/>
+      <c r="H151" s="26"/>
+      <c r="I151" s="26"/>
+      <c r="J151" s="22"/>
+      <c r="K151" s="26"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" s="15"/>
+      <c r="B152" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C152" s="3">
+        <v>2</v>
+      </c>
+      <c r="D152" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3">
+        <f>4.5/3.281</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="G152" s="3">
+        <f>PRODUCT(C152:F152)</f>
+        <v>4.9375190490704055</v>
+      </c>
+      <c r="H152" s="15"/>
+      <c r="I152" s="15"/>
+      <c r="J152" s="15"/>
+      <c r="K152" s="15"/>
+    </row>
+    <row r="153" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="17"/>
+      <c r="B153" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" s="19"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="20"/>
+      <c r="F153" s="20"/>
+      <c r="G153" s="2">
+        <f>SUM(G151:G152)</f>
+        <v>4.9375190490704055</v>
+      </c>
+      <c r="H153" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I153" s="2">
+        <v>2485.56</v>
+      </c>
+      <c r="J153" s="22">
+        <f>G153*I153</f>
+        <v>12272.499847607436</v>
+      </c>
+      <c r="K153" s="20"/>
+    </row>
+    <row r="154" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="24"/>
+      <c r="B154" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C154" s="26"/>
+      <c r="D154" s="27"/>
+      <c r="E154" s="27"/>
+      <c r="F154" s="27"/>
+      <c r="G154" s="27"/>
+      <c r="H154" s="26"/>
+      <c r="I154" s="26"/>
+      <c r="J154" s="22">
+        <f>0.13*J153</f>
+        <v>1595.4249801889669</v>
+      </c>
+      <c r="K154" s="26"/>
+    </row>
+    <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="24"/>
+      <c r="B155" s="25"/>
+      <c r="C155" s="26"/>
+      <c r="D155" s="27"/>
+      <c r="E155" s="27"/>
+      <c r="F155" s="27"/>
+      <c r="G155" s="27"/>
+      <c r="H155" s="26"/>
+      <c r="I155" s="26"/>
+      <c r="J155" s="22"/>
+      <c r="K155" s="26"/>
+    </row>
+    <row r="156" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="17">
+        <v>14</v>
+      </c>
+      <c r="B156" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C156" s="19">
         <v>1</v>
       </c>
-      <c r="H148" s="21" t="s">
+      <c r="D156" s="1"/>
+      <c r="E156" s="20"/>
+      <c r="F156" s="20"/>
+      <c r="G156" s="21">
+        <f t="shared" ref="G156" si="21">PRODUCT(C156:F156)</f>
+        <v>1</v>
+      </c>
+      <c r="H156" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="I148" s="2">
+      <c r="I156" s="2">
         <v>5000</v>
       </c>
-      <c r="J148" s="21">
-        <f>G148*I148</f>
+      <c r="J156" s="21">
+        <f>G156*I156</f>
         <v>5000</v>
       </c>
-      <c r="K148" s="20"/>
-    </row>
-    <row r="149" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="17"/>
-      <c r="B149" s="31"/>
-      <c r="C149" s="19"/>
-      <c r="D149" s="1"/>
-      <c r="E149" s="20"/>
-      <c r="F149" s="20"/>
-      <c r="G149" s="2"/>
-      <c r="H149" s="21"/>
-      <c r="I149" s="2"/>
-      <c r="J149" s="22"/>
-      <c r="K149" s="20"/>
-    </row>
-    <row r="150" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="17">
+      <c r="K156" s="20"/>
+    </row>
+    <row r="157" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="17"/>
+      <c r="B157" s="31"/>
+      <c r="C157" s="19"/>
+      <c r="D157" s="1"/>
+      <c r="E157" s="20"/>
+      <c r="F157" s="20"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="21"/>
+      <c r="I157" s="2"/>
+      <c r="J157" s="22"/>
+      <c r="K157" s="20"/>
+    </row>
+    <row r="158" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="17">
         <v>15</v>
       </c>
-      <c r="B150" s="30" t="s">
+      <c r="B158" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C150" s="19">
+      <c r="C158" s="19">
         <v>1</v>
       </c>
-      <c r="D150" s="1"/>
-      <c r="E150" s="20"/>
-      <c r="F150" s="20"/>
-      <c r="G150" s="21">
-        <f t="shared" ref="G150" si="14">PRODUCT(C150:F150)</f>
+      <c r="D158" s="1"/>
+      <c r="E158" s="20"/>
+      <c r="F158" s="20"/>
+      <c r="G158" s="21">
+        <f t="shared" ref="G158" si="22">PRODUCT(C158:F158)</f>
         <v>1</v>
       </c>
-      <c r="H150" s="21" t="s">
+      <c r="H158" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="I150" s="2">
+      <c r="I158" s="2">
         <v>500</v>
       </c>
-      <c r="J150" s="21">
-        <f>G150*I150</f>
+      <c r="J158" s="21">
+        <f>G158*I158</f>
         <v>500</v>
       </c>
-      <c r="K150" s="20"/>
-    </row>
-    <row r="151" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="17"/>
-      <c r="B151" s="31"/>
-      <c r="C151" s="19"/>
-      <c r="D151" s="1"/>
-      <c r="E151" s="20"/>
-      <c r="F151" s="20"/>
-      <c r="G151" s="2"/>
-      <c r="H151" s="21"/>
-      <c r="I151" s="2"/>
-      <c r="J151" s="22"/>
-      <c r="K151" s="20"/>
-    </row>
-    <row r="152" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="32"/>
-      <c r="B152" s="33" t="s">
+      <c r="K158" s="20"/>
+    </row>
+    <row r="159" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="17"/>
+      <c r="B159" s="31"/>
+      <c r="C159" s="19"/>
+      <c r="D159" s="1"/>
+      <c r="E159" s="20"/>
+      <c r="F159" s="20"/>
+      <c r="G159" s="2"/>
+      <c r="H159" s="21"/>
+      <c r="I159" s="2"/>
+      <c r="J159" s="22"/>
+      <c r="K159" s="20"/>
+    </row>
+    <row r="160" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="32"/>
+      <c r="B160" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C152" s="34"/>
-      <c r="D152" s="35"/>
-      <c r="E152" s="35"/>
-      <c r="F152" s="35"/>
-      <c r="G152" s="22"/>
-      <c r="H152" s="22"/>
-      <c r="I152" s="22"/>
-      <c r="J152" s="22">
-        <f>SUM(J10:J150)</f>
-        <v>792822.35641454847</v>
-      </c>
-      <c r="K152" s="36"/>
-    </row>
-    <row r="153" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="37"/>
-      <c r="B154" s="38" t="s">
+      <c r="C160" s="34"/>
+      <c r="D160" s="35"/>
+      <c r="E160" s="35"/>
+      <c r="F160" s="35"/>
+      <c r="G160" s="22"/>
+      <c r="H160" s="22"/>
+      <c r="I160" s="22"/>
+      <c r="J160" s="22">
+        <f>SUM(J10:J158)</f>
+        <v>842852.05071615078</v>
+      </c>
+      <c r="K160" s="36"/>
+    </row>
+    <row r="161" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="162" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="37"/>
+      <c r="B162" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C154" s="55">
-        <f>J152</f>
-        <v>792822.35641454847</v>
-      </c>
-      <c r="D154" s="56"/>
-      <c r="E154" s="39">
+      <c r="C162" s="49">
+        <f>J160</f>
+        <v>842852.05071615078</v>
+      </c>
+      <c r="D162" s="50"/>
+      <c r="E162" s="39">
         <v>100</v>
       </c>
-      <c r="F154" s="37"/>
-      <c r="G154" s="40"/>
-      <c r="H154" s="37"/>
-      <c r="I154" s="41"/>
-      <c r="J154" s="42"/>
-      <c r="K154" s="43"/>
-    </row>
-    <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="38" t="s">
+      <c r="F162" s="37"/>
+      <c r="G162" s="40"/>
+      <c r="H162" s="37"/>
+      <c r="I162" s="41"/>
+      <c r="J162" s="42"/>
+      <c r="K162" s="43"/>
+    </row>
+    <row r="163" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B163" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C155" s="57">
+      <c r="C163" s="51">
         <v>700000</v>
       </c>
-      <c r="D155" s="58"/>
-      <c r="E155" s="39"/>
-    </row>
-    <row r="156" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="38" t="s">
+      <c r="D163" s="52"/>
+      <c r="E163" s="39"/>
+    </row>
+    <row r="164" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B164" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C156" s="57">
-        <f>C155-C158-C159</f>
+      <c r="C164" s="51">
+        <f>C163-C166-C167</f>
         <v>665000</v>
       </c>
-      <c r="D156" s="58"/>
-      <c r="E156" s="39">
-        <f>C156/C154*100</f>
-        <v>83.877553984147099</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="38" t="s">
+      <c r="D164" s="52"/>
+      <c r="E164" s="39">
+        <f>C164/C162*100</f>
+        <v>78.898781753567036</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B165" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C157" s="59">
-        <f>C154-C156</f>
-        <v>127822.35641454847</v>
-      </c>
-      <c r="D157" s="59"/>
-      <c r="E157" s="39">
-        <f>100-E156</f>
-        <v>16.122446015852901</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B158" s="38" t="s">
+      <c r="C165" s="53">
+        <f>C162-C164</f>
+        <v>177852.05071615078</v>
+      </c>
+      <c r="D165" s="53"/>
+      <c r="E165" s="39">
+        <f>100-E164</f>
+        <v>21.101218246432964</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B166" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C158" s="55">
-        <f>C155*0.03</f>
+      <c r="C166" s="49">
+        <f>C163*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D158" s="56"/>
-      <c r="E158" s="39">
+      <c r="D166" s="50"/>
+      <c r="E166" s="39">
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="38" t="s">
+    <row r="167" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B167" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C159" s="55">
-        <f>C155*0.02</f>
+      <c r="C167" s="49">
+        <f>C163*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D159" s="56"/>
-      <c r="E159" s="39">
+      <c r="D167" s="50"/>
+      <c r="E167" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C159:D159"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C166:D166"/>
+    <mergeCell ref="C167:D167"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="C164:D164"/>
+    <mergeCell ref="C165:D165"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -11894,4 +12241,231 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD11BB8-440B-4866-9ABD-75354584ECA7}">
+  <dimension ref="B2:W4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.85546875" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" customWidth="1"/>
+    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B2" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="68"/>
+      <c r="R2" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="V2" s="65"/>
+      <c r="W2" s="65"/>
+    </row>
+    <row r="3" spans="2:23" s="70" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="64" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="64" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="K3" s="69" t="s">
+        <v>98</v>
+      </c>
+      <c r="L3" s="69" t="s">
+        <v>100</v>
+      </c>
+      <c r="M3" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="N3" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="O3" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="P3" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q3" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="R3" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="S3" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="T3" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="U3" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="V3" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="W3" s="69" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B4" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="C4" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="D4" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="E4" s="23">
+        <f>3.083/3.281</f>
+        <v>0.93965254495580619</v>
+      </c>
+      <c r="F4" s="23">
+        <f>3.083/3.281</f>
+        <v>0.93965254495580619</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0.35</v>
+      </c>
+      <c r="H4" s="23">
+        <f>14/3.281</f>
+        <v>4.2669917708015843</v>
+      </c>
+      <c r="I4" s="23">
+        <f>14/3.281</f>
+        <v>4.2669917708015843</v>
+      </c>
+      <c r="J4" s="23">
+        <v>0.45</v>
+      </c>
+      <c r="K4" s="23">
+        <f>H4-E4*2</f>
+        <v>2.3876866808899719</v>
+      </c>
+      <c r="L4" s="23">
+        <f>0.5-0.055-0.075+J4</f>
+        <v>0.82000000000000006</v>
+      </c>
+      <c r="M4" s="23">
+        <f>E4-1.17/3.281</f>
+        <v>0.5830539469673881</v>
+      </c>
+      <c r="N4" s="23">
+        <f>D4-G4+J4</f>
+        <v>1.5999999999999999</v>
+      </c>
+      <c r="O4" s="23">
+        <v>0.35</v>
+      </c>
+      <c r="P4" s="23">
+        <f>D4-G4+J4-T4</f>
+        <v>1.3699999999999999</v>
+      </c>
+      <c r="Q4" s="23">
+        <f>(10.5-0.42)/3.281</f>
+        <v>3.0722340749771408</v>
+      </c>
+      <c r="R4" s="3">
+        <f>H4-O4*2</f>
+        <v>3.5669917708015841</v>
+      </c>
+      <c r="S4" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="U4" s="3">
+        <f>K4-R4*2</f>
+        <v>-4.7462968607131959</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0.35</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="E2:G2"/>
+  </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/बजेट माग estimate/नगर बजेट estimate/bhotange chihaanpaati/2.bhotange chihaanpaati.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/bhotange chihaanpaati/2.bhotange chihaanpaati.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4231312-D497-48D0-A20F-EC4E75643B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B724E4A-01FA-4138-BA9F-542CFC96CA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'bhotange chihaanpaati'!$A$1:$K$158</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">chihaan!$A$1:$K$167</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">chihaan!$A$1:$K$157</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$158</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'bhotange chihaanpaati'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">chihaan!$1:$8</definedName>
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="114">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -454,6 +454,15 @@
   <si>
     <t>-top roof</t>
   </si>
+  <si>
+    <t>-at column</t>
+  </si>
+  <si>
+    <t>Knfi6/ dfly @) dL=dL= afSnf] emNn/ jf kfgL k§L agfpg] sfd</t>
+  </si>
+  <si>
+    <t>-13% VAT for water-proofing</t>
+  </si>
 </sst>
 </file>
 
@@ -675,7 +684,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -795,23 +804,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -826,20 +829,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -853,19 +860,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1407,113 +1427,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="61" t="s">
+      <c r="H6" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="55" t="s">
+      <c r="H7" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -4816,11 +4836,11 @@
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="49">
+      <c r="C153" s="58">
         <f>J151</f>
         <v>791637.34255256748</v>
       </c>
-      <c r="D153" s="50"/>
+      <c r="D153" s="59"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -4835,21 +4855,21 @@
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="51">
+      <c r="C154" s="62">
         <v>700000</v>
       </c>
-      <c r="D154" s="52"/>
+      <c r="D154" s="63"/>
       <c r="E154" s="39"/>
     </row>
     <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="51">
+      <c r="C155" s="62">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="52"/>
+      <c r="D155" s="63"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>84.003111558098539</v>
@@ -4859,11 +4879,11 @@
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="53">
+      <c r="C156" s="64">
         <f>C153-C155</f>
         <v>126637.34255256748</v>
       </c>
-      <c r="D156" s="53"/>
+      <c r="D156" s="64"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>15.996888441901461</v>
@@ -4873,11 +4893,11 @@
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="49">
+      <c r="C157" s="58">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="50"/>
+      <c r="D157" s="59"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
@@ -4886,17 +4906,23 @@
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="49">
+      <c r="C158" s="58">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="50"/>
+      <c r="D158" s="59"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -4906,12 +4932,6 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -4938,113 +4958,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="61" t="s">
+      <c r="H6" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="55" t="s">
+      <c r="H7" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -8347,11 +8367,11 @@
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="49">
+      <c r="C153" s="58">
         <f>J151</f>
         <v>791637.34255256748</v>
       </c>
-      <c r="D153" s="50"/>
+      <c r="D153" s="59"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -8366,21 +8386,21 @@
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="51">
+      <c r="C154" s="62">
         <v>700000</v>
       </c>
-      <c r="D154" s="52"/>
+      <c r="D154" s="63"/>
       <c r="E154" s="39"/>
     </row>
     <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="51">
+      <c r="C155" s="62">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="52"/>
+      <c r="D155" s="63"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>84.003111558098539</v>
@@ -8390,11 +8410,11 @@
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="53">
+      <c r="C156" s="64">
         <f>C153-C155</f>
         <v>126637.34255256748</v>
       </c>
-      <c r="D156" s="53"/>
+      <c r="D156" s="64"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>15.996888441901461</v>
@@ -8404,11 +8424,11 @@
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="49">
+      <c r="C157" s="58">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="50"/>
+      <c r="D157" s="59"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
@@ -8417,24 +8437,17 @@
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="49">
+      <c r="C158" s="58">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="50"/>
+      <c r="D158" s="59"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="C158:D158"/>
     <mergeCell ref="A7:F7"/>
@@ -8443,6 +8456,13 @@
     <mergeCell ref="C154:D154"/>
     <mergeCell ref="C155:D155"/>
     <mergeCell ref="C156:D156"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -8454,12 +8474,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAEEC707-87B5-428A-A0F5-809434590EB3}">
-  <dimension ref="A1:M167"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" customWidth="1"/>
     <col min="5" max="5" width="8.5703125" customWidth="1"/>
     <col min="6" max="6" width="7.28515625" customWidth="1"/>
@@ -8470,113 +8490,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="61" t="s">
+      <c r="H6" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="55" t="s">
+      <c r="H7" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -8993,11 +9013,11 @@
         <v>3.5669917708015841</v>
       </c>
       <c r="F25" s="3">
-        <v>7.4999999999999997E-2</v>
+        <v>0.1</v>
       </c>
       <c r="G25" s="3">
         <f>PRODUCT(C25:F25)</f>
-        <v>0.95425727197246646</v>
+        <v>1.2723430292966222</v>
       </c>
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
@@ -9015,7 +9035,7 @@
       <c r="F26" s="20"/>
       <c r="G26" s="2">
         <f>SUM(G23:G25)</f>
-        <v>1.7940076529538744</v>
+        <v>2.11209341027803</v>
       </c>
       <c r="H26" s="21" t="s">
         <v>28</v>
@@ -9025,7 +9045,7 @@
       </c>
       <c r="J26" s="22">
         <f>G26*I26</f>
-        <v>8065.2125649255568</v>
+        <v>9495.2116189823228</v>
       </c>
       <c r="K26" s="20"/>
     </row>
@@ -9043,7 +9063,7 @@
       <c r="I27" s="26"/>
       <c r="J27" s="22">
         <f>0.13*G26*2866.82</f>
-        <v>668.60261255335945</v>
+        <v>787.14891195892403</v>
       </c>
       <c r="K27" s="26"/>
     </row>
@@ -9061,7 +9081,7 @@
       <c r="I28" s="26"/>
       <c r="J28" s="22">
         <f>0.13*G26*(2065.63+805.06)</f>
-        <v>669.50517780356051</v>
+        <v>788.2115061536349</v>
       </c>
       <c r="K28" s="26"/>
     </row>
@@ -9079,7 +9099,7 @@
       <c r="I29" s="26"/>
       <c r="J29" s="22">
         <f>0.13*G26*1493.61</f>
-        <v>348.3412101686967</v>
+        <v>410.10369900829784</v>
       </c>
       <c r="K29" s="26"/>
     </row>
@@ -9097,7 +9117,7 @@
       <c r="I30" s="15"/>
       <c r="J30" s="22">
         <f>0.13*G26*33.6</f>
-        <v>7.8362254281025248</v>
+        <v>9.2256240160944341</v>
       </c>
       <c r="K30" s="15"/>
     </row>
@@ -9269,12 +9289,11 @@
         <v>0.23</v>
       </c>
       <c r="F37" s="3">
-        <f>Sheet1!W4</f>
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="G37" s="3">
         <f t="shared" si="3"/>
-        <v>1.1485713501981101</v>
+        <v>0.75477545870161533</v>
       </c>
       <c r="H37" s="15"/>
       <c r="I37" s="15"/>
@@ -9373,8 +9392,8 @@
         <v>4</v>
       </c>
       <c r="D41" s="3">
-        <f>((12.75+7.25)/2)/3.281</f>
-        <v>3.047851264858275</v>
+        <f>((12.75+7.5)/2)/3.281</f>
+        <v>3.0859494056690031</v>
       </c>
       <c r="E41" s="3">
         <f>3/3.281</f>
@@ -9385,7 +9404,7 @@
       </c>
       <c r="G41" s="3">
         <f t="shared" si="3"/>
-        <v>1.1147276799237824</v>
+        <v>1.1286617759228297</v>
       </c>
       <c r="H41" s="15"/>
       <c r="I41" s="15"/>
@@ -9481,8 +9500,8 @@
         <v>4</v>
       </c>
       <c r="D45" s="3">
-        <f>3.25/3.281</f>
-        <v>0.99055166107893933</v>
+        <f>3.33/3.281</f>
+        <v>1.0149344711978054</v>
       </c>
       <c r="E45" s="3">
         <f>4/3.281</f>
@@ -9493,7 +9512,7 @@
       </c>
       <c r="G45" s="3">
         <f t="shared" si="4"/>
-        <v>0.36228649597522916</v>
+        <v>0.3712043174146194</v>
       </c>
       <c r="H45" s="15"/>
       <c r="I45" s="15"/>
@@ -9565,7 +9584,7 @@
       <c r="F48" s="20"/>
       <c r="G48" s="2">
         <f>SUM(G33:G45)</f>
-        <v>11.668702307566186</v>
+        <v>11.29775833350813</v>
       </c>
       <c r="H48" s="21" t="s">
         <v>28</v>
@@ -9575,7 +9594,7 @@
       </c>
       <c r="J48" s="22">
         <f>G48*I48</f>
-        <v>162863.46203037046</v>
+        <v>157686.08941068969</v>
       </c>
       <c r="K48" s="20"/>
     </row>
@@ -9593,7 +9612,7 @@
       <c r="I49" s="26"/>
       <c r="J49" s="22">
         <f>0.13*G48*5212.4</f>
-        <v>7906.8527080345384</v>
+        <v>7655.4966198851107</v>
       </c>
       <c r="K49" s="26"/>
     </row>
@@ -9611,7 +9630,7 @@
       <c r="I50" s="26"/>
       <c r="J50" s="22">
         <f>0.13*G48*(1912.03+921.59)</f>
-        <v>4298.4068702595405</v>
+        <v>4161.7620159693897</v>
       </c>
       <c r="K50" s="26"/>
     </row>
@@ -9629,7 +9648,7 @@
       <c r="I51" s="26"/>
       <c r="J51" s="22">
         <f>0.13*G48*1350.6</f>
-        <v>2048.7674137578556</v>
+        <v>1983.6378126806903</v>
       </c>
       <c r="K51" s="26"/>
     </row>
@@ -9647,7 +9666,7 @@
       <c r="I52" s="15"/>
       <c r="J52" s="22">
         <f>0.13*G48*56</f>
-        <v>84.948152799081839</v>
+        <v>82.247680667939193</v>
       </c>
       <c r="K52" s="15"/>
     </row>
@@ -9665,7 +9684,7 @@
       <c r="I53" s="26"/>
       <c r="J53" s="22">
         <f>0.13*G48*392.92</f>
-        <v>596.03264638955784</v>
+        <v>577.08497657226189</v>
       </c>
       <c r="K53" s="26"/>
     </row>
@@ -9683,7 +9702,7 @@
       <c r="I54" s="15"/>
       <c r="J54" s="22">
         <f>0.13*G48*14.15</f>
-        <v>21.464577894767999</v>
+        <v>20.782226454488207</v>
       </c>
       <c r="K54" s="15"/>
     </row>
@@ -9748,11 +9767,11 @@
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="15"/>
       <c r="B58" s="16" t="str">
-        <f>B35</f>
+        <f t="shared" ref="B58:C62" si="5">B35</f>
         <v>-for tie beam</v>
       </c>
       <c r="C58" s="15">
-        <f>C35</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="D58" s="3">
@@ -9776,11 +9795,11 @@
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="15"/>
       <c r="B59" s="16" t="str">
-        <f>B36</f>
+        <f t="shared" si="5"/>
         <v>-GF column</v>
       </c>
       <c r="C59" s="15">
-        <f>C36</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="D59" s="3">
@@ -9793,7 +9812,7 @@
         <v>3.0722340749771408</v>
       </c>
       <c r="G59" s="3">
-        <f t="shared" ref="G59:G63" si="5">PRODUCT(C59:F59)</f>
+        <f t="shared" ref="G59:G64" si="6">PRODUCT(C59:F59)</f>
         <v>17.204510819871988</v>
       </c>
       <c r="H59" s="15"/>
@@ -9804,11 +9823,11 @@
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="15"/>
       <c r="B60" s="16" t="str">
-        <f>B37</f>
+        <f t="shared" si="5"/>
         <v>-for beam</v>
       </c>
       <c r="C60" s="15">
-        <f>C37</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="D60" s="3">
@@ -9821,7 +9840,7 @@
         <v>0.46</v>
       </c>
       <c r="G60" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.5632648582749153</v>
       </c>
       <c r="H60" s="15"/>
@@ -9832,11 +9851,11 @@
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="15"/>
       <c r="B61" s="16" t="str">
-        <f>B38</f>
+        <f t="shared" si="5"/>
         <v>-for support beam</v>
       </c>
       <c r="C61" s="15">
-        <f>C38</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="D61" s="3">
@@ -9849,7 +9868,7 @@
         <v>0.46</v>
       </c>
       <c r="G61" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.2816324291374577</v>
       </c>
       <c r="H61" s="15"/>
@@ -9860,11 +9879,11 @@
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="15"/>
       <c r="B62" s="16" t="str">
-        <f>B39</f>
+        <f t="shared" si="5"/>
         <v>-for column over support beam</v>
       </c>
       <c r="C62" s="15">
-        <f>C39</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="D62" s="3">
@@ -9877,7 +9896,7 @@
         <v>1.8</v>
       </c>
       <c r="G62" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.6560000000000001</v>
       </c>
       <c r="H62" s="15"/>
@@ -9887,26 +9906,25 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="15"/>
-      <c r="B63" s="16" t="str">
-        <f>B41</f>
-        <v>-for inclined slab</v>
+      <c r="B63" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="C63" s="15">
-        <f>C41</f>
+        <f>4</f>
         <v>4</v>
       </c>
       <c r="D63" s="3">
-        <f>D41</f>
-        <v>3.047851264858275</v>
-      </c>
-      <c r="E63" s="3">
-        <f>E41</f>
-        <v>0.91435537945748246</v>
-      </c>
-      <c r="F63" s="3"/>
+        <f>6.5/3.281</f>
+        <v>1.9811033221578787</v>
+      </c>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3">
+        <f>2*0.23</f>
+        <v>0.46</v>
+      </c>
       <c r="G63" s="3">
-        <f t="shared" si="5"/>
-        <v>11.147276799237824</v>
+        <f t="shared" si="6"/>
+        <v>3.6452301127704967</v>
       </c>
       <c r="H63" s="15"/>
       <c r="I63" s="15"/>
@@ -9916,89 +9934,89 @@
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="15"/>
       <c r="B64" s="16" t="str">
-        <f t="shared" ref="B64:E64" si="6">B42</f>
-        <v>-for cantilever</v>
+        <f>B41</f>
+        <v>-for inclined slab</v>
       </c>
       <c r="C64" s="15">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <f>C41</f>
+        <v>4</v>
       </c>
       <c r="D64" s="3">
-        <f t="shared" si="6"/>
-        <v>4.2669917708015843</v>
+        <f>D41</f>
+        <v>3.0859494056690031</v>
       </c>
       <c r="E64" s="3">
-        <f t="shared" si="6"/>
-        <v>0.6</v>
+        <f>E41</f>
+        <v>0.91435537945748246</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3">
-        <f t="shared" ref="G64:G69" si="7">PRODUCT(C64:F64)</f>
-        <v>5.1203901249619008</v>
+        <f t="shared" si="6"/>
+        <v>11.286617759228296</v>
       </c>
       <c r="H64" s="15"/>
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
       <c r="K64" s="15"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="15"/>
-      <c r="B65" s="16"/>
+      <c r="B65" s="16" t="str">
+        <f t="shared" ref="B65:E65" si="7">B42</f>
+        <v>-for cantilever</v>
+      </c>
       <c r="C65" s="15">
-        <f t="shared" ref="B65:E65" si="8">C43</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="D65" s="3">
-        <f t="shared" si="8"/>
-        <v>5.4669917708015845</v>
+        <f t="shared" si="7"/>
+        <v>4.2669917708015843</v>
       </c>
       <c r="E65" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.6</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3">
-        <f t="shared" si="7"/>
-        <v>6.5603901249619012</v>
+        <f t="shared" ref="G65:G70" si="8">PRODUCT(C65:F65)</f>
+        <v>5.1203901249619008</v>
       </c>
       <c r="H65" s="15"/>
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
       <c r="K65" s="15"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="15"/>
-      <c r="B66" s="16" t="str">
-        <f t="shared" ref="B66:E66" si="9">B44</f>
-        <v>-beam for top roof inclined support</v>
-      </c>
+      <c r="B66" s="16"/>
       <c r="C66" s="15">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" ref="C66:E66" si="9">C43</f>
+        <v>2</v>
       </c>
       <c r="D66" s="3">
         <f t="shared" si="9"/>
-        <v>1.9811033221578787</v>
-      </c>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3">
-        <f>F44*2</f>
-        <v>0.46</v>
-      </c>
+        <v>5.4669917708015845</v>
+      </c>
+      <c r="E66" s="3">
+        <f t="shared" si="9"/>
+        <v>0.6</v>
+      </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3">
-        <f t="shared" si="7"/>
-        <v>3.6452301127704967</v>
+        <f t="shared" si="8"/>
+        <v>6.5603901249619012</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="15"/>
       <c r="J66" s="15"/>
       <c r="K66" s="15"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="15"/>
       <c r="B67" s="16" t="str">
-        <f t="shared" ref="B67:F67" si="10">B45</f>
-        <v>-top roof</v>
+        <f t="shared" ref="B67:D67" si="10">B44</f>
+        <v>-beam for top roof inclined support</v>
       </c>
       <c r="C67" s="15">
         <f t="shared" si="10"/>
@@ -10006,60 +10024,63 @@
       </c>
       <c r="D67" s="3">
         <f t="shared" si="10"/>
-        <v>0.99055166107893933</v>
-      </c>
-      <c r="E67" s="3">
-        <f t="shared" si="10"/>
-        <v>1.2191405059433098</v>
-      </c>
-      <c r="F67" s="3"/>
+        <v>1.9811033221578787</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3">
+        <f>F44*2</f>
+        <v>0.46</v>
+      </c>
       <c r="G67" s="3">
-        <f t="shared" si="7"/>
-        <v>4.8304866130030559</v>
+        <f t="shared" si="8"/>
+        <v>3.6452301127704967</v>
       </c>
       <c r="H67" s="15"/>
       <c r="I67" s="15"/>
       <c r="J67" s="15"/>
       <c r="K67" s="15"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="15"/>
       <c r="B68" s="16" t="str">
-        <f t="shared" ref="B68:F68" si="11">B46</f>
-        <v>-for cantilever</v>
+        <f t="shared" ref="B68:E68" si="11">B45</f>
+        <v>-top roof</v>
       </c>
       <c r="C68" s="15">
         <f t="shared" si="11"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D68" s="3">
         <f t="shared" si="11"/>
-        <v>3.5050289545870159</v>
+        <v>1.0149344711978054</v>
       </c>
       <c r="E68" s="3">
         <f t="shared" si="11"/>
-        <v>0.53337397135019804</v>
+        <v>1.2191405059433098</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3">
-        <f t="shared" si="7"/>
-        <v>3.7389824264110194</v>
+        <f t="shared" si="8"/>
+        <v>4.9493908988615924</v>
       </c>
       <c r="H68" s="15"/>
       <c r="I68" s="15"/>
       <c r="J68" s="15"/>
       <c r="K68" s="15"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="15"/>
-      <c r="B69" s="16"/>
+      <c r="B69" s="16" t="str">
+        <f t="shared" ref="B69:E69" si="12">B46</f>
+        <v>-for cantilever</v>
+      </c>
       <c r="C69" s="15">
-        <f t="shared" ref="B69:F69" si="12">C47</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="D69" s="3">
         <f t="shared" si="12"/>
-        <v>2.4382810118866196</v>
+        <v>3.5050289545870159</v>
       </c>
       <c r="E69" s="3">
         <f t="shared" si="12"/>
@@ -10067,61 +10088,68 @@
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3">
-        <f t="shared" si="7"/>
-        <v>2.6010312531554916</v>
+        <f t="shared" si="8"/>
+        <v>3.7389824264110194</v>
       </c>
       <c r="H69" s="15"/>
       <c r="I69" s="15"/>
       <c r="J69" s="15"/>
       <c r="K69" s="15"/>
     </row>
-    <row r="70" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="17"/>
-      <c r="B70" s="18" t="s">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="15"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="15">
+        <f t="shared" ref="C70:E70" si="13">C47</f>
+        <v>2</v>
+      </c>
+      <c r="D70" s="3">
+        <f t="shared" si="13"/>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E70" s="3">
+        <f t="shared" si="13"/>
+        <v>0.53337397135019804</v>
+      </c>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3">
+        <f t="shared" si="8"/>
+        <v>2.6010312531554916</v>
+      </c>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+    </row>
+    <row r="71" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="17"/>
+      <c r="B71" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C70" s="19"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="2">
-        <f>SUM(G57:G69)</f>
-        <v>74.830460420060959</v>
-      </c>
-      <c r="H70" s="21" t="s">
+      <c r="C71" s="19"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="2">
+        <f>SUM(G57:G70)</f>
+        <v>78.733935778680461</v>
+      </c>
+      <c r="H71" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="I70" s="2">
+      <c r="I71" s="2">
         <v>922.71</v>
       </c>
-      <c r="J70" s="22">
-        <f>G70*I70</f>
-        <v>69046.814134194443</v>
-      </c>
-      <c r="K70" s="20"/>
-    </row>
-    <row r="71" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="24"/>
-      <c r="B71" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C71" s="26"/>
-      <c r="D71" s="27"/>
-      <c r="E71" s="27"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="26"/>
-      <c r="I71" s="26"/>
       <c r="J71" s="22">
-        <f>0.13*G70*20062.02/100</f>
-        <v>1951.6252516234129</v>
-      </c>
-      <c r="K71" s="26"/>
-    </row>
-    <row r="72" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <f>G71*I71</f>
+        <v>72648.589882346248</v>
+      </c>
+      <c r="K71" s="20"/>
+    </row>
+    <row r="72" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="24"/>
       <c r="B72" s="25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C72" s="26"/>
       <c r="D72" s="27"/>
@@ -10131,15 +10159,15 @@
       <c r="H72" s="26"/>
       <c r="I72" s="26"/>
       <c r="J72" s="22">
-        <f>0.13*G70*13328.25/100</f>
-        <v>1296.5668093217805</v>
+        <f>0.13*G71*20062.02/100</f>
+        <v>2053.430332551784</v>
       </c>
       <c r="K72" s="26"/>
     </row>
-    <row r="73" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="24"/>
       <c r="B73" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C73" s="26"/>
       <c r="D73" s="27"/>
@@ -10149,106 +10177,97 @@
       <c r="H73" s="26"/>
       <c r="I73" s="26"/>
       <c r="J73" s="22">
-        <f>0.13*G70*10137.6/100</f>
-        <v>986.18165822073297</v>
+        <f>0.13*G71*13328.25/100</f>
+        <v>1364.2012534048574</v>
       </c>
       <c r="K73" s="26"/>
     </row>
-    <row r="74" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="71"/>
-      <c r="B74" s="72" t="s">
+    <row r="74" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="24"/>
+      <c r="B74" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C74" s="26"/>
+      <c r="D74" s="27"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="27"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="22">
+        <f>0.13*G71*10137.6/100</f>
+        <v>1037.6250915549365</v>
+      </c>
+      <c r="K74" s="26"/>
+    </row>
+    <row r="75" spans="1:11" s="75" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="71"/>
+      <c r="B75" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="C74" s="71"/>
-      <c r="D74" s="73"/>
-      <c r="E74" s="73"/>
-      <c r="F74" s="73"/>
-      <c r="G74" s="73"/>
-      <c r="H74" s="71"/>
-      <c r="I74" s="71"/>
-      <c r="J74" s="74">
-        <f>0.13*G70*3300/100</f>
-        <v>321.02267520206152</v>
-      </c>
-      <c r="K74" s="71"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="15"/>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="15"/>
-      <c r="I75" s="15"/>
-      <c r="J75" s="15"/>
-      <c r="K75" s="15"/>
-    </row>
-    <row r="76" spans="1:13" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A76" s="11">
+      <c r="C75" s="71"/>
+      <c r="D75" s="73"/>
+      <c r="E75" s="73"/>
+      <c r="F75" s="73"/>
+      <c r="G75" s="73"/>
+      <c r="H75" s="71"/>
+      <c r="I75" s="71"/>
+      <c r="J75" s="74">
+        <f>0.13*G71*3300/100</f>
+        <v>337.76858449053924</v>
+      </c>
+      <c r="K75" s="71"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="15"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
+      <c r="J76" s="15"/>
+      <c r="K76" s="15"/>
+    </row>
+    <row r="77" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A77" s="11">
         <v>6</v>
       </c>
-      <c r="B76" s="28" t="s">
+      <c r="B77" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C77" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D76" s="29" t="s">
+      <c r="D77" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="E76" s="29" t="s">
+      <c r="E77" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F76" s="29" t="s">
+      <c r="F77" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="G76" s="23"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
-      <c r="J76" s="13"/>
-      <c r="K76" s="13"/>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="15"/>
-      <c r="B77" s="16" t="str">
+      <c r="G77" s="23"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+      <c r="K77" s="13"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="15"/>
+      <c r="B78" s="16" t="str">
         <f>B33</f>
         <v>-for foundation</v>
       </c>
-      <c r="C77" s="15">
-        <f>TRUNC((1.5-0.1)/0.15,0)+1</f>
+      <c r="C78" s="15">
+        <f>TRUNC((E33-0.1)/0.15,0)+1</f>
         <v>10</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D78" s="3">
         <f>1.5</f>
-        <v>1.5</v>
-      </c>
-      <c r="E77" s="3">
-        <f>12*12/162</f>
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="F77" s="3">
-        <f t="shared" ref="F77:F95" si="13">PRODUCT(C77:E77)</f>
-        <v>13.333333333333332</v>
-      </c>
-      <c r="G77" s="3">
-        <f t="shared" ref="G77:G95" si="14">F77/1000</f>
-        <v>1.3333333333333332E-2</v>
-      </c>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
-      <c r="K77" s="15"/>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="15"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="15">
-        <f>TRUNC((1.5-0.1)/0.15,0)+1</f>
-        <v>10</v>
-      </c>
-      <c r="D78" s="3">
         <v>1.5</v>
       </c>
       <c r="E78" s="3">
@@ -10256,11 +10275,11 @@
         <v>0.88888888888888884</v>
       </c>
       <c r="F78" s="3">
-        <f t="shared" si="13"/>
+        <f>PRODUCT(C78:E78)</f>
         <v>13.333333333333332</v>
       </c>
       <c r="G78" s="3">
-        <f t="shared" si="14"/>
+        <f>F78/1000</f>
         <v>1.3333333333333332E-2</v>
       </c>
       <c r="H78" s="15"/>
@@ -10268,92 +10287,85 @@
       <c r="J78" s="15"/>
       <c r="K78" s="15"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="15"/>
-      <c r="B79" s="16" t="s">
-        <v>70</v>
-      </c>
+      <c r="B79" s="16"/>
       <c r="C79" s="15">
-        <f>4*4</f>
-        <v>16</v>
+        <f>TRUNC((D33-0.1)/0.15,0)+1</f>
+        <v>10</v>
       </c>
       <c r="D79" s="3">
-        <f>(10.5+1.5+5-0.17*2)/3.281+0.45+0.45</f>
-        <v>5.9777202072538858</v>
+        <v>1.5</v>
       </c>
       <c r="E79" s="3">
-        <f t="shared" ref="E79" si="15">12*12/162</f>
+        <f>12*12/162</f>
         <v>0.88888888888888884</v>
       </c>
       <c r="F79" s="3">
-        <f t="shared" si="13"/>
-        <v>85.01646516983304</v>
+        <f t="shared" ref="F79:F106" si="14">PRODUCT(C79:E79)</f>
+        <v>13.333333333333332</v>
       </c>
       <c r="G79" s="3">
-        <f t="shared" si="14"/>
-        <v>8.5016465169833036E-2</v>
+        <f t="shared" ref="G79:G106" si="15">F79/1000</f>
+        <v>1.3333333333333332E-2</v>
       </c>
       <c r="H79" s="15"/>
       <c r="I79" s="15"/>
       <c r="J79" s="15"/>
       <c r="K79" s="15"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="15"/>
-      <c r="B80" s="16"/>
+      <c r="B80" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="C80" s="15">
         <f>4*4</f>
         <v>16</v>
       </c>
       <c r="D80" s="3">
-        <f>(10.5+1.5+5-0.17*2)/3.281+0.45+0.45</f>
-        <v>5.9777202072538858</v>
+        <f>(10.5+1.5+5-0.17*2)/3.281+0.3+0.45</f>
+        <v>5.8277202072538854</v>
       </c>
       <c r="E80" s="3">
-        <f>16*16/162</f>
-        <v>1.5802469135802468</v>
+        <f t="shared" ref="E80" si="16">12*12/162</f>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F80" s="3">
-        <f t="shared" si="13"/>
-        <v>151.14038252414761</v>
+        <f t="shared" si="14"/>
+        <v>82.8831318364997</v>
       </c>
       <c r="G80" s="3">
-        <f t="shared" si="14"/>
-        <v>0.1511403825241476</v>
+        <f t="shared" si="15"/>
+        <v>8.2883131836499702E-2</v>
       </c>
       <c r="H80" s="15"/>
       <c r="I80" s="15"/>
       <c r="J80" s="15"/>
       <c r="K80" s="15"/>
-      <c r="M80">
-        <f>(10.5+1.5+5-0.17*2)/3.281</f>
-        <v>5.0777202072538854</v>
-      </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="15"/>
-      <c r="B81" s="16" t="s">
-        <v>71</v>
-      </c>
+      <c r="B81" s="16"/>
       <c r="C81" s="15">
-        <f>4*(TRUNC((D80-0.45-0.45)/0.15,0)+1)</f>
-        <v>136</v>
+        <f>4*4</f>
+        <v>16</v>
       </c>
       <c r="D81" s="3">
-        <f>0.917*4/3.281</f>
-        <v>1.1179518439500153</v>
+        <f>(10.5+1.5+5-0.17*2)/3.281+0.3+0.45</f>
+        <v>5.8277202072538854</v>
       </c>
       <c r="E81" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
+        <f>16*16/162</f>
+        <v>1.5802469135802468</v>
       </c>
       <c r="F81" s="3">
-        <f t="shared" si="13"/>
-        <v>60.065758331734159</v>
+        <f t="shared" si="14"/>
+        <v>147.34778993155501</v>
       </c>
       <c r="G81" s="3">
-        <f t="shared" si="14"/>
-        <v>6.0065758331734158E-2</v>
+        <f t="shared" si="15"/>
+        <v>0.14734778993155501</v>
       </c>
       <c r="H81" s="15"/>
       <c r="I81" s="15"/>
@@ -10362,26 +10374,28 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="15"/>
-      <c r="B82" s="16"/>
+      <c r="B82" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="C82" s="15">
-        <f>4*(TRUNC((D80-0.45-0.45)/0.15,0)+1)</f>
-        <v>136</v>
+        <f>4*(TRUNC((D81-0.45-0.45-0.35-0.23)/0.15,0)+1)</f>
+        <v>116</v>
       </c>
       <c r="D82" s="3">
-        <f>0.833*4/3.281</f>
-        <v>1.015544041450777</v>
+        <f>0.917*4/3.281</f>
+        <v>1.1179518439500153</v>
       </c>
       <c r="E82" s="3">
         <f>8*8/162</f>
         <v>0.39506172839506171</v>
       </c>
       <c r="F82" s="3">
-        <f t="shared" si="13"/>
-        <v>54.56355146165162</v>
+        <f t="shared" si="14"/>
+        <v>51.232558577067373</v>
       </c>
       <c r="G82" s="3">
-        <f t="shared" si="14"/>
-        <v>5.4563551461651622E-2</v>
+        <f t="shared" si="15"/>
+        <v>5.1232558577067371E-2</v>
       </c>
       <c r="H82" s="15"/>
       <c r="I82" s="15"/>
@@ -10390,29 +10404,26 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="15"/>
-      <c r="B83" s="16" t="str">
-        <f>B58</f>
-        <v>-for tie beam</v>
-      </c>
+      <c r="B83" s="16"/>
       <c r="C83" s="15">
-        <f>4*4</f>
-        <v>16</v>
+        <f>4*(TRUNC((D81-0.45-0.45-0.35-0.23)/0.15,0)+1)</f>
+        <v>116</v>
       </c>
       <c r="D83" s="3">
-        <f>(12+0.75*2)/3.281</f>
-        <v>4.1145992075586708</v>
+        <f>0.213*4+0.05*2</f>
+        <v>0.95199999999999996</v>
       </c>
       <c r="E83" s="3">
-        <f>12*12/162</f>
-        <v>0.88888888888888884</v>
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
       </c>
       <c r="F83" s="3">
-        <f t="shared" si="13"/>
-        <v>58.518744285278871</v>
+        <f t="shared" si="14"/>
+        <v>43.627456790123446</v>
       </c>
       <c r="G83" s="3">
-        <f t="shared" si="14"/>
-        <v>5.8518744285278868E-2</v>
+        <f t="shared" si="15"/>
+        <v>4.3627456790123448E-2</v>
       </c>
       <c r="H83" s="15"/>
       <c r="I83" s="15"/>
@@ -10421,28 +10432,29 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="15"/>
-      <c r="B84" s="16" t="s">
-        <v>72</v>
+      <c r="B84" s="16" t="str">
+        <f>B58</f>
+        <v>-for tie beam</v>
       </c>
       <c r="C84" s="15">
-        <f>4*(TRUNC((D58-0.1)/0.15,0)+1)</f>
-        <v>96</v>
+        <f>4*6</f>
+        <v>24</v>
       </c>
       <c r="D84" s="3">
-        <f>(0.583*4+0.17*2)/3.281</f>
-        <v>0.81438585797013097</v>
+        <f>(14+0.75*2-0.17*2)/3.281</f>
+        <v>4.6205425175251449</v>
       </c>
       <c r="E84" s="3">
-        <f>8*8/162</f>
-        <v>0.39506172839506171</v>
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F84" s="3">
-        <f t="shared" si="13"/>
-        <v>30.886337724496816</v>
+        <f t="shared" si="14"/>
+        <v>98.571573707203086</v>
       </c>
       <c r="G84" s="3">
-        <f t="shared" si="14"/>
-        <v>3.0886337724496817E-2</v>
+        <f t="shared" si="15"/>
+        <v>9.8571573707203083E-2</v>
       </c>
       <c r="H84" s="15"/>
       <c r="I84" s="15"/>
@@ -10451,9 +10463,8 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="15"/>
-      <c r="B85" s="16" t="str">
-        <f>B60</f>
-        <v>-for beam</v>
+      <c r="B85" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="C85" s="15">
         <f>4*(TRUNC((D58-0.1)/0.15,0)+1)</f>
@@ -10468,11 +10479,11 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F85" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>30.886337724496816</v>
       </c>
       <c r="G85" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.0886337724496817E-2</v>
       </c>
       <c r="H85" s="15"/>
@@ -10483,28 +10494,28 @@
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="15"/>
       <c r="B86" s="16" t="str">
-        <f>B61</f>
-        <v>-for support beam</v>
+        <f>B60</f>
+        <v>-for beam</v>
       </c>
       <c r="C86" s="15">
-        <f>4*4</f>
-        <v>16</v>
+        <f>4*6</f>
+        <v>24</v>
       </c>
       <c r="D86" s="3">
-        <f>(12+0.75*2)/3.281</f>
-        <v>4.1145992075586708</v>
+        <f>(14+0.75*2-0.17*2)/3.281</f>
+        <v>4.6205425175251449</v>
       </c>
       <c r="E86" s="3">
         <f>12*12/162</f>
         <v>0.88888888888888884</v>
       </c>
       <c r="F86" s="3">
-        <f t="shared" si="13"/>
-        <v>58.518744285278871</v>
+        <f t="shared" si="14"/>
+        <v>98.571573707203086</v>
       </c>
       <c r="G86" s="3">
-        <f t="shared" si="14"/>
-        <v>5.8518744285278868E-2</v>
+        <f t="shared" si="15"/>
+        <v>9.8571573707203083E-2</v>
       </c>
       <c r="H86" s="15"/>
       <c r="I86" s="15"/>
@@ -10513,10 +10524,12 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="15"/>
-      <c r="B87" s="16"/>
+      <c r="B87" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="C87" s="15">
-        <f>2*(TRUNC((D60-0.1)/0.15,0)+1)</f>
-        <v>48</v>
+        <f>4*(TRUNC((D60-0.1)/0.15,0)+1)</f>
+        <v>96</v>
       </c>
       <c r="D87" s="3">
         <f>(0.583*4+0.17*2)/3.281</f>
@@ -10527,12 +10540,12 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F87" s="3">
-        <f t="shared" si="13"/>
-        <v>15.443168862248408</v>
+        <f t="shared" si="14"/>
+        <v>30.886337724496816</v>
       </c>
       <c r="G87" s="3">
-        <f t="shared" si="14"/>
-        <v>1.5443168862248408E-2</v>
+        <f t="shared" si="15"/>
+        <v>3.0886337724496817E-2</v>
       </c>
       <c r="H87" s="15"/>
       <c r="I87" s="15"/>
@@ -10542,28 +10555,28 @@
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="15"/>
       <c r="B88" s="16" t="str">
-        <f>B62</f>
-        <v>-for column over support beam</v>
+        <f>B61</f>
+        <v>-for support beam</v>
       </c>
       <c r="C88" s="15">
-        <f>C62*4</f>
-        <v>16</v>
+        <f>2*6</f>
+        <v>12</v>
       </c>
       <c r="D88" s="3">
-        <f>1.5+0.45+0.45</f>
-        <v>2.4</v>
+        <f>(14+0.75*2)/3.281</f>
+        <v>4.7241694605303257</v>
       </c>
       <c r="E88" s="3">
         <f>12*12/162</f>
         <v>0.88888888888888884</v>
       </c>
       <c r="F88" s="3">
-        <f t="shared" si="13"/>
-        <v>34.133333333333333</v>
+        <f t="shared" si="14"/>
+        <v>50.391140912323465</v>
       </c>
       <c r="G88" s="3">
-        <f t="shared" si="14"/>
-        <v>3.4133333333333335E-2</v>
+        <f t="shared" si="15"/>
+        <v>5.0391140912323468E-2</v>
       </c>
       <c r="H88" s="15"/>
       <c r="I88" s="15"/>
@@ -10573,27 +10586,27 @@
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="15"/>
       <c r="B89" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" s="15">
-        <f>4*(TRUNC((D88-0.1)/0.15,0)+1)</f>
-        <v>64</v>
+        <f>2*(TRUNC((D60-0.1)/0.15,0)+1)</f>
+        <v>48</v>
       </c>
       <c r="D89" s="3">
-        <f>0.917*4/3.281</f>
-        <v>1.1179518439500153</v>
+        <f>(0.583*4+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
       </c>
       <c r="E89" s="3">
         <f>8*8/162</f>
         <v>0.39506172839506171</v>
       </c>
       <c r="F89" s="3">
-        <f t="shared" si="13"/>
-        <v>28.266239214933719</v>
+        <f t="shared" si="14"/>
+        <v>15.443168862248408</v>
       </c>
       <c r="G89" s="3">
-        <f t="shared" si="14"/>
-        <v>2.8266239214933719E-2</v>
+        <f t="shared" si="15"/>
+        <v>1.5443168862248408E-2</v>
       </c>
       <c r="H89" s="15"/>
       <c r="I89" s="15"/>
@@ -10603,28 +10616,28 @@
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="15"/>
       <c r="B90" s="16" t="str">
-        <f>B63</f>
-        <v>-for inclined slab</v>
+        <f>B62</f>
+        <v>-for column over support beam</v>
       </c>
       <c r="C90" s="15">
-        <f>4*(TRUNC((D91/0.15),0)+1)</f>
-        <v>4</v>
+        <f>C62*8</f>
+        <v>32</v>
       </c>
       <c r="D90" s="3">
-        <f>D63</f>
-        <v>3.047851264858275</v>
+        <f>1.8+0.3+0.3</f>
+        <v>2.4</v>
       </c>
       <c r="E90" s="3">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F90" s="3">
-        <f t="shared" si="13"/>
-        <v>7.5255586786624065</v>
+        <f t="shared" si="14"/>
+        <v>68.266666666666666</v>
       </c>
       <c r="G90" s="3">
-        <f t="shared" si="14"/>
-        <v>7.5255586786624066E-3</v>
+        <f t="shared" si="15"/>
+        <v>6.826666666666667E-2</v>
       </c>
       <c r="H90" s="15"/>
       <c r="I90" s="15"/>
@@ -10633,26 +10646,28 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="15"/>
-      <c r="B91" s="16"/>
+      <c r="B91" s="16" t="s">
+        <v>71</v>
+      </c>
       <c r="C91" s="15">
-        <f>4*(TRUNC((D90/0.15),0)+1)</f>
-        <v>84</v>
+        <f>4*(TRUNC((D90-0.1-0.3-0.3-0.23-0.23)/0.15,0)+1)</f>
+        <v>36</v>
       </c>
       <c r="D91" s="3">
-        <f>F63</f>
-        <v>0</v>
+        <f>0.5*4/3.281</f>
+        <v>0.6095702529716549</v>
       </c>
       <c r="E91" s="3">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
       </c>
       <c r="F91" s="3">
-        <f t="shared" si="13"/>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>8.6694435978190914</v>
       </c>
       <c r="G91" s="3">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>8.6694435978190917E-3</v>
       </c>
       <c r="H91" s="15"/>
       <c r="I91" s="15"/>
@@ -10661,27 +10676,26 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="15"/>
-      <c r="B92" s="16" t="s">
-        <v>84</v>
-      </c>
+      <c r="B92" s="16"/>
       <c r="C92" s="15">
-        <v>3</v>
+        <f>C91</f>
+        <v>36</v>
       </c>
       <c r="D92" s="3">
-        <f>(12+2+2)/3.281</f>
-        <v>4.8765620237732392</v>
+        <f>0.333*4/3.281</f>
+        <v>0.40597378847912224</v>
       </c>
       <c r="E92" s="3">
-        <f>10*10/162</f>
-        <v>0.61728395061728392</v>
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
       </c>
       <c r="F92" s="3">
-        <f t="shared" si="13"/>
-        <v>9.030670414394887</v>
+        <f t="shared" si="14"/>
+        <v>5.7738494361475166</v>
       </c>
       <c r="G92" s="3">
-        <f t="shared" si="14"/>
-        <v>9.0306704143948875E-3</v>
+        <f t="shared" si="15"/>
+        <v>5.7738494361475167E-3</v>
       </c>
       <c r="H92" s="15"/>
       <c r="I92" s="15"/>
@@ -10690,25 +10704,28 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="15"/>
-      <c r="B93" s="16"/>
+      <c r="B93" s="16" t="s">
+        <v>108</v>
+      </c>
       <c r="C93" s="15">
-        <f>26</f>
-        <v>26</v>
+        <f>2*(4*5)</f>
+        <v>40</v>
       </c>
       <c r="D93" s="3">
-        <v>0.6</v>
+        <f>(8+0.5*2)/3.281</f>
+        <v>2.7430661383724475</v>
       </c>
       <c r="E93" s="3">
-        <f t="shared" ref="E93:E95" si="16">10*10/162</f>
-        <v>0.61728395061728392</v>
+        <f>12*12/162</f>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F93" s="3">
-        <f t="shared" si="13"/>
-        <v>9.6296296296296298</v>
+        <f t="shared" si="14"/>
+        <v>97.531240475464799</v>
       </c>
       <c r="G93" s="3">
-        <f t="shared" si="14"/>
-        <v>9.6296296296296303E-3</v>
+        <f t="shared" si="15"/>
+        <v>9.7531240475464798E-2</v>
       </c>
       <c r="H93" s="15"/>
       <c r="I93" s="15"/>
@@ -10717,25 +10734,28 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="15"/>
-      <c r="B94" s="16"/>
+      <c r="B94" s="16" t="s">
+        <v>72</v>
+      </c>
       <c r="C94" s="15">
-        <v>3</v>
+        <f>4*(TRUNC((8-0.33-0.75-0.75)/0.5,0)+1)</f>
+        <v>52</v>
       </c>
       <c r="D94" s="3">
-        <f>(12+2+2)/3.281</f>
-        <v>4.8765620237732392</v>
+        <f>(0.583*4+0.17*2)/3.281</f>
+        <v>0.81438585797013097</v>
       </c>
       <c r="E94" s="3">
-        <f t="shared" si="16"/>
-        <v>0.61728395061728392</v>
+        <f>8*8/162</f>
+        <v>0.39506172839506171</v>
       </c>
       <c r="F94" s="3">
-        <f t="shared" si="13"/>
-        <v>9.030670414394887</v>
+        <f t="shared" si="14"/>
+        <v>16.730099600769112</v>
       </c>
       <c r="G94" s="3">
-        <f t="shared" si="14"/>
-        <v>9.0306704143948875E-3</v>
+        <f t="shared" si="15"/>
+        <v>1.6730099600769113E-2</v>
       </c>
       <c r="H94" s="15"/>
       <c r="I94" s="15"/>
@@ -10744,117 +10764,170 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="15"/>
-      <c r="B95" s="16"/>
+      <c r="B95" s="16" t="str">
+        <f>B64</f>
+        <v>-for inclined slab</v>
+      </c>
       <c r="C95" s="15">
-        <f>C93</f>
-        <v>26</v>
+        <f>4*(TRUNC(((D96-0.1)/0.15),0)+1)</f>
+        <v>24</v>
       </c>
       <c r="D95" s="3">
-        <v>0.6</v>
+        <f>D64</f>
+        <v>3.0859494056690031</v>
       </c>
       <c r="E95" s="3">
-        <f t="shared" si="16"/>
+        <f>10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
       <c r="F95" s="3">
-        <f t="shared" si="13"/>
-        <v>9.6296296296296298</v>
+        <f t="shared" si="14"/>
+        <v>45.717768972874119</v>
       </c>
       <c r="G95" s="3">
-        <f t="shared" si="14"/>
-        <v>9.6296296296296303E-3</v>
+        <f t="shared" si="15"/>
+        <v>4.571776897287412E-2</v>
       </c>
       <c r="H95" s="15"/>
       <c r="I95" s="15"/>
       <c r="J95" s="15"/>
       <c r="K95" s="15"/>
     </row>
-    <row r="96" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="17"/>
-      <c r="B96" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" s="19"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="20"/>
-      <c r="F96" s="20"/>
-      <c r="G96" s="2">
-        <f>SUM(G77:G95)</f>
-        <v>0.67895188835081155</v>
-      </c>
-      <c r="H96" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="I96" s="46">
-        <v>132360</v>
-      </c>
-      <c r="J96" s="22">
-        <f>G96*I96</f>
-        <v>89866.071942113413</v>
-      </c>
-      <c r="K96" s="20"/>
-    </row>
-    <row r="97" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="24"/>
-      <c r="B97" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C97" s="26"/>
-      <c r="D97" s="26"/>
-      <c r="E97" s="26"/>
-      <c r="F97" s="26"/>
-      <c r="G97" s="26"/>
-      <c r="H97" s="26"/>
-      <c r="I97" s="26"/>
-      <c r="J97" s="22">
-        <f>0.13*G96*105000</f>
-        <v>9267.6932759885785</v>
-      </c>
-      <c r="K97" s="26"/>
-    </row>
-    <row r="98" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24"/>
-      <c r="B98" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C98" s="26"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="26"/>
-      <c r="I98" s="26"/>
-      <c r="J98" s="22">
-        <f>0.13*G96*1200</f>
-        <v>105.9164945827266</v>
-      </c>
-      <c r="K98" s="26"/>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="15"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="15">
+        <f>4*(TRUNC(((D95-0.1)/0.15),0)+1)</f>
+        <v>80</v>
+      </c>
+      <c r="D96" s="3">
+        <f>E64</f>
+        <v>0.91435537945748246</v>
+      </c>
+      <c r="E96" s="3">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F96" s="3">
+        <f t="shared" si="14"/>
+        <v>45.153352071974439</v>
+      </c>
+      <c r="G96" s="3">
+        <f t="shared" si="15"/>
+        <v>4.5153352071974441E-2</v>
+      </c>
+      <c r="H96" s="15"/>
+      <c r="I96" s="15"/>
+      <c r="J96" s="15"/>
+      <c r="K96" s="15"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="15"/>
+      <c r="B97" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C97" s="15">
+        <f>2*(TRUNC((D98-0.1)/0.15,0)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="D97" s="3">
+        <f>(14+2+2-0.333)/3.281</f>
+        <v>5.3846388296251142</v>
+      </c>
+      <c r="E97" s="3">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F97" s="3">
+        <f t="shared" si="14"/>
+        <v>26.590809035185746</v>
+      </c>
+      <c r="G97" s="3">
+        <f t="shared" si="15"/>
+        <v>2.6590809035185747E-2</v>
+      </c>
+      <c r="H97" s="15"/>
+      <c r="I97" s="15"/>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="15"/>
+      <c r="B98" s="16"/>
+      <c r="C98" s="15">
+        <f>2*(TRUNC((D97-0.1-0.23*2)/0.15,0)+1)</f>
+        <v>66</v>
+      </c>
+      <c r="D98" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E98" s="3">
+        <f t="shared" ref="E98:E100" si="17">10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F98" s="3">
+        <f t="shared" si="14"/>
+        <v>24.444444444444443</v>
+      </c>
+      <c r="G98" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4444444444444442E-2</v>
+      </c>
+      <c r="H98" s="15"/>
+      <c r="I98" s="15"/>
+      <c r="J98" s="15"/>
+      <c r="K98" s="15"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="15"/>
-      <c r="B99" s="15"/>
-      <c r="C99" s="15"/>
-      <c r="D99" s="15"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="15"/>
-      <c r="G99" s="15"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="15">
+        <f>2*(TRUNC((D100-0.1)/0.15,0)+1)</f>
+        <v>8</v>
+      </c>
+      <c r="D99" s="3">
+        <f>(14-0.33)/3.281</f>
+        <v>4.1664126790612617</v>
+      </c>
+      <c r="E99" s="3">
+        <f t="shared" si="17"/>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F99" s="3">
+        <f t="shared" si="14"/>
+        <v>20.574877427463019</v>
+      </c>
+      <c r="G99" s="3">
+        <f t="shared" si="15"/>
+        <v>2.0574877427463018E-2</v>
+      </c>
       <c r="H99" s="15"/>
       <c r="I99" s="15"/>
       <c r="J99" s="15"/>
       <c r="K99" s="15"/>
     </row>
-    <row r="100" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="11">
-        <v>7</v>
-      </c>
-      <c r="B100" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C100" s="15"/>
-      <c r="D100" s="15"/>
-      <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="15"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="15">
+        <f>2*(TRUNC((D99-0.1-0.23*2)/0.15,0)+1)</f>
+        <v>50</v>
+      </c>
+      <c r="D100" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="E100" s="3">
+        <f t="shared" si="17"/>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F100" s="3">
+        <f t="shared" si="14"/>
+        <v>18.518518518518519</v>
+      </c>
+      <c r="G100" s="3">
+        <f t="shared" si="15"/>
+        <v>1.8518518518518517E-2</v>
+      </c>
       <c r="H100" s="15"/>
       <c r="I100" s="15"/>
       <c r="J100" s="15"/>
@@ -10862,333 +10935,394 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="15"/>
-      <c r="B101" s="16" t="s">
-        <v>66</v>
+      <c r="B101" s="16" t="str">
+        <f>B68</f>
+        <v>-top roof</v>
       </c>
       <c r="C101" s="15">
-        <v>1</v>
+        <f>4*(TRUNC(((D102-0.1)/0.15),0)+1)</f>
+        <v>32</v>
       </c>
       <c r="D101" s="3">
-        <f>(18.5-0.75*2)/3.281</f>
-        <v>5.1813471502590671</v>
+        <f>D68</f>
+        <v>1.0149344711978054</v>
       </c>
       <c r="E101" s="3">
-        <f>(8.75+17.5-0.75*2)/3.281</f>
-        <v>7.5434318805242304</v>
-      </c>
-      <c r="F101" s="15"/>
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F101" s="3">
+        <f t="shared" si="14"/>
+        <v>20.048088319956651</v>
+      </c>
       <c r="G101" s="3">
-        <f>PRODUCT(C101:F101)</f>
-        <v>39.08513927732762</v>
+        <f t="shared" si="15"/>
+        <v>2.004808831995665E-2</v>
       </c>
       <c r="H101" s="15"/>
       <c r="I101" s="15"/>
       <c r="J101" s="15"/>
       <c r="K101" s="15"/>
     </row>
-    <row r="102" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="17"/>
-      <c r="B102" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" s="19"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="20"/>
-      <c r="F102" s="20"/>
-      <c r="G102" s="2">
-        <f>SUM(G101)</f>
-        <v>39.08513927732762</v>
-      </c>
-      <c r="H102" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I102" s="2">
-        <v>689.98</v>
-      </c>
-      <c r="J102" s="22">
-        <f>G102*I102</f>
-        <v>26967.964398570512</v>
-      </c>
-      <c r="K102" s="20"/>
-    </row>
-    <row r="103" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="24"/>
-      <c r="B103" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C103" s="26"/>
-      <c r="D103" s="27"/>
-      <c r="E103" s="27"/>
-      <c r="F103" s="27"/>
-      <c r="G103" s="27"/>
-      <c r="H103" s="26"/>
-      <c r="I103" s="26"/>
-      <c r="J103" s="22">
-        <f>0.13*G102*1694.03/10</f>
-        <v>860.74818036962699</v>
-      </c>
-      <c r="K103" s="26"/>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="15"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="15">
+        <f>4*(TRUNC(((D101-0.1)/0.15),0)+1)</f>
+        <v>28</v>
+      </c>
+      <c r="D102" s="3">
+        <f>E68</f>
+        <v>1.2191405059433098</v>
+      </c>
+      <c r="E102" s="3">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F102" s="3">
+        <f t="shared" si="14"/>
+        <v>21.071564300254735</v>
+      </c>
+      <c r="G102" s="3">
+        <f t="shared" si="15"/>
+        <v>2.1071564300254735E-2</v>
+      </c>
+      <c r="H102" s="15"/>
+      <c r="I102" s="15"/>
+      <c r="J102" s="15"/>
+      <c r="K102" s="15"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="15"/>
+      <c r="B103" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C103" s="15">
+        <f>2*(TRUNC((D104-0.1)/0.15,0)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="D103" s="3">
+        <f>(8+1.75+1.75-0.333)/3.281</f>
+        <v>3.4035355074672355</v>
+      </c>
+      <c r="E103" s="3">
+        <f>10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F103" s="3">
+        <f t="shared" si="14"/>
+        <v>12.605687064693464</v>
+      </c>
+      <c r="G103" s="3">
+        <f t="shared" si="15"/>
+        <v>1.2605687064693465E-2</v>
+      </c>
+      <c r="H103" s="15"/>
+      <c r="I103" s="15"/>
+      <c r="J103" s="15"/>
+      <c r="K103" s="15"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="15"/>
-      <c r="B104" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C104" s="26"/>
-      <c r="D104" s="27"/>
-      <c r="E104" s="27"/>
-      <c r="F104" s="27"/>
-      <c r="G104" s="27"/>
-      <c r="H104" s="26"/>
-      <c r="I104" s="26"/>
-      <c r="J104" s="22">
-        <f>0.13*G102*472.02/10</f>
-        <v>239.83657674189439</v>
-      </c>
+      <c r="B104" s="16"/>
+      <c r="C104" s="15">
+        <f>2*(TRUNC((D103-0.1-0.23*2)/0.15,0)+1)</f>
+        <v>38</v>
+      </c>
+      <c r="D104" s="3">
+        <f>1.75/3.281</f>
+        <v>0.53337397135019804</v>
+      </c>
+      <c r="E104" s="3">
+        <f t="shared" ref="E104:E106" si="18">10*10/162</f>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F104" s="3">
+        <f t="shared" si="14"/>
+        <v>12.51124130327625</v>
+      </c>
+      <c r="G104" s="3">
+        <f t="shared" si="15"/>
+        <v>1.2511241303276251E-2</v>
+      </c>
+      <c r="H104" s="15"/>
+      <c r="I104" s="15"/>
+      <c r="J104" s="15"/>
       <c r="K104" s="15"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="15"/>
-      <c r="B105" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C105" s="26"/>
-      <c r="D105" s="27"/>
-      <c r="E105" s="27"/>
-      <c r="F105" s="27"/>
-      <c r="G105" s="27"/>
-      <c r="H105" s="26"/>
-      <c r="I105" s="26"/>
-      <c r="J105" s="22">
-        <f>0.13*G102*1207.6/10</f>
-        <v>613.58978448691084</v>
-      </c>
+      <c r="B105" s="16"/>
+      <c r="C105" s="15">
+        <f>2*(TRUNC((D106-0.1)/0.15,0)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="D105" s="3">
+        <f>(8-0.33)/3.281</f>
+        <v>2.3377019201462965</v>
+      </c>
+      <c r="E105" s="3">
+        <f t="shared" si="18"/>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F105" s="3">
+        <f t="shared" si="14"/>
+        <v>8.6581552598010987</v>
+      </c>
+      <c r="G105" s="3">
+        <f t="shared" si="15"/>
+        <v>8.658155259801098E-3</v>
+      </c>
+      <c r="H105" s="15"/>
+      <c r="I105" s="15"/>
+      <c r="J105" s="15"/>
       <c r="K105" s="15"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="15"/>
-      <c r="B106" s="15"/>
-      <c r="C106" s="15"/>
-      <c r="D106" s="15"/>
-      <c r="E106" s="15"/>
-      <c r="F106" s="15"/>
-      <c r="G106" s="15"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="15">
+        <f>2*(TRUNC((D105-0.1-0.23*2)/0.15,0)+1)</f>
+        <v>24</v>
+      </c>
+      <c r="D106" s="3">
+        <f>1.75/3.281</f>
+        <v>0.53337397135019804</v>
+      </c>
+      <c r="E106" s="3">
+        <f t="shared" si="18"/>
+        <v>0.61728395061728392</v>
+      </c>
+      <c r="F106" s="3">
+        <f t="shared" si="14"/>
+        <v>7.9018366125955257</v>
+      </c>
+      <c r="G106" s="3">
+        <f t="shared" si="15"/>
+        <v>7.9018366125955253E-3</v>
+      </c>
       <c r="H106" s="15"/>
       <c r="I106" s="15"/>
       <c r="J106" s="15"/>
       <c r="K106" s="15"/>
     </row>
-    <row r="107" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A107" s="11">
-        <v>8</v>
-      </c>
-      <c r="B107" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C107" s="15"/>
-      <c r="D107" s="15"/>
-      <c r="E107" s="15"/>
-      <c r="F107" s="15"/>
-      <c r="G107" s="15"/>
-      <c r="H107" s="15"/>
-      <c r="I107" s="15"/>
-      <c r="J107" s="15"/>
-      <c r="K107" s="15"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="15"/>
-      <c r="B108" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C108" s="45">
-        <f>2*2</f>
-        <v>4</v>
-      </c>
-      <c r="D108" s="3">
-        <f>D125</f>
-        <v>5.6385248399878085</v>
-      </c>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3">
-        <f>F125</f>
-        <v>2.2858884486437061</v>
-      </c>
-      <c r="G108" s="3">
-        <f>PRODUCT(C108:F108)</f>
-        <v>51.556155196474933</v>
-      </c>
-      <c r="H108" s="15"/>
-      <c r="I108" s="15"/>
-      <c r="J108" s="15"/>
-      <c r="K108" s="15"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="15"/>
-      <c r="B109" s="16"/>
-      <c r="C109" s="45">
-        <f>2*C126</f>
-        <v>4</v>
-      </c>
-      <c r="D109" s="3">
-        <f>D126</f>
-        <v>8.0006095702529709</v>
-      </c>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3">
-        <f>F126</f>
-        <v>2.2858884486437061</v>
-      </c>
-      <c r="G109" s="3">
-        <f>PRODUCT(C109:F109)</f>
-        <v>73.154003994998206</v>
-      </c>
-      <c r="H109" s="15"/>
-      <c r="I109" s="15"/>
-      <c r="J109" s="15"/>
-      <c r="K109" s="15"/>
+    <row r="107" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="17"/>
+      <c r="B107" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" s="19"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="20"/>
+      <c r="F107" s="20"/>
+      <c r="G107" s="2">
+        <f>SUM(G78:G106)</f>
+        <v>1.1372753795477895</v>
+      </c>
+      <c r="H107" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I107" s="46">
+        <v>132360</v>
+      </c>
+      <c r="J107" s="76">
+        <f>G107*I107</f>
+        <v>150529.7692369454</v>
+      </c>
+      <c r="K107" s="20"/>
+    </row>
+    <row r="108" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="24"/>
+      <c r="B108" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C108" s="26"/>
+      <c r="D108" s="26"/>
+      <c r="E108" s="26"/>
+      <c r="F108" s="26"/>
+      <c r="G108" s="26"/>
+      <c r="H108" s="26"/>
+      <c r="I108" s="26"/>
+      <c r="J108" s="22">
+        <f>0.13*G107*105000</f>
+        <v>15523.808930827327</v>
+      </c>
+      <c r="K108" s="26"/>
+    </row>
+    <row r="109" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="24"/>
+      <c r="B109" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C109" s="26"/>
+      <c r="D109" s="26"/>
+      <c r="E109" s="26"/>
+      <c r="F109" s="26"/>
+      <c r="G109" s="26"/>
+      <c r="H109" s="26"/>
+      <c r="I109" s="26"/>
+      <c r="J109" s="22">
+        <f>0.13*G107*1200</f>
+        <v>177.41495920945516</v>
+      </c>
+      <c r="K109" s="26"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="15"/>
-      <c r="B110" s="16" t="str">
-        <f>B128</f>
-        <v>-deduction for window</v>
-      </c>
-      <c r="C110" s="45">
-        <f>2*C128</f>
-        <v>-4</v>
-      </c>
-      <c r="D110" s="3">
-        <f t="shared" ref="D110:D111" si="17">D128</f>
-        <v>1.8</v>
-      </c>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3">
-        <f t="shared" ref="F110:F111" si="18">F128</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G110" s="3">
-        <f t="shared" ref="G110:G111" si="19">PRODUCT(C110:F110)</f>
-        <v>-9.875038098140811</v>
-      </c>
+      <c r="B110" s="15"/>
+      <c r="C110" s="15"/>
+      <c r="D110" s="15"/>
+      <c r="E110" s="15"/>
+      <c r="F110" s="15"/>
+      <c r="G110" s="15"/>
       <c r="H110" s="15"/>
       <c r="I110" s="15"/>
       <c r="J110" s="15"/>
       <c r="K110" s="15"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="15"/>
-      <c r="B111" s="16" t="str">
-        <f>B129</f>
-        <v>-deduction for chain gate</v>
-      </c>
-      <c r="C111" s="45">
-        <f>2*C129</f>
-        <v>-2</v>
-      </c>
-      <c r="D111" s="3">
-        <f t="shared" si="17"/>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3">
-        <f t="shared" si="18"/>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G111" s="3">
-        <f t="shared" si="19"/>
-        <v>-6.6883660795426936</v>
-      </c>
+    <row r="111" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A111" s="11">
+        <v>8</v>
+      </c>
+      <c r="B111" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C111" s="15"/>
+      <c r="D111" s="15"/>
+      <c r="E111" s="15"/>
+      <c r="F111" s="15"/>
+      <c r="G111" s="15"/>
       <c r="H111" s="15"/>
       <c r="I111" s="15"/>
       <c r="J111" s="15"/>
       <c r="K111" s="15"/>
     </row>
-    <row r="112" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="17"/>
-      <c r="B112" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" s="19"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="20"/>
-      <c r="F112" s="20"/>
-      <c r="G112" s="2">
-        <f>SUM(G108:G111)</f>
-        <v>108.14675501378964</v>
-      </c>
-      <c r="H112" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I112" s="2">
-        <v>415.5</v>
-      </c>
-      <c r="J112" s="22">
-        <f>G112*I112</f>
-        <v>44934.976708229595</v>
-      </c>
-      <c r="K112" s="20"/>
-    </row>
-    <row r="113" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="24"/>
-      <c r="B113" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C113" s="26"/>
-      <c r="D113" s="27"/>
-      <c r="E113" s="27"/>
-      <c r="F113" s="27"/>
-      <c r="G113" s="27"/>
-      <c r="H113" s="26"/>
-      <c r="I113" s="26"/>
-      <c r="J113" s="22">
-        <f>0.13*G112*7010.67/100</f>
-        <v>985.63557426428201</v>
-      </c>
-      <c r="K113" s="26"/>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="15"/>
+      <c r="B112" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C112" s="45">
+        <f>2*2</f>
+        <v>4</v>
+      </c>
+      <c r="D112" s="3">
+        <f>0.35*4</f>
+        <v>1.4</v>
+      </c>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3">
+        <f>Sheet1!Q4-Sheet1!W4</f>
+        <v>2.7222340749771408</v>
+      </c>
+      <c r="G112" s="3">
+        <f>PRODUCT(C112:F112)</f>
+        <v>15.244510819871987</v>
+      </c>
+      <c r="H112" s="15"/>
+      <c r="I112" s="15"/>
+      <c r="J112" s="15"/>
+      <c r="K112" s="15"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="15"/>
+      <c r="B113" s="16" t="str">
+        <f>B62</f>
+        <v>-for column over support beam</v>
+      </c>
+      <c r="C113" s="45">
+        <v>4</v>
+      </c>
+      <c r="D113" s="3">
+        <f>0.23*4</f>
+        <v>0.92</v>
+      </c>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3">
+        <f>3/3.281</f>
+        <v>0.91435537945748246</v>
+      </c>
+      <c r="G113" s="3">
+        <f>PRODUCT(C113:F113)</f>
+        <v>3.3648277964035356</v>
+      </c>
+      <c r="H113" s="15"/>
+      <c r="I113" s="15"/>
+      <c r="J113" s="15"/>
+      <c r="K113" s="15"/>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="15"/>
-      <c r="B114" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C114" s="26"/>
-      <c r="D114" s="27"/>
-      <c r="E114" s="27"/>
-      <c r="F114" s="27"/>
-      <c r="G114" s="27"/>
-      <c r="H114" s="26"/>
-      <c r="I114" s="26"/>
-      <c r="J114" s="22">
-        <f>0.13*G112*4639.73/100</f>
-        <v>652.30326673216928</v>
-      </c>
+      <c r="B114" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C114" s="45">
+        <v>4</v>
+      </c>
+      <c r="D114" s="3">
+        <f>(14-1.17*2)/3.281</f>
+        <v>3.5537945748247486</v>
+      </c>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3">
+        <f>0.23*3</f>
+        <v>0.69000000000000006</v>
+      </c>
+      <c r="G114" s="3">
+        <f>PRODUCT(C114:F114)</f>
+        <v>9.8084730265163067</v>
+      </c>
+      <c r="H114" s="15"/>
+      <c r="I114" s="15"/>
+      <c r="J114" s="15"/>
       <c r="K114" s="15"/>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="15"/>
-      <c r="B115" s="15"/>
-      <c r="C115" s="15"/>
-      <c r="D115" s="15"/>
-      <c r="E115" s="15"/>
-      <c r="F115" s="15"/>
-      <c r="G115" s="15"/>
+      <c r="B115" s="16"/>
+      <c r="C115" s="45">
+        <v>2</v>
+      </c>
+      <c r="D115" s="3">
+        <f>(14-1.17*2)/3.281</f>
+        <v>3.5537945748247486</v>
+      </c>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3">
+        <f>0.23*3</f>
+        <v>0.69000000000000006</v>
+      </c>
+      <c r="G115" s="3">
+        <f>PRODUCT(C115:F115)</f>
+        <v>4.9042365132581534</v>
+      </c>
       <c r="H115" s="15"/>
       <c r="I115" s="15"/>
       <c r="J115" s="15"/>
       <c r="K115" s="15"/>
     </row>
-    <row r="116" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="11">
-        <v>9</v>
-      </c>
-      <c r="B116" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C116" s="15"/>
-      <c r="D116" s="15"/>
-      <c r="E116" s="15"/>
-      <c r="F116" s="15"/>
-      <c r="G116" s="15"/>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="15"/>
+      <c r="B116" s="16" t="str">
+        <f>B67</f>
+        <v>-beam for top roof inclined support</v>
+      </c>
+      <c r="C116" s="45">
+        <v>4</v>
+      </c>
+      <c r="D116" s="3">
+        <f>6.5/3.281</f>
+        <v>1.9811033221578787</v>
+      </c>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3">
+        <f>0.23*3</f>
+        <v>0.69000000000000006</v>
+      </c>
+      <c r="G116" s="3">
+        <f>PRODUCT(C116:F116)</f>
+        <v>5.4678451691557459</v>
+      </c>
       <c r="H116" s="15"/>
       <c r="I116" s="15"/>
       <c r="J116" s="15"/>
@@ -11197,257 +11331,251 @@
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="15"/>
       <c r="B117" s="16" t="str">
-        <f>B101</f>
-        <v>-for flooring at existing paati</v>
-      </c>
-      <c r="C117" s="15">
-        <f>C101</f>
-        <v>1</v>
+        <f>B41</f>
+        <v>-for inclined slab</v>
+      </c>
+      <c r="C117" s="45">
+        <f>C41</f>
+        <v>4</v>
       </c>
       <c r="D117" s="3">
-        <f>D101</f>
-        <v>5.1813471502590671</v>
+        <f t="shared" ref="D117:E117" si="19">D41</f>
+        <v>3.0859494056690031</v>
       </c>
       <c r="E117" s="3">
-        <f>E101</f>
-        <v>7.5434318805242304</v>
-      </c>
-      <c r="F117" s="15"/>
+        <f t="shared" si="19"/>
+        <v>0.91435537945748246</v>
+      </c>
+      <c r="F117" s="45"/>
       <c r="G117" s="3">
-        <f>PRODUCT(C117:F117)</f>
-        <v>39.08513927732762</v>
+        <f t="shared" ref="G117:G122" si="20">PRODUCT(C117:F117)</f>
+        <v>11.286617759228296</v>
       </c>
       <c r="H117" s="15"/>
       <c r="I117" s="15"/>
       <c r="J117" s="15"/>
       <c r="K117" s="15"/>
     </row>
-    <row r="118" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="17"/>
-      <c r="B118" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" s="19"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="20"/>
-      <c r="F118" s="20"/>
-      <c r="G118" s="2">
-        <f>SUM(G117:G117)</f>
-        <v>39.08513927732762</v>
-      </c>
-      <c r="H118" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I118" s="2">
-        <v>415.5</v>
-      </c>
-      <c r="J118" s="22">
-        <f>G118*I118</f>
-        <v>16239.875369729627</v>
-      </c>
-      <c r="K118" s="20"/>
-    </row>
-    <row r="119" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="24"/>
-      <c r="B119" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C119" s="26"/>
-      <c r="D119" s="27"/>
-      <c r="E119" s="27"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="27"/>
-      <c r="H119" s="26"/>
-      <c r="I119" s="26"/>
-      <c r="J119" s="22">
-        <f>0.13*G118*7010.67/100</f>
-        <v>356.21691739059713</v>
-      </c>
-      <c r="K119" s="26"/>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="15"/>
+      <c r="B118" s="16" t="str">
+        <f>B42</f>
+        <v>-for cantilever</v>
+      </c>
+      <c r="C118" s="78">
+        <f t="shared" ref="C118:E119" si="21">C42</f>
+        <v>2</v>
+      </c>
+      <c r="D118" s="77">
+        <f t="shared" si="21"/>
+        <v>4.2669917708015843</v>
+      </c>
+      <c r="E118" s="77">
+        <f t="shared" si="21"/>
+        <v>0.6</v>
+      </c>
+      <c r="F118" s="77"/>
+      <c r="G118" s="3">
+        <f t="shared" si="20"/>
+        <v>5.1203901249619008</v>
+      </c>
+      <c r="H118" s="15"/>
+      <c r="I118" s="15"/>
+      <c r="J118" s="15"/>
+      <c r="K118" s="15"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="15"/>
+      <c r="B119" s="16"/>
+      <c r="C119" s="78">
+        <f t="shared" si="21"/>
+        <v>2</v>
+      </c>
+      <c r="D119" s="77">
+        <f t="shared" si="21"/>
+        <v>5.4669917708015845</v>
+      </c>
+      <c r="E119" s="77">
+        <f t="shared" si="21"/>
+        <v>0.6</v>
+      </c>
+      <c r="F119" s="77"/>
+      <c r="G119" s="3">
+        <f t="shared" si="20"/>
+        <v>6.5603901249619012</v>
+      </c>
+      <c r="H119" s="15"/>
+      <c r="I119" s="15"/>
+      <c r="J119" s="15"/>
+      <c r="K119" s="15"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="15"/>
-      <c r="B120" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C120" s="26"/>
-      <c r="D120" s="27"/>
-      <c r="E120" s="27"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="27"/>
-      <c r="H120" s="26"/>
-      <c r="I120" s="26"/>
-      <c r="J120" s="22">
-        <f>0.13*G118*4639.73/100</f>
-        <v>235.74784123695386</v>
-      </c>
+      <c r="B120" s="16" t="str">
+        <f>B45</f>
+        <v>-top roof</v>
+      </c>
+      <c r="C120" s="78">
+        <f t="shared" ref="C120:E120" si="22">C45</f>
+        <v>4</v>
+      </c>
+      <c r="D120" s="77">
+        <f t="shared" si="22"/>
+        <v>1.0149344711978054</v>
+      </c>
+      <c r="E120" s="77">
+        <f t="shared" si="22"/>
+        <v>1.2191405059433098</v>
+      </c>
+      <c r="F120" s="77"/>
+      <c r="G120" s="3">
+        <f t="shared" si="20"/>
+        <v>4.9493908988615924</v>
+      </c>
+      <c r="H120" s="15"/>
+      <c r="I120" s="15"/>
+      <c r="J120" s="15"/>
       <c r="K120" s="15"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="15"/>
-      <c r="B121" s="15"/>
-      <c r="C121" s="15"/>
-      <c r="D121" s="15"/>
-      <c r="E121" s="15"/>
-      <c r="F121" s="15"/>
-      <c r="G121" s="15"/>
+      <c r="B121" s="16" t="str">
+        <f t="shared" ref="B121:E121" si="23">B46</f>
+        <v>-for cantilever</v>
+      </c>
+      <c r="C121" s="78">
+        <f t="shared" si="23"/>
+        <v>2</v>
+      </c>
+      <c r="D121" s="77">
+        <f t="shared" si="23"/>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E121" s="77">
+        <f t="shared" si="23"/>
+        <v>0.53337397135019804</v>
+      </c>
+      <c r="F121" s="77"/>
+      <c r="G121" s="3">
+        <f t="shared" si="20"/>
+        <v>3.7389824264110194</v>
+      </c>
       <c r="H121" s="15"/>
       <c r="I121" s="15"/>
       <c r="J121" s="15"/>
       <c r="K121" s="15"/>
     </row>
-    <row r="122" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="11">
-        <v>10</v>
-      </c>
-      <c r="B122" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C122" s="15"/>
-      <c r="D122" s="15"/>
-      <c r="E122" s="15"/>
-      <c r="F122" s="15"/>
-      <c r="G122" s="15"/>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="15"/>
+      <c r="B122" s="16"/>
+      <c r="C122" s="78">
+        <f t="shared" ref="C122:E122" si="24">C47</f>
+        <v>2</v>
+      </c>
+      <c r="D122" s="77">
+        <f t="shared" si="24"/>
+        <v>2.4382810118866196</v>
+      </c>
+      <c r="E122" s="77">
+        <f t="shared" si="24"/>
+        <v>0.53337397135019804</v>
+      </c>
+      <c r="F122" s="77"/>
+      <c r="G122" s="3">
+        <f t="shared" si="20"/>
+        <v>2.6010312531554916</v>
+      </c>
       <c r="H122" s="15"/>
       <c r="I122" s="15"/>
       <c r="J122" s="15"/>
       <c r="K122" s="15"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="15"/>
-      <c r="B123" s="47" t="str">
-        <f>B35</f>
-        <v>-for tie beam</v>
-      </c>
-      <c r="C123" s="48">
-        <f>C35</f>
-        <v>4</v>
-      </c>
-      <c r="D123" s="48">
-        <f>D35</f>
-        <v>3.5669917708015841</v>
-      </c>
-      <c r="E123" s="48">
-        <v>0.23</v>
-      </c>
-      <c r="F123" s="48">
-        <v>1.2</v>
-      </c>
-      <c r="G123" s="48">
-        <f t="shared" ref="G123:G129" si="20">PRODUCT(C123:F123)</f>
-        <v>3.9379589149649492</v>
-      </c>
-      <c r="H123" s="15"/>
-      <c r="I123" s="15"/>
-      <c r="J123" s="15"/>
-      <c r="K123" s="15"/>
-      <c r="M123">
-        <f>7.833/3.281</f>
-        <v>2.3873818957634869</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="15"/>
-      <c r="B124" s="47"/>
-      <c r="C124" s="48">
-        <v>4</v>
-      </c>
-      <c r="D124" s="48">
-        <f>(1.917/3.281)*2</f>
-        <v>1.1685461749466626</v>
-      </c>
-      <c r="E124" s="48">
-        <v>0.23</v>
-      </c>
-      <c r="F124" s="48">
-        <f>0.6-0.075-0.055</f>
-        <v>0.47000000000000003</v>
-      </c>
-      <c r="G124" s="48">
-        <f>PRODUCT(C124:F124)</f>
-        <v>0.50527936604693702</v>
-      </c>
-      <c r="H124" s="15"/>
-      <c r="I124" s="15"/>
-      <c r="J124" s="15"/>
-      <c r="K124" s="15"/>
+    <row r="123" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="17"/>
+      <c r="B123" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" s="19"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="20"/>
+      <c r="F123" s="20"/>
+      <c r="G123" s="2">
+        <f>SUM(G112:G122)</f>
+        <v>73.046695912785921</v>
+      </c>
+      <c r="H123" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I123" s="2">
+        <v>415.5</v>
+      </c>
+      <c r="J123" s="22">
+        <f>G123*I123</f>
+        <v>30350.902151762552</v>
+      </c>
+      <c r="K123" s="20"/>
+    </row>
+    <row r="124" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="24"/>
+      <c r="B124" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C124" s="26"/>
+      <c r="D124" s="27"/>
+      <c r="E124" s="27"/>
+      <c r="F124" s="27"/>
+      <c r="G124" s="27"/>
+      <c r="H124" s="26"/>
+      <c r="I124" s="26"/>
+      <c r="J124" s="22">
+        <f>0.13*G123*7010.67/100</f>
+        <v>665.73816352535812</v>
+      </c>
+      <c r="K124" s="26"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="15"/>
-      <c r="B125" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C125" s="3">
-        <v>2</v>
-      </c>
-      <c r="D125" s="3">
-        <f>18.5/3.281</f>
-        <v>5.6385248399878085</v>
-      </c>
-      <c r="E125" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F125" s="3">
-        <f>7.5/3.281</f>
-        <v>2.2858884486437061</v>
-      </c>
-      <c r="G125" s="3">
-        <f t="shared" si="20"/>
-        <v>5.9289578475946181</v>
-      </c>
-      <c r="H125" s="15"/>
-      <c r="I125" s="15"/>
-      <c r="J125" s="15"/>
+      <c r="B125" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C125" s="26"/>
+      <c r="D125" s="27"/>
+      <c r="E125" s="27"/>
+      <c r="F125" s="27"/>
+      <c r="G125" s="27"/>
+      <c r="H125" s="26"/>
+      <c r="I125" s="26"/>
+      <c r="J125" s="51">
+        <f>0.13*G123*4639.73/100</f>
+        <v>440.59203035565923</v>
+      </c>
       <c r="K125" s="15"/>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="15"/>
-      <c r="B126" s="16"/>
-      <c r="C126" s="3">
-        <v>2</v>
-      </c>
-      <c r="D126" s="3">
-        <f>(8.75+17.5)/3.281</f>
-        <v>8.0006095702529709</v>
-      </c>
-      <c r="E126" s="3">
-        <v>0.23</v>
-      </c>
-      <c r="F126" s="3">
-        <f>7.5/3.281</f>
-        <v>2.2858884486437061</v>
-      </c>
-      <c r="G126" s="3">
-        <f t="shared" si="20"/>
-        <v>8.4127104594247939</v>
-      </c>
+      <c r="B126" s="15"/>
+      <c r="C126" s="15"/>
+      <c r="D126" s="15"/>
+      <c r="E126" s="15"/>
+      <c r="F126" s="15"/>
+      <c r="G126" s="15"/>
       <c r="H126" s="15"/>
       <c r="I126" s="15"/>
       <c r="J126" s="15"/>
       <c r="K126" s="15"/>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="15"/>
-      <c r="B127" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C127" s="3">
-        <v>1</v>
-      </c>
-      <c r="D127" s="3">
-        <f>D126</f>
-        <v>8.0006095702529709</v>
-      </c>
-      <c r="E127" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="F127" s="3">
-        <v>0.45</v>
-      </c>
-      <c r="G127" s="3">
-        <f t="shared" si="20"/>
-        <v>1.0800822919841511</v>
-      </c>
+    <row r="127" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A127" s="11">
+        <v>10</v>
+      </c>
+      <c r="B127" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C127" s="15"/>
+      <c r="D127" s="15"/>
+      <c r="E127" s="15"/>
+      <c r="F127" s="15"/>
+      <c r="G127" s="15"/>
       <c r="H127" s="15"/>
       <c r="I127" s="15"/>
       <c r="J127" s="15"/>
@@ -11455,61 +11583,64 @@
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="15"/>
-      <c r="B128" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C128" s="3">
-        <v>-2</v>
-      </c>
-      <c r="D128" s="3">
-        <f>1.8</f>
-        <v>1.8</v>
-      </c>
-      <c r="E128" s="3">
+      <c r="B128" s="47" t="str">
+        <f>B35</f>
+        <v>-for tie beam</v>
+      </c>
+      <c r="C128" s="48">
+        <f>C35</f>
+        <v>4</v>
+      </c>
+      <c r="D128" s="48">
+        <f>(1.917/3.281)*2</f>
+        <v>1.1685461749466626</v>
+      </c>
+      <c r="E128" s="48">
         <v>0.23</v>
       </c>
-      <c r="F128" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G128" s="3">
-        <f t="shared" si="20"/>
-        <v>-1.1356293812861933</v>
+      <c r="F128" s="48">
+        <v>1.2</v>
+      </c>
+      <c r="G128" s="48">
+        <f t="shared" ref="G128" si="25">PRODUCT(C128:F128)</f>
+        <v>1.2900749771411155</v>
       </c>
       <c r="H128" s="15"/>
       <c r="I128" s="15"/>
       <c r="J128" s="15"/>
       <c r="K128" s="15"/>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M128">
+        <f>7.833/3.281</f>
+        <v>2.3873818957634869</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="15"/>
-      <c r="B129" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C129" s="3">
-        <v>-1</v>
-      </c>
-      <c r="D129" s="3">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E129" s="3">
+      <c r="B129" s="47"/>
+      <c r="C129" s="48">
+        <v>4</v>
+      </c>
+      <c r="D129" s="48">
+        <f>7.833/3.281</f>
+        <v>2.3873818957634869</v>
+      </c>
+      <c r="E129" s="48">
         <v>0.23</v>
       </c>
-      <c r="F129" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G129" s="3">
-        <f t="shared" si="20"/>
-        <v>-0.76916209914740985</v>
+      <c r="F129" s="48">
+        <f>0.6-0.075-0.055</f>
+        <v>0.47000000000000003</v>
+      </c>
+      <c r="G129" s="48">
+        <f>PRODUCT(C129:F129)</f>
+        <v>1.032303931728132</v>
       </c>
       <c r="H129" s="15"/>
       <c r="I129" s="15"/>
       <c r="J129" s="15"/>
       <c r="K129" s="15"/>
     </row>
-    <row r="130" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="17"/>
       <c r="B130" s="18" t="s">
         <v>16</v>
@@ -11519,8 +11650,8 @@
       <c r="E130" s="20"/>
       <c r="F130" s="20"/>
       <c r="G130" s="2">
-        <f>SUM(G123:G129)</f>
-        <v>17.960197399581848</v>
+        <f>SUM(G128:G129)</f>
+        <v>2.3223789088692475</v>
       </c>
       <c r="H130" s="21" t="s">
         <v>28</v>
@@ -11531,11 +11662,11 @@
       </c>
       <c r="J130" s="22">
         <f>G130*I130</f>
-        <v>260276.30708315619</v>
+        <v>33655.543566707718</v>
       </c>
       <c r="K130" s="20"/>
     </row>
-    <row r="131" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="24"/>
       <c r="B131" s="25" t="s">
         <v>55</v>
@@ -11549,11 +11680,11 @@
       <c r="I131" s="26"/>
       <c r="J131" s="22">
         <f>0.13*G130*8481.2</f>
-        <v>19802.123404093367</v>
+        <v>2560.5528002472424</v>
       </c>
       <c r="K131" s="26"/>
     </row>
-    <row r="132" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="24"/>
       <c r="B132" s="25" t="s">
         <v>32</v>
@@ -11567,11 +11698,11 @@
       <c r="I132" s="26"/>
       <c r="J132" s="22">
         <f>0.13*G130*912.17</f>
-        <v>2129.7579240569548</v>
+        <v>275.392568009424</v>
       </c>
       <c r="K132" s="26"/>
     </row>
-    <row r="133" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="24"/>
       <c r="B133" s="25" t="s">
         <v>64</v>
@@ -11585,11 +11716,11 @@
       <c r="I133" s="26"/>
       <c r="J133" s="22">
         <f>0.13*G130*953.37</f>
-        <v>2225.9527413291153</v>
+        <v>287.83122944532766</v>
       </c>
       <c r="K133" s="26"/>
     </row>
-    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="24"/>
       <c r="B134" s="25" t="s">
         <v>36</v>
@@ -11603,147 +11734,139 @@
       <c r="I134" s="26"/>
       <c r="J134" s="22">
         <f>0.13*G130*28</f>
-        <v>65.375118534477934</v>
+        <v>8.4534592282840606</v>
       </c>
       <c r="K134" s="26"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" s="15"/>
-      <c r="B135" s="15"/>
-      <c r="C135" s="15"/>
-      <c r="D135" s="15"/>
-      <c r="E135" s="15"/>
-      <c r="F135" s="15"/>
-      <c r="G135" s="15"/>
-      <c r="H135" s="15"/>
-      <c r="I135" s="15"/>
-      <c r="J135" s="15"/>
-      <c r="K135" s="15"/>
-    </row>
-    <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A136" s="11">
-        <v>11</v>
+    <row r="135" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="24"/>
+      <c r="B135" s="25"/>
+      <c r="C135" s="26"/>
+      <c r="D135" s="27"/>
+      <c r="E135" s="27"/>
+      <c r="F135" s="27"/>
+      <c r="G135" s="27"/>
+      <c r="H135" s="26"/>
+      <c r="I135" s="26"/>
+      <c r="J135" s="22"/>
+      <c r="K135" s="26"/>
+    </row>
+    <row r="136" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A136" s="24">
+        <v>10</v>
       </c>
       <c r="B136" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="C136" s="15"/>
-      <c r="D136" s="15"/>
-      <c r="E136" s="15"/>
-      <c r="F136" s="15"/>
-      <c r="G136" s="15"/>
-      <c r="H136" s="15"/>
-      <c r="I136" s="15"/>
-      <c r="J136" s="15"/>
+        <v>112</v>
+      </c>
+      <c r="C136" s="26"/>
+      <c r="D136" s="26"/>
+      <c r="E136" s="26"/>
+      <c r="F136" s="26"/>
+      <c r="G136" s="26"/>
+      <c r="H136" s="26"/>
+      <c r="I136" s="26"/>
+      <c r="J136" s="26"/>
       <c r="K136" s="15"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" s="15"/>
-      <c r="B137" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C137" s="3">
-        <f>C108</f>
-        <v>4</v>
-      </c>
-      <c r="D137" s="3">
-        <f>18.5/3.281</f>
-        <v>5.6385248399878085</v>
-      </c>
-      <c r="E137" s="3"/>
-      <c r="F137" s="3">
-        <f>F108</f>
-        <v>2.2858884486437061</v>
-      </c>
-      <c r="G137" s="3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" s="26"/>
+      <c r="B137" s="25" t="str">
+        <f>B118</f>
+        <v>-for cantilever</v>
+      </c>
+      <c r="C137" s="79">
+        <f t="shared" ref="C137" si="26">C118</f>
+        <v>2</v>
+      </c>
+      <c r="D137" s="80">
+        <f>Sheet1!H4+0.6*2</f>
+        <v>5.4669917708015845</v>
+      </c>
+      <c r="E137" s="80"/>
+      <c r="F137" s="80"/>
+      <c r="G137" s="27">
         <f>PRODUCT(C137:F137)</f>
-        <v>51.556155196474933</v>
-      </c>
-      <c r="H137" s="15"/>
-      <c r="I137" s="15"/>
-      <c r="J137" s="15"/>
+        <v>10.933983541603169</v>
+      </c>
+      <c r="H137" s="26"/>
+      <c r="I137" s="26"/>
+      <c r="J137" s="26"/>
       <c r="K137" s="15"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" s="15"/>
-      <c r="B138" s="16"/>
-      <c r="C138" s="3">
-        <f>C109</f>
-        <v>4</v>
-      </c>
-      <c r="D138" s="3">
-        <f>(8.75+17.5)/3.281</f>
-        <v>8.0006095702529709</v>
-      </c>
-      <c r="E138" s="3"/>
-      <c r="F138" s="3">
-        <f>7.5/3.281</f>
-        <v>2.2858884486437061</v>
-      </c>
-      <c r="G138" s="3">
-        <f>PRODUCT(C138:F138)</f>
-        <v>73.154003994998206</v>
-      </c>
-      <c r="H138" s="15"/>
-      <c r="I138" s="15"/>
-      <c r="J138" s="15"/>
+      <c r="M137">
+        <f>7.833/3.281</f>
+        <v>2.3873818957634869</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" s="26"/>
+      <c r="B138" s="25"/>
+      <c r="C138" s="79">
+        <f t="shared" ref="C138" si="27">C119</f>
+        <v>2</v>
+      </c>
+      <c r="D138" s="80">
+        <f>Sheet1!H4+0.6*2</f>
+        <v>5.4669917708015845</v>
+      </c>
+      <c r="E138" s="80"/>
+      <c r="F138" s="80"/>
+      <c r="G138" s="27">
+        <f t="shared" ref="G138:G140" si="28">PRODUCT(C138:F138)</f>
+        <v>10.933983541603169</v>
+      </c>
+      <c r="H138" s="26"/>
+      <c r="I138" s="26"/>
+      <c r="J138" s="26"/>
       <c r="K138" s="15"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139" s="15"/>
-      <c r="B139" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C139" s="3">
-        <f>-2*2</f>
-        <v>-4</v>
-      </c>
-      <c r="D139" s="3">
-        <f>1.8</f>
-        <v>1.8</v>
-      </c>
-      <c r="E139" s="3"/>
-      <c r="F139" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G139" s="3">
-        <f>PRODUCT(C139:F139)</f>
-        <v>-9.875038098140811</v>
-      </c>
-      <c r="H139" s="15"/>
-      <c r="I139" s="15"/>
-      <c r="J139" s="15"/>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" s="26"/>
+      <c r="B139" s="25" t="str">
+        <f t="shared" ref="B139:C139" si="29">B121</f>
+        <v>-for cantilever</v>
+      </c>
+      <c r="C139" s="79">
+        <f t="shared" si="29"/>
+        <v>2</v>
+      </c>
+      <c r="D139" s="80">
+        <f>(8+1.75*2)/3.281</f>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E139" s="80"/>
+      <c r="F139" s="80"/>
+      <c r="G139" s="27">
+        <f t="shared" si="28"/>
+        <v>7.0100579091740318</v>
+      </c>
+      <c r="H139" s="26"/>
+      <c r="I139" s="26"/>
+      <c r="J139" s="26"/>
       <c r="K139" s="15"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A140" s="15"/>
-      <c r="B140" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C140" s="3">
-        <f>-1*2</f>
-        <v>-2</v>
-      </c>
-      <c r="D140" s="3">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E140" s="3"/>
-      <c r="F140" s="3">
-        <f>7/3.281</f>
-        <v>2.1334958854007922</v>
-      </c>
-      <c r="G140" s="3">
-        <f>PRODUCT(C140:F140)</f>
-        <v>-10.404125012621966</v>
-      </c>
-      <c r="H140" s="15"/>
-      <c r="I140" s="15"/>
-      <c r="J140" s="15"/>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" s="26"/>
+      <c r="B140" s="25"/>
+      <c r="C140" s="79">
+        <f t="shared" ref="C140" si="30">C122</f>
+        <v>2</v>
+      </c>
+      <c r="D140" s="80">
+        <f>(8+1.75*2)/3.281</f>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E140" s="80"/>
+      <c r="F140" s="80"/>
+      <c r="G140" s="27">
+        <f t="shared" si="28"/>
+        <v>7.0100579091740318</v>
+      </c>
+      <c r="H140" s="26"/>
+      <c r="I140" s="26"/>
+      <c r="J140" s="26"/>
       <c r="K140" s="15"/>
     </row>
-    <row r="141" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17"/>
       <c r="B141" s="18" t="s">
         <v>16</v>
@@ -11754,24 +11877,24 @@
       <c r="F141" s="20"/>
       <c r="G141" s="2">
         <f>SUM(G137:G140)</f>
-        <v>104.43099608071037</v>
+        <v>35.888082901554398</v>
       </c>
       <c r="H141" s="21" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I141" s="2">
-        <v>253.8</v>
+        <v>144.41</v>
       </c>
       <c r="J141" s="22">
         <f>G141*I141</f>
-        <v>26504.586805284292</v>
+        <v>5182.5980518134702</v>
       </c>
       <c r="K141" s="20"/>
     </row>
-    <row r="142" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="24"/>
       <c r="B142" s="25" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="C142" s="26"/>
       <c r="D142" s="27"/>
@@ -11781,15 +11904,15 @@
       <c r="H142" s="26"/>
       <c r="I142" s="26"/>
       <c r="J142" s="22">
-        <f>0.13*G141*2304/100</f>
-        <v>312.79171946094374</v>
+        <f>0.13*G141*91.21</f>
+        <v>425.53576538860091</v>
       </c>
       <c r="K142" s="26"/>
     </row>
-    <row r="143" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="24"/>
       <c r="B143" s="25" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="C143" s="26"/>
       <c r="D143" s="27"/>
@@ -11799,14 +11922,16 @@
       <c r="H143" s="26"/>
       <c r="I143" s="26"/>
       <c r="J143" s="22">
-        <f>0.13*G141*10432/100</f>
-        <v>1416.251396448162</v>
+        <f>0.13*G141*12.71</f>
+        <v>59.297879378238335</v>
       </c>
       <c r="K143" s="26"/>
     </row>
-    <row r="144" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="24"/>
-      <c r="B144" s="25"/>
+      <c r="B144" s="25" t="s">
+        <v>113</v>
+      </c>
       <c r="C144" s="26"/>
       <c r="D144" s="27"/>
       <c r="E144" s="27"/>
@@ -11814,410 +11939,222 @@
       <c r="G144" s="27"/>
       <c r="H144" s="26"/>
       <c r="I144" s="26"/>
-      <c r="J144" s="22"/>
+      <c r="J144" s="22">
+        <f>0.13*G141*0.02</f>
+        <v>9.3309015544041432E-2</v>
+      </c>
       <c r="K144" s="26"/>
     </row>
-    <row r="145" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A145" s="11">
-        <v>12</v>
-      </c>
-      <c r="B145" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C145" s="15"/>
-      <c r="D145" s="15"/>
-      <c r="E145" s="15"/>
-      <c r="F145" s="15"/>
-      <c r="G145" s="15"/>
-      <c r="H145" s="15"/>
-      <c r="I145" s="15"/>
-      <c r="J145" s="15"/>
-      <c r="K145" s="15"/>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" s="15"/>
-      <c r="B146" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C146" s="3"/>
-      <c r="D146" s="3"/>
-      <c r="E146" s="3"/>
-      <c r="F146" s="3"/>
-      <c r="G146" s="3"/>
-      <c r="H146" s="15"/>
-      <c r="I146" s="15"/>
-      <c r="J146" s="15"/>
-      <c r="K146" s="15"/>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" s="15"/>
-      <c r="B147" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C147" s="3">
+    <row r="145" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="24"/>
+      <c r="B145" s="25"/>
+      <c r="C145" s="26"/>
+      <c r="D145" s="27"/>
+      <c r="E145" s="27"/>
+      <c r="F145" s="27"/>
+      <c r="G145" s="27"/>
+      <c r="H145" s="26"/>
+      <c r="I145" s="26"/>
+      <c r="J145" s="22"/>
+      <c r="K145" s="26"/>
+    </row>
+    <row r="146" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="17">
+        <v>14</v>
+      </c>
+      <c r="B146" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C146" s="19">
         <v>1</v>
       </c>
-      <c r="D147" s="3">
-        <f>8/3.281</f>
-        <v>2.4382810118866196</v>
-      </c>
-      <c r="E147" s="3"/>
-      <c r="F147" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G147" s="3">
-        <f>PRODUCT(C147:F147)</f>
-        <v>3.3441830397713468</v>
-      </c>
-      <c r="H147" s="15"/>
-      <c r="I147" s="15"/>
-      <c r="J147" s="15"/>
-      <c r="K147" s="15"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="20"/>
+      <c r="F146" s="20"/>
+      <c r="G146" s="21">
+        <f t="shared" ref="G146" si="31">PRODUCT(C146:F146)</f>
+        <v>1</v>
+      </c>
+      <c r="H146" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I146" s="2">
+        <v>5000</v>
+      </c>
+      <c r="J146" s="21">
+        <f>G146*I146</f>
+        <v>5000</v>
+      </c>
+      <c r="K146" s="20"/>
+    </row>
+    <row r="147" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="17"/>
+      <c r="B147" s="31"/>
+      <c r="C147" s="19"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="20"/>
+      <c r="F147" s="20"/>
+      <c r="G147" s="2"/>
+      <c r="H147" s="21"/>
+      <c r="I147" s="2"/>
+      <c r="J147" s="22"/>
+      <c r="K147" s="20"/>
     </row>
     <row r="148" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="17"/>
-      <c r="B148" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" s="19"/>
+      <c r="A148" s="17">
+        <v>15</v>
+      </c>
+      <c r="B148" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C148" s="19">
+        <v>1</v>
+      </c>
       <c r="D148" s="1"/>
       <c r="E148" s="20"/>
       <c r="F148" s="20"/>
-      <c r="G148" s="2">
-        <f>SUM(G146:G147)</f>
-        <v>3.3441830397713468</v>
+      <c r="G148" s="21">
+        <f t="shared" ref="G148" si="32">PRODUCT(C148:F148)</f>
+        <v>1</v>
       </c>
       <c r="H148" s="21" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="I148" s="2">
-        <v>6391.43</v>
-      </c>
-      <c r="J148" s="22">
+        <v>500</v>
+      </c>
+      <c r="J148" s="21">
         <f>G148*I148</f>
-        <v>21374.111805885779</v>
+        <v>500</v>
       </c>
       <c r="K148" s="20"/>
     </row>
     <row r="149" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="24"/>
-      <c r="B149" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C149" s="26"/>
-      <c r="D149" s="27"/>
-      <c r="E149" s="27"/>
-      <c r="F149" s="27"/>
-      <c r="G149" s="27"/>
-      <c r="H149" s="26"/>
-      <c r="I149" s="26"/>
-      <c r="J149" s="22">
-        <f>0.13*G148*2304/100</f>
-        <v>10.016497040723138</v>
-      </c>
-      <c r="K149" s="26"/>
+      <c r="A149" s="17"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="19"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="20"/>
+      <c r="F149" s="20"/>
+      <c r="G149" s="2"/>
+      <c r="H149" s="21"/>
+      <c r="I149" s="2"/>
+      <c r="J149" s="22"/>
+      <c r="K149" s="20"/>
     </row>
     <row r="150" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="24"/>
-      <c r="B150" s="25"/>
-      <c r="C150" s="26"/>
-      <c r="D150" s="27"/>
-      <c r="E150" s="27"/>
-      <c r="F150" s="27"/>
-      <c r="G150" s="27"/>
-      <c r="H150" s="26"/>
-      <c r="I150" s="26"/>
-      <c r="J150" s="22"/>
-      <c r="K150" s="26"/>
-    </row>
-    <row r="151" spans="1:11" s="10" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A151" s="24">
-        <v>13</v>
-      </c>
-      <c r="B151" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C151" s="26"/>
-      <c r="D151" s="27"/>
-      <c r="E151" s="27"/>
-      <c r="F151" s="27"/>
-      <c r="G151" s="27"/>
-      <c r="H151" s="26"/>
-      <c r="I151" s="26"/>
-      <c r="J151" s="22"/>
-      <c r="K151" s="26"/>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A152" s="15"/>
-      <c r="B152" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C152" s="3">
-        <v>2</v>
-      </c>
-      <c r="D152" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="E152" s="3"/>
-      <c r="F152" s="3">
-        <f>4.5/3.281</f>
-        <v>1.3715330691862238</v>
-      </c>
-      <c r="G152" s="3">
-        <f>PRODUCT(C152:F152)</f>
-        <v>4.9375190490704055</v>
-      </c>
-      <c r="H152" s="15"/>
-      <c r="I152" s="15"/>
-      <c r="J152" s="15"/>
-      <c r="K152" s="15"/>
-    </row>
-    <row r="153" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="17"/>
-      <c r="B153" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" s="19"/>
-      <c r="D153" s="1"/>
-      <c r="E153" s="20"/>
-      <c r="F153" s="20"/>
-      <c r="G153" s="2">
-        <f>SUM(G151:G152)</f>
-        <v>4.9375190490704055</v>
-      </c>
-      <c r="H153" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I153" s="2">
-        <v>2485.56</v>
-      </c>
-      <c r="J153" s="22">
-        <f>G153*I153</f>
-        <v>12272.499847607436</v>
-      </c>
-      <c r="K153" s="20"/>
+      <c r="A150" s="32"/>
+      <c r="B150" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="C150" s="34"/>
+      <c r="D150" s="35"/>
+      <c r="E150" s="35"/>
+      <c r="F150" s="35"/>
+      <c r="G150" s="22"/>
+      <c r="H150" s="22"/>
+      <c r="I150" s="22"/>
+      <c r="J150" s="22">
+        <f>SUM(J10:J148)</f>
+        <v>543600.77369292674</v>
+      </c>
+      <c r="K150" s="36"/>
+    </row>
+    <row r="151" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="37"/>
+      <c r="B152" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C152" s="58">
+        <f>J150</f>
+        <v>543600.77369292674</v>
+      </c>
+      <c r="D152" s="59"/>
+      <c r="E152" s="39">
+        <v>100</v>
+      </c>
+      <c r="F152" s="37"/>
+      <c r="G152" s="40"/>
+      <c r="H152" s="37"/>
+      <c r="I152" s="41"/>
+      <c r="J152" s="42"/>
+      <c r="K152" s="43"/>
+    </row>
+    <row r="153" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C153" s="62">
+        <v>700000</v>
+      </c>
+      <c r="D153" s="63"/>
+      <c r="E153" s="39"/>
     </row>
     <row r="154" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="24"/>
-      <c r="B154" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C154" s="26"/>
-      <c r="D154" s="27"/>
-      <c r="E154" s="27"/>
-      <c r="F154" s="27"/>
-      <c r="G154" s="27"/>
-      <c r="H154" s="26"/>
-      <c r="I154" s="26"/>
-      <c r="J154" s="22">
-        <f>0.13*J153</f>
-        <v>1595.4249801889669</v>
-      </c>
-      <c r="K154" s="26"/>
+      <c r="B154" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C154" s="62">
+        <f>C153-C156-C157</f>
+        <v>665000</v>
+      </c>
+      <c r="D154" s="63"/>
+      <c r="E154" s="39">
+        <f>C154/C152*100</f>
+        <v>122.33242338533724</v>
+      </c>
     </row>
     <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="24"/>
-      <c r="B155" s="25"/>
-      <c r="C155" s="26"/>
-      <c r="D155" s="27"/>
-      <c r="E155" s="27"/>
-      <c r="F155" s="27"/>
-      <c r="G155" s="27"/>
-      <c r="H155" s="26"/>
-      <c r="I155" s="26"/>
-      <c r="J155" s="22"/>
-      <c r="K155" s="26"/>
-    </row>
-    <row r="156" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="17">
-        <v>14</v>
-      </c>
-      <c r="B156" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C156" s="19">
-        <v>1</v>
-      </c>
-      <c r="D156" s="1"/>
-      <c r="E156" s="20"/>
-      <c r="F156" s="20"/>
-      <c r="G156" s="21">
-        <f t="shared" ref="G156" si="21">PRODUCT(C156:F156)</f>
-        <v>1</v>
-      </c>
-      <c r="H156" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="I156" s="2">
-        <v>5000</v>
-      </c>
-      <c r="J156" s="21">
-        <f>G156*I156</f>
-        <v>5000</v>
-      </c>
-      <c r="K156" s="20"/>
+      <c r="B155" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" s="64">
+        <f>C152-C154</f>
+        <v>-121399.22630707326</v>
+      </c>
+      <c r="D155" s="64"/>
+      <c r="E155" s="39">
+        <f>100-E154</f>
+        <v>-22.332423385337236</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B156" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C156" s="58">
+        <f>C153*0.03</f>
+        <v>21000</v>
+      </c>
+      <c r="D156" s="59"/>
+      <c r="E156" s="39">
+        <v>3</v>
+      </c>
     </row>
     <row r="157" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="17"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="19"/>
-      <c r="D157" s="1"/>
-      <c r="E157" s="20"/>
-      <c r="F157" s="20"/>
-      <c r="G157" s="2"/>
-      <c r="H157" s="21"/>
-      <c r="I157" s="2"/>
-      <c r="J157" s="22"/>
-      <c r="K157" s="20"/>
-    </row>
-    <row r="158" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="17">
-        <v>15</v>
-      </c>
-      <c r="B158" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C158" s="19">
-        <v>1</v>
-      </c>
-      <c r="D158" s="1"/>
-      <c r="E158" s="20"/>
-      <c r="F158" s="20"/>
-      <c r="G158" s="21">
-        <f t="shared" ref="G158" si="22">PRODUCT(C158:F158)</f>
-        <v>1</v>
-      </c>
-      <c r="H158" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="I158" s="2">
-        <v>500</v>
-      </c>
-      <c r="J158" s="21">
-        <f>G158*I158</f>
-        <v>500</v>
-      </c>
-      <c r="K158" s="20"/>
-    </row>
-    <row r="159" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="17"/>
-      <c r="B159" s="31"/>
-      <c r="C159" s="19"/>
-      <c r="D159" s="1"/>
-      <c r="E159" s="20"/>
-      <c r="F159" s="20"/>
-      <c r="G159" s="2"/>
-      <c r="H159" s="21"/>
-      <c r="I159" s="2"/>
-      <c r="J159" s="22"/>
-      <c r="K159" s="20"/>
-    </row>
-    <row r="160" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="32"/>
-      <c r="B160" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C160" s="34"/>
-      <c r="D160" s="35"/>
-      <c r="E160" s="35"/>
-      <c r="F160" s="35"/>
-      <c r="G160" s="22"/>
-      <c r="H160" s="22"/>
-      <c r="I160" s="22"/>
-      <c r="J160" s="22">
-        <f>SUM(J10:J158)</f>
-        <v>842852.05071615078</v>
-      </c>
-      <c r="K160" s="36"/>
-    </row>
-    <row r="161" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="37"/>
-      <c r="B162" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C162" s="49">
-        <f>J160</f>
-        <v>842852.05071615078</v>
-      </c>
-      <c r="D162" s="50"/>
-      <c r="E162" s="39">
-        <v>100</v>
-      </c>
-      <c r="F162" s="37"/>
-      <c r="G162" s="40"/>
-      <c r="H162" s="37"/>
-      <c r="I162" s="41"/>
-      <c r="J162" s="42"/>
-      <c r="K162" s="43"/>
-    </row>
-    <row r="163" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C163" s="51">
-        <v>700000</v>
-      </c>
-      <c r="D163" s="52"/>
-      <c r="E163" s="39"/>
-    </row>
-    <row r="164" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="C164" s="51">
-        <f>C163-C166-C167</f>
-        <v>665000</v>
-      </c>
-      <c r="D164" s="52"/>
-      <c r="E164" s="39">
-        <f>C164/C162*100</f>
-        <v>78.898781753567036</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="C165" s="53">
-        <f>C162-C164</f>
-        <v>177852.05071615078</v>
-      </c>
-      <c r="D165" s="53"/>
-      <c r="E165" s="39">
-        <f>100-E164</f>
-        <v>21.101218246432964</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="C166" s="49">
-        <f>C163*0.03</f>
-        <v>21000</v>
-      </c>
-      <c r="D166" s="50"/>
-      <c r="E166" s="39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="38" t="s">
+      <c r="B157" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C167" s="49">
-        <f>C163*0.02</f>
+      <c r="C157" s="58">
+        <f>C153*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D167" s="50"/>
-      <c r="E167" s="39">
+      <c r="D157" s="59"/>
+      <c r="E157" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -12225,14 +12162,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C166:D166"/>
-    <mergeCell ref="C167:D167"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C162:D162"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="C164:D164"/>
-    <mergeCell ref="C165:D165"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -12270,21 +12199,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62" t="s">
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="63" t="s">
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="66" t="s">
         <v>97</v>
       </c>
@@ -12307,71 +12236,71 @@
       <c r="V2" s="65"/>
       <c r="W2" s="65"/>
     </row>
-    <row r="3" spans="2:23" s="70" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="64" t="s">
+    <row r="3" spans="2:23" s="50" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="H3" s="64" t="s">
+      <c r="H3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="64" t="s">
+      <c r="I3" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="64" t="s">
+      <c r="J3" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="K3" s="69" t="s">
+      <c r="K3" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="L3" s="69" t="s">
+      <c r="L3" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="M3" s="69" t="s">
+      <c r="M3" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="N3" s="69" t="s">
+      <c r="N3" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="O3" s="69" t="s">
+      <c r="O3" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="P3" s="69" t="s">
+      <c r="P3" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="Q3" s="69" t="s">
+      <c r="Q3" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="R3" s="69" t="s">
+      <c r="R3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="S3" s="69" t="s">
+      <c r="S3" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="T3" s="69" t="s">
+      <c r="T3" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="U3" s="69" t="s">
+      <c r="U3" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="V3" s="69" t="s">
+      <c r="V3" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="W3" s="69" t="s">
+      <c r="W3" s="49" t="s">
         <v>10</v>
       </c>
     </row>

--- a/बजेट माग estimate/नगर बजेट estimate/bhotange chihaanpaati/2.bhotange chihaanpaati.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/bhotange chihaanpaati/2.bhotange chihaanpaati.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD60A422-983D-4D70-B884-51ADE376380D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="13" r:id="rId1"/>
@@ -42,7 +41,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">chihaan!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -60,12 +59,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="D39" authorId="0" shapeId="0" xr:uid="{1385C7FC-690E-4DEF-B1D5-B9F73F5D188D}">
+    <comment ref="D39" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -541,10 +540,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -753,9 +752,9 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -771,14 +770,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -807,7 +806,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -844,7 +843,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -862,7 +861,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -871,8 +870,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -884,18 +883,41 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -910,24 +932,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -947,24 +956,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2" xfId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 3" xfId="5"/>
+    <cellStyle name="Percent 2" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -980,7 +979,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1074,7 +1073,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1133,7 +1132,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1197,9 +1196,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1237,9 +1236,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1274,7 +1273,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1309,7 +1308,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1482,131 +1481,131 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M158"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="59" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+    </row>
+    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="62" t="s">
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="63" t="s">
+      <c r="H7" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="63"/>
-    </row>
-    <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+    </row>
+    <row r="8" spans="1:11" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -1641,7 +1640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>1</v>
       </c>
@@ -1658,7 +1657,7 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16" t="s">
         <v>57</v>
@@ -1684,7 +1683,7 @@
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="15"/>
       <c r="B11" s="16" t="s">
         <v>59</v>
@@ -1712,7 +1711,7 @@
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="s">
         <v>16</v>
@@ -1737,7 +1736,7 @@
       </c>
       <c r="K12" s="20"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -1750,7 +1749,7 @@
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
     </row>
-    <row r="14" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" s="14" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>2</v>
       </c>
@@ -1767,7 +1766,7 @@
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="str">
         <f t="shared" ref="B15:E16" si="0">B10</f>
@@ -1795,7 +1794,7 @@
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="str">
         <f t="shared" si="0"/>
@@ -1823,7 +1822,7 @@
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="15"/>
       <c r="B17" s="16" t="s">
         <v>52</v>
@@ -1849,7 +1848,7 @@
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
     </row>
-    <row r="18" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17"/>
       <c r="B18" s="18" t="s">
         <v>16</v>
@@ -1874,7 +1873,7 @@
       </c>
       <c r="K18" s="20"/>
     </row>
-    <row r="19" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="24"/>
       <c r="B19" s="25" t="s">
         <v>55</v>
@@ -1892,7 +1891,7 @@
       </c>
       <c r="K19" s="26"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="25" t="s">
         <v>31</v>
@@ -1910,7 +1909,7 @@
       </c>
       <c r="K20" s="15"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -1923,7 +1922,7 @@
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
     </row>
-    <row r="22" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>3</v>
       </c>
@@ -1940,7 +1939,7 @@
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="str">
         <f t="shared" ref="B23:E24" si="1">B15</f>
@@ -1970,7 +1969,7 @@
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2000,7 +1999,7 @@
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="15"/>
       <c r="B25" s="16" t="str">
         <f>B17</f>
@@ -2030,7 +2029,7 @@
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16" t="str">
         <f>B93</f>
@@ -2060,7 +2059,7 @@
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
     </row>
-    <row r="27" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="18" t="s">
         <v>16</v>
@@ -2085,7 +2084,7 @@
       </c>
       <c r="K27" s="20"/>
     </row>
-    <row r="28" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="24"/>
       <c r="B28" s="25" t="s">
         <v>32</v>
@@ -2103,7 +2102,7 @@
       </c>
       <c r="K28" s="26"/>
     </row>
-    <row r="29" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="24"/>
       <c r="B29" s="25" t="s">
         <v>33</v>
@@ -2121,7 +2120,7 @@
       </c>
       <c r="K29" s="26"/>
     </row>
-    <row r="30" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="24"/>
       <c r="B30" s="25" t="s">
         <v>31</v>
@@ -2139,7 +2138,7 @@
       </c>
       <c r="K30" s="26"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="15"/>
       <c r="B31" s="25" t="s">
         <v>36</v>
@@ -2157,7 +2156,7 @@
       </c>
       <c r="K31" s="15"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="15"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -2170,7 +2169,7 @@
       <c r="J32" s="15"/>
       <c r="K32" s="15"/>
     </row>
-    <row r="33" spans="1:13" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>4</v>
       </c>
@@ -2187,7 +2186,7 @@
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="15"/>
       <c r="B34" s="16" t="str">
         <f>B23</f>
@@ -2217,7 +2216,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="15"/>
       <c r="B35" s="16" t="s">
         <v>59</v>
@@ -2246,7 +2245,7 @@
       <c r="J35" s="15"/>
       <c r="K35" s="15"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="15"/>
       <c r="B36" s="16" t="s">
         <v>60</v>
@@ -2274,7 +2273,7 @@
       <c r="J36" s="15"/>
       <c r="K36" s="15"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="15"/>
       <c r="B37" s="16" t="s">
         <v>61</v>
@@ -2301,7 +2300,7 @@
       <c r="J37" s="15"/>
       <c r="K37" s="15"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="15"/>
       <c r="B38" s="16" t="s">
         <v>62</v>
@@ -2329,7 +2328,7 @@
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="15"/>
       <c r="B39" s="16" t="s">
         <v>81</v>
@@ -2356,7 +2355,7 @@
       <c r="J39" s="15"/>
       <c r="K39" s="15"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="15"/>
       <c r="B40" s="16" t="s">
         <v>82</v>
@@ -2383,7 +2382,7 @@
       <c r="J40" s="15"/>
       <c r="K40" s="15"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
       <c r="B41" s="16" t="s">
         <v>83</v>
@@ -2411,7 +2410,7 @@
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="15"/>
       <c r="B42" s="16" t="s">
         <v>84</v>
@@ -2438,7 +2437,7 @@
       <c r="J42" s="15"/>
       <c r="K42" s="15"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="15"/>
       <c r="B43" s="16"/>
       <c r="C43" s="15">
@@ -2463,7 +2462,7 @@
       <c r="J43" s="15"/>
       <c r="K43" s="15"/>
     </row>
-    <row r="44" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="17"/>
       <c r="B44" s="18" t="s">
         <v>16</v>
@@ -2488,7 +2487,7 @@
       </c>
       <c r="K44" s="20"/>
     </row>
-    <row r="45" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="24"/>
       <c r="B45" s="25" t="s">
         <v>32</v>
@@ -2506,7 +2505,7 @@
       </c>
       <c r="K45" s="26"/>
     </row>
-    <row r="46" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="24"/>
       <c r="B46" s="25" t="s">
         <v>33</v>
@@ -2524,7 +2523,7 @@
       </c>
       <c r="K46" s="26"/>
     </row>
-    <row r="47" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="24"/>
       <c r="B47" s="25" t="s">
         <v>31</v>
@@ -2542,7 +2541,7 @@
       </c>
       <c r="K47" s="26"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
       <c r="B48" s="25" t="s">
         <v>36</v>
@@ -2560,7 +2559,7 @@
       </c>
       <c r="K48" s="15"/>
     </row>
-    <row r="49" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="24"/>
       <c r="B49" s="25" t="s">
         <v>44</v>
@@ -2578,7 +2577,7 @@
       </c>
       <c r="K49" s="26"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="15"/>
       <c r="B50" s="25" t="s">
         <v>45</v>
@@ -2596,7 +2595,7 @@
       </c>
       <c r="K50" s="15"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="15"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -2609,7 +2608,7 @@
       <c r="J51" s="15"/>
       <c r="K51" s="15"/>
     </row>
-    <row r="52" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="11">
         <v>5</v>
       </c>
@@ -2626,7 +2625,7 @@
       <c r="J52" s="13"/>
       <c r="K52" s="13"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="15"/>
       <c r="B53" s="16" t="str">
         <f>B36</f>
@@ -2654,7 +2653,7 @@
       <c r="J53" s="15"/>
       <c r="K53" s="15"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="15"/>
       <c r="B54" s="16" t="str">
         <f>B35</f>
@@ -2682,7 +2681,7 @@
       <c r="J54" s="15"/>
       <c r="K54" s="15"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="15"/>
       <c r="B55" s="16" t="str">
         <f t="shared" ref="B55:C60" si="5">B37</f>
@@ -2710,7 +2709,7 @@
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="15"/>
       <c r="B56" s="16" t="str">
         <f t="shared" si="5"/>
@@ -2738,7 +2737,7 @@
       <c r="J56" s="15"/>
       <c r="K56" s="15"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="15"/>
       <c r="B57" s="16" t="str">
         <f t="shared" si="5"/>
@@ -2766,7 +2765,7 @@
       <c r="J57" s="15"/>
       <c r="K57" s="15"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="15"/>
       <c r="B58" s="16" t="str">
         <f t="shared" si="5"/>
@@ -2794,7 +2793,7 @@
       <c r="J58" s="15"/>
       <c r="K58" s="15"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="15"/>
       <c r="B59" s="16" t="str">
         <f t="shared" si="5"/>
@@ -2822,7 +2821,7 @@
       <c r="J59" s="15"/>
       <c r="K59" s="15"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="15"/>
       <c r="B60" s="16" t="str">
         <f t="shared" si="5"/>
@@ -2850,7 +2849,7 @@
       <c r="J60" s="15"/>
       <c r="K60" s="15"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="15"/>
       <c r="B61" s="16"/>
       <c r="C61" s="15">
@@ -2875,7 +2874,7 @@
       <c r="J61" s="15"/>
       <c r="K61" s="15"/>
     </row>
-    <row r="62" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="17"/>
       <c r="B62" s="18" t="s">
         <v>16</v>
@@ -2900,7 +2899,7 @@
       </c>
       <c r="K62" s="20"/>
     </row>
-    <row r="63" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="24"/>
       <c r="B63" s="25" t="s">
         <v>47</v>
@@ -2918,7 +2917,7 @@
       </c>
       <c r="K63" s="26"/>
     </row>
-    <row r="64" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="24"/>
       <c r="B64" s="25" t="s">
         <v>48</v>
@@ -2936,7 +2935,7 @@
       </c>
       <c r="K64" s="26"/>
     </row>
-    <row r="65" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="24"/>
       <c r="B65" s="25" t="s">
         <v>49</v>
@@ -2954,7 +2953,7 @@
       </c>
       <c r="K65" s="26"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="15"/>
       <c r="B66" s="25" t="s">
         <v>50</v>
@@ -2972,7 +2971,7 @@
       </c>
       <c r="K66" s="15"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="15"/>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -2985,7 +2984,7 @@
       <c r="J67" s="15"/>
       <c r="K67" s="15"/>
     </row>
-    <row r="68" spans="1:13" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A68" s="11">
         <v>6</v>
       </c>
@@ -3010,7 +3009,7 @@
       <c r="J68" s="13"/>
       <c r="K68" s="13"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="15"/>
       <c r="B69" s="16" t="str">
         <f>B34</f>
@@ -3041,7 +3040,7 @@
       <c r="J69" s="15"/>
       <c r="K69" s="15"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="15"/>
       <c r="B70" s="16"/>
       <c r="C70" s="15">
@@ -3068,7 +3067,7 @@
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="15"/>
       <c r="B71" s="16" t="s">
         <v>70</v>
@@ -3098,7 +3097,7 @@
       <c r="J71" s="15"/>
       <c r="K71" s="15"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="15"/>
       <c r="B72" s="16"/>
       <c r="C72" s="15">
@@ -3130,7 +3129,7 @@
         <v>5.0777202072538854</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="15"/>
       <c r="B73" s="16" t="s">
         <v>71</v>
@@ -3160,7 +3159,7 @@
       <c r="J73" s="15"/>
       <c r="K73" s="15"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="15"/>
       <c r="B74" s="16"/>
       <c r="C74" s="15">
@@ -3188,7 +3187,7 @@
       <c r="J74" s="15"/>
       <c r="K74" s="15"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="15"/>
       <c r="B75" s="16" t="str">
         <f>B54</f>
@@ -3219,7 +3218,7 @@
       <c r="J75" s="15"/>
       <c r="K75" s="15"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="15"/>
       <c r="B76" s="16" t="s">
         <v>72</v>
@@ -3249,7 +3248,7 @@
       <c r="J76" s="15"/>
       <c r="K76" s="15"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="15"/>
       <c r="B77" s="16" t="str">
         <f>B56</f>
@@ -3280,7 +3279,7 @@
       <c r="J77" s="15"/>
       <c r="K77" s="15"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="15"/>
       <c r="B78" s="16" t="str">
         <f>B57</f>
@@ -3311,7 +3310,7 @@
       <c r="J78" s="15"/>
       <c r="K78" s="15"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="15"/>
       <c r="B79" s="16"/>
       <c r="C79" s="15">
@@ -3339,7 +3338,7 @@
       <c r="J79" s="15"/>
       <c r="K79" s="15"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="15"/>
       <c r="B80" s="16" t="str">
         <f>B58</f>
@@ -3370,7 +3369,7 @@
       <c r="J80" s="15"/>
       <c r="K80" s="15"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="15"/>
       <c r="B81" s="16" t="s">
         <v>71</v>
@@ -3400,7 +3399,7 @@
       <c r="J81" s="15"/>
       <c r="K81" s="15"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="15"/>
       <c r="B82" s="16" t="str">
         <f>B59</f>
@@ -3431,7 +3430,7 @@
       <c r="J82" s="15"/>
       <c r="K82" s="15"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="15"/>
       <c r="B83" s="16"/>
       <c r="C83" s="15">
@@ -3459,7 +3458,7 @@
       <c r="J83" s="15"/>
       <c r="K83" s="15"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="15"/>
       <c r="B84" s="16" t="s">
         <v>84</v>
@@ -3488,7 +3487,7 @@
       <c r="J84" s="15"/>
       <c r="K84" s="15"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="15"/>
       <c r="B85" s="16"/>
       <c r="C85" s="15">
@@ -3515,7 +3514,7 @@
       <c r="J85" s="15"/>
       <c r="K85" s="15"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="15"/>
       <c r="B86" s="16"/>
       <c r="C86" s="15">
@@ -3542,7 +3541,7 @@
       <c r="J86" s="15"/>
       <c r="K86" s="15"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="15"/>
       <c r="B87" s="16"/>
       <c r="C87" s="15">
@@ -3569,7 +3568,7 @@
       <c r="J87" s="15"/>
       <c r="K87" s="15"/>
     </row>
-    <row r="88" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="17"/>
       <c r="B88" s="18" t="s">
         <v>16</v>
@@ -3594,7 +3593,7 @@
       </c>
       <c r="K88" s="20"/>
     </row>
-    <row r="89" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="24"/>
       <c r="B89" s="25" t="s">
         <v>39</v>
@@ -3612,7 +3611,7 @@
       </c>
       <c r="K89" s="26"/>
     </row>
-    <row r="90" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="24"/>
       <c r="B90" s="25" t="s">
         <v>38</v>
@@ -3630,7 +3629,7 @@
       </c>
       <c r="K90" s="26"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="15"/>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
@@ -3643,7 +3642,7 @@
       <c r="J91" s="15"/>
       <c r="K91" s="15"/>
     </row>
-    <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A92" s="11">
         <v>7</v>
       </c>
@@ -3660,7 +3659,7 @@
       <c r="J92" s="15"/>
       <c r="K92" s="15"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="15"/>
       <c r="B93" s="16" t="s">
         <v>66</v>
@@ -3686,7 +3685,7 @@
       <c r="J93" s="15"/>
       <c r="K93" s="15"/>
     </row>
-    <row r="94" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="17"/>
       <c r="B94" s="18" t="s">
         <v>16</v>
@@ -3711,7 +3710,7 @@
       </c>
       <c r="K94" s="20"/>
     </row>
-    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="24"/>
       <c r="B95" s="25" t="s">
         <v>32</v>
@@ -3729,7 +3728,7 @@
       </c>
       <c r="K95" s="26"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="15"/>
       <c r="B96" s="25" t="s">
         <v>31</v>
@@ -3747,7 +3746,7 @@
       </c>
       <c r="K96" s="15"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="15"/>
       <c r="B97" s="25" t="s">
         <v>33</v>
@@ -3765,7 +3764,7 @@
       </c>
       <c r="K97" s="15"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="15"/>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -3778,7 +3777,7 @@
       <c r="J98" s="15"/>
       <c r="K98" s="15"/>
     </row>
-    <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A99" s="11">
         <v>8</v>
       </c>
@@ -3795,7 +3794,7 @@
       <c r="J99" s="15"/>
       <c r="K99" s="15"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="15"/>
       <c r="B100" s="16" t="s">
         <v>67</v>
@@ -3822,7 +3821,7 @@
       <c r="J100" s="15"/>
       <c r="K100" s="15"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="15"/>
       <c r="B101" s="16"/>
       <c r="C101" s="45">
@@ -3847,7 +3846,7 @@
       <c r="J101" s="15"/>
       <c r="K101" s="15"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="15"/>
       <c r="B102" s="16" t="str">
         <f>B119</f>
@@ -3875,7 +3874,7 @@
       <c r="J102" s="15"/>
       <c r="K102" s="15"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="15"/>
       <c r="B103" s="16" t="str">
         <f>B120</f>
@@ -3903,7 +3902,7 @@
       <c r="J103" s="15"/>
       <c r="K103" s="15"/>
     </row>
-    <row r="104" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="17"/>
       <c r="B104" s="18" t="s">
         <v>16</v>
@@ -3928,7 +3927,7 @@
       </c>
       <c r="K104" s="20"/>
     </row>
-    <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="24"/>
       <c r="B105" s="25" t="s">
         <v>32</v>
@@ -3946,7 +3945,7 @@
       </c>
       <c r="K105" s="26"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="15"/>
       <c r="B106" s="25" t="s">
         <v>31</v>
@@ -3964,7 +3963,7 @@
       </c>
       <c r="K106" s="15"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
@@ -3977,7 +3976,7 @@
       <c r="J107" s="15"/>
       <c r="K107" s="15"/>
     </row>
-    <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A108" s="11">
         <v>9</v>
       </c>
@@ -3994,7 +3993,7 @@
       <c r="J108" s="15"/>
       <c r="K108" s="15"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="15"/>
       <c r="B109" s="16" t="str">
         <f>B93</f>
@@ -4022,7 +4021,7 @@
       <c r="J109" s="15"/>
       <c r="K109" s="15"/>
     </row>
-    <row r="110" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="17"/>
       <c r="B110" s="18" t="s">
         <v>16</v>
@@ -4047,7 +4046,7 @@
       </c>
       <c r="K110" s="20"/>
     </row>
-    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="24"/>
       <c r="B111" s="25" t="s">
         <v>32</v>
@@ -4065,7 +4064,7 @@
       </c>
       <c r="K111" s="26"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="15"/>
       <c r="B112" s="25" t="s">
         <v>31</v>
@@ -4083,7 +4082,7 @@
       </c>
       <c r="K112" s="15"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -4096,7 +4095,7 @@
       <c r="J113" s="15"/>
       <c r="K113" s="15"/>
     </row>
-    <row r="114" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A114" s="11">
         <v>10</v>
       </c>
@@ -4113,7 +4112,7 @@
       <c r="J114" s="15"/>
       <c r="K114" s="15"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="15"/>
       <c r="B115" s="16" t="str">
         <f>B35</f>
@@ -4142,7 +4141,7 @@
       <c r="J115" s="15"/>
       <c r="K115" s="15"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="15"/>
       <c r="B116" s="16" t="s">
         <v>65</v>
@@ -4170,7 +4169,7 @@
       <c r="J116" s="15"/>
       <c r="K116" s="15"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="15"/>
       <c r="B117" s="16"/>
       <c r="C117" s="3">
@@ -4196,7 +4195,7 @@
       <c r="J117" s="15"/>
       <c r="K117" s="15"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="15"/>
       <c r="B118" s="16" t="s">
         <v>80</v>
@@ -4223,7 +4222,7 @@
       <c r="J118" s="15"/>
       <c r="K118" s="15"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="15"/>
       <c r="B119" s="16" t="s">
         <v>68</v>
@@ -4251,7 +4250,7 @@
       <c r="J119" s="15"/>
       <c r="K119" s="15"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="15"/>
       <c r="B120" s="16" t="s">
         <v>69</v>
@@ -4279,7 +4278,7 @@
       <c r="J120" s="15"/>
       <c r="K120" s="15"/>
     </row>
-    <row r="121" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="17"/>
       <c r="B121" s="18" t="s">
         <v>16</v>
@@ -4305,7 +4304,7 @@
       </c>
       <c r="K121" s="20"/>
     </row>
-    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="24"/>
       <c r="B122" s="25" t="s">
         <v>55</v>
@@ -4323,7 +4322,7 @@
       </c>
       <c r="K122" s="26"/>
     </row>
-    <row r="123" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="24"/>
       <c r="B123" s="25" t="s">
         <v>32</v>
@@ -4341,7 +4340,7 @@
       </c>
       <c r="K123" s="26"/>
     </row>
-    <row r="124" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="24"/>
       <c r="B124" s="25" t="s">
         <v>64</v>
@@ -4359,7 +4358,7 @@
       </c>
       <c r="K124" s="26"/>
     </row>
-    <row r="125" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="24"/>
       <c r="B125" s="25" t="s">
         <v>36</v>
@@ -4377,7 +4376,7 @@
       </c>
       <c r="K125" s="26"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -4390,7 +4389,7 @@
       <c r="J126" s="15"/>
       <c r="K126" s="15"/>
     </row>
-    <row r="127" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A127" s="11">
         <v>11</v>
       </c>
@@ -4407,7 +4406,7 @@
       <c r="J127" s="15"/>
       <c r="K127" s="15"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="15"/>
       <c r="B128" s="16" t="s">
         <v>65</v>
@@ -4434,7 +4433,7 @@
       <c r="J128" s="15"/>
       <c r="K128" s="15"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="15"/>
       <c r="B129" s="16"/>
       <c r="C129" s="3">
@@ -4459,7 +4458,7 @@
       <c r="J129" s="15"/>
       <c r="K129" s="15"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="15"/>
       <c r="B130" s="16" t="s">
         <v>68</v>
@@ -4486,7 +4485,7 @@
       <c r="J130" s="15"/>
       <c r="K130" s="15"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="15"/>
       <c r="B131" s="16" t="s">
         <v>69</v>
@@ -4513,7 +4512,7 @@
       <c r="J131" s="15"/>
       <c r="K131" s="15"/>
     </row>
-    <row r="132" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="17"/>
       <c r="B132" s="18" t="s">
         <v>16</v>
@@ -4538,7 +4537,7 @@
       </c>
       <c r="K132" s="20"/>
     </row>
-    <row r="133" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="24"/>
       <c r="B133" s="25" t="s">
         <v>74</v>
@@ -4556,7 +4555,7 @@
       </c>
       <c r="K133" s="26"/>
     </row>
-    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="24"/>
       <c r="B134" s="25" t="s">
         <v>75</v>
@@ -4574,7 +4573,7 @@
       </c>
       <c r="K134" s="26"/>
     </row>
-    <row r="135" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A135" s="24"/>
       <c r="B135" s="25"/>
       <c r="C135" s="26"/>
@@ -4587,7 +4586,7 @@
       <c r="J135" s="22"/>
       <c r="K135" s="26"/>
     </row>
-    <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A136" s="11">
         <v>12</v>
       </c>
@@ -4604,7 +4603,7 @@
       <c r="J136" s="15"/>
       <c r="K136" s="15"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="15"/>
       <c r="B137" s="16" t="s">
         <v>65</v>
@@ -4619,7 +4618,7 @@
       <c r="J137" s="15"/>
       <c r="K137" s="15"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="15"/>
       <c r="B138" s="16" t="s">
         <v>77</v>
@@ -4645,7 +4644,7 @@
       <c r="J138" s="15"/>
       <c r="K138" s="15"/>
     </row>
-    <row r="139" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="17"/>
       <c r="B139" s="18" t="s">
         <v>16</v>
@@ -4670,7 +4669,7 @@
       </c>
       <c r="K139" s="20"/>
     </row>
-    <row r="140" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="24"/>
       <c r="B140" s="25" t="s">
         <v>74</v>
@@ -4688,7 +4687,7 @@
       </c>
       <c r="K140" s="26"/>
     </row>
-    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="24"/>
       <c r="B141" s="25"/>
       <c r="C141" s="26"/>
@@ -4701,7 +4700,7 @@
       <c r="J141" s="22"/>
       <c r="K141" s="26"/>
     </row>
-    <row r="142" spans="1:11" s="10" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" s="10" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A142" s="24">
         <v>13</v>
       </c>
@@ -4718,7 +4717,7 @@
       <c r="J142" s="22"/>
       <c r="K142" s="26"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="15"/>
       <c r="B143" s="16" t="s">
         <v>79</v>
@@ -4743,7 +4742,7 @@
       <c r="J143" s="15"/>
       <c r="K143" s="15"/>
     </row>
-    <row r="144" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="17"/>
       <c r="B144" s="18" t="s">
         <v>16</v>
@@ -4768,7 +4767,7 @@
       </c>
       <c r="K144" s="20"/>
     </row>
-    <row r="145" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="24"/>
       <c r="B145" s="25" t="s">
         <v>74</v>
@@ -4786,7 +4785,7 @@
       </c>
       <c r="K145" s="26"/>
     </row>
-    <row r="146" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A146" s="24"/>
       <c r="B146" s="25"/>
       <c r="C146" s="26"/>
@@ -4799,7 +4798,7 @@
       <c r="J146" s="22"/>
       <c r="K146" s="26"/>
     </row>
-    <row r="147" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="17">
         <v>14</v>
       </c>
@@ -4828,7 +4827,7 @@
       </c>
       <c r="K147" s="20"/>
     </row>
-    <row r="148" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A148" s="17"/>
       <c r="B148" s="31"/>
       <c r="C148" s="19"/>
@@ -4841,7 +4840,7 @@
       <c r="J148" s="22"/>
       <c r="K148" s="20"/>
     </row>
-    <row r="149" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="17">
         <v>15</v>
       </c>
@@ -4870,7 +4869,7 @@
       </c>
       <c r="K149" s="20"/>
     </row>
-    <row r="150" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A150" s="17"/>
       <c r="B150" s="31"/>
       <c r="C150" s="19"/>
@@ -4883,7 +4882,7 @@
       <c r="J150" s="22"/>
       <c r="K150" s="20"/>
     </row>
-    <row r="151" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A151" s="32"/>
       <c r="B151" s="33" t="s">
         <v>20</v>
@@ -4901,17 +4900,17 @@
       </c>
       <c r="K151" s="36"/>
     </row>
-    <row r="152" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="153" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="37"/>
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="60">
+      <c r="C153" s="58">
         <f>J151</f>
         <v>791637.34255256748</v>
       </c>
-      <c r="D153" s="61"/>
+      <c r="D153" s="59"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -4922,78 +4921,72 @@
       <c r="J153" s="42"/>
       <c r="K153" s="43"/>
     </row>
-    <row r="154" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="64">
+      <c r="C154" s="60">
         <v>700000</v>
       </c>
-      <c r="D154" s="65"/>
+      <c r="D154" s="61"/>
       <c r="E154" s="39"/>
     </row>
-    <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="64">
+      <c r="C155" s="60">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="65"/>
+      <c r="D155" s="61"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>84.003111558098539</v>
       </c>
     </row>
-    <row r="156" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="66">
+      <c r="C156" s="62">
         <f>C153-C155</f>
         <v>126637.34255256748</v>
       </c>
-      <c r="D156" s="66"/>
+      <c r="D156" s="62"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>15.996888441901461</v>
       </c>
     </row>
-    <row r="157" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="60">
+      <c r="C157" s="58">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="61"/>
+      <c r="D157" s="59"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="60">
+      <c r="C158" s="58">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="61"/>
+      <c r="D158" s="59"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -5003,6 +4996,12 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -5013,131 +5012,131 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0935FBD1-0150-4C79-B1B2-6227680F604C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P144"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-    </row>
-    <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+    </row>
+    <row r="2" spans="1:16" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-    </row>
-    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="59" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+    </row>
+    <row r="5" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-    </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="69" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="62" t="s">
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="63" t="s">
+      <c r="H7" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="63"/>
-    </row>
-    <row r="8" spans="1:16" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+    </row>
+    <row r="8" spans="1:16" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -5184,7 +5183,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>1</v>
       </c>
@@ -5200,15 +5199,15 @@
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
-      <c r="M9" s="73">
+      <c r="M9" s="54">
         <f>(8.75+17.5)/3.281</f>
         <v>8.0006095702529709</v>
       </c>
-      <c r="N9" s="73">
+      <c r="N9" s="54">
         <f>(18.5)/3.281</f>
         <v>5.6385248399878085</v>
       </c>
-      <c r="O9" s="73">
+      <c r="O9" s="54">
         <f>7.17/3.281</f>
         <v>2.185309356903383</v>
       </c>
@@ -5216,7 +5215,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="16" t="s">
         <v>52</v>
@@ -5243,10 +5242,10 @@
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
-      <c r="M10" s="74"/>
-      <c r="N10" s="74"/>
-    </row>
-    <row r="11" spans="1:16" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" s="55"/>
+      <c r="N10" s="55"/>
+    </row>
+    <row r="11" spans="1:16" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17"/>
       <c r="B11" s="18" t="s">
         <v>16</v>
@@ -5271,7 +5270,7 @@
       </c>
       <c r="K11" s="20"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -5284,7 +5283,7 @@
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
     </row>
-    <row r="13" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" s="14" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>2</v>
       </c>
@@ -5301,7 +5300,7 @@
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="str">
         <f>B10</f>
@@ -5329,7 +5328,7 @@
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
     </row>
-    <row r="15" spans="1:16" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="s">
         <v>16</v>
@@ -5354,7 +5353,7 @@
       </c>
       <c r="K15" s="20"/>
     </row>
-    <row r="16" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="24"/>
       <c r="B16" s="25" t="s">
         <v>55</v>
@@ -5372,7 +5371,7 @@
       </c>
       <c r="K16" s="26"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="15"/>
       <c r="B17" s="25" t="s">
         <v>31</v>
@@ -5390,7 +5389,7 @@
       </c>
       <c r="K17" s="15"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -5403,7 +5402,7 @@
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
     </row>
-    <row r="19" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>3</v>
       </c>
@@ -5420,7 +5419,7 @@
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
       <c r="B20" s="16" t="str">
         <f>B10</f>
@@ -5450,7 +5449,7 @@
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
     </row>
-    <row r="21" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="18" t="s">
         <v>16</v>
@@ -5475,7 +5474,7 @@
       </c>
       <c r="K21" s="20"/>
     </row>
-    <row r="22" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24"/>
       <c r="B22" s="25" t="s">
         <v>32</v>
@@ -5493,7 +5492,7 @@
       </c>
       <c r="K22" s="26"/>
     </row>
-    <row r="23" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="24"/>
       <c r="B23" s="25" t="s">
         <v>33</v>
@@ -5511,7 +5510,7 @@
       </c>
       <c r="K23" s="26"/>
     </row>
-    <row r="24" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="24"/>
       <c r="B24" s="25" t="s">
         <v>31</v>
@@ -5529,7 +5528,7 @@
       </c>
       <c r="K24" s="26"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="15"/>
       <c r="B25" s="25" t="s">
         <v>36</v>
@@ -5547,7 +5546,7 @@
       </c>
       <c r="K25" s="15"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="25" t="s">
         <v>36</v>
@@ -5565,7 +5564,7 @@
       </c>
       <c r="K26" s="15"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="15"/>
       <c r="B27" s="25" t="s">
         <v>36</v>
@@ -5583,7 +5582,7 @@
       </c>
       <c r="K27" s="15"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -5596,7 +5595,7 @@
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
     </row>
-    <row r="29" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>4</v>
       </c>
@@ -5613,7 +5612,7 @@
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="15"/>
       <c r="B30" s="16" t="str">
         <f>B71</f>
@@ -5642,7 +5641,7 @@
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
     </row>
-    <row r="31" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17"/>
       <c r="B31" s="18" t="s">
         <v>16</v>
@@ -5667,7 +5666,7 @@
       </c>
       <c r="K31" s="20"/>
     </row>
-    <row r="32" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="24"/>
       <c r="B32" s="25" t="s">
         <v>32</v>
@@ -5685,7 +5684,7 @@
       </c>
       <c r="K32" s="26"/>
     </row>
-    <row r="33" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="24"/>
       <c r="B33" s="25" t="s">
         <v>33</v>
@@ -5703,7 +5702,7 @@
       </c>
       <c r="K33" s="26"/>
     </row>
-    <row r="34" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="24"/>
       <c r="B34" s="25" t="s">
         <v>31</v>
@@ -5721,7 +5720,7 @@
       </c>
       <c r="K34" s="26"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="15"/>
       <c r="B35" s="25" t="s">
         <v>36</v>
@@ -5739,7 +5738,7 @@
       </c>
       <c r="K35" s="15"/>
     </row>
-    <row r="36" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="24"/>
       <c r="B36" s="25" t="s">
         <v>44</v>
@@ -5757,7 +5756,7 @@
       </c>
       <c r="K36" s="26"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="15"/>
       <c r="B37" s="25" t="s">
         <v>45</v>
@@ -5775,7 +5774,7 @@
       </c>
       <c r="K37" s="15"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="15"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -5788,7 +5787,7 @@
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
     </row>
-    <row r="39" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
         <v>5</v>
       </c>
@@ -5805,7 +5804,7 @@
       <c r="J39" s="13"/>
       <c r="K39" s="13"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="15"/>
       <c r="B40" s="16" t="str">
         <f>B30</f>
@@ -5833,7 +5832,7 @@
       <c r="J40" s="15"/>
       <c r="K40" s="15"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
       <c r="B41" s="16" t="s">
         <v>122</v>
@@ -5859,7 +5858,7 @@
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
     </row>
-    <row r="42" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="17"/>
       <c r="B42" s="18" t="s">
         <v>16</v>
@@ -5884,7 +5883,7 @@
       </c>
       <c r="K42" s="20"/>
     </row>
-    <row r="43" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="24"/>
       <c r="B43" s="25" t="s">
         <v>47</v>
@@ -5902,7 +5901,7 @@
       </c>
       <c r="K43" s="26"/>
     </row>
-    <row r="44" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="24"/>
       <c r="B44" s="25" t="s">
         <v>48</v>
@@ -5920,7 +5919,7 @@
       </c>
       <c r="K44" s="26"/>
     </row>
-    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="24"/>
       <c r="B45" s="25" t="s">
         <v>49</v>
@@ -5938,7 +5937,7 @@
       </c>
       <c r="K45" s="26"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="15"/>
       <c r="B46" s="25" t="s">
         <v>50</v>
@@ -5956,7 +5955,7 @@
       </c>
       <c r="K46" s="15"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="15"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -5969,7 +5968,7 @@
       <c r="J47" s="15"/>
       <c r="K47" s="15"/>
     </row>
-    <row r="48" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="11">
         <v>6</v>
       </c>
@@ -5994,7 +5993,7 @@
       <c r="J48" s="13"/>
       <c r="K48" s="13"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
       <c r="B49" s="16" t="str">
         <f>B30</f>
@@ -6025,7 +6024,7 @@
       <c r="J49" s="15"/>
       <c r="K49" s="15"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="15"/>
       <c r="B50" s="16"/>
       <c r="C50" s="15">
@@ -6053,7 +6052,7 @@
       <c r="J50" s="15"/>
       <c r="K50" s="15"/>
     </row>
-    <row r="51" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17"/>
       <c r="B51" s="18" t="s">
         <v>16</v>
@@ -6078,7 +6077,7 @@
       </c>
       <c r="K51" s="20"/>
     </row>
-    <row r="52" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="24"/>
       <c r="B52" s="25" t="s">
         <v>39</v>
@@ -6096,7 +6095,7 @@
       </c>
       <c r="K52" s="26"/>
     </row>
-    <row r="53" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="24"/>
       <c r="B53" s="25" t="s">
         <v>38</v>
@@ -6114,7 +6113,7 @@
       </c>
       <c r="K53" s="26"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="15"/>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -6127,7 +6126,7 @@
       <c r="J54" s="15"/>
       <c r="K54" s="15"/>
     </row>
-    <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A55" s="11">
         <v>7</v>
       </c>
@@ -6144,7 +6143,7 @@
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="15"/>
       <c r="B56" s="16" t="str">
         <f>B10</f>
@@ -6171,7 +6170,7 @@
       <c r="J56" s="15"/>
       <c r="K56" s="15"/>
     </row>
-    <row r="57" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="17"/>
       <c r="B57" s="18" t="s">
         <v>16</v>
@@ -6196,7 +6195,7 @@
       </c>
       <c r="K57" s="20"/>
     </row>
-    <row r="58" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="24"/>
       <c r="B58" s="25" t="s">
         <v>32</v>
@@ -6214,7 +6213,7 @@
       </c>
       <c r="K58" s="26"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="15"/>
       <c r="B59" s="25" t="s">
         <v>31</v>
@@ -6232,7 +6231,7 @@
       </c>
       <c r="K59" s="15"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="15"/>
       <c r="B60" s="25" t="s">
         <v>33</v>
@@ -6250,7 +6249,7 @@
       </c>
       <c r="K60" s="15"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="15"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -6263,7 +6262,7 @@
       <c r="J61" s="15"/>
       <c r="K61" s="15"/>
     </row>
-    <row r="62" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A62" s="11">
         <v>8</v>
       </c>
@@ -6280,7 +6279,7 @@
       <c r="J62" s="15"/>
       <c r="K62" s="15"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="15"/>
       <c r="B63" s="16" t="str">
         <f>B56</f>
@@ -6308,7 +6307,7 @@
       <c r="J63" s="15"/>
       <c r="K63" s="15"/>
     </row>
-    <row r="64" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="17"/>
       <c r="B64" s="18" t="s">
         <v>16</v>
@@ -6333,7 +6332,7 @@
       </c>
       <c r="K64" s="20"/>
     </row>
-    <row r="65" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="24"/>
       <c r="B65" s="25" t="s">
         <v>32</v>
@@ -6351,7 +6350,7 @@
       </c>
       <c r="K65" s="26"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="15"/>
       <c r="B66" s="25" t="s">
         <v>31</v>
@@ -6369,7 +6368,7 @@
       </c>
       <c r="K66" s="15"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="15"/>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -6382,7 +6381,7 @@
       <c r="J67" s="15"/>
       <c r="K67" s="15"/>
     </row>
-    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A68" s="11">
         <v>9</v>
       </c>
@@ -6399,7 +6398,7 @@
       <c r="J68" s="15"/>
       <c r="K68" s="15"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="15"/>
       <c r="B69" s="16" t="s">
         <v>118</v>
@@ -6427,7 +6426,7 @@
       <c r="J69" s="15"/>
       <c r="K69" s="15"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="15"/>
       <c r="B70" s="16"/>
       <c r="C70" s="3">
@@ -6453,7 +6452,7 @@
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="15"/>
       <c r="B71" s="16" t="s">
         <v>120</v>
@@ -6481,7 +6480,7 @@
       <c r="J71" s="15"/>
       <c r="K71" s="15"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="15"/>
       <c r="B72" s="16" t="s">
         <v>119</v>
@@ -6510,7 +6509,7 @@
       <c r="J72" s="15"/>
       <c r="K72" s="15"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="15"/>
       <c r="B73" s="16" t="s">
         <v>68</v>
@@ -6536,7 +6535,7 @@
       <c r="J73" s="15"/>
       <c r="K73" s="15"/>
     </row>
-    <row r="74" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="17"/>
       <c r="B74" s="18" t="s">
         <v>16</v>
@@ -6562,7 +6561,7 @@
       </c>
       <c r="K74" s="20"/>
     </row>
-    <row r="75" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="24"/>
       <c r="B75" s="25" t="s">
         <v>55</v>
@@ -6580,7 +6579,7 @@
       </c>
       <c r="K75" s="26"/>
     </row>
-    <row r="76" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="24"/>
       <c r="B76" s="25" t="s">
         <v>32</v>
@@ -6598,7 +6597,7 @@
       </c>
       <c r="K76" s="26"/>
     </row>
-    <row r="77" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="24"/>
       <c r="B77" s="25" t="s">
         <v>64</v>
@@ -6616,7 +6615,7 @@
       </c>
       <c r="K77" s="26"/>
     </row>
-    <row r="78" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="24"/>
       <c r="B78" s="25" t="s">
         <v>36</v>
@@ -6634,7 +6633,7 @@
       </c>
       <c r="K78" s="26"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="15"/>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -6647,7 +6646,7 @@
       <c r="J79" s="15"/>
       <c r="K79" s="15"/>
     </row>
-    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A80" s="11">
         <v>10</v>
       </c>
@@ -6664,7 +6663,7 @@
       <c r="J80" s="15"/>
       <c r="K80" s="15"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="15"/>
       <c r="B81" s="16" t="str">
         <f>B69</f>
@@ -6691,7 +6690,7 @@
       <c r="J81" s="15"/>
       <c r="K81" s="15"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="15"/>
       <c r="B82" s="16"/>
       <c r="C82" s="45">
@@ -6715,7 +6714,7 @@
       <c r="J82" s="15"/>
       <c r="K82" s="15"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="15"/>
       <c r="B83" s="16" t="str">
         <f>B73</f>
@@ -6743,7 +6742,7 @@
       <c r="J83" s="15"/>
       <c r="K83" s="15"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="15"/>
       <c r="B84" s="16" t="str">
         <f>B71</f>
@@ -6771,7 +6770,7 @@
       <c r="J84" s="15"/>
       <c r="K84" s="15"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="15"/>
       <c r="B85" s="16" t="str">
         <f>B72</f>
@@ -6799,7 +6798,7 @@
       <c r="J85" s="15"/>
       <c r="K85" s="15"/>
     </row>
-    <row r="86" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="17"/>
       <c r="B86" s="18" t="s">
         <v>16</v>
@@ -6824,7 +6823,7 @@
       </c>
       <c r="K86" s="20"/>
     </row>
-    <row r="87" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="24"/>
       <c r="B87" s="25" t="s">
         <v>32</v>
@@ -6842,7 +6841,7 @@
       </c>
       <c r="K87" s="26"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="15"/>
       <c r="B88" s="25" t="s">
         <v>31</v>
@@ -6860,7 +6859,7 @@
       </c>
       <c r="K88" s="15"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="15"/>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -6873,7 +6872,7 @@
       <c r="J89" s="15"/>
       <c r="K89" s="15"/>
     </row>
-    <row r="90" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A90" s="11">
         <v>11</v>
       </c>
@@ -6890,7 +6889,7 @@
       <c r="J90" s="15"/>
       <c r="K90" s="15"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="15"/>
       <c r="B91" s="16" t="s">
         <v>121</v>
@@ -6911,7 +6910,7 @@
       <c r="J91" s="15"/>
       <c r="K91" s="15"/>
     </row>
-    <row r="92" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="17"/>
       <c r="B92" s="18" t="s">
         <v>16</v>
@@ -6936,7 +6935,7 @@
       </c>
       <c r="K92" s="20"/>
     </row>
-    <row r="93" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="24"/>
       <c r="B93" s="25" t="s">
         <v>74</v>
@@ -6954,7 +6953,7 @@
       </c>
       <c r="K93" s="26"/>
     </row>
-    <row r="94" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="24"/>
       <c r="B94" s="25" t="s">
         <v>75</v>
@@ -6972,7 +6971,7 @@
       </c>
       <c r="K94" s="26"/>
     </row>
-    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="24"/>
       <c r="B95" s="25"/>
       <c r="C95" s="26"/>
@@ -6985,7 +6984,7 @@
       <c r="J95" s="22"/>
       <c r="K95" s="26"/>
     </row>
-    <row r="96" spans="1:11" s="10" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" s="10" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A96" s="24">
         <v>13</v>
       </c>
@@ -7002,7 +7001,7 @@
       <c r="J96" s="22"/>
       <c r="K96" s="26"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="15"/>
       <c r="B97" s="16" t="s">
         <v>79</v>
@@ -7028,7 +7027,7 @@
       <c r="J97" s="15"/>
       <c r="K97" s="15"/>
     </row>
-    <row r="98" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="17"/>
       <c r="B98" s="18" t="s">
         <v>16</v>
@@ -7053,7 +7052,7 @@
       </c>
       <c r="K98" s="20"/>
     </row>
-    <row r="99" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="24"/>
       <c r="B99" s="25" t="s">
         <v>74</v>
@@ -7071,7 +7070,7 @@
       </c>
       <c r="K99" s="26"/>
     </row>
-    <row r="100" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="24"/>
       <c r="B100" s="25"/>
       <c r="C100" s="26"/>
@@ -7084,11 +7083,11 @@
       <c r="J100" s="22"/>
       <c r="K100" s="26"/>
     </row>
-    <row r="101" spans="1:11" s="10" customFormat="1" ht="166.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" s="10" customFormat="1" ht="166.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="24">
         <v>1</v>
       </c>
-      <c r="B101" s="75" t="s">
+      <c r="B101" s="56" t="s">
         <v>123</v>
       </c>
       <c r="C101" s="26"/>
@@ -7101,7 +7100,7 @@
       <c r="J101" s="26"/>
       <c r="K101" s="26"/>
     </row>
-    <row r="102" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="24"/>
       <c r="B102" s="25" t="s">
         <v>130</v>
@@ -7110,25 +7109,26 @@
         <v>0.5</v>
       </c>
       <c r="D102" s="27">
-        <v>7.5</v>
+        <f>D124</f>
+        <v>5.64</v>
       </c>
       <c r="E102" s="27">
         <f>E108</f>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="F102" s="27">
         <v>1.5</v>
       </c>
       <c r="G102" s="27">
         <f>PRODUCT(C102:F102)</f>
-        <v>8.4375</v>
+        <v>5.2874999999999996</v>
       </c>
       <c r="H102" s="26"/>
       <c r="I102" s="26"/>
       <c r="J102" s="26"/>
       <c r="K102" s="26"/>
     </row>
-    <row r="103" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="24"/>
       <c r="B103" s="25"/>
       <c r="C103" s="26">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="D103" s="27">
         <f>D109</f>
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="E103" s="27">
         <f>E109</f>
@@ -7147,14 +7147,14 @@
       </c>
       <c r="G103" s="27">
         <f>PRODUCT(C103:F103)</f>
-        <v>5</v>
+        <v>7.8125</v>
       </c>
       <c r="H103" s="26"/>
       <c r="I103" s="26"/>
       <c r="J103" s="26"/>
       <c r="K103" s="26"/>
     </row>
-    <row r="104" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="17"/>
       <c r="B104" s="18" t="s">
         <v>16</v>
@@ -7165,7 +7165,7 @@
       <c r="F104" s="20"/>
       <c r="G104" s="2">
         <f>SUM(G102:G103)</f>
-        <v>13.4375</v>
+        <v>13.1</v>
       </c>
       <c r="H104" s="21" t="s">
         <v>124</v>
@@ -7175,11 +7175,11 @@
       </c>
       <c r="J104" s="22">
         <f>G104*I104</f>
-        <v>845.890625</v>
+        <v>824.64499999999998</v>
       </c>
       <c r="K104" s="20"/>
     </row>
-    <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="24"/>
       <c r="B105" s="25" t="s">
         <v>125</v>
@@ -7193,11 +7193,11 @@
       <c r="I105" s="26"/>
       <c r="J105" s="22">
         <f>0.13*G104*(18612)/360</f>
-        <v>90.313437499999992</v>
+        <v>88.045100000000005</v>
       </c>
       <c r="K105" s="26"/>
     </row>
-    <row r="106" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="24"/>
       <c r="B106" s="26"/>
       <c r="C106" s="26"/>
@@ -7210,11 +7210,11 @@
       <c r="J106" s="26"/>
       <c r="K106" s="26"/>
     </row>
-    <row r="107" spans="1:11" s="10" customFormat="1" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" s="10" customFormat="1" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A107" s="24">
         <v>2</v>
       </c>
-      <c r="B107" s="75" t="s">
+      <c r="B107" s="56" t="s">
         <v>126</v>
       </c>
       <c r="C107" s="26"/>
@@ -7227,7 +7227,7 @@
       <c r="J107" s="26"/>
       <c r="K107" s="26"/>
     </row>
-    <row r="108" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="24"/>
       <c r="B108" s="25" t="str">
         <f>B102</f>
@@ -7237,26 +7237,26 @@
         <v>1</v>
       </c>
       <c r="D108" s="27">
-        <f>D102</f>
-        <v>7.5</v>
+        <f>D124</f>
+        <v>5.64</v>
       </c>
       <c r="E108" s="27">
         <f>E114</f>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="F108" s="27">
         <v>0.15</v>
       </c>
       <c r="G108" s="27">
         <f>PRODUCT(C108:F108)</f>
-        <v>1.6875</v>
+        <v>1.0574999999999999</v>
       </c>
       <c r="H108" s="26"/>
       <c r="I108" s="26"/>
       <c r="J108" s="26"/>
       <c r="K108" s="26"/>
     </row>
-    <row r="109" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" s="24"/>
       <c r="B109" s="25"/>
       <c r="C109" s="26">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D109" s="27">
         <f>D115</f>
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="E109" s="27">
         <f>E115</f>
@@ -7275,14 +7275,14 @@
       </c>
       <c r="G109" s="27">
         <f>PRODUCT(C109:F109)</f>
-        <v>1.5</v>
+        <v>2.34375</v>
       </c>
       <c r="H109" s="26"/>
       <c r="I109" s="26"/>
       <c r="J109" s="26"/>
       <c r="K109" s="26"/>
     </row>
-    <row r="110" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="17"/>
       <c r="B110" s="18" t="s">
         <v>16</v>
@@ -7293,7 +7293,7 @@
       <c r="F110" s="20"/>
       <c r="G110" s="2">
         <f>SUM(G108:G109)</f>
-        <v>3.1875</v>
+        <v>3.4012500000000001</v>
       </c>
       <c r="H110" s="21" t="s">
         <v>124</v>
@@ -7303,11 +7303,11 @@
       </c>
       <c r="J110" s="22">
         <f>G110*I110</f>
-        <v>14211.532500000001</v>
+        <v>15164.541150000003</v>
       </c>
       <c r="K110" s="20"/>
     </row>
-    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="24"/>
       <c r="B111" s="25" t="s">
         <v>125</v>
@@ -7321,11 +7321,11 @@
       <c r="I111" s="26"/>
       <c r="J111" s="22">
         <f>0.13*G110*(14817.6)/5</f>
-        <v>1228.0085999999999</v>
+        <v>1310.3574120000001</v>
       </c>
       <c r="K111" s="26"/>
     </row>
-    <row r="112" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="24"/>
       <c r="B112" s="26"/>
       <c r="C112" s="26"/>
@@ -7338,11 +7338,11 @@
       <c r="J112" s="26"/>
       <c r="K112" s="26"/>
     </row>
-    <row r="113" spans="1:11" s="10" customFormat="1" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" s="10" customFormat="1" ht="78" x14ac:dyDescent="0.3">
       <c r="A113" s="24">
         <v>3</v>
       </c>
-      <c r="B113" s="75" t="s">
+      <c r="B113" s="56" t="s">
         <v>127</v>
       </c>
       <c r="C113" s="26"/>
@@ -7355,7 +7355,7 @@
       <c r="J113" s="26"/>
       <c r="K113" s="26"/>
     </row>
-    <row r="114" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="24"/>
       <c r="B114" s="25" t="str">
         <f>B108</f>
@@ -7365,26 +7365,26 @@
         <v>1</v>
       </c>
       <c r="D114" s="27">
-        <f>D108</f>
-        <v>7.5</v>
+        <f>D124</f>
+        <v>5.64</v>
       </c>
       <c r="E114" s="27">
         <f>F124/2</f>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="F114" s="27">
         <v>0.05</v>
       </c>
       <c r="G114" s="27">
         <f>PRODUCT(C114:F114)</f>
-        <v>0.5625</v>
+        <v>0.35250000000000004</v>
       </c>
       <c r="H114" s="26"/>
       <c r="I114" s="26"/>
       <c r="J114" s="26"/>
       <c r="K114" s="26"/>
     </row>
-    <row r="115" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="24"/>
       <c r="B115" s="25"/>
       <c r="C115" s="26">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="D115" s="27">
         <f>D125</f>
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="E115" s="27">
         <f>F125/2</f>
@@ -7403,14 +7403,14 @@
       </c>
       <c r="G115" s="27">
         <f>PRODUCT(C115:F115)</f>
-        <v>0.5</v>
+        <v>0.78125</v>
       </c>
       <c r="H115" s="26"/>
       <c r="I115" s="26"/>
       <c r="J115" s="26"/>
       <c r="K115" s="26"/>
     </row>
-    <row r="116" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="17"/>
       <c r="B116" s="18" t="s">
         <v>16</v>
@@ -7421,7 +7421,7 @@
       <c r="F116" s="20"/>
       <c r="G116" s="2">
         <f>SUM(G114:G115)</f>
-        <v>1.0625</v>
+        <v>1.13375</v>
       </c>
       <c r="H116" s="21" t="s">
         <v>124</v>
@@ -7431,11 +7431,11 @@
       </c>
       <c r="J116" s="22">
         <f>G116*I116</f>
-        <v>11649.738749999999</v>
+        <v>12430.956525</v>
       </c>
       <c r="K116" s="20"/>
     </row>
-    <row r="117" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="24"/>
       <c r="B117" s="25" t="s">
         <v>32</v>
@@ -7449,11 +7449,11 @@
       <c r="I117" s="26"/>
       <c r="J117" s="22">
         <f>0.13*G116*(53818.03)/15</f>
-        <v>495.57435958333332</v>
+        <v>528.80699310833336</v>
       </c>
       <c r="K117" s="26"/>
     </row>
-    <row r="118" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="24"/>
       <c r="B118" s="25" t="s">
         <v>31</v>
@@ -7467,11 +7467,11 @@
       <c r="I118" s="26"/>
       <c r="J118" s="22">
         <f>0.13*G116*(21432.6)/15</f>
-        <v>197.35852499999999</v>
+        <v>210.59315549999999</v>
       </c>
       <c r="K118" s="26"/>
     </row>
-    <row r="119" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="24"/>
       <c r="B119" s="25" t="s">
         <v>33</v>
@@ -7485,11 +7485,11 @@
       <c r="I119" s="26"/>
       <c r="J119" s="22">
         <f>0.13*G116*(25719.12+13573.98+4286.52)/15</f>
-        <v>401.29566749999992</v>
+        <v>428.20608284999997</v>
       </c>
       <c r="K119" s="26"/>
     </row>
-    <row r="120" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="24"/>
       <c r="B120" s="25" t="s">
         <v>128</v>
@@ -7503,11 +7503,11 @@
       <c r="I120" s="26"/>
       <c r="J120" s="22">
         <f>0.13*G116*(6325.7)/15</f>
-        <v>58.249154166666663</v>
+        <v>62.155273916666673</v>
       </c>
       <c r="K120" s="26"/>
     </row>
-    <row r="121" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="24"/>
       <c r="B121" s="25" t="s">
         <v>36</v>
@@ -7521,11 +7521,11 @@
       <c r="I121" s="26"/>
       <c r="J121" s="22">
         <f>0.13*G116*(310)/5</f>
-        <v>8.5637500000000006</v>
+        <v>9.1380250000000007</v>
       </c>
       <c r="K121" s="26"/>
     </row>
-    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="24"/>
       <c r="B122" s="26"/>
       <c r="C122" s="26"/>
@@ -7538,11 +7538,11 @@
       <c r="J122" s="26"/>
       <c r="K122" s="26"/>
     </row>
-    <row r="123" spans="1:11" s="10" customFormat="1" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" s="10" customFormat="1" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A123" s="24">
         <v>4</v>
       </c>
-      <c r="B123" s="75" t="s">
+      <c r="B123" s="56" t="s">
         <v>129</v>
       </c>
       <c r="C123" s="26"/>
@@ -7555,7 +7555,7 @@
       <c r="J123" s="26"/>
       <c r="K123" s="26"/>
     </row>
-    <row r="124" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="24"/>
       <c r="B124" s="25" t="str">
         <f>B114</f>
@@ -7565,32 +7565,32 @@
         <v>1</v>
       </c>
       <c r="D124" s="27">
-        <v>7.5</v>
+        <v>5.64</v>
       </c>
       <c r="E124" s="27">
         <f>((F124/2)+0.45)/2</f>
-        <v>0.97499999999999998</v>
+        <v>0.85</v>
       </c>
       <c r="F124" s="27">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G124" s="27">
         <f>PRODUCT(C124:F124)</f>
-        <v>21.9375</v>
+        <v>11.984999999999999</v>
       </c>
       <c r="H124" s="26"/>
       <c r="I124" s="26"/>
       <c r="J124" s="26"/>
       <c r="K124" s="26"/>
     </row>
-    <row r="125" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="24"/>
       <c r="B125" s="25"/>
       <c r="C125" s="26">
         <v>1</v>
       </c>
       <c r="D125" s="27">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="E125" s="27">
         <f>((F125/2)+0.45)/2</f>
@@ -7601,14 +7601,14 @@
       </c>
       <c r="G125" s="27">
         <f>PRODUCT(C125:F125)</f>
-        <v>17</v>
+        <v>26.5625</v>
       </c>
       <c r="H125" s="26"/>
       <c r="I125" s="26"/>
       <c r="J125" s="26"/>
       <c r="K125" s="26"/>
     </row>
-    <row r="126" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="17"/>
       <c r="B126" s="18" t="s">
         <v>16</v>
@@ -7619,7 +7619,7 @@
       <c r="F126" s="20"/>
       <c r="G126" s="2">
         <f>SUM(G124:G125)</f>
-        <v>38.9375</v>
+        <v>38.547499999999999</v>
       </c>
       <c r="H126" s="21" t="s">
         <v>124</v>
@@ -7629,11 +7629,11 @@
       </c>
       <c r="J126" s="22">
         <f>G126*I126</f>
-        <v>383940.49312500004</v>
+        <v>380094.92542500002</v>
       </c>
       <c r="K126" s="20"/>
     </row>
-    <row r="127" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="24"/>
       <c r="B127" s="25" t="s">
         <v>32</v>
@@ -7647,11 +7647,11 @@
       <c r="I127" s="26"/>
       <c r="J127" s="22">
         <f>0.13*G126*(22152.7)/10</f>
-        <v>11213.419831250001</v>
+        <v>11101.105642250001</v>
       </c>
       <c r="K127" s="26"/>
     </row>
-    <row r="128" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="24"/>
       <c r="B128" s="25" t="s">
         <v>31</v>
@@ -7665,11 +7665,11 @@
       <c r="I128" s="26"/>
       <c r="J128" s="22">
         <f>0.13*G126*(9525.6)/10</f>
-        <v>4821.7396500000013</v>
+        <v>4773.4448579999998</v>
       </c>
       <c r="K128" s="26"/>
     </row>
-    <row r="129" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="24"/>
       <c r="B129" s="25" t="s">
         <v>131</v>
@@ -7683,11 +7683,11 @@
       <c r="I129" s="26"/>
       <c r="J129" s="22">
         <f>0.13*G126*(11331.936)/10</f>
-        <v>5736.0843540000005</v>
+        <v>5678.6314384799998</v>
       </c>
       <c r="K129" s="26"/>
     </row>
-    <row r="130" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="24"/>
       <c r="B130" s="25" t="s">
         <v>33</v>
@@ -7701,13 +7701,13 @@
       <c r="I130" s="26"/>
       <c r="J130" s="22">
         <f>0.13*G126*(10954.44+5228.496+2286.144)/10</f>
-        <v>9348.8174325000018</v>
+        <v>9255.1791969000005</v>
       </c>
       <c r="K130" s="26"/>
     </row>
-    <row r="131" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A131" s="24"/>
-      <c r="B131" s="76" t="s">
+      <c r="B131" s="57" t="s">
         <v>132</v>
       </c>
       <c r="C131" s="26"/>
@@ -7719,11 +7719,11 @@
       <c r="I131" s="26"/>
       <c r="J131" s="22">
         <f>0.13*G126*(3564.01)/10</f>
-        <v>1804.0573118750003</v>
+        <v>1785.987781175</v>
       </c>
       <c r="K131" s="26"/>
     </row>
-    <row r="132" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A132" s="24"/>
       <c r="B132" s="26"/>
       <c r="C132" s="26"/>
@@ -7736,7 +7736,7 @@
       <c r="J132" s="26"/>
       <c r="K132" s="26"/>
     </row>
-    <row r="133" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" s="10" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A133" s="17">
         <v>14</v>
       </c>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="K133" s="20"/>
     </row>
-    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="17"/>
       <c r="B134" s="31"/>
       <c r="C134" s="19"/>
@@ -7778,7 +7778,7 @@
       <c r="J134" s="22"/>
       <c r="K134" s="20"/>
     </row>
-    <row r="135" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="17">
         <v>15</v>
       </c>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="K135" s="20"/>
     </row>
-    <row r="136" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="17"/>
       <c r="B136" s="31"/>
       <c r="C136" s="19"/>
@@ -7820,7 +7820,7 @@
       <c r="J136" s="22"/>
       <c r="K136" s="20"/>
     </row>
-    <row r="137" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="32"/>
       <c r="B137" s="33" t="s">
         <v>20</v>
@@ -7834,21 +7834,21 @@
       <c r="I137" s="22"/>
       <c r="J137" s="22">
         <f>SUM(J10:J135)</f>
-        <v>813165.68224879541</v>
+        <v>810861.26423460047</v>
       </c>
       <c r="K137" s="36"/>
     </row>
-    <row r="138" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="139" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="37"/>
       <c r="B139" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C139" s="60">
+      <c r="C139" s="58">
         <f>J137</f>
-        <v>813165.68224879541</v>
-      </c>
-      <c r="D139" s="61"/>
+        <v>810861.26423460047</v>
+      </c>
+      <c r="D139" s="59"/>
       <c r="E139" s="39">
         <v>100</v>
       </c>
@@ -7859,72 +7859,79 @@
       <c r="J139" s="42"/>
       <c r="K139" s="43"/>
     </row>
-    <row r="140" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B140" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C140" s="64">
+      <c r="C140" s="60">
         <v>700000</v>
       </c>
-      <c r="D140" s="65"/>
+      <c r="D140" s="61"/>
       <c r="E140" s="39"/>
     </row>
-    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B141" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C141" s="64">
+      <c r="C141" s="60">
         <f>C140-C143-C144</f>
         <v>665000</v>
       </c>
-      <c r="D141" s="65"/>
+      <c r="D141" s="61"/>
       <c r="E141" s="39">
         <f>C141/C139*100</f>
-        <v>81.779152086319513</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>82.011563424196382</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B142" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C142" s="66">
+      <c r="C142" s="62">
         <f>C139-C141</f>
-        <v>148165.68224879541</v>
-      </c>
-      <c r="D142" s="66"/>
+        <v>145861.26423460047</v>
+      </c>
+      <c r="D142" s="62"/>
       <c r="E142" s="39">
         <f>100-E141</f>
-        <v>18.220847913680487</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>17.988436575803618</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B143" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C143" s="60">
+      <c r="C143" s="58">
         <f>C140*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D143" s="61"/>
+      <c r="D143" s="59"/>
       <c r="E143" s="39">
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B144" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C144" s="60">
+      <c r="C144" s="58">
         <f>C140*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D144" s="61"/>
+      <c r="D144" s="59"/>
       <c r="E144" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C143:D143"/>
     <mergeCell ref="C144:D144"/>
     <mergeCell ref="A7:F7"/>
@@ -7933,13 +7940,6 @@
     <mergeCell ref="C140:D140"/>
     <mergeCell ref="C141:D141"/>
     <mergeCell ref="C142:D142"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -7950,133 +7950,133 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAEEC707-87B5-428A-A0F5-809434590EB3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K202"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="8.5703125" style="10" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="10"/>
+    <col min="1" max="1" width="4.6640625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="4.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" style="10" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="10"/>
     <col min="8" max="8" width="5" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="10"/>
+    <col min="9" max="9" width="9.5546875" style="10" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="59" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+    </row>
+    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="68" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="54" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="62" t="s">
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="63" t="s">
+      <c r="H7" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="63"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -8111,11 +8111,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A9" s="24">
         <v>1</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="56" t="s">
         <v>123</v>
       </c>
       <c r="C9" s="26"/>
@@ -8128,7 +8128,7 @@
       <c r="J9" s="26"/>
       <c r="K9" s="26"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="24"/>
       <c r="B10" s="25" t="s">
         <v>130</v>
@@ -8154,7 +8154,7 @@
       <c r="J10" s="26"/>
       <c r="K10" s="26"/>
     </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17"/>
       <c r="B11" s="18" t="s">
         <v>16</v>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="K11" s="20"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="24"/>
       <c r="B12" s="25" t="s">
         <v>125</v>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="K12" s="26"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="24"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
@@ -8210,11 +8210,11 @@
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
     </row>
-    <row r="14" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A14" s="24">
         <v>2</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="56" t="s">
         <v>126</v>
       </c>
       <c r="C14" s="26"/>
@@ -8227,7 +8227,7 @@
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="24"/>
       <c r="B15" s="25" t="str">
         <f>B10</f>
@@ -8238,25 +8238,25 @@
       </c>
       <c r="D15" s="27">
         <f>D29</f>
-        <v>5.64</v>
+        <v>7.6</v>
       </c>
       <c r="E15" s="27">
         <f>E20</f>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="F15" s="27">
         <v>0.15</v>
       </c>
       <c r="G15" s="27">
         <f>PRODUCT(C15:F15)</f>
-        <v>1.2689999999999999</v>
+        <v>1.425</v>
       </c>
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
       <c r="K15" s="26"/>
     </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17"/>
       <c r="B16" s="18" t="s">
         <v>16</v>
@@ -8267,7 +8267,7 @@
       <c r="F16" s="20"/>
       <c r="G16" s="2">
         <f>SUM(G15:G15)</f>
-        <v>1.2689999999999999</v>
+        <v>1.425</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>124</v>
@@ -8277,11 +8277,11 @@
       </c>
       <c r="J16" s="22">
         <f>G16*I16</f>
-        <v>5657.8618800000004</v>
+        <v>6353.3910000000005</v>
       </c>
       <c r="K16" s="20"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="24"/>
       <c r="B17" s="25" t="s">
         <v>125</v>
@@ -8295,11 +8295,11 @@
       <c r="I17" s="26"/>
       <c r="J17" s="22">
         <f>0.13*G16*(14817.6)/5</f>
-        <v>488.89189440000001</v>
+        <v>548.9920800000001</v>
       </c>
       <c r="K17" s="26"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="24"/>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
@@ -8312,11 +8312,11 @@
       <c r="J18" s="26"/>
       <c r="K18" s="26"/>
     </row>
-    <row r="19" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="78" x14ac:dyDescent="0.3">
       <c r="A19" s="24">
         <v>3</v>
       </c>
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="56" t="s">
         <v>127</v>
       </c>
       <c r="C19" s="26"/>
@@ -8329,7 +8329,7 @@
       <c r="J19" s="26"/>
       <c r="K19" s="26"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="24"/>
       <c r="B20" s="25" t="str">
         <f>B15</f>
@@ -8340,25 +8340,25 @@
       </c>
       <c r="D20" s="27">
         <f>D29</f>
-        <v>5.64</v>
+        <v>7.6</v>
       </c>
       <c r="E20" s="27">
         <f>F29/2</f>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="F20" s="27">
         <v>0.05</v>
       </c>
       <c r="G20" s="27">
         <f>PRODUCT(C20:F20)</f>
-        <v>0.42299999999999999</v>
+        <v>0.47500000000000003</v>
       </c>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
       <c r="K20" s="26"/>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="18" t="s">
         <v>16</v>
@@ -8369,7 +8369,7 @@
       <c r="F21" s="20"/>
       <c r="G21" s="2">
         <f>SUM(G20:G20)</f>
-        <v>0.42299999999999999</v>
+        <v>0.47500000000000003</v>
       </c>
       <c r="H21" s="21" t="s">
         <v>124</v>
@@ -8379,11 +8379,11 @@
       </c>
       <c r="J21" s="22">
         <f>G21*I21</f>
-        <v>4637.9665799999993</v>
+        <v>5208.1184999999996</v>
       </c>
       <c r="K21" s="20"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="24"/>
       <c r="B22" s="25" t="s">
         <v>32</v>
@@ -8397,11 +8397,11 @@
       <c r="I22" s="26"/>
       <c r="J22" s="22">
         <f>0.13*G21*(53818.03)/15</f>
-        <v>197.29689797999998</v>
+        <v>221.55089016666668</v>
       </c>
       <c r="K22" s="26"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="24"/>
       <c r="B23" s="25" t="s">
         <v>31</v>
@@ -8415,11 +8415,11 @@
       <c r="I23" s="26"/>
       <c r="J23" s="22">
         <f>0.13*G21*(21432.6)/15</f>
-        <v>78.571911599999993</v>
+        <v>88.23087000000001</v>
       </c>
       <c r="K23" s="26"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="24"/>
       <c r="B24" s="25" t="s">
         <v>33</v>
@@ -8433,11 +8433,11 @@
       <c r="I24" s="26"/>
       <c r="J24" s="22">
         <f>0.13*G21*(25719.12+13573.98+4286.52)/15</f>
-        <v>159.76288691999997</v>
+        <v>179.40276899999998</v>
       </c>
       <c r="K24" s="26"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="24"/>
       <c r="B25" s="25" t="s">
         <v>128</v>
@@ -8451,11 +8451,11 @@
       <c r="I25" s="26"/>
       <c r="J25" s="22">
         <f>0.13*G21*(6325.7)/15</f>
-        <v>23.190016199999999</v>
+        <v>26.040798333333335</v>
       </c>
       <c r="K25" s="26"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="24"/>
       <c r="B26" s="25" t="s">
         <v>36</v>
@@ -8469,11 +8469,11 @@
       <c r="I26" s="26"/>
       <c r="J26" s="22">
         <f>0.13*G21*(310)/5</f>
-        <v>3.4093800000000001</v>
+        <v>3.8285000000000005</v>
       </c>
       <c r="K26" s="26"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="24"/>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -8486,11 +8486,11 @@
       <c r="J27" s="26"/>
       <c r="K27" s="26"/>
     </row>
-    <row r="28" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A28" s="24">
         <v>4</v>
       </c>
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="56" t="s">
         <v>129</v>
       </c>
       <c r="C28" s="26"/>
@@ -8503,7 +8503,7 @@
       <c r="J28" s="26"/>
       <c r="K28" s="26"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="24"/>
       <c r="B29" s="25" t="str">
         <f>B20</f>
@@ -8513,25 +8513,25 @@
         <v>1</v>
       </c>
       <c r="D29" s="27">
-        <v>5.64</v>
+        <v>7.6</v>
       </c>
       <c r="E29" s="27">
         <f>((F29/2)+0.45)/2</f>
-        <v>0.97499999999999998</v>
+        <v>0.85</v>
       </c>
       <c r="F29" s="27">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G29" s="27">
         <f>PRODUCT(C29:F29)</f>
-        <v>16.497</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
       <c r="K29" s="26"/>
     </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17"/>
       <c r="B30" s="18" t="s">
         <v>16</v>
@@ -8542,7 +8542,7 @@
       <c r="F30" s="20"/>
       <c r="G30" s="2">
         <f>SUM(G29:G29)</f>
-        <v>16.497</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="H30" s="21" t="s">
         <v>124</v>
@@ -8552,11 +8552,11 @@
       </c>
       <c r="J30" s="22">
         <f>G30*I30</f>
-        <v>162667.51371</v>
+        <v>159245.94449999998</v>
       </c>
       <c r="K30" s="20"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="24"/>
       <c r="B31" s="25" t="s">
         <v>32</v>
@@ -8570,11 +8570,11 @@
       <c r="I31" s="26"/>
       <c r="J31" s="22">
         <f>0.13*G30*(22152.7)/10</f>
-        <v>4750.8901947000004</v>
+        <v>4650.9593650000006</v>
       </c>
       <c r="K31" s="26"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="24"/>
       <c r="B32" s="25" t="s">
         <v>31</v>
@@ -8588,11 +8588,11 @@
       <c r="I32" s="26"/>
       <c r="J32" s="22">
         <f>0.13*G30*(9525.6)/10</f>
-        <v>2042.8697016000001</v>
+        <v>1999.8997200000001</v>
       </c>
       <c r="K32" s="26"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="24"/>
       <c r="B33" s="25" t="s">
         <v>131</v>
@@ -8606,11 +8606,11 @@
       <c r="I33" s="26"/>
       <c r="J33" s="22">
         <f>0.13*G30*(11331.936)/10</f>
-        <v>2430.2583264960003</v>
+        <v>2379.1399631999998</v>
       </c>
       <c r="K33" s="26"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="24"/>
       <c r="B34" s="25" t="s">
         <v>33</v>
@@ -8624,13 +8624,13 @@
       <c r="I34" s="26"/>
       <c r="J34" s="22">
         <f>0.13*G30*(10954.44+5228.496+2286.144)/10</f>
-        <v>3960.897365880001</v>
+        <v>3877.5833460000003</v>
       </c>
       <c r="K34" s="26"/>
     </row>
-    <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="24"/>
-      <c r="B35" s="76" t="s">
+      <c r="B35" s="57" t="s">
         <v>132</v>
       </c>
       <c r="C35" s="26"/>
@@ -8642,11 +8642,11 @@
       <c r="I35" s="26"/>
       <c r="J35" s="22">
         <f>0.13*G30*(3564.01)/10</f>
-        <v>764.34114861000012</v>
+        <v>748.26389949999998</v>
       </c>
       <c r="K35" s="26"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="24"/>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
@@ -8659,7 +8659,7 @@
       <c r="J36" s="26"/>
       <c r="K36" s="26"/>
     </row>
-    <row r="37" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="24">
         <v>1</v>
       </c>
@@ -8676,7 +8676,7 @@
       <c r="J37" s="38"/>
       <c r="K37" s="38"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="26"/>
       <c r="B38" s="25" t="s">
         <v>57</v>
@@ -8705,7 +8705,7 @@
       <c r="J38" s="26"/>
       <c r="K38" s="26"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="26"/>
       <c r="B39" s="25" t="s">
         <v>89</v>
@@ -8732,7 +8732,7 @@
       <c r="J39" s="26"/>
       <c r="K39" s="26"/>
     </row>
-    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="17"/>
       <c r="B40" s="18" t="s">
         <v>16</v>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="K40" s="20"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="26"/>
       <c r="B41" s="26"/>
       <c r="C41" s="26"/>
@@ -8770,7 +8770,7 @@
       <c r="J41" s="26"/>
       <c r="K41" s="26"/>
     </row>
-    <row r="42" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="24">
         <v>2</v>
       </c>
@@ -8787,7 +8787,7 @@
       <c r="J42" s="38"/>
       <c r="K42" s="38"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="26"/>
       <c r="B43" s="25" t="str">
         <f t="shared" ref="B43:E44" si="0">B38</f>
@@ -8815,7 +8815,7 @@
       <c r="J43" s="26"/>
       <c r="K43" s="26"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="26"/>
       <c r="B44" s="25" t="str">
         <f t="shared" si="0"/>
@@ -8843,7 +8843,7 @@
       <c r="J44" s="26"/>
       <c r="K44" s="26"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="26"/>
       <c r="B45" s="25" t="s">
         <v>52</v>
@@ -8869,7 +8869,7 @@
       <c r="J45" s="26"/>
       <c r="K45" s="26"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="26"/>
       <c r="B46" s="25" t="str">
         <f>B173</f>
@@ -8895,7 +8895,7 @@
       <c r="J46" s="26"/>
       <c r="K46" s="26"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="26"/>
       <c r="B47" s="25"/>
       <c r="C47" s="26">
@@ -8918,7 +8918,7 @@
       <c r="J47" s="26"/>
       <c r="K47" s="26"/>
     </row>
-    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="17"/>
       <c r="B48" s="18" t="s">
         <v>16</v>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="K48" s="20"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="24"/>
       <c r="B49" s="25" t="s">
         <v>55</v>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="K49" s="26"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="26"/>
       <c r="B50" s="25" t="s">
         <v>31</v>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="K50" s="26"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="26"/>
       <c r="B51" s="26"/>
       <c r="C51" s="26"/>
@@ -8992,7 +8992,7 @@
       <c r="J51" s="26"/>
       <c r="K51" s="26"/>
     </row>
-    <row r="52" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="24">
         <v>3</v>
       </c>
@@ -9009,7 +9009,7 @@
       <c r="J52" s="38"/>
       <c r="K52" s="38"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="26"/>
       <c r="B53" s="25" t="str">
         <f>B43</f>
@@ -9039,7 +9039,7 @@
       <c r="J53" s="26"/>
       <c r="K53" s="26"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="26"/>
       <c r="B54" s="25" t="str">
         <f>B44</f>
@@ -9069,7 +9069,7 @@
       <c r="J54" s="26"/>
       <c r="K54" s="26"/>
     </row>
-    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="17"/>
       <c r="B55" s="18" t="s">
         <v>16</v>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="K55" s="20"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="24"/>
       <c r="B56" s="25" t="s">
         <v>32</v>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="K56" s="26"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="24"/>
       <c r="B57" s="25" t="s">
         <v>33</v>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="K57" s="26"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="24"/>
       <c r="B58" s="25" t="s">
         <v>31</v>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="K58" s="26"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="26"/>
       <c r="B59" s="25" t="s">
         <v>36</v>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="K59" s="26"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="26"/>
       <c r="B60" s="25" t="s">
         <v>44</v>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="K60" s="26"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="26"/>
       <c r="B61" s="25" t="s">
         <v>45</v>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="K61" s="26"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="26"/>
       <c r="B62" s="26"/>
       <c r="C62" s="26"/>
@@ -9215,7 +9215,7 @@
       <c r="J62" s="26"/>
       <c r="K62" s="26"/>
     </row>
-    <row r="63" spans="1:11" s="44" customFormat="1" ht="45" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" s="44" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="24">
         <v>4</v>
       </c>
@@ -9232,22 +9232,22 @@
       <c r="J63" s="38"/>
       <c r="K63" s="38"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="26"/>
       <c r="B64" s="25" t="str">
-        <f>B45</f>
+        <f t="shared" ref="B64:E65" si="2">B45</f>
         <v>-for flooring</v>
       </c>
       <c r="C64" s="26">
-        <f>C45</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D64" s="27">
-        <f>D45</f>
+        <f t="shared" si="2"/>
         <v>3.5669917708015841</v>
       </c>
       <c r="E64" s="27">
-        <f>E45</f>
+        <f t="shared" si="2"/>
         <v>3.5669917708015841</v>
       </c>
       <c r="F64" s="27">
@@ -9262,29 +9262,29 @@
       <c r="J64" s="26"/>
       <c r="K64" s="26"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="26"/>
       <c r="B65" s="25" t="str">
-        <f>B46</f>
+        <f t="shared" si="2"/>
         <v>-for peti works</v>
       </c>
       <c r="C65" s="26">
-        <f>C46</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="D65" s="27">
-        <f>D46</f>
+        <f t="shared" si="2"/>
         <v>4.2669917708015843</v>
       </c>
       <c r="E65" s="27">
-        <f>E46</f>
+        <f t="shared" si="2"/>
         <v>0.45</v>
       </c>
       <c r="F65" s="27">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G65" s="27">
-        <f t="shared" ref="G65:G66" si="2">PRODUCT(C65:F65)</f>
+        <f t="shared" ref="G65:G66" si="3">PRODUCT(C65:F65)</f>
         <v>0.28802194452910695</v>
       </c>
       <c r="H65" s="26"/>
@@ -9292,7 +9292,7 @@
       <c r="J65" s="26"/>
       <c r="K65" s="26"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="26"/>
       <c r="B66" s="25"/>
       <c r="C66" s="26">
@@ -9311,7 +9311,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G66" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.31839694452910694</v>
       </c>
       <c r="H66" s="26"/>
@@ -9319,7 +9319,7 @@
       <c r="J66" s="26"/>
       <c r="K66" s="26"/>
     </row>
-    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="17"/>
       <c r="B67" s="18" t="s">
         <v>16</v>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="K67" s="20"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="24"/>
       <c r="B68" s="25" t="s">
         <v>32</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="K68" s="26"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="24"/>
       <c r="B69" s="25" t="s">
         <v>33</v>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="K69" s="26"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="24"/>
       <c r="B70" s="25" t="s">
         <v>31</v>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K70" s="26"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="26"/>
       <c r="B71" s="25" t="s">
         <v>36</v>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="K71" s="26"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="26"/>
       <c r="B72" s="25" t="s">
         <v>36</v>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="K72" s="26"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="26"/>
       <c r="B73" s="25" t="s">
         <v>36</v>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="K73" s="26"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="26"/>
       <c r="B74" s="26"/>
       <c r="C74" s="26"/>
@@ -9465,7 +9465,7 @@
       <c r="J74" s="26"/>
       <c r="K74" s="26"/>
     </row>
-    <row r="75" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="24">
         <v>5</v>
       </c>
@@ -9482,7 +9482,7 @@
       <c r="J75" s="38"/>
       <c r="K75" s="38"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="26"/>
       <c r="B76" s="25" t="str">
         <f>B53</f>
@@ -9512,7 +9512,7 @@
       <c r="J76" s="26"/>
       <c r="K76" s="26"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="26"/>
       <c r="B77" s="25" t="s">
         <v>60</v>
@@ -9541,7 +9541,7 @@
       <c r="J77" s="26"/>
       <c r="K77" s="26"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="26"/>
       <c r="B78" s="25" t="s">
         <v>59</v>
@@ -9571,7 +9571,7 @@
       <c r="J78" s="26"/>
       <c r="K78" s="26"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="26"/>
       <c r="B79" s="25" t="s">
         <v>61</v>
@@ -9592,7 +9592,7 @@
         <v>3.0722340749771408</v>
       </c>
       <c r="G79" s="27">
-        <f t="shared" ref="G79:G86" si="3">PRODUCT(C79:F79)</f>
+        <f t="shared" ref="G79:G86" si="4">PRODUCT(C79:F79)</f>
         <v>1.5053946967387988</v>
       </c>
       <c r="H79" s="26"/>
@@ -9600,7 +9600,7 @@
       <c r="J79" s="26"/>
       <c r="K79" s="26"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="26"/>
       <c r="B80" s="25" t="s">
         <v>62</v>
@@ -9620,7 +9620,7 @@
         <v>0.23</v>
       </c>
       <c r="G80" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.75477545870161533</v>
       </c>
       <c r="H80" s="26"/>
@@ -9628,7 +9628,7 @@
       <c r="J80" s="26"/>
       <c r="K80" s="26"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="26"/>
       <c r="B81" s="25" t="s">
         <v>81</v>
@@ -9648,7 +9648,7 @@
         <v>0.35</v>
       </c>
       <c r="G81" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.57428567509905504</v>
       </c>
       <c r="H81" s="26"/>
@@ -9656,7 +9656,7 @@
       <c r="J81" s="26"/>
       <c r="K81" s="26"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="26"/>
       <c r="B82" s="25" t="s">
         <v>82</v>
@@ -9675,7 +9675,7 @@
         <v>1.8</v>
       </c>
       <c r="G82" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.38088000000000005</v>
       </c>
       <c r="H82" s="26"/>
@@ -9683,7 +9683,7 @@
       <c r="J82" s="26"/>
       <c r="K82" s="26"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="26"/>
       <c r="B83" s="25" t="s">
         <v>108</v>
@@ -9703,7 +9703,7 @@
         <v>0.23</v>
       </c>
       <c r="G83" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.41920146296860716</v>
       </c>
       <c r="H83" s="26"/>
@@ -9711,7 +9711,7 @@
       <c r="J83" s="26"/>
       <c r="K83" s="26"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="26"/>
       <c r="B84" s="25" t="s">
         <v>83</v>
@@ -9731,7 +9731,7 @@
         <v>0.1</v>
       </c>
       <c r="G84" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.1286617759228297</v>
       </c>
       <c r="H84" s="26"/>
@@ -9739,7 +9739,7 @@
       <c r="J84" s="26"/>
       <c r="K84" s="26"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="26"/>
       <c r="B85" s="25" t="s">
         <v>84</v>
@@ -9758,7 +9758,7 @@
         <v>0.1</v>
       </c>
       <c r="G85" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.5120390124961901</v>
       </c>
       <c r="H85" s="26"/>
@@ -9766,7 +9766,7 @@
       <c r="J85" s="26"/>
       <c r="K85" s="26"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="26"/>
       <c r="B86" s="25"/>
       <c r="C86" s="26">
@@ -9783,7 +9783,7 @@
         <v>0.1</v>
       </c>
       <c r="G86" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.65603901249619012</v>
       </c>
       <c r="H86" s="26"/>
@@ -9791,7 +9791,7 @@
       <c r="J86" s="26"/>
       <c r="K86" s="26"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="26"/>
       <c r="B87" s="25" t="s">
         <v>109</v>
@@ -9811,7 +9811,7 @@
         <v>0.23</v>
       </c>
       <c r="G87" s="27">
-        <f t="shared" ref="G87:G90" si="4">PRODUCT(C87:F87)</f>
+        <f t="shared" ref="G87:G90" si="5">PRODUCT(C87:F87)</f>
         <v>0.41920146296860716</v>
       </c>
       <c r="H87" s="26"/>
@@ -9819,7 +9819,7 @@
       <c r="J87" s="26"/>
       <c r="K87" s="26"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="26"/>
       <c r="B88" s="25" t="s">
         <v>110</v>
@@ -9839,7 +9839,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G88" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.3712043174146194</v>
       </c>
       <c r="H88" s="26"/>
@@ -9847,7 +9847,7 @@
       <c r="J88" s="26"/>
       <c r="K88" s="26"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="26"/>
       <c r="B89" s="25" t="s">
         <v>84</v>
@@ -9867,7 +9867,7 @@
         <v>0.1</v>
       </c>
       <c r="G89" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.37389824264110194</v>
       </c>
       <c r="H89" s="26"/>
@@ -9875,7 +9875,7 @@
       <c r="J89" s="26"/>
       <c r="K89" s="26"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="26"/>
       <c r="B90" s="25"/>
       <c r="C90" s="26">
@@ -9893,7 +9893,7 @@
         <v>0.1</v>
       </c>
       <c r="G90" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.26010312531554919</v>
       </c>
       <c r="H90" s="26"/>
@@ -9901,7 +9901,7 @@
       <c r="J90" s="26"/>
       <c r="K90" s="26"/>
     </row>
-    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="17"/>
       <c r="B91" s="18" t="s">
         <v>16</v>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K91" s="20"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="24"/>
       <c r="B92" s="25" t="s">
         <v>32</v>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="K92" s="26"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="24"/>
       <c r="B93" s="25" t="s">
         <v>33</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="K93" s="26"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="24"/>
       <c r="B94" s="25" t="s">
         <v>31</v>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="K94" s="26"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="26"/>
       <c r="B95" s="25" t="s">
         <v>36</v>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="K95" s="26"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="24"/>
       <c r="B96" s="25" t="s">
         <v>44</v>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="K96" s="26"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="26"/>
       <c r="B97" s="25" t="s">
         <v>45</v>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="K97" s="26"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="26"/>
       <c r="B98" s="26"/>
       <c r="C98" s="26"/>
@@ -10047,7 +10047,7 @@
       <c r="J98" s="26"/>
       <c r="K98" s="26"/>
     </row>
-    <row r="99" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="24">
         <v>6</v>
       </c>
@@ -10064,7 +10064,7 @@
       <c r="J99" s="38"/>
       <c r="K99" s="38"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="26"/>
       <c r="B100" s="25" t="str">
         <f>B77</f>
@@ -10092,14 +10092,14 @@
       <c r="J100" s="26"/>
       <c r="K100" s="26"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="26"/>
       <c r="B101" s="25" t="str">
-        <f t="shared" ref="B101:C105" si="5">B78</f>
+        <f t="shared" ref="B101:C105" si="6">B78</f>
         <v>-for tie beam</v>
       </c>
       <c r="C101" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D101" s="27">
@@ -10120,14 +10120,14 @@
       <c r="J101" s="26"/>
       <c r="K101" s="26"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="26"/>
       <c r="B102" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-GF column</v>
       </c>
       <c r="C102" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D102" s="27">
@@ -10140,7 +10140,7 @@
         <v>3.0722340749771408</v>
       </c>
       <c r="G102" s="27">
-        <f t="shared" ref="G102:G107" si="6">PRODUCT(C102:F102)</f>
+        <f t="shared" ref="G102:G107" si="7">PRODUCT(C102:F102)</f>
         <v>17.204510819871988</v>
       </c>
       <c r="H102" s="26"/>
@@ -10148,14 +10148,14 @@
       <c r="J102" s="26"/>
       <c r="K102" s="26"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="26"/>
       <c r="B103" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-for beam</v>
       </c>
       <c r="C103" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D103" s="27">
@@ -10168,7 +10168,7 @@
         <v>0.46</v>
       </c>
       <c r="G103" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.5632648582749153</v>
       </c>
       <c r="H103" s="26"/>
@@ -10176,14 +10176,14 @@
       <c r="J103" s="26"/>
       <c r="K103" s="26"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="26"/>
       <c r="B104" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-for support beam</v>
       </c>
       <c r="C104" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="D104" s="27">
@@ -10196,7 +10196,7 @@
         <v>0.46</v>
       </c>
       <c r="G104" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.2816324291374577</v>
       </c>
       <c r="H104" s="26"/>
@@ -10204,14 +10204,14 @@
       <c r="J104" s="26"/>
       <c r="K104" s="26"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="26"/>
       <c r="B105" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-for column over support beam</v>
       </c>
       <c r="C105" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="D105" s="27">
@@ -10224,7 +10224,7 @@
         <v>1.8</v>
       </c>
       <c r="G105" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.6560000000000001</v>
       </c>
       <c r="H105" s="26"/>
@@ -10232,7 +10232,7 @@
       <c r="J105" s="26"/>
       <c r="K105" s="26"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="26"/>
       <c r="B106" s="25" t="s">
         <v>108</v>
@@ -10251,7 +10251,7 @@
         <v>0.46</v>
       </c>
       <c r="G106" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.6452301127704967</v>
       </c>
       <c r="H106" s="26"/>
@@ -10259,7 +10259,7 @@
       <c r="J106" s="26"/>
       <c r="K106" s="26"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="26"/>
       <c r="B107" s="25" t="str">
         <f>B84</f>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="F107" s="27"/>
       <c r="G107" s="27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11.286617759228296</v>
       </c>
       <c r="H107" s="26"/>
@@ -10287,27 +10287,27 @@
       <c r="J107" s="26"/>
       <c r="K107" s="26"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="26"/>
       <c r="B108" s="25" t="str">
-        <f t="shared" ref="B108:E108" si="7">B85</f>
+        <f t="shared" ref="B108:E108" si="8">B85</f>
         <v>-for cantilever</v>
       </c>
       <c r="C108" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="D108" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.2669917708015843</v>
       </c>
       <c r="E108" s="27">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.6</v>
       </c>
       <c r="F108" s="27"/>
       <c r="G108" s="27">
-        <f t="shared" ref="G108:G113" si="8">PRODUCT(C108:F108)</f>
+        <f t="shared" ref="G108:G113" si="9">PRODUCT(C108:F108)</f>
         <v>5.1203901249619008</v>
       </c>
       <c r="H108" s="26"/>
@@ -10315,24 +10315,24 @@
       <c r="J108" s="26"/>
       <c r="K108" s="26"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="26"/>
       <c r="B109" s="25"/>
       <c r="C109" s="26">
-        <f t="shared" ref="C109:E109" si="9">C86</f>
+        <f t="shared" ref="C109:E109" si="10">C86</f>
         <v>2</v>
       </c>
       <c r="D109" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.4669917708015845</v>
       </c>
       <c r="E109" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
       <c r="F109" s="27"/>
       <c r="G109" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.5603901249619012</v>
       </c>
       <c r="H109" s="26"/>
@@ -10340,18 +10340,18 @@
       <c r="J109" s="26"/>
       <c r="K109" s="26"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="26"/>
       <c r="B110" s="25" t="str">
-        <f t="shared" ref="B110:D110" si="10">B87</f>
+        <f t="shared" ref="B110:D110" si="11">B87</f>
         <v>-beam for top roof inclined support</v>
       </c>
       <c r="C110" s="26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="D110" s="27">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.9811033221578787</v>
       </c>
       <c r="E110" s="27"/>
@@ -10360,7 +10360,7 @@
         <v>0.46</v>
       </c>
       <c r="G110" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.6452301127704967</v>
       </c>
       <c r="H110" s="26"/>
@@ -10368,27 +10368,27 @@
       <c r="J110" s="26"/>
       <c r="K110" s="26"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="26"/>
       <c r="B111" s="25" t="str">
-        <f t="shared" ref="B111:E111" si="11">B88</f>
+        <f t="shared" ref="B111:E111" si="12">B88</f>
         <v>-top roof</v>
       </c>
       <c r="C111" s="26">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="D111" s="27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.0149344711978054</v>
       </c>
       <c r="E111" s="27">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.2191405059433098</v>
       </c>
       <c r="F111" s="27"/>
       <c r="G111" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.9493908988615924</v>
       </c>
       <c r="H111" s="26"/>
@@ -10396,27 +10396,27 @@
       <c r="J111" s="26"/>
       <c r="K111" s="26"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="26"/>
       <c r="B112" s="25" t="str">
-        <f t="shared" ref="B112:E112" si="12">B89</f>
+        <f t="shared" ref="B112:E112" si="13">B89</f>
         <v>-for cantilever</v>
       </c>
       <c r="C112" s="26">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="D112" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.5050289545870159</v>
       </c>
       <c r="E112" s="27">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0.53337397135019804</v>
       </c>
       <c r="F112" s="27"/>
       <c r="G112" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.7389824264110194</v>
       </c>
       <c r="H112" s="26"/>
@@ -10424,24 +10424,24 @@
       <c r="J112" s="26"/>
       <c r="K112" s="26"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="26"/>
       <c r="B113" s="25"/>
       <c r="C113" s="26">
-        <f t="shared" ref="C113:E113" si="13">C90</f>
+        <f t="shared" ref="C113:E113" si="14">C90</f>
         <v>2</v>
       </c>
       <c r="D113" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.4382810118866196</v>
       </c>
       <c r="E113" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.53337397135019804</v>
       </c>
       <c r="F113" s="27"/>
       <c r="G113" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.6010312531554916</v>
       </c>
       <c r="H113" s="26"/>
@@ -10449,7 +10449,7 @@
       <c r="J113" s="26"/>
       <c r="K113" s="26"/>
     </row>
-    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="17"/>
       <c r="B114" s="18" t="s">
         <v>16</v>
@@ -10474,7 +10474,7 @@
       </c>
       <c r="K114" s="20"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="24"/>
       <c r="B115" s="25" t="s">
         <v>47</v>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="K115" s="26"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="24"/>
       <c r="B116" s="25" t="s">
         <v>48</v>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="K116" s="26"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="24"/>
       <c r="B117" s="25" t="s">
         <v>49</v>
@@ -10528,7 +10528,7 @@
       </c>
       <c r="K117" s="26"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="26"/>
       <c r="B118" s="25" t="s">
         <v>50</v>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="K118" s="26"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="26"/>
       <c r="B119" s="26"/>
       <c r="C119" s="26"/>
@@ -10559,7 +10559,7 @@
       <c r="J119" s="26"/>
       <c r="K119" s="26"/>
     </row>
-    <row r="120" spans="1:11" s="44" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" s="44" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A120" s="24">
         <v>7</v>
       </c>
@@ -10584,7 +10584,7 @@
       <c r="J120" s="38"/>
       <c r="K120" s="38"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="26"/>
       <c r="B121" s="25" t="str">
         <f>B76</f>
@@ -10615,7 +10615,7 @@
       <c r="J121" s="26"/>
       <c r="K121" s="26"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="26"/>
       <c r="B122" s="25"/>
       <c r="C122" s="26">
@@ -10630,11 +10630,11 @@
         <v>0.88888888888888884</v>
       </c>
       <c r="F122" s="27">
-        <f t="shared" ref="F122:F149" si="14">PRODUCT(C122:E122)</f>
+        <f t="shared" ref="F122:F149" si="15">PRODUCT(C122:E122)</f>
         <v>13.333333333333332</v>
       </c>
       <c r="G122" s="27">
-        <f t="shared" ref="G122:G149" si="15">F122/1000</f>
+        <f t="shared" ref="G122:G149" si="16">F122/1000</f>
         <v>1.3333333333333332E-2</v>
       </c>
       <c r="H122" s="26"/>
@@ -10642,7 +10642,7 @@
       <c r="J122" s="26"/>
       <c r="K122" s="26"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="26"/>
       <c r="B123" s="25" t="s">
         <v>70</v>
@@ -10656,15 +10656,15 @@
         <v>5.8277202072538854</v>
       </c>
       <c r="E123" s="27">
-        <f t="shared" ref="E123" si="16">12*12/162</f>
+        <f t="shared" ref="E123" si="17">12*12/162</f>
         <v>0.88888888888888884</v>
       </c>
       <c r="F123" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>82.8831318364997</v>
       </c>
       <c r="G123" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.2883131836499702E-2</v>
       </c>
       <c r="H123" s="26"/>
@@ -10672,7 +10672,7 @@
       <c r="J123" s="26"/>
       <c r="K123" s="26"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="26"/>
       <c r="B124" s="25"/>
       <c r="C124" s="26">
@@ -10688,11 +10688,11 @@
         <v>1.5802469135802468</v>
       </c>
       <c r="F124" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>147.34778993155501</v>
       </c>
       <c r="G124" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.14734778993155501</v>
       </c>
       <c r="H124" s="26"/>
@@ -10700,7 +10700,7 @@
       <c r="J124" s="26"/>
       <c r="K124" s="26"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="26"/>
       <c r="B125" s="25" t="s">
         <v>71</v>
@@ -10718,11 +10718,11 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F125" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>51.232558577067373</v>
       </c>
       <c r="G125" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.1232558577067371E-2</v>
       </c>
       <c r="H125" s="26"/>
@@ -10730,7 +10730,7 @@
       <c r="J125" s="26"/>
       <c r="K125" s="26"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="26"/>
       <c r="B126" s="25"/>
       <c r="C126" s="26">
@@ -10746,11 +10746,11 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F126" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>43.627456790123446</v>
       </c>
       <c r="G126" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.3627456790123448E-2</v>
       </c>
       <c r="H126" s="26"/>
@@ -10758,7 +10758,7 @@
       <c r="J126" s="26"/>
       <c r="K126" s="26"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="26"/>
       <c r="B127" s="25" t="str">
         <f>B101</f>
@@ -10777,11 +10777,11 @@
         <v>0.88888888888888884</v>
       </c>
       <c r="F127" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>98.571573707203086</v>
       </c>
       <c r="G127" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9.8571573707203083E-2</v>
       </c>
       <c r="H127" s="26"/>
@@ -10789,7 +10789,7 @@
       <c r="J127" s="26"/>
       <c r="K127" s="26"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="26"/>
       <c r="B128" s="25" t="s">
         <v>72</v>
@@ -10807,11 +10807,11 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F128" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>30.886337724496816</v>
       </c>
       <c r="G128" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.0886337724496817E-2</v>
       </c>
       <c r="H128" s="26"/>
@@ -10819,7 +10819,7 @@
       <c r="J128" s="26"/>
       <c r="K128" s="26"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="26"/>
       <c r="B129" s="25" t="str">
         <f>B103</f>
@@ -10838,11 +10838,11 @@
         <v>0.88888888888888884</v>
       </c>
       <c r="F129" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>98.571573707203086</v>
       </c>
       <c r="G129" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9.8571573707203083E-2</v>
       </c>
       <c r="H129" s="26"/>
@@ -10850,7 +10850,7 @@
       <c r="J129" s="26"/>
       <c r="K129" s="26"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="26"/>
       <c r="B130" s="25" t="s">
         <v>72</v>
@@ -10868,11 +10868,11 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F130" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>30.886337724496816</v>
       </c>
       <c r="G130" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.0886337724496817E-2</v>
       </c>
       <c r="H130" s="26"/>
@@ -10880,7 +10880,7 @@
       <c r="J130" s="26"/>
       <c r="K130" s="26"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="26"/>
       <c r="B131" s="25" t="str">
         <f>B104</f>
@@ -10899,11 +10899,11 @@
         <v>0.88888888888888884</v>
       </c>
       <c r="F131" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>50.391140912323465</v>
       </c>
       <c r="G131" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.0391140912323468E-2</v>
       </c>
       <c r="H131" s="26"/>
@@ -10911,7 +10911,7 @@
       <c r="J131" s="26"/>
       <c r="K131" s="26"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="26"/>
       <c r="B132" s="25" t="s">
         <v>72</v>
@@ -10929,11 +10929,11 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F132" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.443168862248408</v>
       </c>
       <c r="G132" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.5443168862248408E-2</v>
       </c>
       <c r="H132" s="26"/>
@@ -10941,7 +10941,7 @@
       <c r="J132" s="26"/>
       <c r="K132" s="26"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="26"/>
       <c r="B133" s="25" t="str">
         <f>B105</f>
@@ -10960,11 +10960,11 @@
         <v>0.88888888888888884</v>
       </c>
       <c r="F133" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>68.266666666666666</v>
       </c>
       <c r="G133" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.826666666666667E-2</v>
       </c>
       <c r="H133" s="26"/>
@@ -10972,7 +10972,7 @@
       <c r="J133" s="26"/>
       <c r="K133" s="26"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="26"/>
       <c r="B134" s="25" t="s">
         <v>71</v>
@@ -10990,11 +10990,11 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F134" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.6694435978190914</v>
       </c>
       <c r="G134" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.6694435978190917E-3</v>
       </c>
       <c r="H134" s="26"/>
@@ -11002,7 +11002,7 @@
       <c r="J134" s="26"/>
       <c r="K134" s="26"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="26"/>
       <c r="B135" s="25"/>
       <c r="C135" s="26">
@@ -11018,11 +11018,11 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F135" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.7738494361475166</v>
       </c>
       <c r="G135" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.7738494361475167E-3</v>
       </c>
       <c r="H135" s="26"/>
@@ -11030,7 +11030,7 @@
       <c r="J135" s="26"/>
       <c r="K135" s="26"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="26"/>
       <c r="B136" s="25" t="s">
         <v>108</v>
@@ -11048,11 +11048,11 @@
         <v>0.88888888888888884</v>
       </c>
       <c r="F136" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>97.531240475464799</v>
       </c>
       <c r="G136" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>9.7531240475464798E-2</v>
       </c>
       <c r="H136" s="26"/>
@@ -11060,7 +11060,7 @@
       <c r="J136" s="26"/>
       <c r="K136" s="26"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="26"/>
       <c r="B137" s="25" t="s">
         <v>72</v>
@@ -11078,11 +11078,11 @@
         <v>0.39506172839506171</v>
       </c>
       <c r="F137" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>16.730099600769112</v>
       </c>
       <c r="G137" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.6730099600769113E-2</v>
       </c>
       <c r="H137" s="26"/>
@@ -11090,7 +11090,7 @@
       <c r="J137" s="26"/>
       <c r="K137" s="26"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="26"/>
       <c r="B138" s="25" t="str">
         <f>B107</f>
@@ -11109,11 +11109,11 @@
         <v>0.61728395061728392</v>
       </c>
       <c r="F138" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>45.717768972874119</v>
       </c>
       <c r="G138" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.571776897287412E-2</v>
       </c>
       <c r="H138" s="26"/>
@@ -11121,7 +11121,7 @@
       <c r="J138" s="26"/>
       <c r="K138" s="26"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="26"/>
       <c r="B139" s="25"/>
       <c r="C139" s="26">
@@ -11137,11 +11137,11 @@
         <v>0.61728395061728392</v>
       </c>
       <c r="F139" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>45.153352071974439</v>
       </c>
       <c r="G139" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.5153352071974441E-2</v>
       </c>
       <c r="H139" s="26"/>
@@ -11149,7 +11149,7 @@
       <c r="J139" s="26"/>
       <c r="K139" s="26"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="26"/>
       <c r="B140" s="25" t="s">
         <v>84</v>
@@ -11167,11 +11167,11 @@
         <v>0.61728395061728392</v>
       </c>
       <c r="F140" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>26.590809035185746</v>
       </c>
       <c r="G140" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.6590809035185747E-2</v>
       </c>
       <c r="H140" s="26"/>
@@ -11179,7 +11179,7 @@
       <c r="J140" s="26"/>
       <c r="K140" s="26"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="26"/>
       <c r="B141" s="25"/>
       <c r="C141" s="26">
@@ -11190,15 +11190,15 @@
         <v>0.6</v>
       </c>
       <c r="E141" s="27">
-        <f t="shared" ref="E141:E143" si="17">10*10/162</f>
+        <f t="shared" ref="E141:E143" si="18">10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
       <c r="F141" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>24.444444444444443</v>
       </c>
       <c r="G141" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.4444444444444442E-2</v>
       </c>
       <c r="H141" s="26"/>
@@ -11206,7 +11206,7 @@
       <c r="J141" s="26"/>
       <c r="K141" s="26"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="26"/>
       <c r="B142" s="25"/>
       <c r="C142" s="26">
@@ -11218,15 +11218,15 @@
         <v>4.1664126790612617</v>
       </c>
       <c r="E142" s="27">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.61728395061728392</v>
       </c>
       <c r="F142" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>20.574877427463019</v>
       </c>
       <c r="G142" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.0574877427463018E-2</v>
       </c>
       <c r="H142" s="26"/>
@@ -11234,7 +11234,7 @@
       <c r="J142" s="26"/>
       <c r="K142" s="26"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="26"/>
       <c r="B143" s="25"/>
       <c r="C143" s="26">
@@ -11245,15 +11245,15 @@
         <v>0.6</v>
       </c>
       <c r="E143" s="27">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.61728395061728392</v>
       </c>
       <c r="F143" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>18.518518518518519</v>
       </c>
       <c r="G143" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.8518518518518517E-2</v>
       </c>
       <c r="H143" s="26"/>
@@ -11261,7 +11261,7 @@
       <c r="J143" s="26"/>
       <c r="K143" s="26"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="26"/>
       <c r="B144" s="25" t="str">
         <f>B111</f>
@@ -11280,11 +11280,11 @@
         <v>0.61728395061728392</v>
       </c>
       <c r="F144" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>20.048088319956651</v>
       </c>
       <c r="G144" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.004808831995665E-2</v>
       </c>
       <c r="H144" s="26"/>
@@ -11292,7 +11292,7 @@
       <c r="J144" s="26"/>
       <c r="K144" s="26"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="26"/>
       <c r="B145" s="25"/>
       <c r="C145" s="26">
@@ -11308,11 +11308,11 @@
         <v>0.61728395061728392</v>
       </c>
       <c r="F145" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>21.071564300254735</v>
       </c>
       <c r="G145" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.1071564300254735E-2</v>
       </c>
       <c r="H145" s="26"/>
@@ -11320,7 +11320,7 @@
       <c r="J145" s="26"/>
       <c r="K145" s="26"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="26"/>
       <c r="B146" s="25" t="s">
         <v>84</v>
@@ -11338,11 +11338,11 @@
         <v>0.61728395061728392</v>
       </c>
       <c r="F146" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.605687064693464</v>
       </c>
       <c r="G146" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.2605687064693465E-2</v>
       </c>
       <c r="H146" s="26"/>
@@ -11350,7 +11350,7 @@
       <c r="J146" s="26"/>
       <c r="K146" s="26"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="26"/>
       <c r="B147" s="25"/>
       <c r="C147" s="26">
@@ -11362,15 +11362,15 @@
         <v>0.53337397135019804</v>
       </c>
       <c r="E147" s="27">
-        <f t="shared" ref="E147:E149" si="18">10*10/162</f>
+        <f t="shared" ref="E147:E149" si="19">10*10/162</f>
         <v>0.61728395061728392</v>
       </c>
       <c r="F147" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>12.51124130327625</v>
       </c>
       <c r="G147" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.2511241303276251E-2</v>
       </c>
       <c r="H147" s="26"/>
@@ -11378,7 +11378,7 @@
       <c r="J147" s="26"/>
       <c r="K147" s="26"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="26"/>
       <c r="B148" s="25"/>
       <c r="C148" s="26">
@@ -11390,15 +11390,15 @@
         <v>2.3377019201462965</v>
       </c>
       <c r="E148" s="27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.61728395061728392</v>
       </c>
       <c r="F148" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.6581552598010987</v>
       </c>
       <c r="G148" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.658155259801098E-3</v>
       </c>
       <c r="H148" s="26"/>
@@ -11406,7 +11406,7 @@
       <c r="J148" s="26"/>
       <c r="K148" s="26"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="26"/>
       <c r="B149" s="25"/>
       <c r="C149" s="26">
@@ -11418,15 +11418,15 @@
         <v>0.53337397135019804</v>
       </c>
       <c r="E149" s="27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.61728395061728392</v>
       </c>
       <c r="F149" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.9018366125955257</v>
       </c>
       <c r="G149" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7.9018366125955253E-3</v>
       </c>
       <c r="H149" s="26"/>
@@ -11434,7 +11434,7 @@
       <c r="J149" s="26"/>
       <c r="K149" s="26"/>
     </row>
-    <row r="150" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="17"/>
       <c r="B150" s="18" t="s">
         <v>16</v>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="K150" s="20"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="24"/>
       <c r="B151" s="25" t="s">
         <v>39</v>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="K151" s="26"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="24"/>
       <c r="B152" s="25" t="s">
         <v>38</v>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="K152" s="26"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="26"/>
       <c r="B153" s="26"/>
       <c r="C153" s="26"/>
@@ -11508,7 +11508,7 @@
       <c r="J153" s="26"/>
       <c r="K153" s="26"/>
     </row>
-    <row r="154" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A154" s="24">
         <v>8</v>
       </c>
@@ -11525,7 +11525,7 @@
       <c r="J154" s="26"/>
       <c r="K154" s="26"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="26"/>
       <c r="B155" s="25" t="s">
         <v>111</v>
@@ -11552,7 +11552,7 @@
       <c r="J155" s="26"/>
       <c r="K155" s="26"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="26"/>
       <c r="B156" s="25" t="str">
         <f>B105</f>
@@ -11579,7 +11579,7 @@
       <c r="J156" s="26"/>
       <c r="K156" s="26"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="26"/>
       <c r="B157" s="25" t="s">
         <v>62</v>
@@ -11605,7 +11605,7 @@
       <c r="J157" s="26"/>
       <c r="K157" s="26"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="26"/>
       <c r="B158" s="25"/>
       <c r="C158" s="51">
@@ -11629,7 +11629,7 @@
       <c r="J158" s="26"/>
       <c r="K158" s="26"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="26"/>
       <c r="B159" s="25" t="str">
         <f>B110</f>
@@ -11656,7 +11656,7 @@
       <c r="J159" s="26"/>
       <c r="K159" s="26"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="26"/>
       <c r="B160" s="25" t="str">
         <f>B84</f>
@@ -11667,16 +11667,16 @@
         <v>4</v>
       </c>
       <c r="D160" s="27">
-        <f t="shared" ref="D160:E160" si="19">D84</f>
+        <f t="shared" ref="D160:E160" si="20">D84</f>
         <v>3.0859494056690031</v>
       </c>
       <c r="E160" s="27">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.91435537945748246</v>
       </c>
       <c r="F160" s="51"/>
       <c r="G160" s="27">
-        <f t="shared" ref="G160:G165" si="20">PRODUCT(C160:F160)</f>
+        <f t="shared" ref="G160:G165" si="21">PRODUCT(C160:F160)</f>
         <v>11.286617759228296</v>
       </c>
       <c r="H160" s="26"/>
@@ -11684,27 +11684,27 @@
       <c r="J160" s="26"/>
       <c r="K160" s="26"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" s="26"/>
       <c r="B161" s="25" t="str">
         <f>B85</f>
         <v>-for cantilever</v>
       </c>
       <c r="C161" s="52">
-        <f t="shared" ref="C161:E162" si="21">C85</f>
+        <f t="shared" ref="C161:E162" si="22">C85</f>
         <v>2</v>
       </c>
       <c r="D161" s="53">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.2669917708015843</v>
       </c>
       <c r="E161" s="53">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.6</v>
       </c>
       <c r="F161" s="53"/>
       <c r="G161" s="27">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.1203901249619008</v>
       </c>
       <c r="H161" s="26"/>
@@ -11712,24 +11712,24 @@
       <c r="J161" s="26"/>
       <c r="K161" s="26"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="26"/>
       <c r="B162" s="25"/>
       <c r="C162" s="52">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="D162" s="53">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5.4669917708015845</v>
       </c>
       <c r="E162" s="53">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.6</v>
       </c>
       <c r="F162" s="53"/>
       <c r="G162" s="27">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.5603901249619012</v>
       </c>
       <c r="H162" s="26"/>
@@ -11737,27 +11737,27 @@
       <c r="J162" s="26"/>
       <c r="K162" s="26"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="26"/>
       <c r="B163" s="25" t="str">
         <f>B88</f>
         <v>-top roof</v>
       </c>
       <c r="C163" s="52">
-        <f t="shared" ref="C163:E163" si="22">C88</f>
+        <f t="shared" ref="C163:E163" si="23">C88</f>
         <v>4</v>
       </c>
       <c r="D163" s="53">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.0149344711978054</v>
       </c>
       <c r="E163" s="53">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.2191405059433098</v>
       </c>
       <c r="F163" s="53"/>
       <c r="G163" s="27">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4.9493908988615924</v>
       </c>
       <c r="H163" s="26"/>
@@ -11765,27 +11765,27 @@
       <c r="J163" s="26"/>
       <c r="K163" s="26"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="26"/>
       <c r="B164" s="25" t="str">
-        <f t="shared" ref="B164:E164" si="23">B89</f>
+        <f t="shared" ref="B164:E164" si="24">B89</f>
         <v>-for cantilever</v>
       </c>
       <c r="C164" s="52">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>2</v>
       </c>
       <c r="D164" s="53">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>3.5050289545870159</v>
       </c>
       <c r="E164" s="53">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.53337397135019804</v>
       </c>
       <c r="F164" s="53"/>
       <c r="G164" s="27">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>3.7389824264110194</v>
       </c>
       <c r="H164" s="26"/>
@@ -11793,24 +11793,24 @@
       <c r="J164" s="26"/>
       <c r="K164" s="26"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="26"/>
       <c r="B165" s="25"/>
       <c r="C165" s="52">
-        <f t="shared" ref="C165:E165" si="24">C90</f>
+        <f t="shared" ref="C165:E165" si="25">C90</f>
         <v>2</v>
       </c>
       <c r="D165" s="53">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.4382810118866196</v>
       </c>
       <c r="E165" s="53">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.53337397135019804</v>
       </c>
       <c r="F165" s="53"/>
       <c r="G165" s="27">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.6010312531554916</v>
       </c>
       <c r="H165" s="26"/>
@@ -11818,7 +11818,7 @@
       <c r="J165" s="26"/>
       <c r="K165" s="26"/>
     </row>
-    <row r="166" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="17"/>
       <c r="B166" s="18" t="s">
         <v>16</v>
@@ -11843,7 +11843,7 @@
       </c>
       <c r="K166" s="20"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="24"/>
       <c r="B167" s="25" t="s">
         <v>32</v>
@@ -11861,7 +11861,7 @@
       </c>
       <c r="K167" s="26"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="26"/>
       <c r="B168" s="25" t="s">
         <v>31</v>
@@ -11879,7 +11879,7 @@
       </c>
       <c r="K168" s="26"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="26"/>
       <c r="B169" s="26"/>
       <c r="C169" s="26"/>
@@ -11892,7 +11892,7 @@
       <c r="J169" s="26"/>
       <c r="K169" s="26"/>
     </row>
-    <row r="170" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A170" s="24">
         <v>9</v>
       </c>
@@ -11909,7 +11909,7 @@
       <c r="J170" s="26"/>
       <c r="K170" s="26"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="26"/>
       <c r="B171" s="25" t="str">
         <f>B78</f>
@@ -11930,7 +11930,7 @@
         <v>1.2</v>
       </c>
       <c r="G171" s="27">
-        <f t="shared" ref="G171" si="25">PRODUCT(C171:F171)</f>
+        <f t="shared" ref="G171" si="26">PRODUCT(C171:F171)</f>
         <v>1.2900749771411155</v>
       </c>
       <c r="H171" s="26"/>
@@ -11938,7 +11938,7 @@
       <c r="J171" s="26"/>
       <c r="K171" s="26"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="26"/>
       <c r="B172" s="25"/>
       <c r="C172" s="51">
@@ -11964,7 +11964,7 @@
       <c r="J172" s="26"/>
       <c r="K172" s="26"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="26"/>
       <c r="B173" s="25" t="s">
         <v>133</v>
@@ -11983,7 +11983,7 @@
         <v>0.3</v>
       </c>
       <c r="G173" s="27">
-        <f t="shared" ref="G173:G174" si="26">PRODUCT(C173:F173)</f>
+        <f t="shared" ref="G173:G174" si="27">PRODUCT(C173:F173)</f>
         <v>0.28301950624809508</v>
       </c>
       <c r="H173" s="26"/>
@@ -11991,7 +11991,7 @@
       <c r="J173" s="26"/>
       <c r="K173" s="26"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="26"/>
       <c r="B174" s="25"/>
       <c r="C174" s="51">
@@ -12008,7 +12008,7 @@
         <v>0.3</v>
       </c>
       <c r="G174" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.28301950624809508</v>
       </c>
       <c r="H174" s="26"/>
@@ -12016,7 +12016,7 @@
       <c r="J174" s="26"/>
       <c r="K174" s="26"/>
     </row>
-    <row r="175" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="17"/>
       <c r="B175" s="18" t="s">
         <v>16</v>
@@ -12042,7 +12042,7 @@
       </c>
       <c r="K175" s="20"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="24"/>
       <c r="B176" s="25" t="s">
         <v>55</v>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="K176" s="26"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="24"/>
       <c r="B177" s="25" t="s">
         <v>32</v>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="K177" s="26"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="24"/>
       <c r="B178" s="25" t="s">
         <v>64</v>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="K178" s="26"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="24"/>
       <c r="B179" s="25" t="s">
         <v>36</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="K179" s="26"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="24"/>
       <c r="B180" s="25"/>
       <c r="C180" s="26"/>
@@ -12127,7 +12127,7 @@
       <c r="J180" s="22"/>
       <c r="K180" s="26"/>
     </row>
-    <row r="181" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A181" s="24">
         <v>10</v>
       </c>
@@ -12144,14 +12144,14 @@
       <c r="J181" s="26"/>
       <c r="K181" s="26"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" s="26"/>
       <c r="B182" s="25" t="str">
         <f>B161</f>
         <v>-for cantilever</v>
       </c>
       <c r="C182" s="52">
-        <f t="shared" ref="C182" si="27">C161</f>
+        <f t="shared" ref="C182" si="28">C161</f>
         <v>2</v>
       </c>
       <c r="D182" s="53">
@@ -12169,11 +12169,11 @@
       <c r="J182" s="26"/>
       <c r="K182" s="26"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="26"/>
       <c r="B183" s="25"/>
       <c r="C183" s="52">
-        <f t="shared" ref="C183" si="28">C162</f>
+        <f t="shared" ref="C183" si="29">C162</f>
         <v>2</v>
       </c>
       <c r="D183" s="53">
@@ -12183,7 +12183,7 @@
       <c r="E183" s="53"/>
       <c r="F183" s="53"/>
       <c r="G183" s="27">
-        <f t="shared" ref="G183:G185" si="29">PRODUCT(C183:F183)</f>
+        <f t="shared" ref="G183:G185" si="30">PRODUCT(C183:F183)</f>
         <v>10.933983541603169</v>
       </c>
       <c r="H183" s="26"/>
@@ -12191,14 +12191,14 @@
       <c r="J183" s="26"/>
       <c r="K183" s="26"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="26"/>
       <c r="B184" s="25" t="str">
-        <f t="shared" ref="B184:C184" si="30">B164</f>
+        <f t="shared" ref="B184:C184" si="31">B164</f>
         <v>-for cantilever</v>
       </c>
       <c r="C184" s="52">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2</v>
       </c>
       <c r="D184" s="53">
@@ -12208,7 +12208,7 @@
       <c r="E184" s="53"/>
       <c r="F184" s="53"/>
       <c r="G184" s="27">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>7.0100579091740318</v>
       </c>
       <c r="H184" s="26"/>
@@ -12216,11 +12216,11 @@
       <c r="J184" s="26"/>
       <c r="K184" s="26"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="26"/>
       <c r="B185" s="25"/>
       <c r="C185" s="52">
-        <f t="shared" ref="C185" si="31">C165</f>
+        <f t="shared" ref="C185" si="32">C165</f>
         <v>2</v>
       </c>
       <c r="D185" s="53">
@@ -12230,7 +12230,7 @@
       <c r="E185" s="53"/>
       <c r="F185" s="53"/>
       <c r="G185" s="27">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>7.0100579091740318</v>
       </c>
       <c r="H185" s="26"/>
@@ -12238,7 +12238,7 @@
       <c r="J185" s="26"/>
       <c r="K185" s="26"/>
     </row>
-    <row r="186" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="17"/>
       <c r="B186" s="18" t="s">
         <v>16</v>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="K186" s="20"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="24"/>
       <c r="B187" s="25" t="s">
         <v>32</v>
@@ -12281,7 +12281,7 @@
       </c>
       <c r="K187" s="26"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="24"/>
       <c r="B188" s="25" t="s">
         <v>31</v>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="K188" s="26"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="24"/>
       <c r="B189" s="25" t="s">
         <v>113</v>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="K189" s="26"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="24"/>
       <c r="B190" s="25"/>
       <c r="C190" s="26"/>
@@ -12330,7 +12330,7 @@
       <c r="J190" s="22"/>
       <c r="K190" s="26"/>
     </row>
-    <row r="191" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="17">
         <v>11</v>
       </c>
@@ -12344,7 +12344,7 @@
       <c r="E191" s="20"/>
       <c r="F191" s="20"/>
       <c r="G191" s="21">
-        <f t="shared" ref="G191" si="32">PRODUCT(C191:F191)</f>
+        <f t="shared" ref="G191" si="33">PRODUCT(C191:F191)</f>
         <v>1</v>
       </c>
       <c r="H191" s="21" t="s">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="K191" s="20"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="17"/>
       <c r="B192" s="31"/>
       <c r="C192" s="19"/>
@@ -12372,7 +12372,7 @@
       <c r="J192" s="22"/>
       <c r="K192" s="20"/>
     </row>
-    <row r="193" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="17">
         <v>12</v>
       </c>
@@ -12386,7 +12386,7 @@
       <c r="E193" s="20"/>
       <c r="F193" s="20"/>
       <c r="G193" s="21">
-        <f t="shared" ref="G193" si="33">PRODUCT(C193:F193)</f>
+        <f t="shared" ref="G193" si="34">PRODUCT(C193:F193)</f>
         <v>1</v>
       </c>
       <c r="H193" s="21" t="s">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="K193" s="20"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="17"/>
       <c r="B194" s="31"/>
       <c r="C194" s="19"/>
@@ -12414,7 +12414,7 @@
       <c r="J194" s="22"/>
       <c r="K194" s="20"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="32"/>
       <c r="B195" s="33" t="s">
         <v>20</v>
@@ -12428,20 +12428,20 @@
       <c r="I195" s="22"/>
       <c r="J195" s="22">
         <f>SUM(J9:J193)</f>
-        <v>785843.93894891557</v>
+        <v>783511.5632557295</v>
       </c>
       <c r="K195" s="36"/>
     </row>
-    <row r="197" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A197" s="37"/>
       <c r="B197" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C197" s="60">
+      <c r="C197" s="58">
         <f>J195</f>
-        <v>785843.93894891557</v>
-      </c>
-      <c r="D197" s="61"/>
+        <v>783511.5632557295</v>
+      </c>
+      <c r="D197" s="59"/>
       <c r="E197" s="39">
         <v>100</v>
       </c>
@@ -12452,72 +12452,79 @@
       <c r="J197" s="42"/>
       <c r="K197" s="43"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B198" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C198" s="64">
+      <c r="C198" s="60">
         <v>700000</v>
       </c>
-      <c r="D198" s="65"/>
+      <c r="D198" s="61"/>
       <c r="E198" s="39"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B199" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C199" s="64">
+      <c r="C199" s="60">
         <f>C198-C201-C202</f>
         <v>665000</v>
       </c>
-      <c r="D199" s="65"/>
+      <c r="D199" s="61"/>
       <c r="E199" s="39">
         <f>C199/C197*100</f>
-        <v>84.622399822724702</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+        <v>84.874305777533408</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B200" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C200" s="66">
+      <c r="C200" s="62">
         <f>C197-C199</f>
-        <v>120843.93894891557</v>
-      </c>
-      <c r="D200" s="66"/>
+        <v>118511.5632557295</v>
+      </c>
+      <c r="D200" s="62"/>
       <c r="E200" s="39">
         <f>100-E199</f>
-        <v>15.377600177275298</v>
-      </c>
-    </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+        <v>15.125694222466592</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B201" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C201" s="60">
+      <c r="C201" s="58">
         <f>C198*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D201" s="61"/>
+      <c r="D201" s="59"/>
       <c r="E201" s="39">
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B202" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C202" s="60">
+      <c r="C202" s="58">
         <f>C198*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D202" s="61"/>
+      <c r="D202" s="59"/>
       <c r="E202" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C201:D201"/>
     <mergeCell ref="C202:D202"/>
     <mergeCell ref="A7:F7"/>
@@ -12526,13 +12533,6 @@
     <mergeCell ref="C198:D198"/>
     <mergeCell ref="C199:D199"/>
     <mergeCell ref="C200:D200"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -12544,70 +12544,70 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD11BB8-440B-4866-9ABD-75354584ECA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:W4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.85546875" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.88671875" customWidth="1"/>
+    <col min="17" max="17" width="11.88671875" customWidth="1"/>
     <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B2" s="71" t="s">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B2" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71" t="s">
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72" t="s">
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="68" t="s">
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="68" t="s">
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="72" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="67" t="s">
+      <c r="P2" s="73"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67" t="s">
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-    </row>
-    <row r="3" spans="2:23" s="48" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="V2" s="71"/>
+      <c r="W2" s="71"/>
+    </row>
+    <row r="3" spans="2:23" s="48" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" s="47" t="s">
         <v>8</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B4" s="23">
         <v>1.5</v>
       </c>

--- a/बजेट माग estimate/नगर बजेट estimate/bhotange chihaanpaati/2.bhotange chihaanpaati.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/bhotange chihaanpaati/2.bhotange chihaanpaati.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05E2225-4877-46F0-BCC2-555FFFA32398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="13" r:id="rId1"/>
@@ -41,7 +42,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">chihaan!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -59,12 +60,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="D39" authorId="0" shapeId="0">
+    <comment ref="D39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -540,10 +541,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -752,9 +753,9 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -770,14 +771,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -806,7 +807,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -843,7 +844,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -861,7 +862,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -870,8 +871,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -883,9 +884,9 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -901,23 +902,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -932,11 +920,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -959,11 +960,11 @@
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3"/>
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="5"/>
-    <cellStyle name="Percent 2" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -979,7 +980,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1073,7 +1074,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1132,7 +1133,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -1196,9 +1197,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1236,9 +1237,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1273,7 +1274,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1308,7 +1309,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1481,131 +1482,131 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M158"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="67" t="s">
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-    </row>
-    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="69" t="s">
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="70" t="s">
+      <c r="H6" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="63" t="s">
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="64" t="s">
+      <c r="H7" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-    </row>
-    <row r="8" spans="1:11" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+    </row>
+    <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -1640,7 +1641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>1</v>
       </c>
@@ -1657,7 +1658,7 @@
       <c r="J9" s="13"/>
       <c r="K9" s="13"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="16" t="s">
         <v>57</v>
@@ -1683,7 +1684,7 @@
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
       <c r="B11" s="16" t="s">
         <v>59</v>
@@ -1711,7 +1712,7 @@
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="17"/>
       <c r="B12" s="18" t="s">
         <v>16</v>
@@ -1736,7 +1737,7 @@
       </c>
       <c r="K12" s="20"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -1749,7 +1750,7 @@
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
     </row>
-    <row r="14" spans="1:11" s="14" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11">
         <v>2</v>
       </c>
@@ -1766,7 +1767,7 @@
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
       <c r="B15" s="16" t="str">
         <f t="shared" ref="B15:E16" si="0">B10</f>
@@ -1794,7 +1795,7 @@
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="str">
         <f t="shared" si="0"/>
@@ -1822,7 +1823,7 @@
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
       <c r="B17" s="16" t="s">
         <v>52</v>
@@ -1848,7 +1849,7 @@
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
     </row>
-    <row r="18" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="18" t="s">
         <v>16</v>
@@ -1873,7 +1874,7 @@
       </c>
       <c r="K18" s="20"/>
     </row>
-    <row r="19" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="24"/>
       <c r="B19" s="25" t="s">
         <v>55</v>
@@ -1891,7 +1892,7 @@
       </c>
       <c r="K19" s="26"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="15"/>
       <c r="B20" s="25" t="s">
         <v>31</v>
@@ -1909,7 +1910,7 @@
       </c>
       <c r="K20" s="15"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="15"/>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -1922,7 +1923,7 @@
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
     </row>
-    <row r="22" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="11">
         <v>3</v>
       </c>
@@ -1939,7 +1940,7 @@
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="15"/>
       <c r="B23" s="16" t="str">
         <f t="shared" ref="B23:E24" si="1">B15</f>
@@ -1969,7 +1970,7 @@
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="15"/>
       <c r="B24" s="16" t="str">
         <f t="shared" si="1"/>
@@ -1999,7 +2000,7 @@
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
       <c r="B25" s="16" t="str">
         <f>B17</f>
@@ -2029,7 +2030,7 @@
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
       <c r="B26" s="16" t="str">
         <f>B93</f>
@@ -2059,7 +2060,7 @@
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
     </row>
-    <row r="27" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
       <c r="B27" s="18" t="s">
         <v>16</v>
@@ -2084,7 +2085,7 @@
       </c>
       <c r="K27" s="20"/>
     </row>
-    <row r="28" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="24"/>
       <c r="B28" s="25" t="s">
         <v>32</v>
@@ -2102,7 +2103,7 @@
       </c>
       <c r="K28" s="26"/>
     </row>
-    <row r="29" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
       <c r="B29" s="25" t="s">
         <v>33</v>
@@ -2120,7 +2121,7 @@
       </c>
       <c r="K29" s="26"/>
     </row>
-    <row r="30" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="24"/>
       <c r="B30" s="25" t="s">
         <v>31</v>
@@ -2138,7 +2139,7 @@
       </c>
       <c r="K30" s="26"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="15"/>
       <c r="B31" s="25" t="s">
         <v>36</v>
@@ -2156,7 +2157,7 @@
       </c>
       <c r="K31" s="15"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="15"/>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -2169,7 +2170,7 @@
       <c r="J32" s="15"/>
       <c r="K32" s="15"/>
     </row>
-    <row r="33" spans="1:13" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
         <v>4</v>
       </c>
@@ -2186,7 +2187,7 @@
       <c r="J33" s="13"/>
       <c r="K33" s="13"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
       <c r="B34" s="16" t="str">
         <f>B23</f>
@@ -2216,7 +2217,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="15"/>
       <c r="B35" s="16" t="s">
         <v>59</v>
@@ -2245,7 +2246,7 @@
       <c r="J35" s="15"/>
       <c r="K35" s="15"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="16" t="s">
         <v>60</v>
@@ -2273,7 +2274,7 @@
       <c r="J36" s="15"/>
       <c r="K36" s="15"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="15"/>
       <c r="B37" s="16" t="s">
         <v>61</v>
@@ -2300,7 +2301,7 @@
       <c r="J37" s="15"/>
       <c r="K37" s="15"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
       <c r="B38" s="16" t="s">
         <v>62</v>
@@ -2328,7 +2329,7 @@
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="15"/>
       <c r="B39" s="16" t="s">
         <v>81</v>
@@ -2355,7 +2356,7 @@
       <c r="J39" s="15"/>
       <c r="K39" s="15"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="15"/>
       <c r="B40" s="16" t="s">
         <v>82</v>
@@ -2382,7 +2383,7 @@
       <c r="J40" s="15"/>
       <c r="K40" s="15"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
       <c r="B41" s="16" t="s">
         <v>83</v>
@@ -2410,7 +2411,7 @@
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="15"/>
       <c r="B42" s="16" t="s">
         <v>84</v>
@@ -2437,7 +2438,7 @@
       <c r="J42" s="15"/>
       <c r="K42" s="15"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="16"/>
       <c r="C43" s="15">
@@ -2462,7 +2463,7 @@
       <c r="J43" s="15"/>
       <c r="K43" s="15"/>
     </row>
-    <row r="44" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="17"/>
       <c r="B44" s="18" t="s">
         <v>16</v>
@@ -2487,7 +2488,7 @@
       </c>
       <c r="K44" s="20"/>
     </row>
-    <row r="45" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="24"/>
       <c r="B45" s="25" t="s">
         <v>32</v>
@@ -2505,7 +2506,7 @@
       </c>
       <c r="K45" s="26"/>
     </row>
-    <row r="46" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="24"/>
       <c r="B46" s="25" t="s">
         <v>33</v>
@@ -2523,7 +2524,7 @@
       </c>
       <c r="K46" s="26"/>
     </row>
-    <row r="47" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="24"/>
       <c r="B47" s="25" t="s">
         <v>31</v>
@@ -2541,7 +2542,7 @@
       </c>
       <c r="K47" s="26"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="15"/>
       <c r="B48" s="25" t="s">
         <v>36</v>
@@ -2559,7 +2560,7 @@
       </c>
       <c r="K48" s="15"/>
     </row>
-    <row r="49" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="24"/>
       <c r="B49" s="25" t="s">
         <v>44</v>
@@ -2577,7 +2578,7 @@
       </c>
       <c r="K49" s="26"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="15"/>
       <c r="B50" s="25" t="s">
         <v>45</v>
@@ -2595,7 +2596,7 @@
       </c>
       <c r="K50" s="15"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="15"/>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -2608,7 +2609,7 @@
       <c r="J51" s="15"/>
       <c r="K51" s="15"/>
     </row>
-    <row r="52" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A52" s="11">
         <v>5</v>
       </c>
@@ -2625,7 +2626,7 @@
       <c r="J52" s="13"/>
       <c r="K52" s="13"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="15"/>
       <c r="B53" s="16" t="str">
         <f>B36</f>
@@ -2653,7 +2654,7 @@
       <c r="J53" s="15"/>
       <c r="K53" s="15"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="15"/>
       <c r="B54" s="16" t="str">
         <f>B35</f>
@@ -2681,7 +2682,7 @@
       <c r="J54" s="15"/>
       <c r="K54" s="15"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="15"/>
       <c r="B55" s="16" t="str">
         <f t="shared" ref="B55:C60" si="5">B37</f>
@@ -2709,7 +2710,7 @@
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="15"/>
       <c r="B56" s="16" t="str">
         <f t="shared" si="5"/>
@@ -2737,7 +2738,7 @@
       <c r="J56" s="15"/>
       <c r="K56" s="15"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="15"/>
       <c r="B57" s="16" t="str">
         <f t="shared" si="5"/>
@@ -2765,7 +2766,7 @@
       <c r="J57" s="15"/>
       <c r="K57" s="15"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="15"/>
       <c r="B58" s="16" t="str">
         <f t="shared" si="5"/>
@@ -2793,7 +2794,7 @@
       <c r="J58" s="15"/>
       <c r="K58" s="15"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="15"/>
       <c r="B59" s="16" t="str">
         <f t="shared" si="5"/>
@@ -2821,7 +2822,7 @@
       <c r="J59" s="15"/>
       <c r="K59" s="15"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="15"/>
       <c r="B60" s="16" t="str">
         <f t="shared" si="5"/>
@@ -2849,7 +2850,7 @@
       <c r="J60" s="15"/>
       <c r="K60" s="15"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="15"/>
       <c r="B61" s="16"/>
       <c r="C61" s="15">
@@ -2874,7 +2875,7 @@
       <c r="J61" s="15"/>
       <c r="K61" s="15"/>
     </row>
-    <row r="62" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="17"/>
       <c r="B62" s="18" t="s">
         <v>16</v>
@@ -2899,7 +2900,7 @@
       </c>
       <c r="K62" s="20"/>
     </row>
-    <row r="63" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="24"/>
       <c r="B63" s="25" t="s">
         <v>47</v>
@@ -2917,7 +2918,7 @@
       </c>
       <c r="K63" s="26"/>
     </row>
-    <row r="64" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="24"/>
       <c r="B64" s="25" t="s">
         <v>48</v>
@@ -2935,7 +2936,7 @@
       </c>
       <c r="K64" s="26"/>
     </row>
-    <row r="65" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="24"/>
       <c r="B65" s="25" t="s">
         <v>49</v>
@@ -2953,7 +2954,7 @@
       </c>
       <c r="K65" s="26"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="15"/>
       <c r="B66" s="25" t="s">
         <v>50</v>
@@ -2971,7 +2972,7 @@
       </c>
       <c r="K66" s="15"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="15"/>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -2984,7 +2985,7 @@
       <c r="J67" s="15"/>
       <c r="K67" s="15"/>
     </row>
-    <row r="68" spans="1:13" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
         <v>6</v>
       </c>
@@ -3009,7 +3010,7 @@
       <c r="J68" s="13"/>
       <c r="K68" s="13"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="15"/>
       <c r="B69" s="16" t="str">
         <f>B34</f>
@@ -3040,7 +3041,7 @@
       <c r="J69" s="15"/>
       <c r="K69" s="15"/>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="15"/>
       <c r="B70" s="16"/>
       <c r="C70" s="15">
@@ -3067,7 +3068,7 @@
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="15"/>
       <c r="B71" s="16" t="s">
         <v>70</v>
@@ -3097,7 +3098,7 @@
       <c r="J71" s="15"/>
       <c r="K71" s="15"/>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="15"/>
       <c r="B72" s="16"/>
       <c r="C72" s="15">
@@ -3129,7 +3130,7 @@
         <v>5.0777202072538854</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="15"/>
       <c r="B73" s="16" t="s">
         <v>71</v>
@@ -3159,7 +3160,7 @@
       <c r="J73" s="15"/>
       <c r="K73" s="15"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="15"/>
       <c r="B74" s="16"/>
       <c r="C74" s="15">
@@ -3187,7 +3188,7 @@
       <c r="J74" s="15"/>
       <c r="K74" s="15"/>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="15"/>
       <c r="B75" s="16" t="str">
         <f>B54</f>
@@ -3218,7 +3219,7 @@
       <c r="J75" s="15"/>
       <c r="K75" s="15"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="15"/>
       <c r="B76" s="16" t="s">
         <v>72</v>
@@ -3248,7 +3249,7 @@
       <c r="J76" s="15"/>
       <c r="K76" s="15"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="15"/>
       <c r="B77" s="16" t="str">
         <f>B56</f>
@@ -3279,7 +3280,7 @@
       <c r="J77" s="15"/>
       <c r="K77" s="15"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="15"/>
       <c r="B78" s="16" t="str">
         <f>B57</f>
@@ -3310,7 +3311,7 @@
       <c r="J78" s="15"/>
       <c r="K78" s="15"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="15"/>
       <c r="B79" s="16"/>
       <c r="C79" s="15">
@@ -3338,7 +3339,7 @@
       <c r="J79" s="15"/>
       <c r="K79" s="15"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="15"/>
       <c r="B80" s="16" t="str">
         <f>B58</f>
@@ -3369,7 +3370,7 @@
       <c r="J80" s="15"/>
       <c r="K80" s="15"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="15"/>
       <c r="B81" s="16" t="s">
         <v>71</v>
@@ -3399,7 +3400,7 @@
       <c r="J81" s="15"/>
       <c r="K81" s="15"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="15"/>
       <c r="B82" s="16" t="str">
         <f>B59</f>
@@ -3430,7 +3431,7 @@
       <c r="J82" s="15"/>
       <c r="K82" s="15"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="15"/>
       <c r="B83" s="16"/>
       <c r="C83" s="15">
@@ -3458,7 +3459,7 @@
       <c r="J83" s="15"/>
       <c r="K83" s="15"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="15"/>
       <c r="B84" s="16" t="s">
         <v>84</v>
@@ -3487,7 +3488,7 @@
       <c r="J84" s="15"/>
       <c r="K84" s="15"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="15"/>
       <c r="B85" s="16"/>
       <c r="C85" s="15">
@@ -3514,7 +3515,7 @@
       <c r="J85" s="15"/>
       <c r="K85" s="15"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="15"/>
       <c r="B86" s="16"/>
       <c r="C86" s="15">
@@ -3541,7 +3542,7 @@
       <c r="J86" s="15"/>
       <c r="K86" s="15"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="15"/>
       <c r="B87" s="16"/>
       <c r="C87" s="15">
@@ -3568,7 +3569,7 @@
       <c r="J87" s="15"/>
       <c r="K87" s="15"/>
     </row>
-    <row r="88" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="17"/>
       <c r="B88" s="18" t="s">
         <v>16</v>
@@ -3593,7 +3594,7 @@
       </c>
       <c r="K88" s="20"/>
     </row>
-    <row r="89" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="24"/>
       <c r="B89" s="25" t="s">
         <v>39</v>
@@ -3611,7 +3612,7 @@
       </c>
       <c r="K89" s="26"/>
     </row>
-    <row r="90" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="24"/>
       <c r="B90" s="25" t="s">
         <v>38</v>
@@ -3629,7 +3630,7 @@
       </c>
       <c r="K90" s="26"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="15"/>
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
@@ -3642,7 +3643,7 @@
       <c r="J91" s="15"/>
       <c r="K91" s="15"/>
     </row>
-    <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="11">
         <v>7</v>
       </c>
@@ -3659,7 +3660,7 @@
       <c r="J92" s="15"/>
       <c r="K92" s="15"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="15"/>
       <c r="B93" s="16" t="s">
         <v>66</v>
@@ -3685,7 +3686,7 @@
       <c r="J93" s="15"/>
       <c r="K93" s="15"/>
     </row>
-    <row r="94" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="17"/>
       <c r="B94" s="18" t="s">
         <v>16</v>
@@ -3710,7 +3711,7 @@
       </c>
       <c r="K94" s="20"/>
     </row>
-    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="24"/>
       <c r="B95" s="25" t="s">
         <v>32</v>
@@ -3728,7 +3729,7 @@
       </c>
       <c r="K95" s="26"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="15"/>
       <c r="B96" s="25" t="s">
         <v>31</v>
@@ -3746,7 +3747,7 @@
       </c>
       <c r="K96" s="15"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="15"/>
       <c r="B97" s="25" t="s">
         <v>33</v>
@@ -3764,7 +3765,7 @@
       </c>
       <c r="K97" s="15"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="15"/>
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
@@ -3777,7 +3778,7 @@
       <c r="J98" s="15"/>
       <c r="K98" s="15"/>
     </row>
-    <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="11">
         <v>8</v>
       </c>
@@ -3794,7 +3795,7 @@
       <c r="J99" s="15"/>
       <c r="K99" s="15"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="15"/>
       <c r="B100" s="16" t="s">
         <v>67</v>
@@ -3821,7 +3822,7 @@
       <c r="J100" s="15"/>
       <c r="K100" s="15"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="15"/>
       <c r="B101" s="16"/>
       <c r="C101" s="45">
@@ -3846,7 +3847,7 @@
       <c r="J101" s="15"/>
       <c r="K101" s="15"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="15"/>
       <c r="B102" s="16" t="str">
         <f>B119</f>
@@ -3874,7 +3875,7 @@
       <c r="J102" s="15"/>
       <c r="K102" s="15"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="15"/>
       <c r="B103" s="16" t="str">
         <f>B120</f>
@@ -3902,7 +3903,7 @@
       <c r="J103" s="15"/>
       <c r="K103" s="15"/>
     </row>
-    <row r="104" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="17"/>
       <c r="B104" s="18" t="s">
         <v>16</v>
@@ -3927,7 +3928,7 @@
       </c>
       <c r="K104" s="20"/>
     </row>
-    <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="24"/>
       <c r="B105" s="25" t="s">
         <v>32</v>
@@ -3945,7 +3946,7 @@
       </c>
       <c r="K105" s="26"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="15"/>
       <c r="B106" s="25" t="s">
         <v>31</v>
@@ -3963,7 +3964,7 @@
       </c>
       <c r="K106" s="15"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
@@ -3976,7 +3977,7 @@
       <c r="J107" s="15"/>
       <c r="K107" s="15"/>
     </row>
-    <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="11">
         <v>9</v>
       </c>
@@ -3993,7 +3994,7 @@
       <c r="J108" s="15"/>
       <c r="K108" s="15"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="15"/>
       <c r="B109" s="16" t="str">
         <f>B93</f>
@@ -4021,7 +4022,7 @@
       <c r="J109" s="15"/>
       <c r="K109" s="15"/>
     </row>
-    <row r="110" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="17"/>
       <c r="B110" s="18" t="s">
         <v>16</v>
@@ -4046,7 +4047,7 @@
       </c>
       <c r="K110" s="20"/>
     </row>
-    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="24"/>
       <c r="B111" s="25" t="s">
         <v>32</v>
@@ -4064,7 +4065,7 @@
       </c>
       <c r="K111" s="26"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="15"/>
       <c r="B112" s="25" t="s">
         <v>31</v>
@@ -4082,7 +4083,7 @@
       </c>
       <c r="K112" s="15"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
@@ -4095,7 +4096,7 @@
       <c r="J113" s="15"/>
       <c r="K113" s="15"/>
     </row>
-    <row r="114" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="11">
         <v>10</v>
       </c>
@@ -4112,7 +4113,7 @@
       <c r="J114" s="15"/>
       <c r="K114" s="15"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="15"/>
       <c r="B115" s="16" t="str">
         <f>B35</f>
@@ -4141,7 +4142,7 @@
       <c r="J115" s="15"/>
       <c r="K115" s="15"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="15"/>
       <c r="B116" s="16" t="s">
         <v>65</v>
@@ -4169,7 +4170,7 @@
       <c r="J116" s="15"/>
       <c r="K116" s="15"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="15"/>
       <c r="B117" s="16"/>
       <c r="C117" s="3">
@@ -4195,7 +4196,7 @@
       <c r="J117" s="15"/>
       <c r="K117" s="15"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="15"/>
       <c r="B118" s="16" t="s">
         <v>80</v>
@@ -4222,7 +4223,7 @@
       <c r="J118" s="15"/>
       <c r="K118" s="15"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="15"/>
       <c r="B119" s="16" t="s">
         <v>68</v>
@@ -4250,7 +4251,7 @@
       <c r="J119" s="15"/>
       <c r="K119" s="15"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="15"/>
       <c r="B120" s="16" t="s">
         <v>69</v>
@@ -4278,7 +4279,7 @@
       <c r="J120" s="15"/>
       <c r="K120" s="15"/>
     </row>
-    <row r="121" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17"/>
       <c r="B121" s="18" t="s">
         <v>16</v>
@@ -4304,7 +4305,7 @@
       </c>
       <c r="K121" s="20"/>
     </row>
-    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="24"/>
       <c r="B122" s="25" t="s">
         <v>55</v>
@@ -4322,7 +4323,7 @@
       </c>
       <c r="K122" s="26"/>
     </row>
-    <row r="123" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="24"/>
       <c r="B123" s="25" t="s">
         <v>32</v>
@@ -4340,7 +4341,7 @@
       </c>
       <c r="K123" s="26"/>
     </row>
-    <row r="124" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="24"/>
       <c r="B124" s="25" t="s">
         <v>64</v>
@@ -4358,7 +4359,7 @@
       </c>
       <c r="K124" s="26"/>
     </row>
-    <row r="125" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="24"/>
       <c r="B125" s="25" t="s">
         <v>36</v>
@@ -4376,7 +4377,7 @@
       </c>
       <c r="K125" s="26"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -4389,7 +4390,7 @@
       <c r="J126" s="15"/>
       <c r="K126" s="15"/>
     </row>
-    <row r="127" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="11">
         <v>11</v>
       </c>
@@ -4406,7 +4407,7 @@
       <c r="J127" s="15"/>
       <c r="K127" s="15"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="15"/>
       <c r="B128" s="16" t="s">
         <v>65</v>
@@ -4433,7 +4434,7 @@
       <c r="J128" s="15"/>
       <c r="K128" s="15"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="15"/>
       <c r="B129" s="16"/>
       <c r="C129" s="3">
@@ -4458,7 +4459,7 @@
       <c r="J129" s="15"/>
       <c r="K129" s="15"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="15"/>
       <c r="B130" s="16" t="s">
         <v>68</v>
@@ -4485,7 +4486,7 @@
       <c r="J130" s="15"/>
       <c r="K130" s="15"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="15"/>
       <c r="B131" s="16" t="s">
         <v>69</v>
@@ -4512,7 +4513,7 @@
       <c r="J131" s="15"/>
       <c r="K131" s="15"/>
     </row>
-    <row r="132" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="17"/>
       <c r="B132" s="18" t="s">
         <v>16</v>
@@ -4537,7 +4538,7 @@
       </c>
       <c r="K132" s="20"/>
     </row>
-    <row r="133" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="24"/>
       <c r="B133" s="25" t="s">
         <v>74</v>
@@ -4555,7 +4556,7 @@
       </c>
       <c r="K133" s="26"/>
     </row>
-    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="24"/>
       <c r="B134" s="25" t="s">
         <v>75</v>
@@ -4573,7 +4574,7 @@
       </c>
       <c r="K134" s="26"/>
     </row>
-    <row r="135" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="24"/>
       <c r="B135" s="25"/>
       <c r="C135" s="26"/>
@@ -4586,7 +4587,7 @@
       <c r="J135" s="22"/>
       <c r="K135" s="26"/>
     </row>
-    <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="11">
         <v>12</v>
       </c>
@@ -4603,7 +4604,7 @@
       <c r="J136" s="15"/>
       <c r="K136" s="15"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="15"/>
       <c r="B137" s="16" t="s">
         <v>65</v>
@@ -4618,7 +4619,7 @@
       <c r="J137" s="15"/>
       <c r="K137" s="15"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="15"/>
       <c r="B138" s="16" t="s">
         <v>77</v>
@@ -4644,7 +4645,7 @@
       <c r="J138" s="15"/>
       <c r="K138" s="15"/>
     </row>
-    <row r="139" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="17"/>
       <c r="B139" s="18" t="s">
         <v>16</v>
@@ -4669,7 +4670,7 @@
       </c>
       <c r="K139" s="20"/>
     </row>
-    <row r="140" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="24"/>
       <c r="B140" s="25" t="s">
         <v>74</v>
@@ -4687,7 +4688,7 @@
       </c>
       <c r="K140" s="26"/>
     </row>
-    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="24"/>
       <c r="B141" s="25"/>
       <c r="C141" s="26"/>
@@ -4700,7 +4701,7 @@
       <c r="J141" s="22"/>
       <c r="K141" s="26"/>
     </row>
-    <row r="142" spans="1:11" s="10" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" s="10" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A142" s="24">
         <v>13</v>
       </c>
@@ -4717,7 +4718,7 @@
       <c r="J142" s="22"/>
       <c r="K142" s="26"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="15"/>
       <c r="B143" s="16" t="s">
         <v>79</v>
@@ -4742,7 +4743,7 @@
       <c r="J143" s="15"/>
       <c r="K143" s="15"/>
     </row>
-    <row r="144" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="17"/>
       <c r="B144" s="18" t="s">
         <v>16</v>
@@ -4767,7 +4768,7 @@
       </c>
       <c r="K144" s="20"/>
     </row>
-    <row r="145" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="24"/>
       <c r="B145" s="25" t="s">
         <v>74</v>
@@ -4785,7 +4786,7 @@
       </c>
       <c r="K145" s="26"/>
     </row>
-    <row r="146" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="24"/>
       <c r="B146" s="25"/>
       <c r="C146" s="26"/>
@@ -4798,7 +4799,7 @@
       <c r="J146" s="22"/>
       <c r="K146" s="26"/>
     </row>
-    <row r="147" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="17">
         <v>14</v>
       </c>
@@ -4827,7 +4828,7 @@
       </c>
       <c r="K147" s="20"/>
     </row>
-    <row r="148" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="17"/>
       <c r="B148" s="31"/>
       <c r="C148" s="19"/>
@@ -4840,7 +4841,7 @@
       <c r="J148" s="22"/>
       <c r="K148" s="20"/>
     </row>
-    <row r="149" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="17">
         <v>15</v>
       </c>
@@ -4869,7 +4870,7 @@
       </c>
       <c r="K149" s="20"/>
     </row>
-    <row r="150" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="17"/>
       <c r="B150" s="31"/>
       <c r="C150" s="19"/>
@@ -4882,7 +4883,7 @@
       <c r="J150" s="22"/>
       <c r="K150" s="20"/>
     </row>
-    <row r="151" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="32"/>
       <c r="B151" s="33" t="s">
         <v>20</v>
@@ -4900,17 +4901,17 @@
       </c>
       <c r="K151" s="36"/>
     </row>
-    <row r="152" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="153" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="37"/>
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="58">
+      <c r="C153" s="64">
         <f>J151</f>
         <v>791637.34255256748</v>
       </c>
-      <c r="D153" s="59"/>
+      <c r="D153" s="65"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -4921,72 +4922,78 @@
       <c r="J153" s="42"/>
       <c r="K153" s="43"/>
     </row>
-    <row r="154" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="60">
+      <c r="C154" s="68">
         <v>700000</v>
       </c>
-      <c r="D154" s="61"/>
+      <c r="D154" s="69"/>
       <c r="E154" s="39"/>
     </row>
-    <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="60">
+      <c r="C155" s="68">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="61"/>
+      <c r="D155" s="69"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>84.003111558098539</v>
       </c>
     </row>
-    <row r="156" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="62">
+      <c r="C156" s="70">
         <f>C153-C155</f>
         <v>126637.34255256748</v>
       </c>
-      <c r="D156" s="62"/>
+      <c r="D156" s="70"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>15.996888441901461</v>
       </c>
     </row>
-    <row r="157" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="58">
+      <c r="C157" s="64">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="59"/>
+      <c r="D157" s="65"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="58">
+      <c r="C158" s="64">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="59"/>
+      <c r="D158" s="65"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -4996,12 +5003,6 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -5012,131 +5013,131 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P144"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" customWidth="1"/>
     <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-    </row>
-    <row r="2" spans="1:16" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+    </row>
+    <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="67" t="s">
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-    </row>
-    <row r="5" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+    </row>
+    <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-    </row>
-    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="69" t="s">
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+    </row>
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="70" t="s">
+      <c r="H6" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="63" t="s">
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="64" t="s">
+      <c r="H7" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-    </row>
-    <row r="8" spans="1:16" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+    </row>
+    <row r="8" spans="1:16" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -5183,7 +5184,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="11">
         <v>1</v>
       </c>
@@ -5215,7 +5216,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="16" t="s">
         <v>52</v>
@@ -5245,7 +5246,7 @@
       <c r="M10" s="55"/>
       <c r="N10" s="55"/>
     </row>
-    <row r="11" spans="1:16" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="18" t="s">
         <v>16</v>
@@ -5270,7 +5271,7 @@
       </c>
       <c r="K11" s="20"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -5283,7 +5284,7 @@
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
     </row>
-    <row r="13" spans="1:16" s="14" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11">
         <v>2</v>
       </c>
@@ -5300,7 +5301,7 @@
       <c r="J13" s="13"/>
       <c r="K13" s="13"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="15"/>
       <c r="B14" s="16" t="str">
         <f>B10</f>
@@ -5328,7 +5329,7 @@
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
     </row>
-    <row r="15" spans="1:16" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17"/>
       <c r="B15" s="18" t="s">
         <v>16</v>
@@ -5353,7 +5354,7 @@
       </c>
       <c r="K15" s="20"/>
     </row>
-    <row r="16" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24"/>
       <c r="B16" s="25" t="s">
         <v>55</v>
@@ -5371,7 +5372,7 @@
       </c>
       <c r="K16" s="26"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
       <c r="B17" s="25" t="s">
         <v>31</v>
@@ -5389,7 +5390,7 @@
       </c>
       <c r="K17" s="15"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="15"/>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -5402,7 +5403,7 @@
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
     </row>
-    <row r="19" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="11">
         <v>3</v>
       </c>
@@ -5419,7 +5420,7 @@
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="15"/>
       <c r="B20" s="16" t="str">
         <f>B10</f>
@@ -5449,7 +5450,7 @@
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
     </row>
-    <row r="21" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="18" t="s">
         <v>16</v>
@@ -5474,7 +5475,7 @@
       </c>
       <c r="K21" s="20"/>
     </row>
-    <row r="22" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="24"/>
       <c r="B22" s="25" t="s">
         <v>32</v>
@@ -5492,7 +5493,7 @@
       </c>
       <c r="K22" s="26"/>
     </row>
-    <row r="23" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24"/>
       <c r="B23" s="25" t="s">
         <v>33</v>
@@ -5510,7 +5511,7 @@
       </c>
       <c r="K23" s="26"/>
     </row>
-    <row r="24" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="24"/>
       <c r="B24" s="25" t="s">
         <v>31</v>
@@ -5528,7 +5529,7 @@
       </c>
       <c r="K24" s="26"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="15"/>
       <c r="B25" s="25" t="s">
         <v>36</v>
@@ -5546,7 +5547,7 @@
       </c>
       <c r="K25" s="15"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
       <c r="B26" s="25" t="s">
         <v>36</v>
@@ -5564,7 +5565,7 @@
       </c>
       <c r="K26" s="15"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="15"/>
       <c r="B27" s="25" t="s">
         <v>36</v>
@@ -5582,7 +5583,7 @@
       </c>
       <c r="K27" s="15"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -5595,7 +5596,7 @@
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
     </row>
-    <row r="29" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" s="11">
         <v>4</v>
       </c>
@@ -5612,7 +5613,7 @@
       <c r="J29" s="13"/>
       <c r="K29" s="13"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="15"/>
       <c r="B30" s="16" t="str">
         <f>B71</f>
@@ -5641,7 +5642,7 @@
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
     </row>
-    <row r="31" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="18" t="s">
         <v>16</v>
@@ -5666,7 +5667,7 @@
       </c>
       <c r="K31" s="20"/>
     </row>
-    <row r="32" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
       <c r="B32" s="25" t="s">
         <v>32</v>
@@ -5684,7 +5685,7 @@
       </c>
       <c r="K32" s="26"/>
     </row>
-    <row r="33" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="24"/>
       <c r="B33" s="25" t="s">
         <v>33</v>
@@ -5702,7 +5703,7 @@
       </c>
       <c r="K33" s="26"/>
     </row>
-    <row r="34" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="24"/>
       <c r="B34" s="25" t="s">
         <v>31</v>
@@ -5720,7 +5721,7 @@
       </c>
       <c r="K34" s="26"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="15"/>
       <c r="B35" s="25" t="s">
         <v>36</v>
@@ -5738,7 +5739,7 @@
       </c>
       <c r="K35" s="15"/>
     </row>
-    <row r="36" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="24"/>
       <c r="B36" s="25" t="s">
         <v>44</v>
@@ -5756,7 +5757,7 @@
       </c>
       <c r="K36" s="26"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="15"/>
       <c r="B37" s="25" t="s">
         <v>45</v>
@@ -5774,7 +5775,7 @@
       </c>
       <c r="K37" s="15"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -5787,7 +5788,7 @@
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
     </row>
-    <row r="39" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A39" s="11">
         <v>5</v>
       </c>
@@ -5804,7 +5805,7 @@
       <c r="J39" s="13"/>
       <c r="K39" s="13"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="15"/>
       <c r="B40" s="16" t="str">
         <f>B30</f>
@@ -5832,7 +5833,7 @@
       <c r="J40" s="15"/>
       <c r="K40" s="15"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="15"/>
       <c r="B41" s="16" t="s">
         <v>122</v>
@@ -5858,7 +5859,7 @@
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
     </row>
-    <row r="42" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="17"/>
       <c r="B42" s="18" t="s">
         <v>16</v>
@@ -5883,7 +5884,7 @@
       </c>
       <c r="K42" s="20"/>
     </row>
-    <row r="43" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="24"/>
       <c r="B43" s="25" t="s">
         <v>47</v>
@@ -5901,7 +5902,7 @@
       </c>
       <c r="K43" s="26"/>
     </row>
-    <row r="44" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="24"/>
       <c r="B44" s="25" t="s">
         <v>48</v>
@@ -5919,7 +5920,7 @@
       </c>
       <c r="K44" s="26"/>
     </row>
-    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="24"/>
       <c r="B45" s="25" t="s">
         <v>49</v>
@@ -5937,7 +5938,7 @@
       </c>
       <c r="K45" s="26"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="15"/>
       <c r="B46" s="25" t="s">
         <v>50</v>
@@ -5955,7 +5956,7 @@
       </c>
       <c r="K46" s="15"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="15"/>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -5968,7 +5969,7 @@
       <c r="J47" s="15"/>
       <c r="K47" s="15"/>
     </row>
-    <row r="48" spans="1:11" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>6</v>
       </c>
@@ -5993,7 +5994,7 @@
       <c r="J48" s="13"/>
       <c r="K48" s="13"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="15"/>
       <c r="B49" s="16" t="str">
         <f>B30</f>
@@ -6024,7 +6025,7 @@
       <c r="J49" s="15"/>
       <c r="K49" s="15"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="15"/>
       <c r="B50" s="16"/>
       <c r="C50" s="15">
@@ -6052,7 +6053,7 @@
       <c r="J50" s="15"/>
       <c r="K50" s="15"/>
     </row>
-    <row r="51" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17"/>
       <c r="B51" s="18" t="s">
         <v>16</v>
@@ -6077,7 +6078,7 @@
       </c>
       <c r="K51" s="20"/>
     </row>
-    <row r="52" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="24"/>
       <c r="B52" s="25" t="s">
         <v>39</v>
@@ -6095,7 +6096,7 @@
       </c>
       <c r="K52" s="26"/>
     </row>
-    <row r="53" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="24"/>
       <c r="B53" s="25" t="s">
         <v>38</v>
@@ -6113,7 +6114,7 @@
       </c>
       <c r="K53" s="26"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="15"/>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -6126,7 +6127,7 @@
       <c r="J54" s="15"/>
       <c r="K54" s="15"/>
     </row>
-    <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="11">
         <v>7</v>
       </c>
@@ -6143,7 +6144,7 @@
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="15"/>
       <c r="B56" s="16" t="str">
         <f>B10</f>
@@ -6170,7 +6171,7 @@
       <c r="J56" s="15"/>
       <c r="K56" s="15"/>
     </row>
-    <row r="57" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="17"/>
       <c r="B57" s="18" t="s">
         <v>16</v>
@@ -6195,7 +6196,7 @@
       </c>
       <c r="K57" s="20"/>
     </row>
-    <row r="58" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="24"/>
       <c r="B58" s="25" t="s">
         <v>32</v>
@@ -6213,7 +6214,7 @@
       </c>
       <c r="K58" s="26"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="15"/>
       <c r="B59" s="25" t="s">
         <v>31</v>
@@ -6231,7 +6232,7 @@
       </c>
       <c r="K59" s="15"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="15"/>
       <c r="B60" s="25" t="s">
         <v>33</v>
@@ -6249,7 +6250,7 @@
       </c>
       <c r="K60" s="15"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="15"/>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -6262,7 +6263,7 @@
       <c r="J61" s="15"/>
       <c r="K61" s="15"/>
     </row>
-    <row r="62" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>8</v>
       </c>
@@ -6279,7 +6280,7 @@
       <c r="J62" s="15"/>
       <c r="K62" s="15"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="15"/>
       <c r="B63" s="16" t="str">
         <f>B56</f>
@@ -6307,7 +6308,7 @@
       <c r="J63" s="15"/>
       <c r="K63" s="15"/>
     </row>
-    <row r="64" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="17"/>
       <c r="B64" s="18" t="s">
         <v>16</v>
@@ -6332,7 +6333,7 @@
       </c>
       <c r="K64" s="20"/>
     </row>
-    <row r="65" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="24"/>
       <c r="B65" s="25" t="s">
         <v>32</v>
@@ -6350,7 +6351,7 @@
       </c>
       <c r="K65" s="26"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="15"/>
       <c r="B66" s="25" t="s">
         <v>31</v>
@@ -6368,7 +6369,7 @@
       </c>
       <c r="K66" s="15"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="15"/>
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
@@ -6381,7 +6382,7 @@
       <c r="J67" s="15"/>
       <c r="K67" s="15"/>
     </row>
-    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="11">
         <v>9</v>
       </c>
@@ -6398,7 +6399,7 @@
       <c r="J68" s="15"/>
       <c r="K68" s="15"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="15"/>
       <c r="B69" s="16" t="s">
         <v>118</v>
@@ -6426,7 +6427,7 @@
       <c r="J69" s="15"/>
       <c r="K69" s="15"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="15"/>
       <c r="B70" s="16"/>
       <c r="C70" s="3">
@@ -6452,7 +6453,7 @@
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="15"/>
       <c r="B71" s="16" t="s">
         <v>120</v>
@@ -6480,7 +6481,7 @@
       <c r="J71" s="15"/>
       <c r="K71" s="15"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="15"/>
       <c r="B72" s="16" t="s">
         <v>119</v>
@@ -6509,7 +6510,7 @@
       <c r="J72" s="15"/>
       <c r="K72" s="15"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="15"/>
       <c r="B73" s="16" t="s">
         <v>68</v>
@@ -6535,7 +6536,7 @@
       <c r="J73" s="15"/>
       <c r="K73" s="15"/>
     </row>
-    <row r="74" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="17"/>
       <c r="B74" s="18" t="s">
         <v>16</v>
@@ -6561,7 +6562,7 @@
       </c>
       <c r="K74" s="20"/>
     </row>
-    <row r="75" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="24"/>
       <c r="B75" s="25" t="s">
         <v>55</v>
@@ -6579,7 +6580,7 @@
       </c>
       <c r="K75" s="26"/>
     </row>
-    <row r="76" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="24"/>
       <c r="B76" s="25" t="s">
         <v>32</v>
@@ -6597,7 +6598,7 @@
       </c>
       <c r="K76" s="26"/>
     </row>
-    <row r="77" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="24"/>
       <c r="B77" s="25" t="s">
         <v>64</v>
@@ -6615,7 +6616,7 @@
       </c>
       <c r="K77" s="26"/>
     </row>
-    <row r="78" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="24"/>
       <c r="B78" s="25" t="s">
         <v>36</v>
@@ -6633,7 +6634,7 @@
       </c>
       <c r="K78" s="26"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="15"/>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -6646,7 +6647,7 @@
       <c r="J79" s="15"/>
       <c r="K79" s="15"/>
     </row>
-    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="11">
         <v>10</v>
       </c>
@@ -6663,7 +6664,7 @@
       <c r="J80" s="15"/>
       <c r="K80" s="15"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="15"/>
       <c r="B81" s="16" t="str">
         <f>B69</f>
@@ -6690,7 +6691,7 @@
       <c r="J81" s="15"/>
       <c r="K81" s="15"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="15"/>
       <c r="B82" s="16"/>
       <c r="C82" s="45">
@@ -6714,7 +6715,7 @@
       <c r="J82" s="15"/>
       <c r="K82" s="15"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="15"/>
       <c r="B83" s="16" t="str">
         <f>B73</f>
@@ -6742,7 +6743,7 @@
       <c r="J83" s="15"/>
       <c r="K83" s="15"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="15"/>
       <c r="B84" s="16" t="str">
         <f>B71</f>
@@ -6770,7 +6771,7 @@
       <c r="J84" s="15"/>
       <c r="K84" s="15"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="15"/>
       <c r="B85" s="16" t="str">
         <f>B72</f>
@@ -6798,7 +6799,7 @@
       <c r="J85" s="15"/>
       <c r="K85" s="15"/>
     </row>
-    <row r="86" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="17"/>
       <c r="B86" s="18" t="s">
         <v>16</v>
@@ -6823,7 +6824,7 @@
       </c>
       <c r="K86" s="20"/>
     </row>
-    <row r="87" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="24"/>
       <c r="B87" s="25" t="s">
         <v>32</v>
@@ -6841,7 +6842,7 @@
       </c>
       <c r="K87" s="26"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="15"/>
       <c r="B88" s="25" t="s">
         <v>31</v>
@@ -6859,7 +6860,7 @@
       </c>
       <c r="K88" s="15"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="15"/>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -6872,7 +6873,7 @@
       <c r="J89" s="15"/>
       <c r="K89" s="15"/>
     </row>
-    <row r="90" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="11">
         <v>11</v>
       </c>
@@ -6889,7 +6890,7 @@
       <c r="J90" s="15"/>
       <c r="K90" s="15"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="15"/>
       <c r="B91" s="16" t="s">
         <v>121</v>
@@ -6910,7 +6911,7 @@
       <c r="J91" s="15"/>
       <c r="K91" s="15"/>
     </row>
-    <row r="92" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="17"/>
       <c r="B92" s="18" t="s">
         <v>16</v>
@@ -6935,7 +6936,7 @@
       </c>
       <c r="K92" s="20"/>
     </row>
-    <row r="93" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="24"/>
       <c r="B93" s="25" t="s">
         <v>74</v>
@@ -6953,7 +6954,7 @@
       </c>
       <c r="K93" s="26"/>
     </row>
-    <row r="94" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="24"/>
       <c r="B94" s="25" t="s">
         <v>75</v>
@@ -6971,7 +6972,7 @@
       </c>
       <c r="K94" s="26"/>
     </row>
-    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="24"/>
       <c r="B95" s="25"/>
       <c r="C95" s="26"/>
@@ -6984,9 +6985,9 @@
       <c r="J95" s="22"/>
       <c r="K95" s="26"/>
     </row>
-    <row r="96" spans="1:11" s="10" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" s="10" customFormat="1" ht="30.75" x14ac:dyDescent="0.25">
       <c r="A96" s="24">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B96" s="28" t="s">
         <v>78</v>
@@ -7001,7 +7002,7 @@
       <c r="J96" s="22"/>
       <c r="K96" s="26"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="15"/>
       <c r="B97" s="16" t="s">
         <v>79</v>
@@ -7027,7 +7028,7 @@
       <c r="J97" s="15"/>
       <c r="K97" s="15"/>
     </row>
-    <row r="98" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="17"/>
       <c r="B98" s="18" t="s">
         <v>16</v>
@@ -7052,7 +7053,7 @@
       </c>
       <c r="K98" s="20"/>
     </row>
-    <row r="99" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="24"/>
       <c r="B99" s="25" t="s">
         <v>74</v>
@@ -7070,7 +7071,7 @@
       </c>
       <c r="K99" s="26"/>
     </row>
-    <row r="100" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="24"/>
       <c r="B100" s="25"/>
       <c r="C100" s="26"/>
@@ -7083,9 +7084,9 @@
       <c r="J100" s="22"/>
       <c r="K100" s="26"/>
     </row>
-    <row r="101" spans="1:11" s="10" customFormat="1" ht="166.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" s="10" customFormat="1" ht="166.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="24">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B101" s="56" t="s">
         <v>123</v>
@@ -7100,7 +7101,7 @@
       <c r="J101" s="26"/>
       <c r="K101" s="26"/>
     </row>
-    <row r="102" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="24"/>
       <c r="B102" s="25" t="s">
         <v>130</v>
@@ -7128,7 +7129,7 @@
       <c r="J102" s="26"/>
       <c r="K102" s="26"/>
     </row>
-    <row r="103" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="24"/>
       <c r="B103" s="25"/>
       <c r="C103" s="26">
@@ -7154,7 +7155,7 @@
       <c r="J103" s="26"/>
       <c r="K103" s="26"/>
     </row>
-    <row r="104" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="17"/>
       <c r="B104" s="18" t="s">
         <v>16</v>
@@ -7179,7 +7180,7 @@
       </c>
       <c r="K104" s="20"/>
     </row>
-    <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="24"/>
       <c r="B105" s="25" t="s">
         <v>125</v>
@@ -7197,7 +7198,7 @@
       </c>
       <c r="K105" s="26"/>
     </row>
-    <row r="106" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="24"/>
       <c r="B106" s="26"/>
       <c r="C106" s="26"/>
@@ -7210,9 +7211,9 @@
       <c r="J106" s="26"/>
       <c r="K106" s="26"/>
     </row>
-    <row r="107" spans="1:11" s="10" customFormat="1" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" s="10" customFormat="1" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A107" s="24">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B107" s="56" t="s">
         <v>126</v>
@@ -7227,7 +7228,7 @@
       <c r="J107" s="26"/>
       <c r="K107" s="26"/>
     </row>
-    <row r="108" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="24"/>
       <c r="B108" s="25" t="str">
         <f>B102</f>
@@ -7256,7 +7257,7 @@
       <c r="J108" s="26"/>
       <c r="K108" s="26"/>
     </row>
-    <row r="109" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="24"/>
       <c r="B109" s="25"/>
       <c r="C109" s="26">
@@ -7282,7 +7283,7 @@
       <c r="J109" s="26"/>
       <c r="K109" s="26"/>
     </row>
-    <row r="110" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="17"/>
       <c r="B110" s="18" t="s">
         <v>16</v>
@@ -7307,7 +7308,7 @@
       </c>
       <c r="K110" s="20"/>
     </row>
-    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="24"/>
       <c r="B111" s="25" t="s">
         <v>125</v>
@@ -7325,7 +7326,7 @@
       </c>
       <c r="K111" s="26"/>
     </row>
-    <row r="112" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="24"/>
       <c r="B112" s="26"/>
       <c r="C112" s="26"/>
@@ -7338,9 +7339,9 @@
       <c r="J112" s="26"/>
       <c r="K112" s="26"/>
     </row>
-    <row r="113" spans="1:11" s="10" customFormat="1" ht="78" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" s="10" customFormat="1" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A113" s="24">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B113" s="56" t="s">
         <v>127</v>
@@ -7355,7 +7356,7 @@
       <c r="J113" s="26"/>
       <c r="K113" s="26"/>
     </row>
-    <row r="114" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="24"/>
       <c r="B114" s="25" t="str">
         <f>B108</f>
@@ -7384,7 +7385,7 @@
       <c r="J114" s="26"/>
       <c r="K114" s="26"/>
     </row>
-    <row r="115" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="24"/>
       <c r="B115" s="25"/>
       <c r="C115" s="26">
@@ -7410,7 +7411,7 @@
       <c r="J115" s="26"/>
       <c r="K115" s="26"/>
     </row>
-    <row r="116" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="17"/>
       <c r="B116" s="18" t="s">
         <v>16</v>
@@ -7435,7 +7436,7 @@
       </c>
       <c r="K116" s="20"/>
     </row>
-    <row r="117" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="24"/>
       <c r="B117" s="25" t="s">
         <v>32</v>
@@ -7453,7 +7454,7 @@
       </c>
       <c r="K117" s="26"/>
     </row>
-    <row r="118" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="24"/>
       <c r="B118" s="25" t="s">
         <v>31</v>
@@ -7471,7 +7472,7 @@
       </c>
       <c r="K118" s="26"/>
     </row>
-    <row r="119" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="24"/>
       <c r="B119" s="25" t="s">
         <v>33</v>
@@ -7489,7 +7490,7 @@
       </c>
       <c r="K119" s="26"/>
     </row>
-    <row r="120" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="24"/>
       <c r="B120" s="25" t="s">
         <v>128</v>
@@ -7507,7 +7508,7 @@
       </c>
       <c r="K120" s="26"/>
     </row>
-    <row r="121" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="24"/>
       <c r="B121" s="25" t="s">
         <v>36</v>
@@ -7525,7 +7526,7 @@
       </c>
       <c r="K121" s="26"/>
     </row>
-    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="24"/>
       <c r="B122" s="26"/>
       <c r="C122" s="26"/>
@@ -7538,9 +7539,9 @@
       <c r="J122" s="26"/>
       <c r="K122" s="26"/>
     </row>
-    <row r="123" spans="1:11" s="10" customFormat="1" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" s="10" customFormat="1" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A123" s="24">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B123" s="56" t="s">
         <v>129</v>
@@ -7555,7 +7556,7 @@
       <c r="J123" s="26"/>
       <c r="K123" s="26"/>
     </row>
-    <row r="124" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="24"/>
       <c r="B124" s="25" t="str">
         <f>B114</f>
@@ -7583,7 +7584,7 @@
       <c r="J124" s="26"/>
       <c r="K124" s="26"/>
     </row>
-    <row r="125" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="24"/>
       <c r="B125" s="25"/>
       <c r="C125" s="26">
@@ -7608,7 +7609,7 @@
       <c r="J125" s="26"/>
       <c r="K125" s="26"/>
     </row>
-    <row r="126" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="17"/>
       <c r="B126" s="18" t="s">
         <v>16</v>
@@ -7633,7 +7634,7 @@
       </c>
       <c r="K126" s="20"/>
     </row>
-    <row r="127" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="24"/>
       <c r="B127" s="25" t="s">
         <v>32</v>
@@ -7651,7 +7652,7 @@
       </c>
       <c r="K127" s="26"/>
     </row>
-    <row r="128" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="24"/>
       <c r="B128" s="25" t="s">
         <v>31</v>
@@ -7669,7 +7670,7 @@
       </c>
       <c r="K128" s="26"/>
     </row>
-    <row r="129" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="24"/>
       <c r="B129" s="25" t="s">
         <v>131</v>
@@ -7687,7 +7688,7 @@
       </c>
       <c r="K129" s="26"/>
     </row>
-    <row r="130" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="24"/>
       <c r="B130" s="25" t="s">
         <v>33</v>
@@ -7705,7 +7706,7 @@
       </c>
       <c r="K130" s="26"/>
     </row>
-    <row r="131" spans="1:11" s="10" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="24"/>
       <c r="B131" s="57" t="s">
         <v>132</v>
@@ -7723,7 +7724,7 @@
       </c>
       <c r="K131" s="26"/>
     </row>
-    <row r="132" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="24"/>
       <c r="B132" s="26"/>
       <c r="C132" s="26"/>
@@ -7736,9 +7737,9 @@
       <c r="J132" s="26"/>
       <c r="K132" s="26"/>
     </row>
-    <row r="133" spans="1:11" s="10" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" s="10" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B133" s="30" t="s">
         <v>115</v>
@@ -7765,7 +7766,7 @@
       </c>
       <c r="K133" s="20"/>
     </row>
-    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="17"/>
       <c r="B134" s="31"/>
       <c r="C134" s="19"/>
@@ -7778,9 +7779,9 @@
       <c r="J134" s="22"/>
       <c r="K134" s="20"/>
     </row>
-    <row r="135" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B135" s="30" t="s">
         <v>17</v>
@@ -7807,7 +7808,7 @@
       </c>
       <c r="K135" s="20"/>
     </row>
-    <row r="136" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="17"/>
       <c r="B136" s="31"/>
       <c r="C136" s="19"/>
@@ -7820,7 +7821,7 @@
       <c r="J136" s="22"/>
       <c r="K136" s="20"/>
     </row>
-    <row r="137" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="32"/>
       <c r="B137" s="33" t="s">
         <v>20</v>
@@ -7838,17 +7839,17 @@
       </c>
       <c r="K137" s="36"/>
     </row>
-    <row r="138" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="139" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="37"/>
       <c r="B139" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C139" s="58">
+      <c r="C139" s="64">
         <f>J137</f>
         <v>810861.26423460047</v>
       </c>
-      <c r="D139" s="59"/>
+      <c r="D139" s="65"/>
       <c r="E139" s="39">
         <v>100</v>
       </c>
@@ -7859,79 +7860,72 @@
       <c r="J139" s="42"/>
       <c r="K139" s="43"/>
     </row>
-    <row r="140" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B140" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C140" s="60">
+      <c r="C140" s="68">
         <v>700000</v>
       </c>
-      <c r="D140" s="61"/>
+      <c r="D140" s="69"/>
       <c r="E140" s="39"/>
     </row>
-    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B141" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C141" s="60">
+      <c r="C141" s="68">
         <f>C140-C143-C144</f>
         <v>665000</v>
       </c>
-      <c r="D141" s="61"/>
+      <c r="D141" s="69"/>
       <c r="E141" s="39">
         <f>C141/C139*100</f>
         <v>82.011563424196382</v>
       </c>
     </row>
-    <row r="142" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B142" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C142" s="62">
+      <c r="C142" s="70">
         <f>C139-C141</f>
         <v>145861.26423460047</v>
       </c>
-      <c r="D142" s="62"/>
+      <c r="D142" s="70"/>
       <c r="E142" s="39">
         <f>100-E141</f>
         <v>17.988436575803618</v>
       </c>
     </row>
-    <row r="143" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B143" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C143" s="58">
+      <c r="C143" s="64">
         <f>C140*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D143" s="59"/>
+      <c r="D143" s="65"/>
       <c r="E143" s="39">
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B144" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C144" s="58">
+      <c r="C144" s="64">
         <f>C140*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D144" s="59"/>
+      <c r="D144" s="65"/>
       <c r="E144" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C143:D143"/>
     <mergeCell ref="C144:D144"/>
     <mergeCell ref="A7:F7"/>
@@ -7940,6 +7934,13 @@
     <mergeCell ref="C140:D140"/>
     <mergeCell ref="C141:D141"/>
     <mergeCell ref="C142:D142"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -7950,133 +7951,133 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K202"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="10" customWidth="1"/>
-    <col min="3" max="3" width="4.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="10"/>
+    <col min="1" max="1" width="4.7109375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="10" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="10"/>
     <col min="8" max="8" width="5" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="10" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="10"/>
+    <col min="9" max="9" width="9.5703125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="67" t="s">
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="62"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-    </row>
-    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="69" t="s">
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="70" t="s">
+      <c r="H6" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="63" t="s">
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="59"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="64" t="s">
+      <c r="H7" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -8111,7 +8112,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="173.25" x14ac:dyDescent="0.25">
       <c r="A9" s="24">
         <v>1</v>
       </c>
@@ -8128,7 +8129,7 @@
       <c r="J9" s="26"/>
       <c r="K9" s="26"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="24"/>
       <c r="B10" s="25" t="s">
         <v>130</v>
@@ -8154,7 +8155,7 @@
       <c r="J10" s="26"/>
       <c r="K10" s="26"/>
     </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17"/>
       <c r="B11" s="18" t="s">
         <v>16</v>
@@ -8179,7 +8180,7 @@
       </c>
       <c r="K11" s="20"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="24"/>
       <c r="B12" s="25" t="s">
         <v>125</v>
@@ -8197,7 +8198,7 @@
       </c>
       <c r="K12" s="26"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="24"/>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
@@ -8210,7 +8211,7 @@
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
     </row>
-    <row r="14" spans="1:11" ht="109.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A14" s="24">
         <v>2</v>
       </c>
@@ -8227,7 +8228,7 @@
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="24"/>
       <c r="B15" s="25" t="str">
         <f>B10</f>
@@ -8256,7 +8257,7 @@
       <c r="J15" s="26"/>
       <c r="K15" s="26"/>
     </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17"/>
       <c r="B16" s="18" t="s">
         <v>16</v>
@@ -8281,7 +8282,7 @@
       </c>
       <c r="K16" s="20"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="24"/>
       <c r="B17" s="25" t="s">
         <v>125</v>
@@ -8299,7 +8300,7 @@
       </c>
       <c r="K17" s="26"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="24"/>
       <c r="B18" s="26"/>
       <c r="C18" s="26"/>
@@ -8312,7 +8313,7 @@
       <c r="J18" s="26"/>
       <c r="K18" s="26"/>
     </row>
-    <row r="19" spans="1:11" ht="78" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A19" s="24">
         <v>3</v>
       </c>
@@ -8329,7 +8330,7 @@
       <c r="J19" s="26"/>
       <c r="K19" s="26"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="24"/>
       <c r="B20" s="25" t="str">
         <f>B15</f>
@@ -8358,7 +8359,7 @@
       <c r="J20" s="26"/>
       <c r="K20" s="26"/>
     </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>
       <c r="B21" s="18" t="s">
         <v>16</v>
@@ -8383,7 +8384,7 @@
       </c>
       <c r="K21" s="20"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="24"/>
       <c r="B22" s="25" t="s">
         <v>32</v>
@@ -8401,7 +8402,7 @@
       </c>
       <c r="K22" s="26"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="24"/>
       <c r="B23" s="25" t="s">
         <v>31</v>
@@ -8419,7 +8420,7 @@
       </c>
       <c r="K23" s="26"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="24"/>
       <c r="B24" s="25" t="s">
         <v>33</v>
@@ -8437,7 +8438,7 @@
       </c>
       <c r="K24" s="26"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="24"/>
       <c r="B25" s="25" t="s">
         <v>128</v>
@@ -8455,7 +8456,7 @@
       </c>
       <c r="K25" s="26"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="24"/>
       <c r="B26" s="25" t="s">
         <v>36</v>
@@ -8473,7 +8474,7 @@
       </c>
       <c r="K26" s="26"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="24"/>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
@@ -8486,7 +8487,7 @@
       <c r="J27" s="26"/>
       <c r="K27" s="26"/>
     </row>
-    <row r="28" spans="1:11" ht="140.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A28" s="24">
         <v>4</v>
       </c>
@@ -8503,7 +8504,7 @@
       <c r="J28" s="26"/>
       <c r="K28" s="26"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="24"/>
       <c r="B29" s="25" t="str">
         <f>B20</f>
@@ -8531,7 +8532,7 @@
       <c r="J29" s="26"/>
       <c r="K29" s="26"/>
     </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17"/>
       <c r="B30" s="18" t="s">
         <v>16</v>
@@ -8556,7 +8557,7 @@
       </c>
       <c r="K30" s="20"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="24"/>
       <c r="B31" s="25" t="s">
         <v>32</v>
@@ -8574,7 +8575,7 @@
       </c>
       <c r="K31" s="26"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="24"/>
       <c r="B32" s="25" t="s">
         <v>31</v>
@@ -8592,7 +8593,7 @@
       </c>
       <c r="K32" s="26"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="24"/>
       <c r="B33" s="25" t="s">
         <v>131</v>
@@ -8610,7 +8611,7 @@
       </c>
       <c r="K33" s="26"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="24"/>
       <c r="B34" s="25" t="s">
         <v>33</v>
@@ -8628,7 +8629,7 @@
       </c>
       <c r="K34" s="26"/>
     </row>
-    <row r="35" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="24"/>
       <c r="B35" s="57" t="s">
         <v>132</v>
@@ -8646,7 +8647,7 @@
       </c>
       <c r="K35" s="26"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="24"/>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
@@ -8659,9 +8660,9 @@
       <c r="J36" s="26"/>
       <c r="K36" s="26"/>
     </row>
-    <row r="37" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A37" s="24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>56</v>
@@ -8676,7 +8677,7 @@
       <c r="J37" s="38"/>
       <c r="K37" s="38"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="26"/>
       <c r="B38" s="25" t="s">
         <v>57</v>
@@ -8705,7 +8706,7 @@
       <c r="J38" s="26"/>
       <c r="K38" s="26"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="26"/>
       <c r="B39" s="25" t="s">
         <v>89</v>
@@ -8732,7 +8733,7 @@
       <c r="J39" s="26"/>
       <c r="K39" s="26"/>
     </row>
-    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="17"/>
       <c r="B40" s="18" t="s">
         <v>16</v>
@@ -8757,7 +8758,7 @@
       </c>
       <c r="K40" s="20"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="26"/>
       <c r="B41" s="26"/>
       <c r="C41" s="26"/>
@@ -8770,9 +8771,9 @@
       <c r="J41" s="26"/>
       <c r="K41" s="26"/>
     </row>
-    <row r="42" spans="1:11" s="44" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>58</v>
@@ -8787,7 +8788,7 @@
       <c r="J42" s="38"/>
       <c r="K42" s="38"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="26"/>
       <c r="B43" s="25" t="str">
         <f t="shared" ref="B43:E44" si="0">B38</f>
@@ -8815,7 +8816,7 @@
       <c r="J43" s="26"/>
       <c r="K43" s="26"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="26"/>
       <c r="B44" s="25" t="str">
         <f t="shared" si="0"/>
@@ -8843,7 +8844,7 @@
       <c r="J44" s="26"/>
       <c r="K44" s="26"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="26"/>
       <c r="B45" s="25" t="s">
         <v>52</v>
@@ -8869,7 +8870,7 @@
       <c r="J45" s="26"/>
       <c r="K45" s="26"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="26"/>
       <c r="B46" s="25" t="str">
         <f>B173</f>
@@ -8895,7 +8896,7 @@
       <c r="J46" s="26"/>
       <c r="K46" s="26"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="26"/>
       <c r="B47" s="25"/>
       <c r="C47" s="26">
@@ -8918,7 +8919,7 @@
       <c r="J47" s="26"/>
       <c r="K47" s="26"/>
     </row>
-    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="17"/>
       <c r="B48" s="18" t="s">
         <v>16</v>
@@ -8943,7 +8944,7 @@
       </c>
       <c r="K48" s="20"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="24"/>
       <c r="B49" s="25" t="s">
         <v>55</v>
@@ -8961,7 +8962,7 @@
       </c>
       <c r="K49" s="26"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="26"/>
       <c r="B50" s="25" t="s">
         <v>31</v>
@@ -8979,7 +8980,7 @@
       </c>
       <c r="K50" s="26"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="26"/>
       <c r="B51" s="26"/>
       <c r="C51" s="26"/>
@@ -8992,9 +8993,9 @@
       <c r="J51" s="26"/>
       <c r="K51" s="26"/>
     </row>
-    <row r="52" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A52" s="24">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>35</v>
@@ -9009,7 +9010,7 @@
       <c r="J52" s="38"/>
       <c r="K52" s="38"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="26"/>
       <c r="B53" s="25" t="str">
         <f>B43</f>
@@ -9039,7 +9040,7 @@
       <c r="J53" s="26"/>
       <c r="K53" s="26"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="26"/>
       <c r="B54" s="25" t="str">
         <f>B44</f>
@@ -9069,7 +9070,7 @@
       <c r="J54" s="26"/>
       <c r="K54" s="26"/>
     </row>
-    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="17"/>
       <c r="B55" s="18" t="s">
         <v>16</v>
@@ -9094,7 +9095,7 @@
       </c>
       <c r="K55" s="20"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="24"/>
       <c r="B56" s="25" t="s">
         <v>32</v>
@@ -9112,7 +9113,7 @@
       </c>
       <c r="K56" s="26"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="24"/>
       <c r="B57" s="25" t="s">
         <v>33</v>
@@ -9130,7 +9131,7 @@
       </c>
       <c r="K57" s="26"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="24"/>
       <c r="B58" s="25" t="s">
         <v>31</v>
@@ -9148,7 +9149,7 @@
       </c>
       <c r="K58" s="26"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="26"/>
       <c r="B59" s="25" t="s">
         <v>36</v>
@@ -9166,7 +9167,7 @@
       </c>
       <c r="K59" s="26"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="26"/>
       <c r="B60" s="25" t="s">
         <v>44</v>
@@ -9184,7 +9185,7 @@
       </c>
       <c r="K60" s="26"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="26"/>
       <c r="B61" s="25" t="s">
         <v>45</v>
@@ -9202,7 +9203,7 @@
       </c>
       <c r="K61" s="26"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="26"/>
       <c r="B62" s="26"/>
       <c r="C62" s="26"/>
@@ -9215,9 +9216,9 @@
       <c r="J62" s="26"/>
       <c r="K62" s="26"/>
     </row>
-    <row r="63" spans="1:11" s="44" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" s="44" customFormat="1" ht="45" x14ac:dyDescent="0.2">
       <c r="A63" s="24">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>116</v>
@@ -9232,7 +9233,7 @@
       <c r="J63" s="38"/>
       <c r="K63" s="38"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="26"/>
       <c r="B64" s="25" t="str">
         <f t="shared" ref="B64:E65" si="2">B45</f>
@@ -9262,7 +9263,7 @@
       <c r="J64" s="26"/>
       <c r="K64" s="26"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="26"/>
       <c r="B65" s="25" t="str">
         <f t="shared" si="2"/>
@@ -9292,7 +9293,7 @@
       <c r="J65" s="26"/>
       <c r="K65" s="26"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="26"/>
       <c r="B66" s="25"/>
       <c r="C66" s="26">
@@ -9319,7 +9320,7 @@
       <c r="J66" s="26"/>
       <c r="K66" s="26"/>
     </row>
-    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17"/>
       <c r="B67" s="18" t="s">
         <v>16</v>
@@ -9344,7 +9345,7 @@
       </c>
       <c r="K67" s="20"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="24"/>
       <c r="B68" s="25" t="s">
         <v>32</v>
@@ -9362,7 +9363,7 @@
       </c>
       <c r="K68" s="26"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="24"/>
       <c r="B69" s="25" t="s">
         <v>33</v>
@@ -9380,7 +9381,7 @@
       </c>
       <c r="K69" s="26"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="24"/>
       <c r="B70" s="25" t="s">
         <v>31</v>
@@ -9398,7 +9399,7 @@
       </c>
       <c r="K70" s="26"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="26"/>
       <c r="B71" s="25" t="s">
         <v>36</v>
@@ -9416,7 +9417,7 @@
       </c>
       <c r="K71" s="26"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="26"/>
       <c r="B72" s="25" t="s">
         <v>36</v>
@@ -9434,7 +9435,7 @@
       </c>
       <c r="K72" s="26"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="26"/>
       <c r="B73" s="25" t="s">
         <v>36</v>
@@ -9452,7 +9453,7 @@
       </c>
       <c r="K73" s="26"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="26"/>
       <c r="B74" s="26"/>
       <c r="C74" s="26"/>
@@ -9465,9 +9466,9 @@
       <c r="J74" s="26"/>
       <c r="K74" s="26"/>
     </row>
-    <row r="75" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A75" s="24">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>43</v>
@@ -9482,7 +9483,7 @@
       <c r="J75" s="38"/>
       <c r="K75" s="38"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="26"/>
       <c r="B76" s="25" t="str">
         <f>B53</f>
@@ -9512,7 +9513,7 @@
       <c r="J76" s="26"/>
       <c r="K76" s="26"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="26"/>
       <c r="B77" s="25" t="s">
         <v>60</v>
@@ -9541,7 +9542,7 @@
       <c r="J77" s="26"/>
       <c r="K77" s="26"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="26"/>
       <c r="B78" s="25" t="s">
         <v>59</v>
@@ -9571,7 +9572,7 @@
       <c r="J78" s="26"/>
       <c r="K78" s="26"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="26"/>
       <c r="B79" s="25" t="s">
         <v>61</v>
@@ -9600,7 +9601,7 @@
       <c r="J79" s="26"/>
       <c r="K79" s="26"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="26"/>
       <c r="B80" s="25" t="s">
         <v>62</v>
@@ -9628,7 +9629,7 @@
       <c r="J80" s="26"/>
       <c r="K80" s="26"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="26"/>
       <c r="B81" s="25" t="s">
         <v>81</v>
@@ -9656,7 +9657,7 @@
       <c r="J81" s="26"/>
       <c r="K81" s="26"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="26"/>
       <c r="B82" s="25" t="s">
         <v>82</v>
@@ -9683,7 +9684,7 @@
       <c r="J82" s="26"/>
       <c r="K82" s="26"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="26"/>
       <c r="B83" s="25" t="s">
         <v>108</v>
@@ -9711,7 +9712,7 @@
       <c r="J83" s="26"/>
       <c r="K83" s="26"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="26"/>
       <c r="B84" s="25" t="s">
         <v>83</v>
@@ -9739,7 +9740,7 @@
       <c r="J84" s="26"/>
       <c r="K84" s="26"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="26"/>
       <c r="B85" s="25" t="s">
         <v>84</v>
@@ -9766,7 +9767,7 @@
       <c r="J85" s="26"/>
       <c r="K85" s="26"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="26"/>
       <c r="B86" s="25"/>
       <c r="C86" s="26">
@@ -9791,7 +9792,7 @@
       <c r="J86" s="26"/>
       <c r="K86" s="26"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="26"/>
       <c r="B87" s="25" t="s">
         <v>109</v>
@@ -9819,7 +9820,7 @@
       <c r="J87" s="26"/>
       <c r="K87" s="26"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="26"/>
       <c r="B88" s="25" t="s">
         <v>110</v>
@@ -9847,7 +9848,7 @@
       <c r="J88" s="26"/>
       <c r="K88" s="26"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="26"/>
       <c r="B89" s="25" t="s">
         <v>84</v>
@@ -9875,7 +9876,7 @@
       <c r="J89" s="26"/>
       <c r="K89" s="26"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="26"/>
       <c r="B90" s="25"/>
       <c r="C90" s="26">
@@ -9901,7 +9902,7 @@
       <c r="J90" s="26"/>
       <c r="K90" s="26"/>
     </row>
-    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17"/>
       <c r="B91" s="18" t="s">
         <v>16</v>
@@ -9926,7 +9927,7 @@
       </c>
       <c r="K91" s="20"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="24"/>
       <c r="B92" s="25" t="s">
         <v>32</v>
@@ -9944,7 +9945,7 @@
       </c>
       <c r="K92" s="26"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="24"/>
       <c r="B93" s="25" t="s">
         <v>33</v>
@@ -9962,7 +9963,7 @@
       </c>
       <c r="K93" s="26"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="24"/>
       <c r="B94" s="25" t="s">
         <v>31</v>
@@ -9980,7 +9981,7 @@
       </c>
       <c r="K94" s="26"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="26"/>
       <c r="B95" s="25" t="s">
         <v>36</v>
@@ -9998,7 +9999,7 @@
       </c>
       <c r="K95" s="26"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="24"/>
       <c r="B96" s="25" t="s">
         <v>44</v>
@@ -10016,7 +10017,7 @@
       </c>
       <c r="K96" s="26"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="26"/>
       <c r="B97" s="25" t="s">
         <v>45</v>
@@ -10034,7 +10035,7 @@
       </c>
       <c r="K97" s="26"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="26"/>
       <c r="B98" s="26"/>
       <c r="C98" s="26"/>
@@ -10047,9 +10048,9 @@
       <c r="J98" s="26"/>
       <c r="K98" s="26"/>
     </row>
-    <row r="99" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" s="44" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A99" s="24">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B99" s="12" t="s">
         <v>46</v>
@@ -10064,7 +10065,7 @@
       <c r="J99" s="38"/>
       <c r="K99" s="38"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="26"/>
       <c r="B100" s="25" t="str">
         <f>B77</f>
@@ -10092,7 +10093,7 @@
       <c r="J100" s="26"/>
       <c r="K100" s="26"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="26"/>
       <c r="B101" s="25" t="str">
         <f t="shared" ref="B101:C105" si="6">B78</f>
@@ -10120,7 +10121,7 @@
       <c r="J101" s="26"/>
       <c r="K101" s="26"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="26"/>
       <c r="B102" s="25" t="str">
         <f t="shared" si="6"/>
@@ -10148,7 +10149,7 @@
       <c r="J102" s="26"/>
       <c r="K102" s="26"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="26"/>
       <c r="B103" s="25" t="str">
         <f t="shared" si="6"/>
@@ -10176,7 +10177,7 @@
       <c r="J103" s="26"/>
       <c r="K103" s="26"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="26"/>
       <c r="B104" s="25" t="str">
         <f t="shared" si="6"/>
@@ -10204,7 +10205,7 @@
       <c r="J104" s="26"/>
       <c r="K104" s="26"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="26"/>
       <c r="B105" s="25" t="str">
         <f t="shared" si="6"/>
@@ -10232,7 +10233,7 @@
       <c r="J105" s="26"/>
       <c r="K105" s="26"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="26"/>
       <c r="B106" s="25" t="s">
         <v>108</v>
@@ -10259,7 +10260,7 @@
       <c r="J106" s="26"/>
       <c r="K106" s="26"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="26"/>
       <c r="B107" s="25" t="str">
         <f>B84</f>
@@ -10287,7 +10288,7 @@
       <c r="J107" s="26"/>
       <c r="K107" s="26"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="26"/>
       <c r="B108" s="25" t="str">
         <f t="shared" ref="B108:E108" si="8">B85</f>
@@ -10315,7 +10316,7 @@
       <c r="J108" s="26"/>
       <c r="K108" s="26"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="26"/>
       <c r="B109" s="25"/>
       <c r="C109" s="26">
@@ -10340,7 +10341,7 @@
       <c r="J109" s="26"/>
       <c r="K109" s="26"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="26"/>
       <c r="B110" s="25" t="str">
         <f t="shared" ref="B110:D110" si="11">B87</f>
@@ -10368,7 +10369,7 @@
       <c r="J110" s="26"/>
       <c r="K110" s="26"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="26"/>
       <c r="B111" s="25" t="str">
         <f t="shared" ref="B111:E111" si="12">B88</f>
@@ -10396,7 +10397,7 @@
       <c r="J111" s="26"/>
       <c r="K111" s="26"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="26"/>
       <c r="B112" s="25" t="str">
         <f t="shared" ref="B112:E112" si="13">B89</f>
@@ -10424,7 +10425,7 @@
       <c r="J112" s="26"/>
       <c r="K112" s="26"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="26"/>
       <c r="B113" s="25"/>
       <c r="C113" s="26">
@@ -10449,7 +10450,7 @@
       <c r="J113" s="26"/>
       <c r="K113" s="26"/>
     </row>
-    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="17"/>
       <c r="B114" s="18" t="s">
         <v>16</v>
@@ -10474,7 +10475,7 @@
       </c>
       <c r="K114" s="20"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="24"/>
       <c r="B115" s="25" t="s">
         <v>47</v>
@@ -10492,7 +10493,7 @@
       </c>
       <c r="K115" s="26"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="24"/>
       <c r="B116" s="25" t="s">
         <v>48</v>
@@ -10510,7 +10511,7 @@
       </c>
       <c r="K116" s="26"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="24"/>
       <c r="B117" s="25" t="s">
         <v>49</v>
@@ -10528,7 +10529,7 @@
       </c>
       <c r="K117" s="26"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="26"/>
       <c r="B118" s="25" t="s">
         <v>50</v>
@@ -10546,7 +10547,7 @@
       </c>
       <c r="K118" s="26"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="26"/>
       <c r="B119" s="26"/>
       <c r="C119" s="26"/>
@@ -10559,9 +10560,9 @@
       <c r="J119" s="26"/>
       <c r="K119" s="26"/>
     </row>
-    <row r="120" spans="1:11" s="44" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" s="44" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="24">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B120" s="28" t="s">
         <v>37</v>
@@ -10584,7 +10585,7 @@
       <c r="J120" s="38"/>
       <c r="K120" s="38"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="26"/>
       <c r="B121" s="25" t="str">
         <f>B76</f>
@@ -10615,7 +10616,7 @@
       <c r="J121" s="26"/>
       <c r="K121" s="26"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="26"/>
       <c r="B122" s="25"/>
       <c r="C122" s="26">
@@ -10642,7 +10643,7 @@
       <c r="J122" s="26"/>
       <c r="K122" s="26"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="26"/>
       <c r="B123" s="25" t="s">
         <v>70</v>
@@ -10672,7 +10673,7 @@
       <c r="J123" s="26"/>
       <c r="K123" s="26"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="26"/>
       <c r="B124" s="25"/>
       <c r="C124" s="26">
@@ -10700,7 +10701,7 @@
       <c r="J124" s="26"/>
       <c r="K124" s="26"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="26"/>
       <c r="B125" s="25" t="s">
         <v>71</v>
@@ -10730,7 +10731,7 @@
       <c r="J125" s="26"/>
       <c r="K125" s="26"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="26"/>
       <c r="B126" s="25"/>
       <c r="C126" s="26">
@@ -10758,7 +10759,7 @@
       <c r="J126" s="26"/>
       <c r="K126" s="26"/>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="26"/>
       <c r="B127" s="25" t="str">
         <f>B101</f>
@@ -10789,7 +10790,7 @@
       <c r="J127" s="26"/>
       <c r="K127" s="26"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="26"/>
       <c r="B128" s="25" t="s">
         <v>72</v>
@@ -10819,7 +10820,7 @@
       <c r="J128" s="26"/>
       <c r="K128" s="26"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="26"/>
       <c r="B129" s="25" t="str">
         <f>B103</f>
@@ -10850,7 +10851,7 @@
       <c r="J129" s="26"/>
       <c r="K129" s="26"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="26"/>
       <c r="B130" s="25" t="s">
         <v>72</v>
@@ -10880,7 +10881,7 @@
       <c r="J130" s="26"/>
       <c r="K130" s="26"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="26"/>
       <c r="B131" s="25" t="str">
         <f>B104</f>
@@ -10911,7 +10912,7 @@
       <c r="J131" s="26"/>
       <c r="K131" s="26"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="26"/>
       <c r="B132" s="25" t="s">
         <v>72</v>
@@ -10941,7 +10942,7 @@
       <c r="J132" s="26"/>
       <c r="K132" s="26"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="26"/>
       <c r="B133" s="25" t="str">
         <f>B105</f>
@@ -10972,7 +10973,7 @@
       <c r="J133" s="26"/>
       <c r="K133" s="26"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="26"/>
       <c r="B134" s="25" t="s">
         <v>71</v>
@@ -11002,7 +11003,7 @@
       <c r="J134" s="26"/>
       <c r="K134" s="26"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="26"/>
       <c r="B135" s="25"/>
       <c r="C135" s="26">
@@ -11030,7 +11031,7 @@
       <c r="J135" s="26"/>
       <c r="K135" s="26"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="26"/>
       <c r="B136" s="25" t="s">
         <v>108</v>
@@ -11060,7 +11061,7 @@
       <c r="J136" s="26"/>
       <c r="K136" s="26"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="26"/>
       <c r="B137" s="25" t="s">
         <v>72</v>
@@ -11090,7 +11091,7 @@
       <c r="J137" s="26"/>
       <c r="K137" s="26"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="26"/>
       <c r="B138" s="25" t="str">
         <f>B107</f>
@@ -11121,7 +11122,7 @@
       <c r="J138" s="26"/>
       <c r="K138" s="26"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="26"/>
       <c r="B139" s="25"/>
       <c r="C139" s="26">
@@ -11149,7 +11150,7 @@
       <c r="J139" s="26"/>
       <c r="K139" s="26"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="26"/>
       <c r="B140" s="25" t="s">
         <v>84</v>
@@ -11179,7 +11180,7 @@
       <c r="J140" s="26"/>
       <c r="K140" s="26"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="26"/>
       <c r="B141" s="25"/>
       <c r="C141" s="26">
@@ -11206,7 +11207,7 @@
       <c r="J141" s="26"/>
       <c r="K141" s="26"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="26"/>
       <c r="B142" s="25"/>
       <c r="C142" s="26">
@@ -11234,7 +11235,7 @@
       <c r="J142" s="26"/>
       <c r="K142" s="26"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="26"/>
       <c r="B143" s="25"/>
       <c r="C143" s="26">
@@ -11261,7 +11262,7 @@
       <c r="J143" s="26"/>
       <c r="K143" s="26"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="26"/>
       <c r="B144" s="25" t="str">
         <f>B111</f>
@@ -11292,7 +11293,7 @@
       <c r="J144" s="26"/>
       <c r="K144" s="26"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="26"/>
       <c r="B145" s="25"/>
       <c r="C145" s="26">
@@ -11320,7 +11321,7 @@
       <c r="J145" s="26"/>
       <c r="K145" s="26"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="26"/>
       <c r="B146" s="25" t="s">
         <v>84</v>
@@ -11350,7 +11351,7 @@
       <c r="J146" s="26"/>
       <c r="K146" s="26"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="26"/>
       <c r="B147" s="25"/>
       <c r="C147" s="26">
@@ -11378,7 +11379,7 @@
       <c r="J147" s="26"/>
       <c r="K147" s="26"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="26"/>
       <c r="B148" s="25"/>
       <c r="C148" s="26">
@@ -11406,7 +11407,7 @@
       <c r="J148" s="26"/>
       <c r="K148" s="26"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="26"/>
       <c r="B149" s="25"/>
       <c r="C149" s="26">
@@ -11434,7 +11435,7 @@
       <c r="J149" s="26"/>
       <c r="K149" s="26"/>
     </row>
-    <row r="150" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="17"/>
       <c r="B150" s="18" t="s">
         <v>16</v>
@@ -11459,7 +11460,7 @@
       </c>
       <c r="K150" s="20"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="24"/>
       <c r="B151" s="25" t="s">
         <v>39</v>
@@ -11477,7 +11478,7 @@
       </c>
       <c r="K151" s="26"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="24"/>
       <c r="B152" s="25" t="s">
         <v>38</v>
@@ -11495,7 +11496,7 @@
       </c>
       <c r="K152" s="26"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="26"/>
       <c r="B153" s="26"/>
       <c r="C153" s="26"/>
@@ -11508,9 +11509,9 @@
       <c r="J153" s="26"/>
       <c r="K153" s="26"/>
     </row>
-    <row r="154" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="24">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B154" s="28" t="s">
         <v>53</v>
@@ -11525,7 +11526,7 @@
       <c r="J154" s="26"/>
       <c r="K154" s="26"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="26"/>
       <c r="B155" s="25" t="s">
         <v>111</v>
@@ -11552,7 +11553,7 @@
       <c r="J155" s="26"/>
       <c r="K155" s="26"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="26"/>
       <c r="B156" s="25" t="str">
         <f>B105</f>
@@ -11579,7 +11580,7 @@
       <c r="J156" s="26"/>
       <c r="K156" s="26"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="26"/>
       <c r="B157" s="25" t="s">
         <v>62</v>
@@ -11605,7 +11606,7 @@
       <c r="J157" s="26"/>
       <c r="K157" s="26"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="26"/>
       <c r="B158" s="25"/>
       <c r="C158" s="51">
@@ -11629,7 +11630,7 @@
       <c r="J158" s="26"/>
       <c r="K158" s="26"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="26"/>
       <c r="B159" s="25" t="str">
         <f>B110</f>
@@ -11656,7 +11657,7 @@
       <c r="J159" s="26"/>
       <c r="K159" s="26"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="26"/>
       <c r="B160" s="25" t="str">
         <f>B84</f>
@@ -11684,7 +11685,7 @@
       <c r="J160" s="26"/>
       <c r="K160" s="26"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="26"/>
       <c r="B161" s="25" t="str">
         <f>B85</f>
@@ -11712,7 +11713,7 @@
       <c r="J161" s="26"/>
       <c r="K161" s="26"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="26"/>
       <c r="B162" s="25"/>
       <c r="C162" s="52">
@@ -11737,7 +11738,7 @@
       <c r="J162" s="26"/>
       <c r="K162" s="26"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="26"/>
       <c r="B163" s="25" t="str">
         <f>B88</f>
@@ -11765,7 +11766,7 @@
       <c r="J163" s="26"/>
       <c r="K163" s="26"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="26"/>
       <c r="B164" s="25" t="str">
         <f t="shared" ref="B164:E164" si="24">B89</f>
@@ -11793,7 +11794,7 @@
       <c r="J164" s="26"/>
       <c r="K164" s="26"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="26"/>
       <c r="B165" s="25"/>
       <c r="C165" s="52">
@@ -11818,7 +11819,7 @@
       <c r="J165" s="26"/>
       <c r="K165" s="26"/>
     </row>
-    <row r="166" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="17"/>
       <c r="B166" s="18" t="s">
         <v>16</v>
@@ -11843,7 +11844,7 @@
       </c>
       <c r="K166" s="20"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="24"/>
       <c r="B167" s="25" t="s">
         <v>32</v>
@@ -11861,7 +11862,7 @@
       </c>
       <c r="K167" s="26"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="26"/>
       <c r="B168" s="25" t="s">
         <v>31</v>
@@ -11879,7 +11880,7 @@
       </c>
       <c r="K168" s="26"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="26"/>
       <c r="B169" s="26"/>
       <c r="C169" s="26"/>
@@ -11892,9 +11893,9 @@
       <c r="J169" s="26"/>
       <c r="K169" s="26"/>
     </row>
-    <row r="170" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A170" s="24">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B170" s="28" t="s">
         <v>63</v>
@@ -11909,7 +11910,7 @@
       <c r="J170" s="26"/>
       <c r="K170" s="26"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="26"/>
       <c r="B171" s="25" t="str">
         <f>B78</f>
@@ -11938,7 +11939,7 @@
       <c r="J171" s="26"/>
       <c r="K171" s="26"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="26"/>
       <c r="B172" s="25"/>
       <c r="C172" s="51">
@@ -11964,7 +11965,7 @@
       <c r="J172" s="26"/>
       <c r="K172" s="26"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="26"/>
       <c r="B173" s="25" t="s">
         <v>133</v>
@@ -11991,7 +11992,7 @@
       <c r="J173" s="26"/>
       <c r="K173" s="26"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="26"/>
       <c r="B174" s="25"/>
       <c r="C174" s="51">
@@ -12016,7 +12017,7 @@
       <c r="J174" s="26"/>
       <c r="K174" s="26"/>
     </row>
-    <row r="175" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="17"/>
       <c r="B175" s="18" t="s">
         <v>16</v>
@@ -12042,7 +12043,7 @@
       </c>
       <c r="K175" s="20"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="24"/>
       <c r="B176" s="25" t="s">
         <v>55</v>
@@ -12060,7 +12061,7 @@
       </c>
       <c r="K176" s="26"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="24"/>
       <c r="B177" s="25" t="s">
         <v>32</v>
@@ -12078,7 +12079,7 @@
       </c>
       <c r="K177" s="26"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="24"/>
       <c r="B178" s="25" t="s">
         <v>64</v>
@@ -12096,7 +12097,7 @@
       </c>
       <c r="K178" s="26"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="24"/>
       <c r="B179" s="25" t="s">
         <v>36</v>
@@ -12114,7 +12115,7 @@
       </c>
       <c r="K179" s="26"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="24"/>
       <c r="B180" s="25"/>
       <c r="C180" s="26"/>
@@ -12127,9 +12128,9 @@
       <c r="J180" s="22"/>
       <c r="K180" s="26"/>
     </row>
-    <row r="181" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" s="24">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B181" s="28" t="s">
         <v>112</v>
@@ -12144,7 +12145,7 @@
       <c r="J181" s="26"/>
       <c r="K181" s="26"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="26"/>
       <c r="B182" s="25" t="str">
         <f>B161</f>
@@ -12169,7 +12170,7 @@
       <c r="J182" s="26"/>
       <c r="K182" s="26"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="26"/>
       <c r="B183" s="25"/>
       <c r="C183" s="52">
@@ -12191,7 +12192,7 @@
       <c r="J183" s="26"/>
       <c r="K183" s="26"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="26"/>
       <c r="B184" s="25" t="str">
         <f t="shared" ref="B184:C184" si="31">B164</f>
@@ -12216,7 +12217,7 @@
       <c r="J184" s="26"/>
       <c r="K184" s="26"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="26"/>
       <c r="B185" s="25"/>
       <c r="C185" s="52">
@@ -12238,7 +12239,7 @@
       <c r="J185" s="26"/>
       <c r="K185" s="26"/>
     </row>
-    <row r="186" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="17"/>
       <c r="B186" s="18" t="s">
         <v>16</v>
@@ -12263,7 +12264,7 @@
       </c>
       <c r="K186" s="20"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="24"/>
       <c r="B187" s="25" t="s">
         <v>32</v>
@@ -12281,7 +12282,7 @@
       </c>
       <c r="K187" s="26"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="24"/>
       <c r="B188" s="25" t="s">
         <v>31</v>
@@ -12299,7 +12300,7 @@
       </c>
       <c r="K188" s="26"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="24"/>
       <c r="B189" s="25" t="s">
         <v>113</v>
@@ -12317,7 +12318,7 @@
       </c>
       <c r="K189" s="26"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="24"/>
       <c r="B190" s="25"/>
       <c r="C190" s="26"/>
@@ -12330,9 +12331,9 @@
       <c r="J190" s="22"/>
       <c r="K190" s="26"/>
     </row>
-    <row r="191" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B191" s="30" t="s">
         <v>85</v>
@@ -12359,7 +12360,7 @@
       </c>
       <c r="K191" s="20"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="17"/>
       <c r="B192" s="31"/>
       <c r="C192" s="19"/>
@@ -12372,9 +12373,9 @@
       <c r="J192" s="22"/>
       <c r="K192" s="20"/>
     </row>
-    <row r="193" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="17">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B193" s="30" t="s">
         <v>17</v>
@@ -12401,7 +12402,7 @@
       </c>
       <c r="K193" s="20"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="17"/>
       <c r="B194" s="31"/>
       <c r="C194" s="19"/>
@@ -12414,7 +12415,7 @@
       <c r="J194" s="22"/>
       <c r="K194" s="20"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="32"/>
       <c r="B195" s="33" t="s">
         <v>20</v>
@@ -12432,16 +12433,16 @@
       </c>
       <c r="K195" s="36"/>
     </row>
-    <row r="197" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="37"/>
       <c r="B197" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C197" s="58">
+      <c r="C197" s="64">
         <f>J195</f>
         <v>783511.5632557295</v>
       </c>
-      <c r="D197" s="59"/>
+      <c r="D197" s="65"/>
       <c r="E197" s="39">
         <v>100</v>
       </c>
@@ -12452,79 +12453,72 @@
       <c r="J197" s="42"/>
       <c r="K197" s="43"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B198" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C198" s="60">
+      <c r="C198" s="68">
         <v>700000</v>
       </c>
-      <c r="D198" s="61"/>
+      <c r="D198" s="69"/>
       <c r="E198" s="39"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B199" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C199" s="60">
+      <c r="C199" s="68">
         <f>C198-C201-C202</f>
         <v>665000</v>
       </c>
-      <c r="D199" s="61"/>
+      <c r="D199" s="69"/>
       <c r="E199" s="39">
         <f>C199/C197*100</f>
         <v>84.874305777533408</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B200" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C200" s="62">
+      <c r="C200" s="70">
         <f>C197-C199</f>
         <v>118511.5632557295</v>
       </c>
-      <c r="D200" s="62"/>
+      <c r="D200" s="70"/>
       <c r="E200" s="39">
         <f>100-E199</f>
         <v>15.125694222466592</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B201" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C201" s="58">
+      <c r="C201" s="64">
         <f>C198*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D201" s="59"/>
+      <c r="D201" s="65"/>
       <c r="E201" s="39">
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B202" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C202" s="58">
+      <c r="C202" s="64">
         <f>C198*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D202" s="59"/>
+      <c r="D202" s="65"/>
       <c r="E202" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C201:D201"/>
     <mergeCell ref="C202:D202"/>
     <mergeCell ref="A7:F7"/>
@@ -12533,6 +12527,13 @@
     <mergeCell ref="C198:D198"/>
     <mergeCell ref="C199:D199"/>
     <mergeCell ref="C200:D200"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -12544,32 +12545,32 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:W4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.88671875" customWidth="1"/>
-    <col min="17" max="17" width="11.88671875" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" customWidth="1"/>
+    <col min="12" max="12" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.85546875" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" customWidth="1"/>
     <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B2" s="75" t="s">
         <v>90</v>
       </c>
@@ -12607,7 +12608,7 @@
       <c r="V2" s="71"/>
       <c r="W2" s="71"/>
     </row>
-    <row r="3" spans="2:23" s="48" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:23" s="48" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="47" t="s">
         <v>8</v>
       </c>
@@ -12675,7 +12676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B4" s="23">
         <v>1.5</v>
       </c>

--- a/बजेट माग estimate/नगर बजेट estimate/bhotange chihaanpaati/2.bhotange chihaanpaati.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/bhotange chihaanpaati/2.bhotange chihaanpaati.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05E2225-4877-46F0-BCC2-555FFFA32398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F9C4EE-7494-46A8-9B4F-24DD179CDFE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -902,24 +902,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -938,6 +920,24 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1498,113 +1498,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="67" t="s">
+      <c r="H7" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
     </row>
     <row r="8" spans="1:11" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -4907,11 +4907,11 @@
       <c r="B153" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="64">
+      <c r="C153" s="58">
         <f>J151</f>
         <v>791637.34255256748</v>
       </c>
-      <c r="D153" s="65"/>
+      <c r="D153" s="59"/>
       <c r="E153" s="39">
         <v>100</v>
       </c>
@@ -4926,21 +4926,21 @@
       <c r="B154" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="68">
+      <c r="C154" s="62">
         <v>700000</v>
       </c>
-      <c r="D154" s="69"/>
+      <c r="D154" s="63"/>
       <c r="E154" s="39"/>
     </row>
     <row r="155" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B155" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C155" s="68">
+      <c r="C155" s="62">
         <f>C154-C157-C158</f>
         <v>665000</v>
       </c>
-      <c r="D155" s="69"/>
+      <c r="D155" s="63"/>
       <c r="E155" s="39">
         <f>C155/C153*100</f>
         <v>84.003111558098539</v>
@@ -4950,11 +4950,11 @@
       <c r="B156" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C156" s="70">
+      <c r="C156" s="64">
         <f>C153-C155</f>
         <v>126637.34255256748</v>
       </c>
-      <c r="D156" s="70"/>
+      <c r="D156" s="64"/>
       <c r="E156" s="39">
         <f>100-E155</f>
         <v>15.996888441901461</v>
@@ -4964,11 +4964,11 @@
       <c r="B157" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="64">
+      <c r="C157" s="58">
         <f>C154*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D157" s="65"/>
+      <c r="D157" s="59"/>
       <c r="E157" s="39">
         <v>3</v>
       </c>
@@ -4977,23 +4977,17 @@
       <c r="B158" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C158" s="64">
+      <c r="C158" s="58">
         <f>C154*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D158" s="65"/>
+      <c r="D158" s="59"/>
       <c r="E158" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C158:D158"/>
-    <mergeCell ref="C153:D153"/>
-    <mergeCell ref="C154:D154"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="C156:D156"/>
-    <mergeCell ref="C157:D157"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="A1:K1"/>
@@ -5003,6 +4997,12 @@
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C157:D157"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -5029,113 +5029,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
     </row>
     <row r="2" spans="1:16" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
     </row>
     <row r="5" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
     </row>
     <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="67" t="s">
+      <c r="H7" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
     </row>
     <row r="8" spans="1:16" s="10" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -7845,11 +7845,11 @@
       <c r="B139" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C139" s="64">
+      <c r="C139" s="58">
         <f>J137</f>
         <v>810861.26423460047</v>
       </c>
-      <c r="D139" s="65"/>
+      <c r="D139" s="59"/>
       <c r="E139" s="39">
         <v>100</v>
       </c>
@@ -7864,21 +7864,21 @@
       <c r="B140" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C140" s="68">
+      <c r="C140" s="62">
         <v>700000</v>
       </c>
-      <c r="D140" s="69"/>
+      <c r="D140" s="63"/>
       <c r="E140" s="39"/>
     </row>
     <row r="141" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B141" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C141" s="68">
+      <c r="C141" s="62">
         <f>C140-C143-C144</f>
         <v>665000</v>
       </c>
-      <c r="D141" s="69"/>
+      <c r="D141" s="63"/>
       <c r="E141" s="39">
         <f>C141/C139*100</f>
         <v>82.011563424196382</v>
@@ -7888,11 +7888,11 @@
       <c r="B142" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C142" s="70">
+      <c r="C142" s="64">
         <f>C139-C141</f>
         <v>145861.26423460047</v>
       </c>
-      <c r="D142" s="70"/>
+      <c r="D142" s="64"/>
       <c r="E142" s="39">
         <f>100-E141</f>
         <v>17.988436575803618</v>
@@ -7902,11 +7902,11 @@
       <c r="B143" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C143" s="64">
+      <c r="C143" s="58">
         <f>C140*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D143" s="65"/>
+      <c r="D143" s="59"/>
       <c r="E143" s="39">
         <v>3</v>
       </c>
@@ -7915,17 +7915,24 @@
       <c r="B144" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C144" s="64">
+      <c r="C144" s="58">
         <f>C140*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D144" s="65"/>
+      <c r="D144" s="59"/>
       <c r="E144" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C143:D143"/>
     <mergeCell ref="C144:D144"/>
     <mergeCell ref="A7:F7"/>
@@ -7934,13 +7941,6 @@
     <mergeCell ref="C140:D140"/>
     <mergeCell ref="C141:D141"/>
     <mergeCell ref="C142:D142"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
@@ -7969,113 +7969,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
     </row>
     <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
     </row>
     <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="59" t="s">
+      <c r="H6" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="59"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="66" t="s">
+      <c r="A7" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="67" t="s">
+      <c r="H7" s="61" t="s">
         <v>88</v>
       </c>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
@@ -8138,7 +8138,7 @@
         <v>0.5</v>
       </c>
       <c r="D10" s="27">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="E10" s="27">
         <v>3</v>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="G10" s="27">
         <f>PRODUCT(C10:F10)</f>
-        <v>16.875</v>
+        <v>17.099999999999998</v>
       </c>
       <c r="H10" s="26"/>
       <c r="I10" s="26"/>
@@ -8166,7 +8166,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="2">
         <f>SUM(G10:G10)</f>
-        <v>16.875</v>
+        <v>17.099999999999998</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>124</v>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="J11" s="22">
         <f>G11*I11</f>
-        <v>1062.28125</v>
+        <v>1076.4449999999999</v>
       </c>
       <c r="K11" s="20"/>
     </row>
@@ -8194,7 +8194,7 @@
       <c r="I12" s="26"/>
       <c r="J12" s="22">
         <f>0.13*G11*(18612)/360</f>
-        <v>113.41687500000002</v>
+        <v>114.92909999999999</v>
       </c>
       <c r="K12" s="26"/>
     </row>
@@ -12429,7 +12429,7 @@
       <c r="I195" s="22"/>
       <c r="J195" s="22">
         <f>SUM(J9:J193)</f>
-        <v>783511.5632557295</v>
+        <v>783527.23923072952</v>
       </c>
       <c r="K195" s="36"/>
     </row>
@@ -12438,11 +12438,11 @@
       <c r="B197" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C197" s="64">
+      <c r="C197" s="58">
         <f>J195</f>
-        <v>783511.5632557295</v>
-      </c>
-      <c r="D197" s="65"/>
+        <v>783527.23923072952</v>
+      </c>
+      <c r="D197" s="59"/>
       <c r="E197" s="39">
         <v>100</v>
       </c>
@@ -12457,49 +12457,49 @@
       <c r="B198" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C198" s="68">
+      <c r="C198" s="62">
         <v>700000</v>
       </c>
-      <c r="D198" s="69"/>
+      <c r="D198" s="63"/>
       <c r="E198" s="39"/>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B199" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C199" s="68">
+      <c r="C199" s="62">
         <f>C198-C201-C202</f>
         <v>665000</v>
       </c>
-      <c r="D199" s="69"/>
+      <c r="D199" s="63"/>
       <c r="E199" s="39">
         <f>C199/C197*100</f>
-        <v>84.874305777533408</v>
+        <v>84.872607703198668</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B200" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C200" s="70">
+      <c r="C200" s="64">
         <f>C197-C199</f>
-        <v>118511.5632557295</v>
-      </c>
-      <c r="D200" s="70"/>
+        <v>118527.23923072952</v>
+      </c>
+      <c r="D200" s="64"/>
       <c r="E200" s="39">
         <f>100-E199</f>
-        <v>15.125694222466592</v>
+        <v>15.127392296801332</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B201" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="C201" s="64">
+      <c r="C201" s="58">
         <f>C198*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D201" s="65"/>
+      <c r="D201" s="59"/>
       <c r="E201" s="39">
         <v>3</v>
       </c>
@@ -12508,17 +12508,24 @@
       <c r="B202" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C202" s="64">
+      <c r="C202" s="58">
         <f>C198*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D202" s="65"/>
+      <c r="D202" s="59"/>
       <c r="E202" s="39">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C201:D201"/>
     <mergeCell ref="C202:D202"/>
     <mergeCell ref="A7:F7"/>
@@ -12527,13 +12534,6 @@
     <mergeCell ref="C198:D198"/>
     <mergeCell ref="C199:D199"/>
     <mergeCell ref="C200:D200"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="portrait" r:id="rId1"/>
